--- a/output/spreadsheet/pyg_ltd_2026.xlsx
+++ b/output/spreadsheet/pyg_ltd_2026.xlsx
@@ -28,7 +28,7 @@
     <numFmt numFmtId="165" formatCode="0.00000000"/>
     <numFmt numFmtId="166" formatCode="0.0%;[Red](0.0%);-"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -52,10 +52,6 @@
     </font>
     <font>
       <b val="1"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <color rgb="00666666"/>
     </font>
     <font>
       <b val="1"/>
@@ -123,9 +119,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -141,17 +137,16 @@
     <xf numFmtId="164" fontId="0" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -526,7 +521,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q46"/>
+  <dimension ref="A1:Q47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -697,23 +692,59 @@
     <row r="3" ht="12" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Actualizado: 03/04/2026 08:03 h</t>
+          <t>Actualizado: 04/04/2026 12:00 h</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
       <c r="C3" s="4" t="n"/>
-      <c r="D3" s="4" t="n"/>
-      <c r="E3" s="4" t="n"/>
-      <c r="F3" s="4" t="n"/>
-      <c r="G3" s="4" t="n"/>
-      <c r="H3" s="4" t="n"/>
-      <c r="I3" s="4" t="n"/>
-      <c r="J3" s="4" t="n"/>
-      <c r="K3" s="4" t="n"/>
-      <c r="L3" s="4" t="n"/>
-      <c r="M3" s="4" t="n"/>
-      <c r="N3" s="4" t="n"/>
-      <c r="O3" s="4" t="n"/>
+      <c r="D3" s="4">
+        <f>IFERROR(IF(DATE(VALUE(LEFT(D$1,4)),VALUE(RIGHT(D$1,2)),1)&gt;TODAY(),"",IF(EOMONTH(DATE(VALUE(LEFT(D$1,4)),VALUE(RIGHT(D$1,2)),1),0)&lt;TODAY(),D5/DAY(EOMONTH(DATE(VALUE(LEFT(D$1,4)),VALUE(RIGHT(D$1,2)),1),0)),D5/MAX(NOW()-DATE(VALUE(LEFT(D$1,4)),VALUE(RIGHT(D$1,2)),1),1/24))),"")</f>
+        <v/>
+      </c>
+      <c r="E3" s="4">
+        <f>IFERROR(IF(DATE(VALUE(LEFT(E$1,4)),VALUE(RIGHT(E$1,2)),1)&gt;TODAY(),"",IF(EOMONTH(DATE(VALUE(LEFT(E$1,4)),VALUE(RIGHT(E$1,2)),1),0)&lt;TODAY(),E5/DAY(EOMONTH(DATE(VALUE(LEFT(E$1,4)),VALUE(RIGHT(E$1,2)),1),0)),E5/MAX(NOW()-DATE(VALUE(LEFT(E$1,4)),VALUE(RIGHT(E$1,2)),1),1/24))),"")</f>
+        <v/>
+      </c>
+      <c r="F3" s="4">
+        <f>IFERROR(IF(DATE(VALUE(LEFT(F$1,4)),VALUE(RIGHT(F$1,2)),1)&gt;TODAY(),"",IF(EOMONTH(DATE(VALUE(LEFT(F$1,4)),VALUE(RIGHT(F$1,2)),1),0)&lt;TODAY(),F5/DAY(EOMONTH(DATE(VALUE(LEFT(F$1,4)),VALUE(RIGHT(F$1,2)),1),0)),F5/MAX(NOW()-DATE(VALUE(LEFT(F$1,4)),VALUE(RIGHT(F$1,2)),1),1/24))),"")</f>
+        <v/>
+      </c>
+      <c r="G3" s="4">
+        <f>IFERROR(IF(DATE(VALUE(LEFT(G$1,4)),VALUE(RIGHT(G$1,2)),1)&gt;TODAY(),"",IF(EOMONTH(DATE(VALUE(LEFT(G$1,4)),VALUE(RIGHT(G$1,2)),1),0)&lt;TODAY(),G5/DAY(EOMONTH(DATE(VALUE(LEFT(G$1,4)),VALUE(RIGHT(G$1,2)),1),0)),G5/MAX(NOW()-DATE(VALUE(LEFT(G$1,4)),VALUE(RIGHT(G$1,2)),1),1/24))),"")</f>
+        <v/>
+      </c>
+      <c r="H3" s="4">
+        <f>IFERROR(IF(DATE(VALUE(LEFT(H$1,4)),VALUE(RIGHT(H$1,2)),1)&gt;TODAY(),"",IF(EOMONTH(DATE(VALUE(LEFT(H$1,4)),VALUE(RIGHT(H$1,2)),1),0)&lt;TODAY(),H5/DAY(EOMONTH(DATE(VALUE(LEFT(H$1,4)),VALUE(RIGHT(H$1,2)),1),0)),H5/MAX(NOW()-DATE(VALUE(LEFT(H$1,4)),VALUE(RIGHT(H$1,2)),1),1/24))),"")</f>
+        <v/>
+      </c>
+      <c r="I3" s="4">
+        <f>IFERROR(IF(DATE(VALUE(LEFT(I$1,4)),VALUE(RIGHT(I$1,2)),1)&gt;TODAY(),"",IF(EOMONTH(DATE(VALUE(LEFT(I$1,4)),VALUE(RIGHT(I$1,2)),1),0)&lt;TODAY(),I5/DAY(EOMONTH(DATE(VALUE(LEFT(I$1,4)),VALUE(RIGHT(I$1,2)),1),0)),I5/MAX(NOW()-DATE(VALUE(LEFT(I$1,4)),VALUE(RIGHT(I$1,2)),1),1/24))),"")</f>
+        <v/>
+      </c>
+      <c r="J3" s="4">
+        <f>IFERROR(IF(DATE(VALUE(LEFT(J$1,4)),VALUE(RIGHT(J$1,2)),1)&gt;TODAY(),"",IF(EOMONTH(DATE(VALUE(LEFT(J$1,4)),VALUE(RIGHT(J$1,2)),1),0)&lt;TODAY(),J5/DAY(EOMONTH(DATE(VALUE(LEFT(J$1,4)),VALUE(RIGHT(J$1,2)),1),0)),J5/MAX(NOW()-DATE(VALUE(LEFT(J$1,4)),VALUE(RIGHT(J$1,2)),1),1/24))),"")</f>
+        <v/>
+      </c>
+      <c r="K3" s="4">
+        <f>IFERROR(IF(DATE(VALUE(LEFT(K$1,4)),VALUE(RIGHT(K$1,2)),1)&gt;TODAY(),"",IF(EOMONTH(DATE(VALUE(LEFT(K$1,4)),VALUE(RIGHT(K$1,2)),1),0)&lt;TODAY(),K5/DAY(EOMONTH(DATE(VALUE(LEFT(K$1,4)),VALUE(RIGHT(K$1,2)),1),0)),K5/MAX(NOW()-DATE(VALUE(LEFT(K$1,4)),VALUE(RIGHT(K$1,2)),1),1/24))),"")</f>
+        <v/>
+      </c>
+      <c r="L3" s="4">
+        <f>IFERROR(IF(DATE(VALUE(LEFT(L$1,4)),VALUE(RIGHT(L$1,2)),1)&gt;TODAY(),"",IF(EOMONTH(DATE(VALUE(LEFT(L$1,4)),VALUE(RIGHT(L$1,2)),1),0)&lt;TODAY(),L5/DAY(EOMONTH(DATE(VALUE(LEFT(L$1,4)),VALUE(RIGHT(L$1,2)),1),0)),L5/MAX(NOW()-DATE(VALUE(LEFT(L$1,4)),VALUE(RIGHT(L$1,2)),1),1/24))),"")</f>
+        <v/>
+      </c>
+      <c r="M3" s="4">
+        <f>IFERROR(IF(DATE(VALUE(LEFT(M$1,4)),VALUE(RIGHT(M$1,2)),1)&gt;TODAY(),"",IF(EOMONTH(DATE(VALUE(LEFT(M$1,4)),VALUE(RIGHT(M$1,2)),1),0)&lt;TODAY(),M5/DAY(EOMONTH(DATE(VALUE(LEFT(M$1,4)),VALUE(RIGHT(M$1,2)),1),0)),M5/MAX(NOW()-DATE(VALUE(LEFT(M$1,4)),VALUE(RIGHT(M$1,2)),1),1/24))),"")</f>
+        <v/>
+      </c>
+      <c r="N3" s="4">
+        <f>IFERROR(IF(DATE(VALUE(LEFT(N$1,4)),VALUE(RIGHT(N$1,2)),1)&gt;TODAY(),"",IF(EOMONTH(DATE(VALUE(LEFT(N$1,4)),VALUE(RIGHT(N$1,2)),1),0)&lt;TODAY(),N5/DAY(EOMONTH(DATE(VALUE(LEFT(N$1,4)),VALUE(RIGHT(N$1,2)),1),0)),N5/MAX(NOW()-DATE(VALUE(LEFT(N$1,4)),VALUE(RIGHT(N$1,2)),1),1/24))),"")</f>
+        <v/>
+      </c>
+      <c r="O3" s="4">
+        <f>IFERROR(IF(DATE(VALUE(LEFT(O$1,4)),VALUE(RIGHT(O$1,2)),1)&gt;TODAY(),"",IF(EOMONTH(DATE(VALUE(LEFT(O$1,4)),VALUE(RIGHT(O$1,2)),1),0)&lt;TODAY(),O5/DAY(EOMONTH(DATE(VALUE(LEFT(O$1,4)),VALUE(RIGHT(O$1,2)),1),0)),O5/MAX(NOW()-DATE(VALUE(LEFT(O$1,4)),VALUE(RIGHT(O$1,2)),1),1/24))),"")</f>
+        <v/>
+      </c>
       <c r="P3" s="4" t="n"/>
       <c r="Q3" s="4" t="n"/>
     </row>
@@ -726,51 +757,51 @@
       <c r="B4" s="6" t="n"/>
       <c r="C4" s="6" t="n"/>
       <c r="D4" s="6">
-        <f>D5+D8</f>
+        <f>D5+D8+D9</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>E5+E8</f>
+        <f>E5+E8+E9</f>
         <v/>
       </c>
       <c r="F4" s="6">
-        <f>F5+F8</f>
+        <f>F5+F8+F9</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>G5+G8</f>
+        <f>G5+G8+G9</f>
         <v/>
       </c>
       <c r="H4" s="6">
-        <f>H5+H8</f>
+        <f>H5+H8+H9</f>
         <v/>
       </c>
       <c r="I4" s="6">
-        <f>I5+I8</f>
+        <f>I5+I8+I9</f>
         <v/>
       </c>
       <c r="J4" s="6">
-        <f>J5+J8</f>
+        <f>J5+J8+J9</f>
         <v/>
       </c>
       <c r="K4" s="6">
-        <f>K5+K8</f>
+        <f>K5+K8+K9</f>
         <v/>
       </c>
       <c r="L4" s="6">
-        <f>L5+L8</f>
+        <f>L5+L8+L9</f>
         <v/>
       </c>
       <c r="M4" s="6">
-        <f>M5+M8</f>
+        <f>M5+M8+M9</f>
         <v/>
       </c>
       <c r="N4" s="6">
-        <f>N5+N8</f>
+        <f>N5+N8+N9</f>
         <v/>
       </c>
       <c r="O4" s="6">
-        <f>O5+O8</f>
+        <f>O5+O8+O9</f>
         <v/>
       </c>
       <c r="P4" s="6">
@@ -973,304 +1004,300 @@
         </is>
       </c>
     </row>
-    <row r="8" hidden="1" outlineLevel="2" ht="12" customHeight="1">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Otros ingresos</t>
-        </is>
-      </c>
-      <c r="B8" s="10" t="n"/>
-      <c r="C8" s="10" t="n"/>
-      <c r="D8" s="10" t="n"/>
-      <c r="E8" s="10" t="n"/>
-      <c r="F8" s="10" t="n"/>
-      <c r="G8" s="10" t="n"/>
-      <c r="H8" s="10" t="n"/>
-      <c r="I8" s="10" t="n"/>
-      <c r="J8" s="10" t="n"/>
-      <c r="K8" s="10" t="n"/>
-      <c r="L8" s="10" t="n"/>
-      <c r="M8" s="10" t="n"/>
-      <c r="N8" s="10" t="n"/>
-      <c r="O8" s="10" t="n"/>
-      <c r="P8" s="10">
+    <row r="8" outlineLevel="1" ht="12" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Services</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="n"/>
+      <c r="C8" s="8" t="n"/>
+      <c r="D8" s="8">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="E8" s="8">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="F8" s="8">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="G8" s="8">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="H8" s="8">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="I8" s="8">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="J8" s="8">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="K8" s="8">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="L8" s="8">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="M8" s="8">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="N8" s="8">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="O8" s="8">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="P8" s="8">
         <f>SUM(D8:O8)</f>
         <v/>
       </c>
-      <c r="Q8" s="10" t="n"/>
-    </row>
-    <row r="9" ht="12" customHeight="1">
-      <c r="B9" s="4" t="n"/>
-      <c r="C9" s="4" t="n"/>
-      <c r="D9" s="4" t="n"/>
-      <c r="E9" s="4" t="n"/>
-      <c r="F9" s="4" t="n"/>
-      <c r="G9" s="4" t="n"/>
-      <c r="H9" s="4" t="n"/>
-      <c r="I9" s="4" t="n"/>
-      <c r="J9" s="4" t="n"/>
-      <c r="K9" s="4" t="n"/>
-      <c r="L9" s="4" t="n"/>
-      <c r="M9" s="4" t="n"/>
-      <c r="N9" s="4" t="n"/>
-      <c r="O9" s="4" t="n"/>
-      <c r="P9" s="4">
+      <c r="Q8" s="8" t="n"/>
+    </row>
+    <row r="9" hidden="1" outlineLevel="2" ht="12" customHeight="1">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Uncategorized income</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="n"/>
+      <c r="C9" s="10" t="n"/>
+      <c r="D9" s="10" t="n"/>
+      <c r="E9" s="10" t="n"/>
+      <c r="F9" s="10" t="n"/>
+      <c r="G9" s="10" t="n"/>
+      <c r="H9" s="10" t="n"/>
+      <c r="I9" s="10" t="n"/>
+      <c r="J9" s="10" t="n"/>
+      <c r="K9" s="10" t="n"/>
+      <c r="L9" s="10" t="n"/>
+      <c r="M9" s="10" t="n"/>
+      <c r="N9" s="10" t="n"/>
+      <c r="O9" s="10" t="n"/>
+      <c r="P9" s="10">
         <f>SUM(D9:O9)</f>
         <v/>
       </c>
-      <c r="Q9" s="4" t="n"/>
+      <c r="Q9" s="10" t="n"/>
     </row>
     <row r="10" ht="12" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="B10" s="4" t="n"/>
+      <c r="C10" s="4" t="n"/>
+      <c r="D10" s="4" t="n"/>
+      <c r="E10" s="4" t="n"/>
+      <c r="F10" s="4" t="n"/>
+      <c r="G10" s="4" t="n"/>
+      <c r="H10" s="4" t="n"/>
+      <c r="I10" s="4" t="n"/>
+      <c r="J10" s="4" t="n"/>
+      <c r="K10" s="4" t="n"/>
+      <c r="L10" s="4" t="n"/>
+      <c r="M10" s="4" t="n"/>
+      <c r="N10" s="4" t="n"/>
+      <c r="O10" s="4" t="n"/>
+      <c r="P10" s="4">
+        <f>SUM(D10:O10)</f>
+        <v/>
+      </c>
+      <c r="Q10" s="4" t="n"/>
+    </row>
+    <row r="11" ht="12" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>Expenses</t>
         </is>
       </c>
-      <c r="B10" s="6" t="n"/>
-      <c r="C10" s="6" t="n"/>
-      <c r="D10" s="6">
-        <f>D11+D32</f>
-        <v/>
-      </c>
-      <c r="E10" s="6">
-        <f>E11+E32</f>
-        <v/>
-      </c>
-      <c r="F10" s="6">
-        <f>F11+F32</f>
-        <v/>
-      </c>
-      <c r="G10" s="6">
-        <f>G11+G32</f>
-        <v/>
-      </c>
-      <c r="H10" s="6">
-        <f>H11+H32</f>
-        <v/>
-      </c>
-      <c r="I10" s="6">
-        <f>I11+I32</f>
-        <v/>
-      </c>
-      <c r="J10" s="6">
-        <f>J11+J32</f>
-        <v/>
-      </c>
-      <c r="K10" s="6">
-        <f>K11+K32</f>
-        <v/>
-      </c>
-      <c r="L10" s="6">
-        <f>L11+L32</f>
-        <v/>
-      </c>
-      <c r="M10" s="6">
-        <f>M11+M32</f>
-        <v/>
-      </c>
-      <c r="N10" s="6">
-        <f>N11+N32</f>
-        <v/>
-      </c>
-      <c r="O10" s="6">
-        <f>O11+O32</f>
-        <v/>
-      </c>
-      <c r="P10" s="6">
-        <f>SUM(D10:O10)</f>
-        <v/>
-      </c>
-      <c r="Q10" s="6" t="n"/>
-    </row>
-    <row r="11" outlineLevel="1" ht="12" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="B11" s="6" t="n"/>
+      <c r="C11" s="6" t="n"/>
+      <c r="D11" s="6">
+        <f>D12+D33</f>
+        <v/>
+      </c>
+      <c r="E11" s="6">
+        <f>E12+E33</f>
+        <v/>
+      </c>
+      <c r="F11" s="6">
+        <f>F12+F33</f>
+        <v/>
+      </c>
+      <c r="G11" s="6">
+        <f>G12+G33</f>
+        <v/>
+      </c>
+      <c r="H11" s="6">
+        <f>H12+H33</f>
+        <v/>
+      </c>
+      <c r="I11" s="6">
+        <f>I12+I33</f>
+        <v/>
+      </c>
+      <c r="J11" s="6">
+        <f>J12+J33</f>
+        <v/>
+      </c>
+      <c r="K11" s="6">
+        <f>K12+K33</f>
+        <v/>
+      </c>
+      <c r="L11" s="6">
+        <f>L12+L33</f>
+        <v/>
+      </c>
+      <c r="M11" s="6">
+        <f>M12+M33</f>
+        <v/>
+      </c>
+      <c r="N11" s="6">
+        <f>N12+N33</f>
+        <v/>
+      </c>
+      <c r="O11" s="6">
+        <f>O12+O33</f>
+        <v/>
+      </c>
+      <c r="P11" s="6">
+        <f>SUM(D11:O11)</f>
+        <v/>
+      </c>
+      <c r="Q11" s="6" t="n"/>
+    </row>
+    <row r="12" outlineLevel="1" ht="12" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  COGS</t>
         </is>
       </c>
-      <c r="B11" s="8" t="n"/>
-      <c r="C11" s="8" t="n"/>
-      <c r="D11" s="8">
-        <f>D12+D18+D22</f>
-        <v/>
-      </c>
-      <c r="E11" s="8">
-        <f>E12+E18+E22</f>
-        <v/>
-      </c>
-      <c r="F11" s="8">
-        <f>F12+F18+F22</f>
-        <v/>
-      </c>
-      <c r="G11" s="8">
-        <f>G12+G18+G22</f>
-        <v/>
-      </c>
-      <c r="H11" s="8">
-        <f>H12+H18+H22</f>
-        <v/>
-      </c>
-      <c r="I11" s="8">
-        <f>I12+I18+I22</f>
-        <v/>
-      </c>
-      <c r="J11" s="8">
-        <f>J12+J18+J22</f>
-        <v/>
-      </c>
-      <c r="K11" s="8">
-        <f>K12+K18+K22</f>
-        <v/>
-      </c>
-      <c r="L11" s="8">
-        <f>L12+L18+L22</f>
-        <v/>
-      </c>
-      <c r="M11" s="8">
-        <f>M12+M18+M22</f>
-        <v/>
-      </c>
-      <c r="N11" s="8">
-        <f>N12+N18+N22</f>
-        <v/>
-      </c>
-      <c r="O11" s="8">
-        <f>O12+O18+O22</f>
-        <v/>
-      </c>
-      <c r="P11" s="8">
-        <f>SUM(D11:O11)</f>
-        <v/>
-      </c>
-      <c r="Q11" s="8" t="n"/>
-    </row>
-    <row r="12" hidden="1" outlineLevel="2" ht="12" customHeight="1">
-      <c r="A12" s="9" t="inlineStr">
+      <c r="B12" s="8" t="n"/>
+      <c r="C12" s="8" t="n"/>
+      <c r="D12" s="8">
+        <f>D13+D19+D23</f>
+        <v/>
+      </c>
+      <c r="E12" s="8">
+        <f>E13+E19+E23</f>
+        <v/>
+      </c>
+      <c r="F12" s="8">
+        <f>F13+F19+F23</f>
+        <v/>
+      </c>
+      <c r="G12" s="8">
+        <f>G13+G19+G23</f>
+        <v/>
+      </c>
+      <c r="H12" s="8">
+        <f>H13+H19+H23</f>
+        <v/>
+      </c>
+      <c r="I12" s="8">
+        <f>I13+I19+I23</f>
+        <v/>
+      </c>
+      <c r="J12" s="8">
+        <f>J13+J19+J23</f>
+        <v/>
+      </c>
+      <c r="K12" s="8">
+        <f>K13+K19+K23</f>
+        <v/>
+      </c>
+      <c r="L12" s="8">
+        <f>L13+L19+L23</f>
+        <v/>
+      </c>
+      <c r="M12" s="8">
+        <f>M13+M19+M23</f>
+        <v/>
+      </c>
+      <c r="N12" s="8">
+        <f>N13+N19+N23</f>
+        <v/>
+      </c>
+      <c r="O12" s="8">
+        <f>O13+O19+O23</f>
+        <v/>
+      </c>
+      <c r="P12" s="8">
+        <f>SUM(D12:O12)</f>
+        <v/>
+      </c>
+      <c r="Q12" s="8" t="n"/>
+    </row>
+    <row r="13" hidden="1" outlineLevel="2" ht="12" customHeight="1">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">    Manufacturing</t>
         </is>
       </c>
-      <c r="B12" s="10" t="n"/>
-      <c r="C12" s="10" t="n"/>
-      <c r="D12" s="10">
-        <f>SUM(D13:D15)+D16</f>
-        <v/>
-      </c>
-      <c r="E12" s="10">
-        <f>SUM(E13:E15)+E16</f>
-        <v/>
-      </c>
-      <c r="F12" s="10">
-        <f>SUM(F13:F15)+F16</f>
-        <v/>
-      </c>
-      <c r="G12" s="10">
-        <f>SUM(G13:G15)+G16</f>
-        <v/>
-      </c>
-      <c r="H12" s="10">
-        <f>SUM(H13:H15)+H16</f>
-        <v/>
-      </c>
-      <c r="I12" s="10">
-        <f>SUM(I13:I15)+I16</f>
-        <v/>
-      </c>
-      <c r="J12" s="10">
-        <f>SUM(J13:J15)+J16</f>
-        <v/>
-      </c>
-      <c r="K12" s="10">
-        <f>SUM(K13:K15)+K16</f>
-        <v/>
-      </c>
-      <c r="L12" s="10">
-        <f>SUM(L13:L15)+L16</f>
-        <v/>
-      </c>
-      <c r="M12" s="10">
-        <f>SUM(M13:M15)+M16</f>
-        <v/>
-      </c>
-      <c r="N12" s="10">
-        <f>SUM(N13:N15)+N16</f>
-        <v/>
-      </c>
-      <c r="O12" s="10">
-        <f>SUM(O13:O15)+O16</f>
-        <v/>
-      </c>
-      <c r="P12" s="10">
-        <f>SUM(D12:O12)</f>
-        <v/>
-      </c>
-      <c r="Q12" s="10" t="inlineStr">
-        <is>
-          <t>-&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" hidden="1" outlineLevel="3" ht="12" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      ARTLINK</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="n"/>
-      <c r="C13" s="4" t="n"/>
-      <c r="D13" s="4">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,D$1,'g-expenses-ltd'!$D:$D,"manufacturing",'g-expenses-ltd'!$E:$E,TRIM($A13))</f>
-        <v/>
-      </c>
-      <c r="E13" s="4">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,E$1,'g-expenses-ltd'!$D:$D,"manufacturing",'g-expenses-ltd'!$E:$E,TRIM($A13))</f>
-        <v/>
-      </c>
-      <c r="F13" s="4">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,F$1,'g-expenses-ltd'!$D:$D,"manufacturing",'g-expenses-ltd'!$E:$E,TRIM($A13))</f>
-        <v/>
-      </c>
-      <c r="G13" s="4">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,G$1,'g-expenses-ltd'!$D:$D,"manufacturing",'g-expenses-ltd'!$E:$E,TRIM($A13))</f>
-        <v/>
-      </c>
-      <c r="H13" s="4">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,H$1,'g-expenses-ltd'!$D:$D,"manufacturing",'g-expenses-ltd'!$E:$E,TRIM($A13))</f>
-        <v/>
-      </c>
-      <c r="I13" s="4">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,I$1,'g-expenses-ltd'!$D:$D,"manufacturing",'g-expenses-ltd'!$E:$E,TRIM($A13))</f>
-        <v/>
-      </c>
-      <c r="J13" s="4">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,J$1,'g-expenses-ltd'!$D:$D,"manufacturing",'g-expenses-ltd'!$E:$E,TRIM($A13))</f>
-        <v/>
-      </c>
-      <c r="K13" s="4">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,K$1,'g-expenses-ltd'!$D:$D,"manufacturing",'g-expenses-ltd'!$E:$E,TRIM($A13))</f>
-        <v/>
-      </c>
-      <c r="L13" s="4">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,L$1,'g-expenses-ltd'!$D:$D,"manufacturing",'g-expenses-ltd'!$E:$E,TRIM($A13))</f>
-        <v/>
-      </c>
-      <c r="M13" s="4">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,M$1,'g-expenses-ltd'!$D:$D,"manufacturing",'g-expenses-ltd'!$E:$E,TRIM($A13))</f>
-        <v/>
-      </c>
-      <c r="N13" s="4">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,N$1,'g-expenses-ltd'!$D:$D,"manufacturing",'g-expenses-ltd'!$E:$E,TRIM($A13))</f>
-        <v/>
-      </c>
-      <c r="O13" s="4">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,O$1,'g-expenses-ltd'!$D:$D,"manufacturing",'g-expenses-ltd'!$E:$E,TRIM($A13))</f>
-        <v/>
-      </c>
-      <c r="P13" s="4">
+      <c r="B13" s="10" t="n"/>
+      <c r="C13" s="10" t="n"/>
+      <c r="D13" s="10">
+        <f>SUM(D14:D16)+D17</f>
+        <v/>
+      </c>
+      <c r="E13" s="10">
+        <f>SUM(E14:E16)+E17</f>
+        <v/>
+      </c>
+      <c r="F13" s="10">
+        <f>SUM(F14:F16)+F17</f>
+        <v/>
+      </c>
+      <c r="G13" s="10">
+        <f>SUM(G14:G16)+G17</f>
+        <v/>
+      </c>
+      <c r="H13" s="10">
+        <f>SUM(H14:H16)+H17</f>
+        <v/>
+      </c>
+      <c r="I13" s="10">
+        <f>SUM(I14:I16)+I17</f>
+        <v/>
+      </c>
+      <c r="J13" s="10">
+        <f>SUM(J14:J16)+J17</f>
+        <v/>
+      </c>
+      <c r="K13" s="10">
+        <f>SUM(K14:K16)+K17</f>
+        <v/>
+      </c>
+      <c r="L13" s="10">
+        <f>SUM(L14:L16)+L17</f>
+        <v/>
+      </c>
+      <c r="M13" s="10">
+        <f>SUM(M14:M16)+M17</f>
+        <v/>
+      </c>
+      <c r="N13" s="10">
+        <f>SUM(N14:N16)+N17</f>
+        <v/>
+      </c>
+      <c r="O13" s="10">
+        <f>SUM(O14:O16)+O17</f>
+        <v/>
+      </c>
+      <c r="P13" s="10">
         <f>SUM(D13:O13)</f>
         <v/>
       </c>
-      <c r="Q13" s="4" t="inlineStr">
+      <c r="Q13" s="10" t="inlineStr">
         <is>
           <t>-&gt;</t>
         </is>
@@ -1279,7 +1306,7 @@
     <row r="14" hidden="1" outlineLevel="3" ht="12" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">      JONDO</t>
+          <t xml:space="preserve">      ARTLINK</t>
         </is>
       </c>
       <c r="B14" s="4" t="n"/>
@@ -1336,12 +1363,16 @@
         <f>SUM(D14:O14)</f>
         <v/>
       </c>
-      <c r="Q14" s="4" t="n"/>
+      <c r="Q14" s="4" t="inlineStr">
+        <is>
+          <t>-&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="15" hidden="1" outlineLevel="3" ht="12" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">      PROCO</t>
+          <t xml:space="preserve">      JONDO</t>
         </is>
       </c>
       <c r="B15" s="4" t="n"/>
@@ -1400,229 +1431,225 @@
       </c>
       <c r="Q15" s="4" t="n"/>
     </row>
-    <row r="16" ht="12" customHeight="1">
+    <row r="16" hidden="1" outlineLevel="3" ht="12" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Consumo marcos</t>
+          <t xml:space="preserve">      PROCO</t>
         </is>
       </c>
       <c r="B16" s="4" t="n"/>
       <c r="C16" s="4" t="n"/>
-      <c r="D16" s="4" t="n">
-        <v>1949.14</v>
-      </c>
-      <c r="E16" s="4" t="n">
-        <v>2398.45</v>
-      </c>
-      <c r="F16" s="4" t="n">
-        <v>2181.65</v>
-      </c>
-      <c r="G16" s="4" t="n">
-        <v>37.35</v>
-      </c>
-      <c r="H16" s="4" t="n"/>
-      <c r="I16" s="4" t="n"/>
-      <c r="J16" s="4" t="n"/>
-      <c r="K16" s="4" t="n"/>
-      <c r="L16" s="4" t="n"/>
-      <c r="M16" s="4" t="n"/>
-      <c r="N16" s="4" t="n"/>
-      <c r="O16" s="4" t="n"/>
+      <c r="D16" s="4">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,D$1,'g-expenses-ltd'!$D:$D,"manufacturing",'g-expenses-ltd'!$E:$E,TRIM($A16))</f>
+        <v/>
+      </c>
+      <c r="E16" s="4">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,E$1,'g-expenses-ltd'!$D:$D,"manufacturing",'g-expenses-ltd'!$E:$E,TRIM($A16))</f>
+        <v/>
+      </c>
+      <c r="F16" s="4">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,F$1,'g-expenses-ltd'!$D:$D,"manufacturing",'g-expenses-ltd'!$E:$E,TRIM($A16))</f>
+        <v/>
+      </c>
+      <c r="G16" s="4">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,G$1,'g-expenses-ltd'!$D:$D,"manufacturing",'g-expenses-ltd'!$E:$E,TRIM($A16))</f>
+        <v/>
+      </c>
+      <c r="H16" s="4">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,H$1,'g-expenses-ltd'!$D:$D,"manufacturing",'g-expenses-ltd'!$E:$E,TRIM($A16))</f>
+        <v/>
+      </c>
+      <c r="I16" s="4">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,I$1,'g-expenses-ltd'!$D:$D,"manufacturing",'g-expenses-ltd'!$E:$E,TRIM($A16))</f>
+        <v/>
+      </c>
+      <c r="J16" s="4">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,J$1,'g-expenses-ltd'!$D:$D,"manufacturing",'g-expenses-ltd'!$E:$E,TRIM($A16))</f>
+        <v/>
+      </c>
+      <c r="K16" s="4">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,K$1,'g-expenses-ltd'!$D:$D,"manufacturing",'g-expenses-ltd'!$E:$E,TRIM($A16))</f>
+        <v/>
+      </c>
+      <c r="L16" s="4">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,L$1,'g-expenses-ltd'!$D:$D,"manufacturing",'g-expenses-ltd'!$E:$E,TRIM($A16))</f>
+        <v/>
+      </c>
+      <c r="M16" s="4">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,M$1,'g-expenses-ltd'!$D:$D,"manufacturing",'g-expenses-ltd'!$E:$E,TRIM($A16))</f>
+        <v/>
+      </c>
+      <c r="N16" s="4">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,N$1,'g-expenses-ltd'!$D:$D,"manufacturing",'g-expenses-ltd'!$E:$E,TRIM($A16))</f>
+        <v/>
+      </c>
+      <c r="O16" s="4">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,O$1,'g-expenses-ltd'!$D:$D,"manufacturing",'g-expenses-ltd'!$E:$E,TRIM($A16))</f>
+        <v/>
+      </c>
       <c r="P16" s="4">
         <f>SUM(D16:O16)</f>
         <v/>
       </c>
       <c r="Q16" s="4" t="n"/>
     </row>
-    <row r="17" hidden="1" outlineLevel="2" ht="12" customHeight="1">
-      <c r="A17" s="11" t="inlineStr">
+    <row r="17" ht="12" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Consumo marcos</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="n"/>
+      <c r="C17" s="4" t="n"/>
+      <c r="D17" s="4" t="n">
+        <v>1949.14</v>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>2398.45</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>2181.65</v>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>67.65000000000001</v>
+      </c>
+      <c r="H17" s="4" t="n"/>
+      <c r="I17" s="4" t="n"/>
+      <c r="J17" s="4" t="n"/>
+      <c r="K17" s="4" t="n"/>
+      <c r="L17" s="4" t="n"/>
+      <c r="M17" s="4" t="n"/>
+      <c r="N17" s="4" t="n"/>
+      <c r="O17" s="4" t="n"/>
+      <c r="P17" s="4">
+        <f>SUM(D17:O17)</f>
+        <v/>
+      </c>
+      <c r="Q17" s="4" t="n"/>
+    </row>
+    <row r="18" hidden="1" outlineLevel="2" ht="12" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">    % Manufacturing / sales</t>
         </is>
       </c>
-      <c r="B17" s="12" t="n"/>
-      <c r="C17" s="12" t="n"/>
-      <c r="D17" s="12">
-        <f>IFERROR(D12/D5,0)</f>
-        <v/>
-      </c>
-      <c r="E17" s="12">
-        <f>IFERROR(E12/E5,0)</f>
-        <v/>
-      </c>
-      <c r="F17" s="12">
-        <f>IFERROR(F12/F5,0)</f>
-        <v/>
-      </c>
-      <c r="G17" s="12">
-        <f>IFERROR(G12/G5,0)</f>
-        <v/>
-      </c>
-      <c r="H17" s="12">
-        <f>IFERROR(H12/H5,0)</f>
-        <v/>
-      </c>
-      <c r="I17" s="12">
-        <f>IFERROR(I12/I5,0)</f>
-        <v/>
-      </c>
-      <c r="J17" s="12">
-        <f>IFERROR(J12/J5,0)</f>
-        <v/>
-      </c>
-      <c r="K17" s="12">
-        <f>IFERROR(K12/K5,0)</f>
-        <v/>
-      </c>
-      <c r="L17" s="12">
-        <f>IFERROR(L12/L5,0)</f>
-        <v/>
-      </c>
-      <c r="M17" s="12">
-        <f>IFERROR(M12/M5,0)</f>
-        <v/>
-      </c>
-      <c r="N17" s="12">
-        <f>IFERROR(N12/N5,0)</f>
-        <v/>
-      </c>
-      <c r="O17" s="12">
-        <f>IFERROR(O12/O5,0)</f>
-        <v/>
-      </c>
-      <c r="P17" s="12">
-        <f>IFERROR(P12/P5,0)</f>
-        <v/>
-      </c>
-      <c r="Q17" s="12" t="n"/>
-    </row>
-    <row r="18" hidden="1" outlineLevel="2" ht="12" customHeight="1">
-      <c r="A18" s="9" t="inlineStr">
+      <c r="B18" s="11" t="n"/>
+      <c r="C18" s="11" t="n"/>
+      <c r="D18" s="11">
+        <f>IFERROR(D13/D5,0)</f>
+        <v/>
+      </c>
+      <c r="E18" s="11">
+        <f>IFERROR(E13/E5,0)</f>
+        <v/>
+      </c>
+      <c r="F18" s="11">
+        <f>IFERROR(F13/F5,0)</f>
+        <v/>
+      </c>
+      <c r="G18" s="11">
+        <f>IFERROR(G13/G5,0)</f>
+        <v/>
+      </c>
+      <c r="H18" s="11">
+        <f>IFERROR(H13/H5,0)</f>
+        <v/>
+      </c>
+      <c r="I18" s="11">
+        <f>IFERROR(I13/I5,0)</f>
+        <v/>
+      </c>
+      <c r="J18" s="11">
+        <f>IFERROR(J13/J5,0)</f>
+        <v/>
+      </c>
+      <c r="K18" s="11">
+        <f>IFERROR(K13/K5,0)</f>
+        <v/>
+      </c>
+      <c r="L18" s="11">
+        <f>IFERROR(L13/L5,0)</f>
+        <v/>
+      </c>
+      <c r="M18" s="11">
+        <f>IFERROR(M13/M5,0)</f>
+        <v/>
+      </c>
+      <c r="N18" s="11">
+        <f>IFERROR(N13/N5,0)</f>
+        <v/>
+      </c>
+      <c r="O18" s="11">
+        <f>IFERROR(O13/O5,0)</f>
+        <v/>
+      </c>
+      <c r="P18" s="11">
+        <f>IFERROR(P13/P5,0)</f>
+        <v/>
+      </c>
+      <c r="Q18" s="11" t="n"/>
+    </row>
+    <row r="19" hidden="1" outlineLevel="2" ht="12" customHeight="1">
+      <c r="A19" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">    Logistics</t>
         </is>
       </c>
-      <c r="B18" s="10" t="n"/>
-      <c r="C18" s="10" t="n"/>
-      <c r="D18" s="10">
-        <f>SUM(D19:D20)</f>
-        <v/>
-      </c>
-      <c r="E18" s="10">
-        <f>SUM(E19:E20)</f>
-        <v/>
-      </c>
-      <c r="F18" s="10">
-        <f>SUM(F19:F20)</f>
-        <v/>
-      </c>
-      <c r="G18" s="10">
-        <f>SUM(G19:G20)</f>
-        <v/>
-      </c>
-      <c r="H18" s="10">
-        <f>SUM(H19:H20)</f>
-        <v/>
-      </c>
-      <c r="I18" s="10">
-        <f>SUM(I19:I20)</f>
-        <v/>
-      </c>
-      <c r="J18" s="10">
-        <f>SUM(J19:J20)</f>
-        <v/>
-      </c>
-      <c r="K18" s="10">
-        <f>SUM(K19:K20)</f>
-        <v/>
-      </c>
-      <c r="L18" s="10">
-        <f>SUM(L19:L20)</f>
-        <v/>
-      </c>
-      <c r="M18" s="10">
-        <f>SUM(M19:M20)</f>
-        <v/>
-      </c>
-      <c r="N18" s="10">
-        <f>SUM(N19:N20)</f>
-        <v/>
-      </c>
-      <c r="O18" s="10">
-        <f>SUM(O19:O20)</f>
-        <v/>
-      </c>
-      <c r="P18" s="10">
-        <f>SUM(D18:O18)</f>
-        <v/>
-      </c>
-      <c r="Q18" s="10" t="inlineStr">
-        <is>
-          <t>-&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" hidden="1" outlineLevel="3" ht="12" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      PROCO</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="n"/>
-      <c r="C19" s="4" t="n"/>
-      <c r="D19" s="4">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,D$1,'g-expenses-ltd'!$D:$D,"logistics",'g-expenses-ltd'!$E:$E,TRIM($A19))</f>
-        <v/>
-      </c>
-      <c r="E19" s="4">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,E$1,'g-expenses-ltd'!$D:$D,"logistics",'g-expenses-ltd'!$E:$E,TRIM($A19))</f>
-        <v/>
-      </c>
-      <c r="F19" s="4">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,F$1,'g-expenses-ltd'!$D:$D,"logistics",'g-expenses-ltd'!$E:$E,TRIM($A19))</f>
-        <v/>
-      </c>
-      <c r="G19" s="4">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,G$1,'g-expenses-ltd'!$D:$D,"logistics",'g-expenses-ltd'!$E:$E,TRIM($A19))</f>
-        <v/>
-      </c>
-      <c r="H19" s="4">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,H$1,'g-expenses-ltd'!$D:$D,"logistics",'g-expenses-ltd'!$E:$E,TRIM($A19))</f>
-        <v/>
-      </c>
-      <c r="I19" s="4">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,I$1,'g-expenses-ltd'!$D:$D,"logistics",'g-expenses-ltd'!$E:$E,TRIM($A19))</f>
-        <v/>
-      </c>
-      <c r="J19" s="4">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,J$1,'g-expenses-ltd'!$D:$D,"logistics",'g-expenses-ltd'!$E:$E,TRIM($A19))</f>
-        <v/>
-      </c>
-      <c r="K19" s="4">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,K$1,'g-expenses-ltd'!$D:$D,"logistics",'g-expenses-ltd'!$E:$E,TRIM($A19))</f>
-        <v/>
-      </c>
-      <c r="L19" s="4">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,L$1,'g-expenses-ltd'!$D:$D,"logistics",'g-expenses-ltd'!$E:$E,TRIM($A19))</f>
-        <v/>
-      </c>
-      <c r="M19" s="4">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,M$1,'g-expenses-ltd'!$D:$D,"logistics",'g-expenses-ltd'!$E:$E,TRIM($A19))</f>
-        <v/>
-      </c>
-      <c r="N19" s="4">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,N$1,'g-expenses-ltd'!$D:$D,"logistics",'g-expenses-ltd'!$E:$E,TRIM($A19))</f>
-        <v/>
-      </c>
-      <c r="O19" s="4">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,O$1,'g-expenses-ltd'!$D:$D,"logistics",'g-expenses-ltd'!$E:$E,TRIM($A19))</f>
-        <v/>
-      </c>
-      <c r="P19" s="4">
+      <c r="B19" s="10" t="n"/>
+      <c r="C19" s="10" t="n"/>
+      <c r="D19" s="10">
+        <f>SUM(D20:D21)</f>
+        <v/>
+      </c>
+      <c r="E19" s="10">
+        <f>SUM(E20:E21)</f>
+        <v/>
+      </c>
+      <c r="F19" s="10">
+        <f>SUM(F20:F21)</f>
+        <v/>
+      </c>
+      <c r="G19" s="10">
+        <f>SUM(G20:G21)</f>
+        <v/>
+      </c>
+      <c r="H19" s="10">
+        <f>SUM(H20:H21)</f>
+        <v/>
+      </c>
+      <c r="I19" s="10">
+        <f>SUM(I20:I21)</f>
+        <v/>
+      </c>
+      <c r="J19" s="10">
+        <f>SUM(J20:J21)</f>
+        <v/>
+      </c>
+      <c r="K19" s="10">
+        <f>SUM(K20:K21)</f>
+        <v/>
+      </c>
+      <c r="L19" s="10">
+        <f>SUM(L20:L21)</f>
+        <v/>
+      </c>
+      <c r="M19" s="10">
+        <f>SUM(M20:M21)</f>
+        <v/>
+      </c>
+      <c r="N19" s="10">
+        <f>SUM(N20:N21)</f>
+        <v/>
+      </c>
+      <c r="O19" s="10">
+        <f>SUM(O20:O21)</f>
+        <v/>
+      </c>
+      <c r="P19" s="10">
         <f>SUM(D19:O19)</f>
         <v/>
       </c>
-      <c r="Q19" s="4" t="inlineStr">
+      <c r="Q19" s="10" t="inlineStr">
         <is>
           <t>-&gt;</t>
         </is>
@@ -1631,7 +1658,7 @@
     <row r="20" hidden="1" outlineLevel="3" ht="12" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">      PORTCLEARANCE</t>
+          <t xml:space="preserve">      PROCO</t>
         </is>
       </c>
       <c r="B20" s="4" t="n"/>
@@ -1688,1094 +1715,1094 @@
         <f>SUM(D20:O20)</f>
         <v/>
       </c>
-      <c r="Q20" s="4" t="n"/>
-    </row>
-    <row r="21" hidden="1" outlineLevel="2" ht="12" customHeight="1">
-      <c r="A21" s="11" t="inlineStr">
+      <c r="Q20" s="4" t="inlineStr">
+        <is>
+          <t>-&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" hidden="1" outlineLevel="3" ht="12" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      PORTCLEARANCE</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="n"/>
+      <c r="C21" s="4" t="n"/>
+      <c r="D21" s="4">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,D$1,'g-expenses-ltd'!$D:$D,"logistics",'g-expenses-ltd'!$E:$E,TRIM($A21))</f>
+        <v/>
+      </c>
+      <c r="E21" s="4">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,E$1,'g-expenses-ltd'!$D:$D,"logistics",'g-expenses-ltd'!$E:$E,TRIM($A21))</f>
+        <v/>
+      </c>
+      <c r="F21" s="4">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,F$1,'g-expenses-ltd'!$D:$D,"logistics",'g-expenses-ltd'!$E:$E,TRIM($A21))</f>
+        <v/>
+      </c>
+      <c r="G21" s="4">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,G$1,'g-expenses-ltd'!$D:$D,"logistics",'g-expenses-ltd'!$E:$E,TRIM($A21))</f>
+        <v/>
+      </c>
+      <c r="H21" s="4">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,H$1,'g-expenses-ltd'!$D:$D,"logistics",'g-expenses-ltd'!$E:$E,TRIM($A21))</f>
+        <v/>
+      </c>
+      <c r="I21" s="4">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,I$1,'g-expenses-ltd'!$D:$D,"logistics",'g-expenses-ltd'!$E:$E,TRIM($A21))</f>
+        <v/>
+      </c>
+      <c r="J21" s="4">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,J$1,'g-expenses-ltd'!$D:$D,"logistics",'g-expenses-ltd'!$E:$E,TRIM($A21))</f>
+        <v/>
+      </c>
+      <c r="K21" s="4">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,K$1,'g-expenses-ltd'!$D:$D,"logistics",'g-expenses-ltd'!$E:$E,TRIM($A21))</f>
+        <v/>
+      </c>
+      <c r="L21" s="4">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,L$1,'g-expenses-ltd'!$D:$D,"logistics",'g-expenses-ltd'!$E:$E,TRIM($A21))</f>
+        <v/>
+      </c>
+      <c r="M21" s="4">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,M$1,'g-expenses-ltd'!$D:$D,"logistics",'g-expenses-ltd'!$E:$E,TRIM($A21))</f>
+        <v/>
+      </c>
+      <c r="N21" s="4">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,N$1,'g-expenses-ltd'!$D:$D,"logistics",'g-expenses-ltd'!$E:$E,TRIM($A21))</f>
+        <v/>
+      </c>
+      <c r="O21" s="4">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,O$1,'g-expenses-ltd'!$D:$D,"logistics",'g-expenses-ltd'!$E:$E,TRIM($A21))</f>
+        <v/>
+      </c>
+      <c r="P21" s="4">
+        <f>SUM(D21:O21)</f>
+        <v/>
+      </c>
+      <c r="Q21" s="4" t="n"/>
+    </row>
+    <row r="22" hidden="1" outlineLevel="2" ht="12" customHeight="1">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">    % Logistics / sales</t>
         </is>
       </c>
-      <c r="B21" s="12" t="n"/>
-      <c r="C21" s="12" t="n"/>
-      <c r="D21" s="12">
-        <f>IFERROR(D18/D5,0)</f>
-        <v/>
-      </c>
-      <c r="E21" s="12">
-        <f>IFERROR(E18/E5,0)</f>
-        <v/>
-      </c>
-      <c r="F21" s="12">
-        <f>IFERROR(F18/F5,0)</f>
-        <v/>
-      </c>
-      <c r="G21" s="12">
-        <f>IFERROR(G18/G5,0)</f>
-        <v/>
-      </c>
-      <c r="H21" s="12">
-        <f>IFERROR(H18/H5,0)</f>
-        <v/>
-      </c>
-      <c r="I21" s="12">
-        <f>IFERROR(I18/I5,0)</f>
-        <v/>
-      </c>
-      <c r="J21" s="12">
-        <f>IFERROR(J18/J5,0)</f>
-        <v/>
-      </c>
-      <c r="K21" s="12">
-        <f>IFERROR(K18/K5,0)</f>
-        <v/>
-      </c>
-      <c r="L21" s="12">
-        <f>IFERROR(L18/L5,0)</f>
-        <v/>
-      </c>
-      <c r="M21" s="12">
-        <f>IFERROR(M18/M5,0)</f>
-        <v/>
-      </c>
-      <c r="N21" s="12">
-        <f>IFERROR(N18/N5,0)</f>
-        <v/>
-      </c>
-      <c r="O21" s="12">
-        <f>IFERROR(O18/O5,0)</f>
-        <v/>
-      </c>
-      <c r="P21" s="12">
-        <f>IFERROR(P18/P5,0)</f>
-        <v/>
-      </c>
-      <c r="Q21" s="12" t="n"/>
-    </row>
-    <row r="22" hidden="1" outlineLevel="2" ht="12" customHeight="1">
-      <c r="A22" s="9" t="inlineStr">
+      <c r="B22" s="11" t="n"/>
+      <c r="C22" s="11" t="n"/>
+      <c r="D22" s="11">
+        <f>IFERROR(D19/D5,0)</f>
+        <v/>
+      </c>
+      <c r="E22" s="11">
+        <f>IFERROR(E19/E5,0)</f>
+        <v/>
+      </c>
+      <c r="F22" s="11">
+        <f>IFERROR(F19/F5,0)</f>
+        <v/>
+      </c>
+      <c r="G22" s="11">
+        <f>IFERROR(G19/G5,0)</f>
+        <v/>
+      </c>
+      <c r="H22" s="11">
+        <f>IFERROR(H19/H5,0)</f>
+        <v/>
+      </c>
+      <c r="I22" s="11">
+        <f>IFERROR(I19/I5,0)</f>
+        <v/>
+      </c>
+      <c r="J22" s="11">
+        <f>IFERROR(J19/J5,0)</f>
+        <v/>
+      </c>
+      <c r="K22" s="11">
+        <f>IFERROR(K19/K5,0)</f>
+        <v/>
+      </c>
+      <c r="L22" s="11">
+        <f>IFERROR(L19/L5,0)</f>
+        <v/>
+      </c>
+      <c r="M22" s="11">
+        <f>IFERROR(M19/M5,0)</f>
+        <v/>
+      </c>
+      <c r="N22" s="11">
+        <f>IFERROR(N19/N5,0)</f>
+        <v/>
+      </c>
+      <c r="O22" s="11">
+        <f>IFERROR(O19/O5,0)</f>
+        <v/>
+      </c>
+      <c r="P22" s="11">
+        <f>IFERROR(P19/P5,0)</f>
+        <v/>
+      </c>
+      <c r="Q22" s="11" t="n"/>
+    </row>
+    <row r="23" hidden="1" outlineLevel="2" ht="12" customHeight="1">
+      <c r="A23" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">    Payment fees</t>
         </is>
       </c>
-      <c r="B22" s="10" t="n"/>
-      <c r="C22" s="10" t="n"/>
-      <c r="D22" s="10">
-        <f>SUM(D23:D23)</f>
-        <v/>
-      </c>
-      <c r="E22" s="10">
-        <f>SUM(E23:E23)</f>
-        <v/>
-      </c>
-      <c r="F22" s="10">
-        <f>SUM(F23:F23)</f>
-        <v/>
-      </c>
-      <c r="G22" s="10">
-        <f>SUM(G23:G23)</f>
-        <v/>
-      </c>
-      <c r="H22" s="10">
-        <f>SUM(H23:H23)</f>
-        <v/>
-      </c>
-      <c r="I22" s="10">
-        <f>SUM(I23:I23)</f>
-        <v/>
-      </c>
-      <c r="J22" s="10">
-        <f>SUM(J23:J23)</f>
-        <v/>
-      </c>
-      <c r="K22" s="10">
-        <f>SUM(K23:K23)</f>
-        <v/>
-      </c>
-      <c r="L22" s="10">
-        <f>SUM(L23:L23)</f>
-        <v/>
-      </c>
-      <c r="M22" s="10">
-        <f>SUM(M23:M23)</f>
-        <v/>
-      </c>
-      <c r="N22" s="10">
-        <f>SUM(N23:N23)</f>
-        <v/>
-      </c>
-      <c r="O22" s="10">
-        <f>SUM(O23:O23)</f>
-        <v/>
-      </c>
-      <c r="P22" s="10">
-        <f>SUM(D22:O22)</f>
-        <v/>
-      </c>
-      <c r="Q22" s="10" t="inlineStr">
+      <c r="B23" s="10" t="n"/>
+      <c r="C23" s="10" t="n"/>
+      <c r="D23" s="10">
+        <f>SUM(D24:D24)</f>
+        <v/>
+      </c>
+      <c r="E23" s="10">
+        <f>SUM(E24:E24)</f>
+        <v/>
+      </c>
+      <c r="F23" s="10">
+        <f>SUM(F24:F24)</f>
+        <v/>
+      </c>
+      <c r="G23" s="10">
+        <f>SUM(G24:G24)</f>
+        <v/>
+      </c>
+      <c r="H23" s="10">
+        <f>SUM(H24:H24)</f>
+        <v/>
+      </c>
+      <c r="I23" s="10">
+        <f>SUM(I24:I24)</f>
+        <v/>
+      </c>
+      <c r="J23" s="10">
+        <f>SUM(J24:J24)</f>
+        <v/>
+      </c>
+      <c r="K23" s="10">
+        <f>SUM(K24:K24)</f>
+        <v/>
+      </c>
+      <c r="L23" s="10">
+        <f>SUM(L24:L24)</f>
+        <v/>
+      </c>
+      <c r="M23" s="10">
+        <f>SUM(M24:M24)</f>
+        <v/>
+      </c>
+      <c r="N23" s="10">
+        <f>SUM(N24:N24)</f>
+        <v/>
+      </c>
+      <c r="O23" s="10">
+        <f>SUM(O24:O24)</f>
+        <v/>
+      </c>
+      <c r="P23" s="10">
+        <f>SUM(D23:O23)</f>
+        <v/>
+      </c>
+      <c r="Q23" s="10" t="inlineStr">
         <is>
           <t>-&gt;</t>
         </is>
       </c>
     </row>
-    <row r="23" hidden="1" outlineLevel="3" ht="12" customHeight="1">
-      <c r="A23" t="inlineStr">
+    <row r="24" hidden="1" outlineLevel="3" ht="12" customHeight="1">
+      <c r="A24" t="inlineStr">
         <is>
           <t xml:space="preserve">      SHOPIFY</t>
         </is>
       </c>
-      <c r="B23" s="4" t="n"/>
-      <c r="C23" s="4" t="n"/>
-      <c r="D23" s="4">
-        <f>SUMIFS('g-payment-fees-ltd'!$H:$H,'g-payment-fees-ltd'!$A:$A,D$1,'g-payment-fees-ltd'!$C:$C,TRIM($A23))</f>
-        <v/>
-      </c>
-      <c r="E23" s="4">
-        <f>SUMIFS('g-payment-fees-ltd'!$H:$H,'g-payment-fees-ltd'!$A:$A,E$1,'g-payment-fees-ltd'!$C:$C,TRIM($A23))</f>
-        <v/>
-      </c>
-      <c r="F23" s="4">
-        <f>SUMIFS('g-payment-fees-ltd'!$H:$H,'g-payment-fees-ltd'!$A:$A,F$1,'g-payment-fees-ltd'!$C:$C,TRIM($A23))</f>
-        <v/>
-      </c>
-      <c r="G23" s="4">
-        <f>SUMIFS('g-payment-fees-ltd'!$H:$H,'g-payment-fees-ltd'!$A:$A,G$1,'g-payment-fees-ltd'!$C:$C,TRIM($A23))</f>
-        <v/>
-      </c>
-      <c r="H23" s="4">
-        <f>SUMIFS('g-payment-fees-ltd'!$H:$H,'g-payment-fees-ltd'!$A:$A,H$1,'g-payment-fees-ltd'!$C:$C,TRIM($A23))</f>
-        <v/>
-      </c>
-      <c r="I23" s="4">
-        <f>SUMIFS('g-payment-fees-ltd'!$H:$H,'g-payment-fees-ltd'!$A:$A,I$1,'g-payment-fees-ltd'!$C:$C,TRIM($A23))</f>
-        <v/>
-      </c>
-      <c r="J23" s="4">
-        <f>SUMIFS('g-payment-fees-ltd'!$H:$H,'g-payment-fees-ltd'!$A:$A,J$1,'g-payment-fees-ltd'!$C:$C,TRIM($A23))</f>
-        <v/>
-      </c>
-      <c r="K23" s="4">
-        <f>SUMIFS('g-payment-fees-ltd'!$H:$H,'g-payment-fees-ltd'!$A:$A,K$1,'g-payment-fees-ltd'!$C:$C,TRIM($A23))</f>
-        <v/>
-      </c>
-      <c r="L23" s="4">
-        <f>SUMIFS('g-payment-fees-ltd'!$H:$H,'g-payment-fees-ltd'!$A:$A,L$1,'g-payment-fees-ltd'!$C:$C,TRIM($A23))</f>
-        <v/>
-      </c>
-      <c r="M23" s="4">
-        <f>SUMIFS('g-payment-fees-ltd'!$H:$H,'g-payment-fees-ltd'!$A:$A,M$1,'g-payment-fees-ltd'!$C:$C,TRIM($A23))</f>
-        <v/>
-      </c>
-      <c r="N23" s="4">
-        <f>SUMIFS('g-payment-fees-ltd'!$H:$H,'g-payment-fees-ltd'!$A:$A,N$1,'g-payment-fees-ltd'!$C:$C,TRIM($A23))</f>
-        <v/>
-      </c>
-      <c r="O23" s="4">
-        <f>SUMIFS('g-payment-fees-ltd'!$H:$H,'g-payment-fees-ltd'!$A:$A,O$1,'g-payment-fees-ltd'!$C:$C,TRIM($A23))</f>
-        <v/>
-      </c>
-      <c r="P23" s="4">
-        <f>SUM(D23:O23)</f>
-        <v/>
-      </c>
-      <c r="Q23" s="4" t="inlineStr">
-        <is>
-          <t>-&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="12" customHeight="1">
       <c r="B24" s="4" t="n"/>
       <c r="C24" s="4" t="n"/>
-      <c r="D24" s="4" t="n"/>
-      <c r="E24" s="4" t="n"/>
-      <c r="F24" s="4" t="n"/>
-      <c r="G24" s="4" t="n"/>
-      <c r="H24" s="4" t="n"/>
-      <c r="I24" s="4" t="n"/>
-      <c r="J24" s="4" t="n"/>
-      <c r="K24" s="4" t="n"/>
-      <c r="L24" s="4" t="n"/>
-      <c r="M24" s="4" t="n"/>
-      <c r="N24" s="4" t="n"/>
-      <c r="O24" s="4" t="n"/>
+      <c r="D24" s="4">
+        <f>SUMIFS('g-payment-fees-ltd'!$H:$H,'g-payment-fees-ltd'!$A:$A,D$1,'g-payment-fees-ltd'!$C:$C,TRIM($A24))</f>
+        <v/>
+      </c>
+      <c r="E24" s="4">
+        <f>SUMIFS('g-payment-fees-ltd'!$H:$H,'g-payment-fees-ltd'!$A:$A,E$1,'g-payment-fees-ltd'!$C:$C,TRIM($A24))</f>
+        <v/>
+      </c>
+      <c r="F24" s="4">
+        <f>SUMIFS('g-payment-fees-ltd'!$H:$H,'g-payment-fees-ltd'!$A:$A,F$1,'g-payment-fees-ltd'!$C:$C,TRIM($A24))</f>
+        <v/>
+      </c>
+      <c r="G24" s="4">
+        <f>SUMIFS('g-payment-fees-ltd'!$H:$H,'g-payment-fees-ltd'!$A:$A,G$1,'g-payment-fees-ltd'!$C:$C,TRIM($A24))</f>
+        <v/>
+      </c>
+      <c r="H24" s="4">
+        <f>SUMIFS('g-payment-fees-ltd'!$H:$H,'g-payment-fees-ltd'!$A:$A,H$1,'g-payment-fees-ltd'!$C:$C,TRIM($A24))</f>
+        <v/>
+      </c>
+      <c r="I24" s="4">
+        <f>SUMIFS('g-payment-fees-ltd'!$H:$H,'g-payment-fees-ltd'!$A:$A,I$1,'g-payment-fees-ltd'!$C:$C,TRIM($A24))</f>
+        <v/>
+      </c>
+      <c r="J24" s="4">
+        <f>SUMIFS('g-payment-fees-ltd'!$H:$H,'g-payment-fees-ltd'!$A:$A,J$1,'g-payment-fees-ltd'!$C:$C,TRIM($A24))</f>
+        <v/>
+      </c>
+      <c r="K24" s="4">
+        <f>SUMIFS('g-payment-fees-ltd'!$H:$H,'g-payment-fees-ltd'!$A:$A,K$1,'g-payment-fees-ltd'!$C:$C,TRIM($A24))</f>
+        <v/>
+      </c>
+      <c r="L24" s="4">
+        <f>SUMIFS('g-payment-fees-ltd'!$H:$H,'g-payment-fees-ltd'!$A:$A,L$1,'g-payment-fees-ltd'!$C:$C,TRIM($A24))</f>
+        <v/>
+      </c>
+      <c r="M24" s="4">
+        <f>SUMIFS('g-payment-fees-ltd'!$H:$H,'g-payment-fees-ltd'!$A:$A,M$1,'g-payment-fees-ltd'!$C:$C,TRIM($A24))</f>
+        <v/>
+      </c>
+      <c r="N24" s="4">
+        <f>SUMIFS('g-payment-fees-ltd'!$H:$H,'g-payment-fees-ltd'!$A:$A,N$1,'g-payment-fees-ltd'!$C:$C,TRIM($A24))</f>
+        <v/>
+      </c>
+      <c r="O24" s="4">
+        <f>SUMIFS('g-payment-fees-ltd'!$H:$H,'g-payment-fees-ltd'!$A:$A,O$1,'g-payment-fees-ltd'!$C:$C,TRIM($A24))</f>
+        <v/>
+      </c>
       <c r="P24" s="4">
         <f>SUM(D24:O24)</f>
         <v/>
       </c>
-      <c r="Q24" s="4" t="n"/>
-    </row>
-    <row r="25" hidden="1" outlineLevel="2" ht="12" customHeight="1">
-      <c r="A25" s="11" t="inlineStr">
+      <c r="Q24" s="4" t="inlineStr">
+        <is>
+          <t>-&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="12" customHeight="1">
+      <c r="B25" s="4" t="n"/>
+      <c r="C25" s="4" t="n"/>
+      <c r="D25" s="4" t="n"/>
+      <c r="E25" s="4" t="n"/>
+      <c r="F25" s="4" t="n"/>
+      <c r="G25" s="4" t="n"/>
+      <c r="H25" s="4" t="n"/>
+      <c r="I25" s="4" t="n"/>
+      <c r="J25" s="4" t="n"/>
+      <c r="K25" s="4" t="n"/>
+      <c r="L25" s="4" t="n"/>
+      <c r="M25" s="4" t="n"/>
+      <c r="N25" s="4" t="n"/>
+      <c r="O25" s="4" t="n"/>
+      <c r="P25" s="4">
+        <f>SUM(D25:O25)</f>
+        <v/>
+      </c>
+      <c r="Q25" s="4" t="n"/>
+    </row>
+    <row r="26" hidden="1" outlineLevel="2" ht="12" customHeight="1">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">    % Payment fees / sales</t>
         </is>
       </c>
-      <c r="B25" s="12" t="n"/>
-      <c r="C25" s="12" t="n"/>
-      <c r="D25" s="12">
-        <f>IFERROR(D22/D5,0)</f>
-        <v/>
-      </c>
-      <c r="E25" s="12">
-        <f>IFERROR(E22/E5,0)</f>
-        <v/>
-      </c>
-      <c r="F25" s="12">
-        <f>IFERROR(F22/F5,0)</f>
-        <v/>
-      </c>
-      <c r="G25" s="12">
-        <f>IFERROR(G22/G5,0)</f>
-        <v/>
-      </c>
-      <c r="H25" s="12">
-        <f>IFERROR(H22/H5,0)</f>
-        <v/>
-      </c>
-      <c r="I25" s="12">
-        <f>IFERROR(I22/I5,0)</f>
-        <v/>
-      </c>
-      <c r="J25" s="12">
-        <f>IFERROR(J22/J5,0)</f>
-        <v/>
-      </c>
-      <c r="K25" s="12">
-        <f>IFERROR(K22/K5,0)</f>
-        <v/>
-      </c>
-      <c r="L25" s="12">
-        <f>IFERROR(L22/L5,0)</f>
-        <v/>
-      </c>
-      <c r="M25" s="12">
-        <f>IFERROR(M22/M5,0)</f>
-        <v/>
-      </c>
-      <c r="N25" s="12">
-        <f>IFERROR(N22/N5,0)</f>
-        <v/>
-      </c>
-      <c r="O25" s="12">
-        <f>IFERROR(O22/O5,0)</f>
-        <v/>
-      </c>
-      <c r="P25" s="12">
-        <f>IFERROR(P22/P5,0)</f>
-        <v/>
-      </c>
-      <c r="Q25" s="12" t="n"/>
-    </row>
-    <row r="26" ht="12" customHeight="1">
-      <c r="B26" s="4" t="n"/>
-      <c r="C26" s="4" t="n"/>
-      <c r="D26" s="4" t="n"/>
-      <c r="E26" s="4" t="n"/>
-      <c r="F26" s="4" t="n"/>
-      <c r="G26" s="4" t="n"/>
-      <c r="H26" s="4" t="n"/>
-      <c r="I26" s="4" t="n"/>
-      <c r="J26" s="4" t="n"/>
-      <c r="K26" s="4" t="n"/>
-      <c r="L26" s="4" t="n"/>
-      <c r="M26" s="4" t="n"/>
-      <c r="N26" s="4" t="n"/>
-      <c r="O26" s="4" t="n"/>
-      <c r="P26" s="4">
-        <f>SUM(D26:O26)</f>
-        <v/>
-      </c>
-      <c r="Q26" s="4" t="n"/>
+      <c r="B26" s="11" t="n"/>
+      <c r="C26" s="11" t="n"/>
+      <c r="D26" s="11">
+        <f>IFERROR(D23/D5,0)</f>
+        <v/>
+      </c>
+      <c r="E26" s="11">
+        <f>IFERROR(E23/E5,0)</f>
+        <v/>
+      </c>
+      <c r="F26" s="11">
+        <f>IFERROR(F23/F5,0)</f>
+        <v/>
+      </c>
+      <c r="G26" s="11">
+        <f>IFERROR(G23/G5,0)</f>
+        <v/>
+      </c>
+      <c r="H26" s="11">
+        <f>IFERROR(H23/H5,0)</f>
+        <v/>
+      </c>
+      <c r="I26" s="11">
+        <f>IFERROR(I23/I5,0)</f>
+        <v/>
+      </c>
+      <c r="J26" s="11">
+        <f>IFERROR(J23/J5,0)</f>
+        <v/>
+      </c>
+      <c r="K26" s="11">
+        <f>IFERROR(K23/K5,0)</f>
+        <v/>
+      </c>
+      <c r="L26" s="11">
+        <f>IFERROR(L23/L5,0)</f>
+        <v/>
+      </c>
+      <c r="M26" s="11">
+        <f>IFERROR(M23/M5,0)</f>
+        <v/>
+      </c>
+      <c r="N26" s="11">
+        <f>IFERROR(N23/N5,0)</f>
+        <v/>
+      </c>
+      <c r="O26" s="11">
+        <f>IFERROR(O23/O5,0)</f>
+        <v/>
+      </c>
+      <c r="P26" s="11">
+        <f>IFERROR(P23/P5,0)</f>
+        <v/>
+      </c>
+      <c r="Q26" s="11" t="n"/>
     </row>
     <row r="27" ht="12" customHeight="1">
-      <c r="A27" s="13" t="inlineStr">
+      <c r="B27" s="4" t="n"/>
+      <c r="C27" s="4" t="n"/>
+      <c r="D27" s="4" t="n"/>
+      <c r="E27" s="4" t="n"/>
+      <c r="F27" s="4" t="n"/>
+      <c r="G27" s="4" t="n"/>
+      <c r="H27" s="4" t="n"/>
+      <c r="I27" s="4" t="n"/>
+      <c r="J27" s="4" t="n"/>
+      <c r="K27" s="4" t="n"/>
+      <c r="L27" s="4" t="n"/>
+      <c r="M27" s="4" t="n"/>
+      <c r="N27" s="4" t="n"/>
+      <c r="O27" s="4" t="n"/>
+      <c r="P27" s="4">
+        <f>SUM(D27:O27)</f>
+        <v/>
+      </c>
+      <c r="Q27" s="4" t="n"/>
+    </row>
+    <row r="28" ht="12" customHeight="1">
+      <c r="A28" s="12" t="inlineStr">
         <is>
           <t>GROSS MARGIN (SALES-MANUFACTURING)</t>
         </is>
       </c>
-      <c r="B27" s="14" t="n"/>
-      <c r="C27" s="14" t="n"/>
-      <c r="D27" s="14">
+      <c r="B28" s="13" t="n"/>
+      <c r="C28" s="13" t="n"/>
+      <c r="D28" s="13">
+        <f>D5-D13</f>
+        <v/>
+      </c>
+      <c r="E28" s="13">
+        <f>E5-E13</f>
+        <v/>
+      </c>
+      <c r="F28" s="13">
+        <f>F5-F13</f>
+        <v/>
+      </c>
+      <c r="G28" s="13">
+        <f>G5-G13</f>
+        <v/>
+      </c>
+      <c r="H28" s="13">
+        <f>H5-H13</f>
+        <v/>
+      </c>
+      <c r="I28" s="13">
+        <f>I5-I13</f>
+        <v/>
+      </c>
+      <c r="J28" s="13">
+        <f>J5-J13</f>
+        <v/>
+      </c>
+      <c r="K28" s="13">
+        <f>K5-K13</f>
+        <v/>
+      </c>
+      <c r="L28" s="13">
+        <f>L5-L13</f>
+        <v/>
+      </c>
+      <c r="M28" s="13">
+        <f>M5-M13</f>
+        <v/>
+      </c>
+      <c r="N28" s="13">
+        <f>N5-N13</f>
+        <v/>
+      </c>
+      <c r="O28" s="13">
+        <f>O5-O13</f>
+        <v/>
+      </c>
+      <c r="P28" s="13">
+        <f>SUM(D28:O28)</f>
+        <v/>
+      </c>
+      <c r="Q28" s="13" t="n"/>
+    </row>
+    <row r="29" hidden="1" outlineLevel="1" ht="12" customHeight="1">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>% gross margin</t>
+        </is>
+      </c>
+      <c r="B29" s="11" t="n"/>
+      <c r="C29" s="11" t="n"/>
+      <c r="D29" s="11">
+        <f>IFERROR(D28/D5,0)</f>
+        <v/>
+      </c>
+      <c r="E29" s="11">
+        <f>IFERROR(E28/E5,0)</f>
+        <v/>
+      </c>
+      <c r="F29" s="11">
+        <f>IFERROR(F28/F5,0)</f>
+        <v/>
+      </c>
+      <c r="G29" s="11">
+        <f>IFERROR(G28/G5,0)</f>
+        <v/>
+      </c>
+      <c r="H29" s="11">
+        <f>IFERROR(H28/H5,0)</f>
+        <v/>
+      </c>
+      <c r="I29" s="11">
+        <f>IFERROR(I28/I5,0)</f>
+        <v/>
+      </c>
+      <c r="J29" s="11">
+        <f>IFERROR(J28/J5,0)</f>
+        <v/>
+      </c>
+      <c r="K29" s="11">
+        <f>IFERROR(K28/K5,0)</f>
+        <v/>
+      </c>
+      <c r="L29" s="11">
+        <f>IFERROR(L28/L5,0)</f>
+        <v/>
+      </c>
+      <c r="M29" s="11">
+        <f>IFERROR(M28/M5,0)</f>
+        <v/>
+      </c>
+      <c r="N29" s="11">
+        <f>IFERROR(N28/N5,0)</f>
+        <v/>
+      </c>
+      <c r="O29" s="11">
+        <f>IFERROR(O28/O5,0)</f>
+        <v/>
+      </c>
+      <c r="P29" s="11">
+        <f>IFERROR(P28/P5,0)</f>
+        <v/>
+      </c>
+      <c r="Q29" s="11" t="n"/>
+    </row>
+    <row r="30" ht="12" customHeight="1">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>Contributive margin (product sales-COGS)</t>
+        </is>
+      </c>
+      <c r="B30" s="13" t="n"/>
+      <c r="C30" s="13" t="n"/>
+      <c r="D30" s="13">
         <f>D5-D12</f>
         <v/>
       </c>
-      <c r="E27" s="14">
+      <c r="E30" s="13">
         <f>E5-E12</f>
         <v/>
       </c>
-      <c r="F27" s="14">
+      <c r="F30" s="13">
         <f>F5-F12</f>
         <v/>
       </c>
-      <c r="G27" s="14">
+      <c r="G30" s="13">
         <f>G5-G12</f>
         <v/>
       </c>
-      <c r="H27" s="14">
+      <c r="H30" s="13">
         <f>H5-H12</f>
         <v/>
       </c>
-      <c r="I27" s="14">
+      <c r="I30" s="13">
         <f>I5-I12</f>
         <v/>
       </c>
-      <c r="J27" s="14">
+      <c r="J30" s="13">
         <f>J5-J12</f>
         <v/>
       </c>
-      <c r="K27" s="14">
+      <c r="K30" s="13">
         <f>K5-K12</f>
         <v/>
       </c>
-      <c r="L27" s="14">
+      <c r="L30" s="13">
         <f>L5-L12</f>
         <v/>
       </c>
-      <c r="M27" s="14">
+      <c r="M30" s="13">
         <f>M5-M12</f>
         <v/>
       </c>
-      <c r="N27" s="14">
+      <c r="N30" s="13">
         <f>N5-N12</f>
         <v/>
       </c>
-      <c r="O27" s="14">
+      <c r="O30" s="13">
         <f>O5-O12</f>
         <v/>
       </c>
-      <c r="P27" s="14">
-        <f>SUM(D27:O27)</f>
-        <v/>
-      </c>
-      <c r="Q27" s="14" t="n"/>
-    </row>
-    <row r="28" hidden="1" outlineLevel="1" ht="12" customHeight="1">
-      <c r="A28" s="11" t="inlineStr">
-        <is>
-          <t>% GROSS MARGIN</t>
-        </is>
-      </c>
-      <c r="B28" s="12" t="n"/>
-      <c r="C28" s="12" t="n"/>
-      <c r="D28" s="12">
-        <f>IFERROR(D27/D5,0)</f>
-        <v/>
-      </c>
-      <c r="E28" s="12">
-        <f>IFERROR(E27/E5,0)</f>
-        <v/>
-      </c>
-      <c r="F28" s="12">
-        <f>IFERROR(F27/F5,0)</f>
-        <v/>
-      </c>
-      <c r="G28" s="12">
-        <f>IFERROR(G27/G5,0)</f>
-        <v/>
-      </c>
-      <c r="H28" s="12">
-        <f>IFERROR(H27/H5,0)</f>
-        <v/>
-      </c>
-      <c r="I28" s="12">
-        <f>IFERROR(I27/I5,0)</f>
-        <v/>
-      </c>
-      <c r="J28" s="12">
-        <f>IFERROR(J27/J5,0)</f>
-        <v/>
-      </c>
-      <c r="K28" s="12">
-        <f>IFERROR(K27/K5,0)</f>
-        <v/>
-      </c>
-      <c r="L28" s="12">
-        <f>IFERROR(L27/L5,0)</f>
-        <v/>
-      </c>
-      <c r="M28" s="12">
-        <f>IFERROR(M27/M5,0)</f>
-        <v/>
-      </c>
-      <c r="N28" s="12">
-        <f>IFERROR(N27/N5,0)</f>
-        <v/>
-      </c>
-      <c r="O28" s="12">
-        <f>IFERROR(O27/O5,0)</f>
-        <v/>
-      </c>
-      <c r="P28" s="12">
-        <f>IFERROR(P27/P5,0)</f>
-        <v/>
-      </c>
-      <c r="Q28" s="12" t="n"/>
-    </row>
-    <row r="29" ht="12" customHeight="1">
-      <c r="A29" s="13" t="inlineStr">
-        <is>
-          <t>CONTRIBUTIVE MARGIN (TURNOVER-COGS)</t>
-        </is>
-      </c>
-      <c r="B29" s="14" t="n"/>
-      <c r="C29" s="14" t="n"/>
-      <c r="D29" s="14">
-        <f>D4-D11</f>
-        <v/>
-      </c>
-      <c r="E29" s="14">
-        <f>E4-E11</f>
-        <v/>
-      </c>
-      <c r="F29" s="14">
-        <f>F4-F11</f>
-        <v/>
-      </c>
-      <c r="G29" s="14">
-        <f>G4-G11</f>
-        <v/>
-      </c>
-      <c r="H29" s="14">
-        <f>H4-H11</f>
-        <v/>
-      </c>
-      <c r="I29" s="14">
-        <f>I4-I11</f>
-        <v/>
-      </c>
-      <c r="J29" s="14">
-        <f>J4-J11</f>
-        <v/>
-      </c>
-      <c r="K29" s="14">
-        <f>K4-K11</f>
-        <v/>
-      </c>
-      <c r="L29" s="14">
-        <f>L4-L11</f>
-        <v/>
-      </c>
-      <c r="M29" s="14">
-        <f>M4-M11</f>
-        <v/>
-      </c>
-      <c r="N29" s="14">
-        <f>N4-N11</f>
-        <v/>
-      </c>
-      <c r="O29" s="14">
-        <f>O4-O11</f>
-        <v/>
-      </c>
-      <c r="P29" s="14">
-        <f>SUM(D29:O29)</f>
-        <v/>
-      </c>
-      <c r="Q29" s="14" t="n"/>
-    </row>
-    <row r="30" hidden="1" outlineLevel="1" ht="12" customHeight="1">
-      <c r="A30" s="11" t="inlineStr">
-        <is>
-          <t>% CONTRIBUTIVE MARGIN</t>
-        </is>
-      </c>
-      <c r="B30" s="12" t="n"/>
-      <c r="C30" s="12" t="n"/>
-      <c r="D30" s="12">
-        <f>IFERROR(D29/D5,0)</f>
-        <v/>
-      </c>
-      <c r="E30" s="12">
-        <f>IFERROR(E29/E5,0)</f>
-        <v/>
-      </c>
-      <c r="F30" s="12">
-        <f>IFERROR(F29/F5,0)</f>
-        <v/>
-      </c>
-      <c r="G30" s="12">
-        <f>IFERROR(G29/G5,0)</f>
-        <v/>
-      </c>
-      <c r="H30" s="12">
-        <f>IFERROR(H29/H5,0)</f>
-        <v/>
-      </c>
-      <c r="I30" s="12">
-        <f>IFERROR(I29/I5,0)</f>
-        <v/>
-      </c>
-      <c r="J30" s="12">
-        <f>IFERROR(J29/J5,0)</f>
-        <v/>
-      </c>
-      <c r="K30" s="12">
-        <f>IFERROR(K29/K5,0)</f>
-        <v/>
-      </c>
-      <c r="L30" s="12">
-        <f>IFERROR(L29/L5,0)</f>
-        <v/>
-      </c>
-      <c r="M30" s="12">
-        <f>IFERROR(M29/M5,0)</f>
-        <v/>
-      </c>
-      <c r="N30" s="12">
-        <f>IFERROR(N29/N5,0)</f>
-        <v/>
-      </c>
-      <c r="O30" s="12">
-        <f>IFERROR(O29/O5,0)</f>
-        <v/>
-      </c>
-      <c r="P30" s="12">
-        <f>IFERROR(P29/P5,0)</f>
-        <v/>
-      </c>
-      <c r="Q30" s="12" t="n"/>
-    </row>
-    <row r="31" ht="12" customHeight="1">
-      <c r="B31" s="4" t="n"/>
-      <c r="C31" s="4" t="n"/>
-      <c r="D31" s="4" t="n"/>
-      <c r="E31" s="4" t="n"/>
-      <c r="F31" s="4" t="n"/>
-      <c r="G31" s="4" t="n"/>
-      <c r="H31" s="4" t="n"/>
-      <c r="I31" s="4" t="n"/>
-      <c r="J31" s="4" t="n"/>
-      <c r="K31" s="4" t="n"/>
-      <c r="L31" s="4" t="n"/>
-      <c r="M31" s="4" t="n"/>
-      <c r="N31" s="4" t="n"/>
-      <c r="O31" s="4" t="n"/>
-      <c r="P31" s="4">
-        <f>SUM(D31:O31)</f>
-        <v/>
-      </c>
-      <c r="Q31" s="4" t="n"/>
-    </row>
-    <row r="32" outlineLevel="1" ht="12" customHeight="1">
-      <c r="A32" s="7" t="inlineStr">
+      <c r="P30" s="13">
+        <f>SUM(D30:O30)</f>
+        <v/>
+      </c>
+      <c r="Q30" s="13" t="n"/>
+    </row>
+    <row r="31" hidden="1" outlineLevel="1" ht="12" customHeight="1">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>% contributive margin</t>
+        </is>
+      </c>
+      <c r="B31" s="11" t="n"/>
+      <c r="C31" s="11" t="n"/>
+      <c r="D31" s="11">
+        <f>IFERROR(D30/D5,0)</f>
+        <v/>
+      </c>
+      <c r="E31" s="11">
+        <f>IFERROR(E30/E5,0)</f>
+        <v/>
+      </c>
+      <c r="F31" s="11">
+        <f>IFERROR(F30/F5,0)</f>
+        <v/>
+      </c>
+      <c r="G31" s="11">
+        <f>IFERROR(G30/G5,0)</f>
+        <v/>
+      </c>
+      <c r="H31" s="11">
+        <f>IFERROR(H30/H5,0)</f>
+        <v/>
+      </c>
+      <c r="I31" s="11">
+        <f>IFERROR(I30/I5,0)</f>
+        <v/>
+      </c>
+      <c r="J31" s="11">
+        <f>IFERROR(J30/J5,0)</f>
+        <v/>
+      </c>
+      <c r="K31" s="11">
+        <f>IFERROR(K30/K5,0)</f>
+        <v/>
+      </c>
+      <c r="L31" s="11">
+        <f>IFERROR(L30/L5,0)</f>
+        <v/>
+      </c>
+      <c r="M31" s="11">
+        <f>IFERROR(M30/M5,0)</f>
+        <v/>
+      </c>
+      <c r="N31" s="11">
+        <f>IFERROR(N30/N5,0)</f>
+        <v/>
+      </c>
+      <c r="O31" s="11">
+        <f>IFERROR(O30/O5,0)</f>
+        <v/>
+      </c>
+      <c r="P31" s="11">
+        <f>IFERROR(P30/P5,0)</f>
+        <v/>
+      </c>
+      <c r="Q31" s="11" t="n"/>
+    </row>
+    <row r="32" ht="12" customHeight="1">
+      <c r="B32" s="4" t="n"/>
+      <c r="C32" s="4" t="n"/>
+      <c r="D32" s="4" t="n"/>
+      <c r="E32" s="4" t="n"/>
+      <c r="F32" s="4" t="n"/>
+      <c r="G32" s="4" t="n"/>
+      <c r="H32" s="4" t="n"/>
+      <c r="I32" s="4" t="n"/>
+      <c r="J32" s="4" t="n"/>
+      <c r="K32" s="4" t="n"/>
+      <c r="L32" s="4" t="n"/>
+      <c r="M32" s="4" t="n"/>
+      <c r="N32" s="4" t="n"/>
+      <c r="O32" s="4" t="n"/>
+      <c r="P32" s="4">
+        <f>SUM(D32:O32)</f>
+        <v/>
+      </c>
+      <c r="Q32" s="4" t="n"/>
+    </row>
+    <row r="33" outlineLevel="1" ht="12" customHeight="1">
+      <c r="A33" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Opex</t>
         </is>
       </c>
-      <c r="B32" s="8" t="n"/>
-      <c r="C32" s="8" t="n"/>
-      <c r="D32" s="8">
-        <f>D33+D35+D37+D39</f>
-        <v/>
-      </c>
-      <c r="E32" s="8">
-        <f>E33+E35+E37+E39</f>
-        <v/>
-      </c>
-      <c r="F32" s="8">
-        <f>F33+F35+F37+F39</f>
-        <v/>
-      </c>
-      <c r="G32" s="8">
-        <f>G33+G35+G37+G39</f>
-        <v/>
-      </c>
-      <c r="H32" s="8">
-        <f>H33+H35+H37+H39</f>
-        <v/>
-      </c>
-      <c r="I32" s="8">
-        <f>I33+I35+I37+I39</f>
-        <v/>
-      </c>
-      <c r="J32" s="8">
-        <f>J33+J35+J37+J39</f>
-        <v/>
-      </c>
-      <c r="K32" s="8">
-        <f>K33+K35+K37+K39</f>
-        <v/>
-      </c>
-      <c r="L32" s="8">
-        <f>L33+L35+L37+L39</f>
-        <v/>
-      </c>
-      <c r="M32" s="8">
-        <f>M33+M35+M37+M39</f>
-        <v/>
-      </c>
-      <c r="N32" s="8">
-        <f>N33+N35+N37+N39</f>
-        <v/>
-      </c>
-      <c r="O32" s="8">
-        <f>O33+O35+O37+O39</f>
-        <v/>
-      </c>
-      <c r="P32" s="8">
-        <f>SUM(D32:O32)</f>
-        <v/>
-      </c>
-      <c r="Q32" s="8" t="n"/>
-    </row>
-    <row r="33" hidden="1" outlineLevel="2" ht="12" customHeight="1">
-      <c r="A33" s="9" t="inlineStr">
+      <c r="B33" s="8" t="n"/>
+      <c r="C33" s="8" t="n"/>
+      <c r="D33" s="8">
+        <f>D34+D36+D38+D40</f>
+        <v/>
+      </c>
+      <c r="E33" s="8">
+        <f>E34+E36+E38+E40</f>
+        <v/>
+      </c>
+      <c r="F33" s="8">
+        <f>F34+F36+F38+F40</f>
+        <v/>
+      </c>
+      <c r="G33" s="8">
+        <f>G34+G36+G38+G40</f>
+        <v/>
+      </c>
+      <c r="H33" s="8">
+        <f>H34+H36+H38+H40</f>
+        <v/>
+      </c>
+      <c r="I33" s="8">
+        <f>I34+I36+I38+I40</f>
+        <v/>
+      </c>
+      <c r="J33" s="8">
+        <f>J34+J36+J38+J40</f>
+        <v/>
+      </c>
+      <c r="K33" s="8">
+        <f>K34+K36+K38+K40</f>
+        <v/>
+      </c>
+      <c r="L33" s="8">
+        <f>L34+L36+L38+L40</f>
+        <v/>
+      </c>
+      <c r="M33" s="8">
+        <f>M34+M36+M38+M40</f>
+        <v/>
+      </c>
+      <c r="N33" s="8">
+        <f>N34+N36+N38+N40</f>
+        <v/>
+      </c>
+      <c r="O33" s="8">
+        <f>O34+O36+O38+O40</f>
+        <v/>
+      </c>
+      <c r="P33" s="8">
+        <f>SUM(D33:O33)</f>
+        <v/>
+      </c>
+      <c r="Q33" s="8" t="n"/>
+    </row>
+    <row r="34" hidden="1" outlineLevel="2" ht="12" customHeight="1">
+      <c r="A34" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">    Shared services</t>
         </is>
       </c>
-      <c r="B33" s="10" t="n"/>
-      <c r="C33" s="10" t="n"/>
-      <c r="D33" s="10">
-        <f>SUM(D34:D34)</f>
-        <v/>
-      </c>
-      <c r="E33" s="10">
-        <f>SUM(E34:E34)</f>
-        <v/>
-      </c>
-      <c r="F33" s="10">
-        <f>SUM(F34:F34)</f>
-        <v/>
-      </c>
-      <c r="G33" s="10">
-        <f>SUM(G34:G34)</f>
-        <v/>
-      </c>
-      <c r="H33" s="10">
-        <f>SUM(H34:H34)</f>
-        <v/>
-      </c>
-      <c r="I33" s="10">
-        <f>SUM(I34:I34)</f>
-        <v/>
-      </c>
-      <c r="J33" s="10">
-        <f>SUM(J34:J34)</f>
-        <v/>
-      </c>
-      <c r="K33" s="10">
-        <f>SUM(K34:K34)</f>
-        <v/>
-      </c>
-      <c r="L33" s="10">
-        <f>SUM(L34:L34)</f>
-        <v/>
-      </c>
-      <c r="M33" s="10">
-        <f>SUM(M34:M34)</f>
-        <v/>
-      </c>
-      <c r="N33" s="10">
-        <f>SUM(N34:N34)</f>
-        <v/>
-      </c>
-      <c r="O33" s="10">
-        <f>SUM(O34:O34)</f>
-        <v/>
-      </c>
-      <c r="P33" s="10">
-        <f>SUM(D33:O33)</f>
-        <v/>
-      </c>
-      <c r="Q33" s="10" t="inlineStr">
+      <c r="B34" s="10" t="n"/>
+      <c r="C34" s="10" t="n"/>
+      <c r="D34" s="10">
+        <f>SUM(D35:D35)</f>
+        <v/>
+      </c>
+      <c r="E34" s="10">
+        <f>SUM(E35:E35)</f>
+        <v/>
+      </c>
+      <c r="F34" s="10">
+        <f>SUM(F35:F35)</f>
+        <v/>
+      </c>
+      <c r="G34" s="10">
+        <f>SUM(G35:G35)</f>
+        <v/>
+      </c>
+      <c r="H34" s="10">
+        <f>SUM(H35:H35)</f>
+        <v/>
+      </c>
+      <c r="I34" s="10">
+        <f>SUM(I35:I35)</f>
+        <v/>
+      </c>
+      <c r="J34" s="10">
+        <f>SUM(J35:J35)</f>
+        <v/>
+      </c>
+      <c r="K34" s="10">
+        <f>SUM(K35:K35)</f>
+        <v/>
+      </c>
+      <c r="L34" s="10">
+        <f>SUM(L35:L35)</f>
+        <v/>
+      </c>
+      <c r="M34" s="10">
+        <f>SUM(M35:M35)</f>
+        <v/>
+      </c>
+      <c r="N34" s="10">
+        <f>SUM(N35:N35)</f>
+        <v/>
+      </c>
+      <c r="O34" s="10">
+        <f>SUM(O35:O35)</f>
+        <v/>
+      </c>
+      <c r="P34" s="10">
+        <f>SUM(D34:O34)</f>
+        <v/>
+      </c>
+      <c r="Q34" s="10" t="inlineStr">
         <is>
           <t>-&gt;</t>
         </is>
       </c>
     </row>
-    <row r="34" hidden="1" outlineLevel="3" ht="12" customHeight="1">
-      <c r="A34" t="inlineStr">
+    <row r="35" hidden="1" outlineLevel="3" ht="12" customHeight="1">
+      <c r="A35" t="inlineStr">
         <is>
           <t xml:space="preserve">      SHAREDSERVICESSL</t>
         </is>
       </c>
-      <c r="B34" s="4" t="n"/>
-      <c r="C34" s="4" t="n"/>
-      <c r="D34" s="4">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,D$1,'g-expenses-ltd'!$D:$D,"shared_services",'g-expenses-ltd'!$E:$E,TRIM($A34))</f>
-        <v/>
-      </c>
-      <c r="E34" s="4">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,E$1,'g-expenses-ltd'!$D:$D,"shared_services",'g-expenses-ltd'!$E:$E,TRIM($A34))</f>
-        <v/>
-      </c>
-      <c r="F34" s="4">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,F$1,'g-expenses-ltd'!$D:$D,"shared_services",'g-expenses-ltd'!$E:$E,TRIM($A34))</f>
-        <v/>
-      </c>
-      <c r="G34" s="4">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,G$1,'g-expenses-ltd'!$D:$D,"shared_services",'g-expenses-ltd'!$E:$E,TRIM($A34))</f>
-        <v/>
-      </c>
-      <c r="H34" s="4">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,H$1,'g-expenses-ltd'!$D:$D,"shared_services",'g-expenses-ltd'!$E:$E,TRIM($A34))</f>
-        <v/>
-      </c>
-      <c r="I34" s="4">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,I$1,'g-expenses-ltd'!$D:$D,"shared_services",'g-expenses-ltd'!$E:$E,TRIM($A34))</f>
-        <v/>
-      </c>
-      <c r="J34" s="4">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,J$1,'g-expenses-ltd'!$D:$D,"shared_services",'g-expenses-ltd'!$E:$E,TRIM($A34))</f>
-        <v/>
-      </c>
-      <c r="K34" s="4">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,K$1,'g-expenses-ltd'!$D:$D,"shared_services",'g-expenses-ltd'!$E:$E,TRIM($A34))</f>
-        <v/>
-      </c>
-      <c r="L34" s="4">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,L$1,'g-expenses-ltd'!$D:$D,"shared_services",'g-expenses-ltd'!$E:$E,TRIM($A34))</f>
-        <v/>
-      </c>
-      <c r="M34" s="4">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,M$1,'g-expenses-ltd'!$D:$D,"shared_services",'g-expenses-ltd'!$E:$E,TRIM($A34))</f>
-        <v/>
-      </c>
-      <c r="N34" s="4">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,N$1,'g-expenses-ltd'!$D:$D,"shared_services",'g-expenses-ltd'!$E:$E,TRIM($A34))</f>
-        <v/>
-      </c>
-      <c r="O34" s="4">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,O$1,'g-expenses-ltd'!$D:$D,"shared_services",'g-expenses-ltd'!$E:$E,TRIM($A34))</f>
-        <v/>
-      </c>
-      <c r="P34" s="4">
-        <f>SUM(D34:O34)</f>
-        <v/>
-      </c>
-      <c r="Q34" s="4" t="inlineStr">
+      <c r="B35" s="4" t="n"/>
+      <c r="C35" s="4" t="n"/>
+      <c r="D35" s="4">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,D$1,'g-expenses-ltd'!$D:$D,"shared_services",'g-expenses-ltd'!$E:$E,TRIM($A35))</f>
+        <v/>
+      </c>
+      <c r="E35" s="4">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,E$1,'g-expenses-ltd'!$D:$D,"shared_services",'g-expenses-ltd'!$E:$E,TRIM($A35))</f>
+        <v/>
+      </c>
+      <c r="F35" s="4">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,F$1,'g-expenses-ltd'!$D:$D,"shared_services",'g-expenses-ltd'!$E:$E,TRIM($A35))</f>
+        <v/>
+      </c>
+      <c r="G35" s="4">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,G$1,'g-expenses-ltd'!$D:$D,"shared_services",'g-expenses-ltd'!$E:$E,TRIM($A35))</f>
+        <v/>
+      </c>
+      <c r="H35" s="4">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,H$1,'g-expenses-ltd'!$D:$D,"shared_services",'g-expenses-ltd'!$E:$E,TRIM($A35))</f>
+        <v/>
+      </c>
+      <c r="I35" s="4">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,I$1,'g-expenses-ltd'!$D:$D,"shared_services",'g-expenses-ltd'!$E:$E,TRIM($A35))</f>
+        <v/>
+      </c>
+      <c r="J35" s="4">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,J$1,'g-expenses-ltd'!$D:$D,"shared_services",'g-expenses-ltd'!$E:$E,TRIM($A35))</f>
+        <v/>
+      </c>
+      <c r="K35" s="4">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,K$1,'g-expenses-ltd'!$D:$D,"shared_services",'g-expenses-ltd'!$E:$E,TRIM($A35))</f>
+        <v/>
+      </c>
+      <c r="L35" s="4">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,L$1,'g-expenses-ltd'!$D:$D,"shared_services",'g-expenses-ltd'!$E:$E,TRIM($A35))</f>
+        <v/>
+      </c>
+      <c r="M35" s="4">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,M$1,'g-expenses-ltd'!$D:$D,"shared_services",'g-expenses-ltd'!$E:$E,TRIM($A35))</f>
+        <v/>
+      </c>
+      <c r="N35" s="4">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,N$1,'g-expenses-ltd'!$D:$D,"shared_services",'g-expenses-ltd'!$E:$E,TRIM($A35))</f>
+        <v/>
+      </c>
+      <c r="O35" s="4">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,O$1,'g-expenses-ltd'!$D:$D,"shared_services",'g-expenses-ltd'!$E:$E,TRIM($A35))</f>
+        <v/>
+      </c>
+      <c r="P35" s="4">
+        <f>SUM(D35:O35)</f>
+        <v/>
+      </c>
+      <c r="Q35" s="4" t="inlineStr">
         <is>
           <t>-&gt;</t>
         </is>
       </c>
     </row>
-    <row r="35" hidden="1" outlineLevel="2" ht="12" customHeight="1">
-      <c r="A35" s="9" t="inlineStr">
+    <row r="36" hidden="1" outlineLevel="2" ht="12" customHeight="1">
+      <c r="A36" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">    Administration</t>
         </is>
       </c>
-      <c r="B35" s="10" t="n"/>
-      <c r="C35" s="10" t="n"/>
-      <c r="D35" s="10">
-        <f>SUM(D36:D36)</f>
-        <v/>
-      </c>
-      <c r="E35" s="10">
-        <f>SUM(E36:E36)</f>
-        <v/>
-      </c>
-      <c r="F35" s="10">
-        <f>SUM(F36:F36)</f>
-        <v/>
-      </c>
-      <c r="G35" s="10">
-        <f>SUM(G36:G36)</f>
-        <v/>
-      </c>
-      <c r="H35" s="10">
-        <f>SUM(H36:H36)</f>
-        <v/>
-      </c>
-      <c r="I35" s="10">
-        <f>SUM(I36:I36)</f>
-        <v/>
-      </c>
-      <c r="J35" s="10">
-        <f>SUM(J36:J36)</f>
-        <v/>
-      </c>
-      <c r="K35" s="10">
-        <f>SUM(K36:K36)</f>
-        <v/>
-      </c>
-      <c r="L35" s="10">
-        <f>SUM(L36:L36)</f>
-        <v/>
-      </c>
-      <c r="M35" s="10">
-        <f>SUM(M36:M36)</f>
-        <v/>
-      </c>
-      <c r="N35" s="10">
-        <f>SUM(N36:N36)</f>
-        <v/>
-      </c>
-      <c r="O35" s="10">
-        <f>SUM(O36:O36)</f>
-        <v/>
-      </c>
-      <c r="P35" s="10">
-        <f>SUM(D35:O35)</f>
-        <v/>
-      </c>
-      <c r="Q35" s="10" t="inlineStr">
+      <c r="B36" s="10" t="n"/>
+      <c r="C36" s="10" t="n"/>
+      <c r="D36" s="10">
+        <f>SUM(D37:D37)</f>
+        <v/>
+      </c>
+      <c r="E36" s="10">
+        <f>SUM(E37:E37)</f>
+        <v/>
+      </c>
+      <c r="F36" s="10">
+        <f>SUM(F37:F37)</f>
+        <v/>
+      </c>
+      <c r="G36" s="10">
+        <f>SUM(G37:G37)</f>
+        <v/>
+      </c>
+      <c r="H36" s="10">
+        <f>SUM(H37:H37)</f>
+        <v/>
+      </c>
+      <c r="I36" s="10">
+        <f>SUM(I37:I37)</f>
+        <v/>
+      </c>
+      <c r="J36" s="10">
+        <f>SUM(J37:J37)</f>
+        <v/>
+      </c>
+      <c r="K36" s="10">
+        <f>SUM(K37:K37)</f>
+        <v/>
+      </c>
+      <c r="L36" s="10">
+        <f>SUM(L37:L37)</f>
+        <v/>
+      </c>
+      <c r="M36" s="10">
+        <f>SUM(M37:M37)</f>
+        <v/>
+      </c>
+      <c r="N36" s="10">
+        <f>SUM(N37:N37)</f>
+        <v/>
+      </c>
+      <c r="O36" s="10">
+        <f>SUM(O37:O37)</f>
+        <v/>
+      </c>
+      <c r="P36" s="10">
+        <f>SUM(D36:O36)</f>
+        <v/>
+      </c>
+      <c r="Q36" s="10" t="inlineStr">
         <is>
           <t>-&gt;</t>
         </is>
       </c>
     </row>
-    <row r="36" hidden="1" outlineLevel="3" ht="12" customHeight="1">
-      <c r="A36" t="inlineStr">
+    <row r="37" hidden="1" outlineLevel="3" ht="12" customHeight="1">
+      <c r="A37" t="inlineStr">
         <is>
           <t xml:space="preserve">      YOURACCOUNTSTAXES</t>
         </is>
       </c>
-      <c r="B36" s="4" t="n"/>
-      <c r="C36" s="4" t="n"/>
-      <c r="D36" s="4">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,D$1,'g-expenses-ltd'!$D:$D,"administration",'g-expenses-ltd'!$E:$E,TRIM($A36))</f>
-        <v/>
-      </c>
-      <c r="E36" s="4">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,E$1,'g-expenses-ltd'!$D:$D,"administration",'g-expenses-ltd'!$E:$E,TRIM($A36))</f>
-        <v/>
-      </c>
-      <c r="F36" s="4">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,F$1,'g-expenses-ltd'!$D:$D,"administration",'g-expenses-ltd'!$E:$E,TRIM($A36))</f>
-        <v/>
-      </c>
-      <c r="G36" s="4">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,G$1,'g-expenses-ltd'!$D:$D,"administration",'g-expenses-ltd'!$E:$E,TRIM($A36))</f>
-        <v/>
-      </c>
-      <c r="H36" s="4">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,H$1,'g-expenses-ltd'!$D:$D,"administration",'g-expenses-ltd'!$E:$E,TRIM($A36))</f>
-        <v/>
-      </c>
-      <c r="I36" s="4">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,I$1,'g-expenses-ltd'!$D:$D,"administration",'g-expenses-ltd'!$E:$E,TRIM($A36))</f>
-        <v/>
-      </c>
-      <c r="J36" s="4">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,J$1,'g-expenses-ltd'!$D:$D,"administration",'g-expenses-ltd'!$E:$E,TRIM($A36))</f>
-        <v/>
-      </c>
-      <c r="K36" s="4">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,K$1,'g-expenses-ltd'!$D:$D,"administration",'g-expenses-ltd'!$E:$E,TRIM($A36))</f>
-        <v/>
-      </c>
-      <c r="L36" s="4">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,L$1,'g-expenses-ltd'!$D:$D,"administration",'g-expenses-ltd'!$E:$E,TRIM($A36))</f>
-        <v/>
-      </c>
-      <c r="M36" s="4">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,M$1,'g-expenses-ltd'!$D:$D,"administration",'g-expenses-ltd'!$E:$E,TRIM($A36))</f>
-        <v/>
-      </c>
-      <c r="N36" s="4">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,N$1,'g-expenses-ltd'!$D:$D,"administration",'g-expenses-ltd'!$E:$E,TRIM($A36))</f>
-        <v/>
-      </c>
-      <c r="O36" s="4">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,O$1,'g-expenses-ltd'!$D:$D,"administration",'g-expenses-ltd'!$E:$E,TRIM($A36))</f>
-        <v/>
-      </c>
-      <c r="P36" s="4">
-        <f>SUM(D36:O36)</f>
-        <v/>
-      </c>
-      <c r="Q36" s="4" t="inlineStr">
+      <c r="B37" s="4" t="n"/>
+      <c r="C37" s="4" t="n"/>
+      <c r="D37" s="4">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,D$1,'g-expenses-ltd'!$D:$D,"administration",'g-expenses-ltd'!$E:$E,TRIM($A37))</f>
+        <v/>
+      </c>
+      <c r="E37" s="4">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,E$1,'g-expenses-ltd'!$D:$D,"administration",'g-expenses-ltd'!$E:$E,TRIM($A37))</f>
+        <v/>
+      </c>
+      <c r="F37" s="4">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,F$1,'g-expenses-ltd'!$D:$D,"administration",'g-expenses-ltd'!$E:$E,TRIM($A37))</f>
+        <v/>
+      </c>
+      <c r="G37" s="4">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,G$1,'g-expenses-ltd'!$D:$D,"administration",'g-expenses-ltd'!$E:$E,TRIM($A37))</f>
+        <v/>
+      </c>
+      <c r="H37" s="4">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,H$1,'g-expenses-ltd'!$D:$D,"administration",'g-expenses-ltd'!$E:$E,TRIM($A37))</f>
+        <v/>
+      </c>
+      <c r="I37" s="4">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,I$1,'g-expenses-ltd'!$D:$D,"administration",'g-expenses-ltd'!$E:$E,TRIM($A37))</f>
+        <v/>
+      </c>
+      <c r="J37" s="4">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,J$1,'g-expenses-ltd'!$D:$D,"administration",'g-expenses-ltd'!$E:$E,TRIM($A37))</f>
+        <v/>
+      </c>
+      <c r="K37" s="4">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,K$1,'g-expenses-ltd'!$D:$D,"administration",'g-expenses-ltd'!$E:$E,TRIM($A37))</f>
+        <v/>
+      </c>
+      <c r="L37" s="4">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,L$1,'g-expenses-ltd'!$D:$D,"administration",'g-expenses-ltd'!$E:$E,TRIM($A37))</f>
+        <v/>
+      </c>
+      <c r="M37" s="4">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,M$1,'g-expenses-ltd'!$D:$D,"administration",'g-expenses-ltd'!$E:$E,TRIM($A37))</f>
+        <v/>
+      </c>
+      <c r="N37" s="4">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,N$1,'g-expenses-ltd'!$D:$D,"administration",'g-expenses-ltd'!$E:$E,TRIM($A37))</f>
+        <v/>
+      </c>
+      <c r="O37" s="4">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,O$1,'g-expenses-ltd'!$D:$D,"administration",'g-expenses-ltd'!$E:$E,TRIM($A37))</f>
+        <v/>
+      </c>
+      <c r="P37" s="4">
+        <f>SUM(D37:O37)</f>
+        <v/>
+      </c>
+      <c r="Q37" s="4" t="inlineStr">
         <is>
           <t>-&gt;</t>
         </is>
       </c>
     </row>
-    <row r="37" hidden="1" outlineLevel="2" ht="12" customHeight="1">
-      <c r="A37" s="9" t="inlineStr">
+    <row r="38" hidden="1" outlineLevel="2" ht="12" customHeight="1">
+      <c r="A38" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">    Technology</t>
         </is>
       </c>
-      <c r="B37" s="10" t="n"/>
-      <c r="C37" s="10" t="n"/>
-      <c r="D37" s="10">
-        <f>SUM(D38:D38)</f>
-        <v/>
-      </c>
-      <c r="E37" s="10">
-        <f>SUM(E38:E38)</f>
-        <v/>
-      </c>
-      <c r="F37" s="10">
-        <f>SUM(F38:F38)</f>
-        <v/>
-      </c>
-      <c r="G37" s="10">
-        <f>SUM(G38:G38)</f>
-        <v/>
-      </c>
-      <c r="H37" s="10">
-        <f>SUM(H38:H38)</f>
-        <v/>
-      </c>
-      <c r="I37" s="10">
-        <f>SUM(I38:I38)</f>
-        <v/>
-      </c>
-      <c r="J37" s="10">
-        <f>SUM(J38:J38)</f>
-        <v/>
-      </c>
-      <c r="K37" s="10">
-        <f>SUM(K38:K38)</f>
-        <v/>
-      </c>
-      <c r="L37" s="10">
-        <f>SUM(L38:L38)</f>
-        <v/>
-      </c>
-      <c r="M37" s="10">
-        <f>SUM(M38:M38)</f>
-        <v/>
-      </c>
-      <c r="N37" s="10">
-        <f>SUM(N38:N38)</f>
-        <v/>
-      </c>
-      <c r="O37" s="10">
-        <f>SUM(O38:O38)</f>
-        <v/>
-      </c>
-      <c r="P37" s="10">
-        <f>SUM(D37:O37)</f>
-        <v/>
-      </c>
-      <c r="Q37" s="10" t="inlineStr">
+      <c r="B38" s="10" t="n"/>
+      <c r="C38" s="10" t="n"/>
+      <c r="D38" s="10">
+        <f>SUM(D39:D39)</f>
+        <v/>
+      </c>
+      <c r="E38" s="10">
+        <f>SUM(E39:E39)</f>
+        <v/>
+      </c>
+      <c r="F38" s="10">
+        <f>SUM(F39:F39)</f>
+        <v/>
+      </c>
+      <c r="G38" s="10">
+        <f>SUM(G39:G39)</f>
+        <v/>
+      </c>
+      <c r="H38" s="10">
+        <f>SUM(H39:H39)</f>
+        <v/>
+      </c>
+      <c r="I38" s="10">
+        <f>SUM(I39:I39)</f>
+        <v/>
+      </c>
+      <c r="J38" s="10">
+        <f>SUM(J39:J39)</f>
+        <v/>
+      </c>
+      <c r="K38" s="10">
+        <f>SUM(K39:K39)</f>
+        <v/>
+      </c>
+      <c r="L38" s="10">
+        <f>SUM(L39:L39)</f>
+        <v/>
+      </c>
+      <c r="M38" s="10">
+        <f>SUM(M39:M39)</f>
+        <v/>
+      </c>
+      <c r="N38" s="10">
+        <f>SUM(N39:N39)</f>
+        <v/>
+      </c>
+      <c r="O38" s="10">
+        <f>SUM(O39:O39)</f>
+        <v/>
+      </c>
+      <c r="P38" s="10">
+        <f>SUM(D38:O38)</f>
+        <v/>
+      </c>
+      <c r="Q38" s="10" t="inlineStr">
         <is>
           <t>-&gt;</t>
         </is>
       </c>
     </row>
-    <row r="38" hidden="1" outlineLevel="3" ht="12" customHeight="1">
-      <c r="A38" t="inlineStr">
+    <row r="39" hidden="1" outlineLevel="3" ht="12" customHeight="1">
+      <c r="A39" t="inlineStr">
         <is>
           <t xml:space="preserve">      REVER</t>
         </is>
       </c>
-      <c r="B38" s="4" t="n"/>
-      <c r="C38" s="4" t="n"/>
-      <c r="D38" s="4">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,D$1,'g-expenses-ltd'!$D:$D,"technology",'g-expenses-ltd'!$E:$E,TRIM($A38))</f>
-        <v/>
-      </c>
-      <c r="E38" s="4">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,E$1,'g-expenses-ltd'!$D:$D,"technology",'g-expenses-ltd'!$E:$E,TRIM($A38))</f>
-        <v/>
-      </c>
-      <c r="F38" s="4">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,F$1,'g-expenses-ltd'!$D:$D,"technology",'g-expenses-ltd'!$E:$E,TRIM($A38))</f>
-        <v/>
-      </c>
-      <c r="G38" s="4">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,G$1,'g-expenses-ltd'!$D:$D,"technology",'g-expenses-ltd'!$E:$E,TRIM($A38))</f>
-        <v/>
-      </c>
-      <c r="H38" s="4">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,H$1,'g-expenses-ltd'!$D:$D,"technology",'g-expenses-ltd'!$E:$E,TRIM($A38))</f>
-        <v/>
-      </c>
-      <c r="I38" s="4">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,I$1,'g-expenses-ltd'!$D:$D,"technology",'g-expenses-ltd'!$E:$E,TRIM($A38))</f>
-        <v/>
-      </c>
-      <c r="J38" s="4">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,J$1,'g-expenses-ltd'!$D:$D,"technology",'g-expenses-ltd'!$E:$E,TRIM($A38))</f>
-        <v/>
-      </c>
-      <c r="K38" s="4">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,K$1,'g-expenses-ltd'!$D:$D,"technology",'g-expenses-ltd'!$E:$E,TRIM($A38))</f>
-        <v/>
-      </c>
-      <c r="L38" s="4">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,L$1,'g-expenses-ltd'!$D:$D,"technology",'g-expenses-ltd'!$E:$E,TRIM($A38))</f>
-        <v/>
-      </c>
-      <c r="M38" s="4">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,M$1,'g-expenses-ltd'!$D:$D,"technology",'g-expenses-ltd'!$E:$E,TRIM($A38))</f>
-        <v/>
-      </c>
-      <c r="N38" s="4">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,N$1,'g-expenses-ltd'!$D:$D,"technology",'g-expenses-ltd'!$E:$E,TRIM($A38))</f>
-        <v/>
-      </c>
-      <c r="O38" s="4">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,O$1,'g-expenses-ltd'!$D:$D,"technology",'g-expenses-ltd'!$E:$E,TRIM($A38))</f>
-        <v/>
-      </c>
-      <c r="P38" s="4">
-        <f>SUM(D38:O38)</f>
-        <v/>
-      </c>
-      <c r="Q38" s="4" t="inlineStr">
-        <is>
-          <t>-&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" hidden="1" outlineLevel="2" ht="12" customHeight="1">
-      <c r="A39" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Otros gastos</t>
-        </is>
-      </c>
-      <c r="B39" s="10" t="n"/>
-      <c r="C39" s="10" t="n"/>
-      <c r="D39" s="10">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,D$1,'g-expenses-ltd'!$D:$D,"otros_gastos")</f>
-        <v/>
-      </c>
-      <c r="E39" s="10">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,E$1,'g-expenses-ltd'!$D:$D,"otros_gastos")</f>
-        <v/>
-      </c>
-      <c r="F39" s="10">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,F$1,'g-expenses-ltd'!$D:$D,"otros_gastos")</f>
-        <v/>
-      </c>
-      <c r="G39" s="10">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,G$1,'g-expenses-ltd'!$D:$D,"otros_gastos")</f>
-        <v/>
-      </c>
-      <c r="H39" s="10">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,H$1,'g-expenses-ltd'!$D:$D,"otros_gastos")</f>
-        <v/>
-      </c>
-      <c r="I39" s="10">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,I$1,'g-expenses-ltd'!$D:$D,"otros_gastos")</f>
-        <v/>
-      </c>
-      <c r="J39" s="10">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,J$1,'g-expenses-ltd'!$D:$D,"otros_gastos")</f>
-        <v/>
-      </c>
-      <c r="K39" s="10">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,K$1,'g-expenses-ltd'!$D:$D,"otros_gastos")</f>
-        <v/>
-      </c>
-      <c r="L39" s="10">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,L$1,'g-expenses-ltd'!$D:$D,"otros_gastos")</f>
-        <v/>
-      </c>
-      <c r="M39" s="10">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,M$1,'g-expenses-ltd'!$D:$D,"otros_gastos")</f>
-        <v/>
-      </c>
-      <c r="N39" s="10">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,N$1,'g-expenses-ltd'!$D:$D,"otros_gastos")</f>
-        <v/>
-      </c>
-      <c r="O39" s="10">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,O$1,'g-expenses-ltd'!$D:$D,"otros_gastos")</f>
-        <v/>
-      </c>
-      <c r="P39" s="10">
+      <c r="B39" s="4" t="n"/>
+      <c r="C39" s="4" t="n"/>
+      <c r="D39" s="4">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,D$1,'g-expenses-ltd'!$D:$D,"technology",'g-expenses-ltd'!$E:$E,TRIM($A39))</f>
+        <v/>
+      </c>
+      <c r="E39" s="4">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,E$1,'g-expenses-ltd'!$D:$D,"technology",'g-expenses-ltd'!$E:$E,TRIM($A39))</f>
+        <v/>
+      </c>
+      <c r="F39" s="4">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,F$1,'g-expenses-ltd'!$D:$D,"technology",'g-expenses-ltd'!$E:$E,TRIM($A39))</f>
+        <v/>
+      </c>
+      <c r="G39" s="4">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,G$1,'g-expenses-ltd'!$D:$D,"technology",'g-expenses-ltd'!$E:$E,TRIM($A39))</f>
+        <v/>
+      </c>
+      <c r="H39" s="4">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,H$1,'g-expenses-ltd'!$D:$D,"technology",'g-expenses-ltd'!$E:$E,TRIM($A39))</f>
+        <v/>
+      </c>
+      <c r="I39" s="4">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,I$1,'g-expenses-ltd'!$D:$D,"technology",'g-expenses-ltd'!$E:$E,TRIM($A39))</f>
+        <v/>
+      </c>
+      <c r="J39" s="4">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,J$1,'g-expenses-ltd'!$D:$D,"technology",'g-expenses-ltd'!$E:$E,TRIM($A39))</f>
+        <v/>
+      </c>
+      <c r="K39" s="4">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,K$1,'g-expenses-ltd'!$D:$D,"technology",'g-expenses-ltd'!$E:$E,TRIM($A39))</f>
+        <v/>
+      </c>
+      <c r="L39" s="4">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,L$1,'g-expenses-ltd'!$D:$D,"technology",'g-expenses-ltd'!$E:$E,TRIM($A39))</f>
+        <v/>
+      </c>
+      <c r="M39" s="4">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,M$1,'g-expenses-ltd'!$D:$D,"technology",'g-expenses-ltd'!$E:$E,TRIM($A39))</f>
+        <v/>
+      </c>
+      <c r="N39" s="4">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,N$1,'g-expenses-ltd'!$D:$D,"technology",'g-expenses-ltd'!$E:$E,TRIM($A39))</f>
+        <v/>
+      </c>
+      <c r="O39" s="4">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,O$1,'g-expenses-ltd'!$D:$D,"technology",'g-expenses-ltd'!$E:$E,TRIM($A39))</f>
+        <v/>
+      </c>
+      <c r="P39" s="4">
         <f>SUM(D39:O39)</f>
         <v/>
       </c>
-      <c r="Q39" s="10" t="inlineStr">
+      <c r="Q39" s="4" t="inlineStr">
         <is>
           <t>-&gt;</t>
         </is>
@@ -2784,212 +2811,247 @@
     <row r="40" hidden="1" outlineLevel="2" ht="12" customHeight="1">
       <c r="A40" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Diferencias divisas</t>
+          <t xml:space="preserve">    Uncategorized Expenses</t>
         </is>
       </c>
       <c r="B40" s="10" t="n"/>
       <c r="C40" s="10" t="n"/>
-      <c r="D40" s="10" t="n"/>
-      <c r="E40" s="10" t="n"/>
-      <c r="F40" s="10" t="n"/>
-      <c r="G40" s="10" t="n"/>
-      <c r="H40" s="10" t="n"/>
-      <c r="I40" s="10" t="n"/>
-      <c r="J40" s="10" t="n"/>
-      <c r="K40" s="10" t="n"/>
-      <c r="L40" s="10" t="n"/>
-      <c r="M40" s="10" t="n"/>
-      <c r="N40" s="10" t="n"/>
-      <c r="O40" s="10" t="n"/>
+      <c r="D40" s="10">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,D$1,'g-expenses-ltd'!$D:$D,"otros_gastos")</f>
+        <v/>
+      </c>
+      <c r="E40" s="10">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,E$1,'g-expenses-ltd'!$D:$D,"otros_gastos")</f>
+        <v/>
+      </c>
+      <c r="F40" s="10">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,F$1,'g-expenses-ltd'!$D:$D,"otros_gastos")</f>
+        <v/>
+      </c>
+      <c r="G40" s="10">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,G$1,'g-expenses-ltd'!$D:$D,"otros_gastos")</f>
+        <v/>
+      </c>
+      <c r="H40" s="10">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,H$1,'g-expenses-ltd'!$D:$D,"otros_gastos")</f>
+        <v/>
+      </c>
+      <c r="I40" s="10">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,I$1,'g-expenses-ltd'!$D:$D,"otros_gastos")</f>
+        <v/>
+      </c>
+      <c r="J40" s="10">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,J$1,'g-expenses-ltd'!$D:$D,"otros_gastos")</f>
+        <v/>
+      </c>
+      <c r="K40" s="10">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,K$1,'g-expenses-ltd'!$D:$D,"otros_gastos")</f>
+        <v/>
+      </c>
+      <c r="L40" s="10">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,L$1,'g-expenses-ltd'!$D:$D,"otros_gastos")</f>
+        <v/>
+      </c>
+      <c r="M40" s="10">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,M$1,'g-expenses-ltd'!$D:$D,"otros_gastos")</f>
+        <v/>
+      </c>
+      <c r="N40" s="10">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,N$1,'g-expenses-ltd'!$D:$D,"otros_gastos")</f>
+        <v/>
+      </c>
+      <c r="O40" s="10">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,O$1,'g-expenses-ltd'!$D:$D,"otros_gastos")</f>
+        <v/>
+      </c>
       <c r="P40" s="10">
         <f>SUM(D40:O40)</f>
         <v/>
       </c>
-      <c r="Q40" s="10" t="n"/>
-    </row>
-    <row r="41" ht="12" customHeight="1">
-      <c r="B41" s="4" t="n"/>
-      <c r="C41" s="4" t="n"/>
-      <c r="D41" s="4" t="n"/>
-      <c r="E41" s="4" t="n"/>
-      <c r="F41" s="4" t="n"/>
-      <c r="G41" s="4" t="n"/>
-      <c r="H41" s="4" t="n"/>
-      <c r="I41" s="4" t="n"/>
-      <c r="J41" s="4" t="n"/>
-      <c r="K41" s="4" t="n"/>
-      <c r="L41" s="4" t="n"/>
-      <c r="M41" s="4" t="n"/>
-      <c r="N41" s="4" t="n"/>
-      <c r="O41" s="4" t="n"/>
-      <c r="P41" s="4">
+      <c r="Q40" s="10" t="inlineStr">
+        <is>
+          <t>-&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" hidden="1" outlineLevel="2" ht="12" customHeight="1">
+      <c r="A41" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Currency Adjustment</t>
+        </is>
+      </c>
+      <c r="B41" s="10" t="n"/>
+      <c r="C41" s="10" t="n"/>
+      <c r="D41" s="10" t="n"/>
+      <c r="E41" s="10" t="n"/>
+      <c r="F41" s="10" t="n"/>
+      <c r="G41" s="10" t="n"/>
+      <c r="H41" s="10" t="n"/>
+      <c r="I41" s="10" t="n"/>
+      <c r="J41" s="10" t="n"/>
+      <c r="K41" s="10" t="n"/>
+      <c r="L41" s="10" t="n"/>
+      <c r="M41" s="10" t="n"/>
+      <c r="N41" s="10" t="n"/>
+      <c r="O41" s="10" t="n"/>
+      <c r="P41" s="10">
         <f>SUM(D41:O41)</f>
         <v/>
       </c>
-      <c r="Q41" s="4" t="n"/>
+      <c r="Q41" s="10" t="n"/>
     </row>
     <row r="42" ht="12" customHeight="1">
-      <c r="A42" s="13" t="inlineStr">
+      <c r="B42" s="4" t="n"/>
+      <c r="C42" s="4" t="n"/>
+      <c r="D42" s="4" t="n"/>
+      <c r="E42" s="4" t="n"/>
+      <c r="F42" s="4" t="n"/>
+      <c r="G42" s="4" t="n"/>
+      <c r="H42" s="4" t="n"/>
+      <c r="I42" s="4" t="n"/>
+      <c r="J42" s="4" t="n"/>
+      <c r="K42" s="4" t="n"/>
+      <c r="L42" s="4" t="n"/>
+      <c r="M42" s="4" t="n"/>
+      <c r="N42" s="4" t="n"/>
+      <c r="O42" s="4" t="n"/>
+      <c r="P42" s="4">
+        <f>SUM(D42:O42)</f>
+        <v/>
+      </c>
+      <c r="Q42" s="4" t="n"/>
+    </row>
+    <row r="43" ht="12" customHeight="1">
+      <c r="A43" s="12" t="inlineStr">
         <is>
           <t>PROFIT</t>
         </is>
       </c>
-      <c r="B42" s="14" t="n"/>
-      <c r="C42" s="14" t="n"/>
-      <c r="D42" s="14">
-        <f>D4-D11-D32-D40</f>
-        <v/>
-      </c>
-      <c r="E42" s="14">
-        <f>E4-E11-E32-E40</f>
-        <v/>
-      </c>
-      <c r="F42" s="14">
-        <f>F4-F11-F32-F40</f>
-        <v/>
-      </c>
-      <c r="G42" s="14">
-        <f>G4-G11-G32-G40</f>
-        <v/>
-      </c>
-      <c r="H42" s="14">
-        <f>H4-H11-H32-H40</f>
-        <v/>
-      </c>
-      <c r="I42" s="14">
-        <f>I4-I11-I32-I40</f>
-        <v/>
-      </c>
-      <c r="J42" s="14">
-        <f>J4-J11-J32-J40</f>
-        <v/>
-      </c>
-      <c r="K42" s="14">
-        <f>K4-K11-K32-K40</f>
-        <v/>
-      </c>
-      <c r="L42" s="14">
-        <f>L4-L11-L32-L40</f>
-        <v/>
-      </c>
-      <c r="M42" s="14">
-        <f>M4-M11-M32-M40</f>
-        <v/>
-      </c>
-      <c r="N42" s="14">
-        <f>N4-N11-N32-N40</f>
-        <v/>
-      </c>
-      <c r="O42" s="14">
-        <f>O4-O11-O32-O40</f>
-        <v/>
-      </c>
-      <c r="P42" s="14">
-        <f>SUM(D42:O42)</f>
-        <v/>
-      </c>
-      <c r="Q42" s="14" t="n"/>
-    </row>
-    <row r="43" hidden="1" outlineLevel="1" ht="12" customHeight="1">
-      <c r="A43" s="11" t="inlineStr">
-        <is>
-          <t>% Profit / product sales</t>
-        </is>
-      </c>
-      <c r="B43" s="12" t="n"/>
-      <c r="C43" s="12" t="n"/>
-      <c r="D43" s="12">
-        <f>IFERROR(D42/D5,0)</f>
-        <v/>
-      </c>
-      <c r="E43" s="12">
-        <f>IFERROR(E42/E5,0)</f>
-        <v/>
-      </c>
-      <c r="F43" s="12">
-        <f>IFERROR(F42/F5,0)</f>
-        <v/>
-      </c>
-      <c r="G43" s="12">
-        <f>IFERROR(G42/G5,0)</f>
-        <v/>
-      </c>
-      <c r="H43" s="12">
-        <f>IFERROR(H42/H5,0)</f>
-        <v/>
-      </c>
-      <c r="I43" s="12">
-        <f>IFERROR(I42/I5,0)</f>
-        <v/>
-      </c>
-      <c r="J43" s="12">
-        <f>IFERROR(J42/J5,0)</f>
-        <v/>
-      </c>
-      <c r="K43" s="12">
-        <f>IFERROR(K42/K5,0)</f>
-        <v/>
-      </c>
-      <c r="L43" s="12">
-        <f>IFERROR(L42/L5,0)</f>
-        <v/>
-      </c>
-      <c r="M43" s="12">
-        <f>IFERROR(M42/M5,0)</f>
-        <v/>
-      </c>
-      <c r="N43" s="12">
-        <f>IFERROR(N42/N5,0)</f>
-        <v/>
-      </c>
-      <c r="O43" s="12">
-        <f>IFERROR(O42/O5,0)</f>
-        <v/>
-      </c>
-      <c r="P43" s="12">
-        <f>IFERROR(P42/P5,0)</f>
-        <v/>
-      </c>
-      <c r="Q43" s="12" t="n"/>
-    </row>
-    <row r="44">
-      <c r="B44" s="4" t="n"/>
-      <c r="C44" s="4" t="n"/>
-      <c r="D44" s="4" t="n"/>
-      <c r="E44" s="4" t="n"/>
-      <c r="F44" s="4" t="n"/>
-      <c r="G44" s="4" t="n"/>
-      <c r="H44" s="4" t="n"/>
-      <c r="I44" s="4" t="n"/>
-      <c r="J44" s="4" t="n"/>
-      <c r="K44" s="4" t="n"/>
-      <c r="L44" s="4" t="n"/>
-      <c r="M44" s="4" t="n"/>
-      <c r="N44" s="4" t="n"/>
-      <c r="O44" s="4" t="n"/>
-      <c r="P44" s="4" t="n"/>
-      <c r="Q44" s="4" t="n"/>
+      <c r="B43" s="13" t="n"/>
+      <c r="C43" s="13" t="n"/>
+      <c r="D43" s="13">
+        <f>D4-D12-D33-D41</f>
+        <v/>
+      </c>
+      <c r="E43" s="13">
+        <f>E4-E12-E33-E41</f>
+        <v/>
+      </c>
+      <c r="F43" s="13">
+        <f>F4-F12-F33-F41</f>
+        <v/>
+      </c>
+      <c r="G43" s="13">
+        <f>G4-G12-G33-G41</f>
+        <v/>
+      </c>
+      <c r="H43" s="13">
+        <f>H4-H12-H33-H41</f>
+        <v/>
+      </c>
+      <c r="I43" s="13">
+        <f>I4-I12-I33-I41</f>
+        <v/>
+      </c>
+      <c r="J43" s="13">
+        <f>J4-J12-J33-J41</f>
+        <v/>
+      </c>
+      <c r="K43" s="13">
+        <f>K4-K12-K33-K41</f>
+        <v/>
+      </c>
+      <c r="L43" s="13">
+        <f>L4-L12-L33-L41</f>
+        <v/>
+      </c>
+      <c r="M43" s="13">
+        <f>M4-M12-M33-M41</f>
+        <v/>
+      </c>
+      <c r="N43" s="13">
+        <f>N4-N12-N33-N41</f>
+        <v/>
+      </c>
+      <c r="O43" s="13">
+        <f>O4-O12-O33-O41</f>
+        <v/>
+      </c>
+      <c r="P43" s="13">
+        <f>SUM(D43:O43)</f>
+        <v/>
+      </c>
+      <c r="Q43" s="13" t="n"/>
+    </row>
+    <row r="44" hidden="1" outlineLevel="1" ht="12" customHeight="1">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>% profit / product sales</t>
+        </is>
+      </c>
+      <c r="B44" s="11" t="n"/>
+      <c r="C44" s="11" t="n"/>
+      <c r="D44" s="11">
+        <f>IFERROR(D43/D5,0)</f>
+        <v/>
+      </c>
+      <c r="E44" s="11">
+        <f>IFERROR(E43/E5,0)</f>
+        <v/>
+      </c>
+      <c r="F44" s="11">
+        <f>IFERROR(F43/F5,0)</f>
+        <v/>
+      </c>
+      <c r="G44" s="11">
+        <f>IFERROR(G43/G5,0)</f>
+        <v/>
+      </c>
+      <c r="H44" s="11">
+        <f>IFERROR(H43/H5,0)</f>
+        <v/>
+      </c>
+      <c r="I44" s="11">
+        <f>IFERROR(I43/I5,0)</f>
+        <v/>
+      </c>
+      <c r="J44" s="11">
+        <f>IFERROR(J43/J5,0)</f>
+        <v/>
+      </c>
+      <c r="K44" s="11">
+        <f>IFERROR(K43/K5,0)</f>
+        <v/>
+      </c>
+      <c r="L44" s="11">
+        <f>IFERROR(L43/L5,0)</f>
+        <v/>
+      </c>
+      <c r="M44" s="11">
+        <f>IFERROR(M43/M5,0)</f>
+        <v/>
+      </c>
+      <c r="N44" s="11">
+        <f>IFERROR(N43/N5,0)</f>
+        <v/>
+      </c>
+      <c r="O44" s="11">
+        <f>IFERROR(O43/O5,0)</f>
+        <v/>
+      </c>
+      <c r="P44" s="11">
+        <f>IFERROR(P43/P5,0)</f>
+        <v/>
+      </c>
+      <c r="Q44" s="11" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="15" t="inlineStr">
-        <is>
-          <t>Stock inicial marcos</t>
-        </is>
-      </c>
       <c r="B45" s="4" t="n"/>
       <c r="C45" s="4" t="n"/>
-      <c r="D45" s="4" t="n">
-        <v>7471.59</v>
-      </c>
-      <c r="E45" s="4" t="n">
-        <v>13032.64</v>
-      </c>
-      <c r="F45" s="4" t="n">
-        <v>10643.86</v>
-      </c>
-      <c r="G45" s="4" t="n">
-        <v>19745.79</v>
-      </c>
+      <c r="D45" s="4" t="n"/>
+      <c r="E45" s="4" t="n"/>
+      <c r="F45" s="4" t="n"/>
+      <c r="G45" s="4" t="n"/>
       <c r="H45" s="4" t="n"/>
       <c r="I45" s="4" t="n"/>
       <c r="J45" s="4" t="n"/>
@@ -2998,31 +3060,28 @@
       <c r="M45" s="4" t="n"/>
       <c r="N45" s="4" t="n"/>
       <c r="O45" s="4" t="n"/>
-      <c r="P45" s="4">
-        <f>SUM(D45:O45)</f>
-        <v/>
-      </c>
+      <c r="P45" s="4" t="n"/>
       <c r="Q45" s="4" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="15" t="inlineStr">
-        <is>
-          <t>Stock final marcos</t>
+      <c r="A46" s="14" t="inlineStr">
+        <is>
+          <t>Stock inicial marcos</t>
         </is>
       </c>
       <c r="B46" s="4" t="n"/>
       <c r="C46" s="4" t="n"/>
       <c r="D46" s="4" t="n">
+        <v>7471.59</v>
+      </c>
+      <c r="E46" s="4" t="n">
         <v>13032.64</v>
       </c>
-      <c r="E46" s="4" t="n">
+      <c r="F46" s="4" t="n">
         <v>10643.86</v>
       </c>
-      <c r="F46" s="4" t="n">
+      <c r="G46" s="4" t="n">
         <v>19745.79</v>
-      </c>
-      <c r="G46" s="4" t="n">
-        <v>19708.44</v>
       </c>
       <c r="H46" s="4" t="n"/>
       <c r="I46" s="4" t="n"/>
@@ -3038,6 +3097,40 @@
       </c>
       <c r="Q46" s="4" t="n"/>
     </row>
+    <row r="47">
+      <c r="A47" s="14" t="inlineStr">
+        <is>
+          <t>Stock final marcos</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="n"/>
+      <c r="C47" s="4" t="n"/>
+      <c r="D47" s="4" t="n">
+        <v>13032.64</v>
+      </c>
+      <c r="E47" s="4" t="n">
+        <v>10643.86</v>
+      </c>
+      <c r="F47" s="4" t="n">
+        <v>19745.79</v>
+      </c>
+      <c r="G47" s="4" t="n">
+        <v>19678.14</v>
+      </c>
+      <c r="H47" s="4" t="n"/>
+      <c r="I47" s="4" t="n"/>
+      <c r="J47" s="4" t="n"/>
+      <c r="K47" s="4" t="n"/>
+      <c r="L47" s="4" t="n"/>
+      <c r="M47" s="4" t="n"/>
+      <c r="N47" s="4" t="n"/>
+      <c r="O47" s="4" t="n"/>
+      <c r="P47" s="4">
+        <f>SUM(D47:O47)</f>
+        <v/>
+      </c>
+      <c r="Q47" s="4" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A3:C3"/>
@@ -3046,19 +3139,19 @@
   <hyperlinks>
     <hyperlink ref="Q6" location="'i-shopify-ltd'!A1" display="-&gt;"/>
     <hyperlink ref="Q7" location="'i-shopify-ltd'!A1" display="-&gt;"/>
-    <hyperlink ref="Q12" location="'g-expenses-ltd'!A1" display="-&gt;"/>
     <hyperlink ref="Q13" location="'g-expenses-ltd'!A1" display="-&gt;"/>
-    <hyperlink ref="Q18" location="'g-expenses-ltd'!A1" display="-&gt;"/>
+    <hyperlink ref="Q14" location="'g-expenses-ltd'!A1" display="-&gt;"/>
     <hyperlink ref="Q19" location="'g-expenses-ltd'!A1" display="-&gt;"/>
-    <hyperlink ref="Q22" location="'g-payment-fees-ltd'!A1" display="-&gt;"/>
+    <hyperlink ref="Q20" location="'g-expenses-ltd'!A1" display="-&gt;"/>
     <hyperlink ref="Q23" location="'g-payment-fees-ltd'!A1" display="-&gt;"/>
-    <hyperlink ref="Q33" location="'g-expenses-ltd'!A1" display="-&gt;"/>
+    <hyperlink ref="Q24" location="'g-payment-fees-ltd'!A1" display="-&gt;"/>
     <hyperlink ref="Q34" location="'g-expenses-ltd'!A1" display="-&gt;"/>
     <hyperlink ref="Q35" location="'g-expenses-ltd'!A1" display="-&gt;"/>
     <hyperlink ref="Q36" location="'g-expenses-ltd'!A1" display="-&gt;"/>
     <hyperlink ref="Q37" location="'g-expenses-ltd'!A1" display="-&gt;"/>
     <hyperlink ref="Q38" location="'g-expenses-ltd'!A1" display="-&gt;"/>
     <hyperlink ref="Q39" location="'g-expenses-ltd'!A1" display="-&gt;"/>
+    <hyperlink ref="Q40" location="'g-expenses-ltd'!A1" display="-&gt;"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3078,19 +3171,19 @@
   </cols>
   <sheetData>
     <row r="1" ht="12" customHeight="1">
-      <c r="A1" s="16" t="inlineStr">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>&lt;- Volver a P&amp;G-LTD</t>
         </is>
       </c>
     </row>
     <row r="2" ht="12" customHeight="1">
-      <c r="A2" s="17" t="inlineStr">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>key</t>
         </is>
       </c>
-      <c r="B2" s="17" t="inlineStr">
+      <c r="B2" s="16" t="inlineStr">
         <is>
           <t>value</t>
         </is>
@@ -3138,7 +3231,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-04-03T06:03:36Z</t>
+          <t>2026-04-04T10:00:15Z</t>
         </is>
       </c>
     </row>
@@ -3172,59 +3265,59 @@
   </cols>
   <sheetData>
     <row r="1" ht="12" customHeight="1">
-      <c r="A1" s="16" t="inlineStr">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>&lt;- Volver a P&amp;G-LTD</t>
         </is>
       </c>
     </row>
     <row r="2" ht="12" customHeight="1">
-      <c r="A2" s="17" t="inlineStr">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>yyyymm</t>
         </is>
       </c>
-      <c r="B2" s="17" t="inlineStr">
+      <c r="B2" s="16" t="inlineStr">
         <is>
           <t>entity</t>
         </is>
       </c>
-      <c r="C2" s="17" t="inlineStr">
+      <c r="C2" s="16" t="inlineStr">
         <is>
           <t>line_item</t>
         </is>
       </c>
-      <c r="D2" s="17" t="inlineStr">
+      <c r="D2" s="16" t="inlineStr">
         <is>
           <t>detail</t>
         </is>
       </c>
-      <c r="E2" s="17" t="inlineStr">
+      <c r="E2" s="16" t="inlineStr">
         <is>
           <t>amount_original</t>
         </is>
       </c>
-      <c r="F2" s="17" t="inlineStr">
+      <c r="F2" s="16" t="inlineStr">
         <is>
           <t>currency_original</t>
         </is>
       </c>
-      <c r="G2" s="17" t="inlineStr">
+      <c r="G2" s="16" t="inlineStr">
         <is>
           <t>reporting_currency</t>
         </is>
       </c>
-      <c r="H2" s="17" t="inlineStr">
+      <c r="H2" s="16" t="inlineStr">
         <is>
           <t>fx_rate</t>
         </is>
       </c>
-      <c r="I2" s="17" t="inlineStr">
+      <c r="I2" s="16" t="inlineStr">
         <is>
           <t>amount_reporting</t>
         </is>
       </c>
-      <c r="J2" s="17" t="inlineStr">
+      <c r="J2" s="16" t="inlineStr">
         <is>
           <t>source</t>
         </is>
@@ -3264,7 +3357,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="H3" s="18" t="n">
+      <c r="H3" s="17" t="n">
         <v>1</v>
       </c>
       <c r="I3" s="4" t="n">
@@ -3310,7 +3403,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="H4" s="18" t="n">
+      <c r="H4" s="17" t="n">
         <v>1</v>
       </c>
       <c r="I4" s="4" t="n">
@@ -3356,7 +3449,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="H5" s="18" t="n">
+      <c r="H5" s="17" t="n">
         <v>1</v>
       </c>
       <c r="I5" s="4" t="n">
@@ -3390,7 +3483,7 @@
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>824.59</v>
+        <v>1333.46</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -3402,11 +3495,11 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="H6" s="18" t="n">
+      <c r="H6" s="17" t="n">
         <v>1</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>824.59</v>
+        <v>1333.46</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -3428,7 +3521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N146"/>
+  <dimension ref="A1:N143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3448,79 +3541,79 @@
   </cols>
   <sheetData>
     <row r="1" ht="12" customHeight="1">
-      <c r="A1" s="16" t="inlineStr">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>&lt;- Volver a P&amp;G-LTD</t>
         </is>
       </c>
     </row>
     <row r="2" ht="12" customHeight="1">
-      <c r="A2" s="17" t="inlineStr">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>yyyymm</t>
         </is>
       </c>
-      <c r="B2" s="17" t="inlineStr">
+      <c r="B2" s="16" t="inlineStr">
         <is>
           <t>entity</t>
         </is>
       </c>
-      <c r="C2" s="17" t="inlineStr">
+      <c r="C2" s="16" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="D2" s="17" t="inlineStr">
+      <c r="D2" s="16" t="inlineStr">
         <is>
           <t>subcategory</t>
         </is>
       </c>
-      <c r="E2" s="17" t="inlineStr">
+      <c r="E2" s="16" t="inlineStr">
         <is>
           <t>supplier_code</t>
         </is>
       </c>
-      <c r="F2" s="17" t="inlineStr">
+      <c r="F2" s="16" t="inlineStr">
         <is>
           <t>detail</t>
         </is>
       </c>
-      <c r="G2" s="17" t="inlineStr">
+      <c r="G2" s="16" t="inlineStr">
         <is>
           <t>amount_original</t>
         </is>
       </c>
-      <c r="H2" s="17" t="inlineStr">
+      <c r="H2" s="16" t="inlineStr">
         <is>
           <t>currency_original</t>
         </is>
       </c>
-      <c r="I2" s="17" t="inlineStr">
+      <c r="I2" s="16" t="inlineStr">
         <is>
           <t>reporting_currency</t>
         </is>
       </c>
-      <c r="J2" s="17" t="inlineStr">
+      <c r="J2" s="16" t="inlineStr">
         <is>
           <t>fx_rate</t>
         </is>
       </c>
-      <c r="K2" s="17" t="inlineStr">
+      <c r="K2" s="16" t="inlineStr">
         <is>
           <t>amount_reporting</t>
         </is>
       </c>
-      <c r="L2" s="17" t="inlineStr">
+      <c r="L2" s="16" t="inlineStr">
         <is>
           <t>source</t>
         </is>
       </c>
-      <c r="M2" s="17" t="inlineStr">
+      <c r="M2" s="16" t="inlineStr">
         <is>
           <t>invoice_number</t>
         </is>
       </c>
-      <c r="N2" s="17" t="inlineStr">
+      <c r="N2" s="16" t="inlineStr">
         <is>
           <t>drive_url</t>
         </is>
@@ -3570,7 +3663,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J3" s="18" t="n">
+      <c r="J3" s="17" t="n">
         <v>0.72673882</v>
       </c>
       <c r="K3" s="4" t="n">
@@ -3581,7 +3674,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M3" s="19" t="inlineStr">
+      <c r="M3" s="18" t="inlineStr">
         <is>
           <t>AS-94763</t>
         </is>
@@ -3636,7 +3729,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J4" s="18" t="n">
+      <c r="J4" s="17" t="n">
         <v>0.72673882</v>
       </c>
       <c r="K4" s="4" t="n">
@@ -3647,7 +3740,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M4" s="19" t="inlineStr">
+      <c r="M4" s="18" t="inlineStr">
         <is>
           <t>AS-94832</t>
         </is>
@@ -3702,7 +3795,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J5" s="18" t="n">
+      <c r="J5" s="17" t="n">
         <v>0.72673882</v>
       </c>
       <c r="K5" s="4" t="n">
@@ -3713,7 +3806,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M5" s="19" t="inlineStr">
+      <c r="M5" s="18" t="inlineStr">
         <is>
           <t>AS-95021</t>
         </is>
@@ -3768,7 +3861,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J6" s="18" t="n">
+      <c r="J6" s="17" t="n">
         <v>0.72673882</v>
       </c>
       <c r="K6" s="4" t="n">
@@ -3779,7 +3872,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M6" s="19" t="inlineStr">
+      <c r="M6" s="18" t="inlineStr">
         <is>
           <t>AS-95024</t>
         </is>
@@ -3834,7 +3927,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J7" s="18" t="n">
+      <c r="J7" s="17" t="n">
         <v>0.72673882</v>
       </c>
       <c r="K7" s="4" t="n">
@@ -3845,7 +3938,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M7" s="19" t="inlineStr">
+      <c r="M7" s="18" t="inlineStr">
         <is>
           <t>AS-95158</t>
         </is>
@@ -3900,7 +3993,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J8" s="18" t="n">
+      <c r="J8" s="17" t="n">
         <v>0.72673882</v>
       </c>
       <c r="K8" s="4" t="n">
@@ -3911,7 +4004,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M8" s="19" t="inlineStr">
+      <c r="M8" s="18" t="inlineStr">
         <is>
           <t>AS-95275</t>
         </is>
@@ -3966,7 +4059,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J9" s="18" t="n">
+      <c r="J9" s="17" t="n">
         <v>0.72673882</v>
       </c>
       <c r="K9" s="4" t="n">
@@ -3977,7 +4070,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M9" s="19" t="inlineStr">
+      <c r="M9" s="18" t="inlineStr">
         <is>
           <t>AS-95319</t>
         </is>
@@ -4032,7 +4125,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J10" s="18" t="n">
+      <c r="J10" s="17" t="n">
         <v>0.72673882</v>
       </c>
       <c r="K10" s="4" t="n">
@@ -4043,7 +4136,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M10" s="19" t="inlineStr">
+      <c r="M10" s="18" t="inlineStr">
         <is>
           <t>AS-95383</t>
         </is>
@@ -4098,7 +4191,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J11" s="18" t="n">
+      <c r="J11" s="17" t="n">
         <v>0.72673882</v>
       </c>
       <c r="K11" s="4" t="n">
@@ -4109,7 +4202,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M11" s="19" t="inlineStr">
+      <c r="M11" s="18" t="inlineStr">
         <is>
           <t>AS-95462</t>
         </is>
@@ -4164,7 +4257,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J12" s="18" t="n">
+      <c r="J12" s="17" t="n">
         <v>0.72673882</v>
       </c>
       <c r="K12" s="4" t="n">
@@ -4175,7 +4268,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M12" s="19" t="inlineStr">
+      <c r="M12" s="18" t="inlineStr">
         <is>
           <t>AS-95630</t>
         </is>
@@ -4230,7 +4323,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J13" s="18" t="n">
+      <c r="J13" s="17" t="n">
         <v>0.72673882</v>
       </c>
       <c r="K13" s="4" t="n">
@@ -4241,7 +4334,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M13" s="19" t="inlineStr">
+      <c r="M13" s="18" t="inlineStr">
         <is>
           <t>AS-95636</t>
         </is>
@@ -4296,7 +4389,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J14" s="18" t="n">
+      <c r="J14" s="17" t="n">
         <v>0.72673882</v>
       </c>
       <c r="K14" s="4" t="n">
@@ -4307,7 +4400,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M14" s="19" t="inlineStr">
+      <c r="M14" s="18" t="inlineStr">
         <is>
           <t>AS-95652</t>
         </is>
@@ -4362,7 +4455,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J15" s="18" t="n">
+      <c r="J15" s="17" t="n">
         <v>0.72673882</v>
       </c>
       <c r="K15" s="4" t="n">
@@ -4373,7 +4466,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M15" s="19" t="inlineStr">
+      <c r="M15" s="18" t="inlineStr">
         <is>
           <t>AS-95716</t>
         </is>
@@ -4428,7 +4521,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J16" s="18" t="n">
+      <c r="J16" s="17" t="n">
         <v>0.72673882</v>
       </c>
       <c r="K16" s="4" t="n">
@@ -4439,7 +4532,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M16" s="19" t="inlineStr">
+      <c r="M16" s="18" t="inlineStr">
         <is>
           <t>AS-95748</t>
         </is>
@@ -4494,7 +4587,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J17" s="18" t="n">
+      <c r="J17" s="17" t="n">
         <v>0.72673882</v>
       </c>
       <c r="K17" s="4" t="n">
@@ -4505,7 +4598,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M17" s="19" t="inlineStr">
+      <c r="M17" s="18" t="inlineStr">
         <is>
           <t>AS-95763</t>
         </is>
@@ -4560,7 +4653,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J18" s="18" t="n">
+      <c r="J18" s="17" t="n">
         <v>0.72673882</v>
       </c>
       <c r="K18" s="4" t="n">
@@ -4571,7 +4664,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M18" s="19" t="inlineStr">
+      <c r="M18" s="18" t="inlineStr">
         <is>
           <t>AS-95778</t>
         </is>
@@ -4626,7 +4719,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J19" s="18" t="n">
+      <c r="J19" s="17" t="n">
         <v>0.72673882</v>
       </c>
       <c r="K19" s="4" t="n">
@@ -4637,7 +4730,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M19" s="19" t="inlineStr">
+      <c r="M19" s="18" t="inlineStr">
         <is>
           <t>AS-96078</t>
         </is>
@@ -4692,7 +4785,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J20" s="18" t="n">
+      <c r="J20" s="17" t="n">
         <v>0.72673882</v>
       </c>
       <c r="K20" s="4" t="n">
@@ -4703,7 +4796,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M20" s="19" t="inlineStr">
+      <c r="M20" s="18" t="inlineStr">
         <is>
           <t>AS-96170</t>
         </is>
@@ -4758,7 +4851,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J21" s="18" t="n">
+      <c r="J21" s="17" t="n">
         <v>0.72673882</v>
       </c>
       <c r="K21" s="4" t="n">
@@ -4769,7 +4862,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M21" s="19" t="inlineStr">
+      <c r="M21" s="18" t="inlineStr">
         <is>
           <t>AS-96234</t>
         </is>
@@ -4824,7 +4917,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J22" s="18" t="n">
+      <c r="J22" s="17" t="n">
         <v>0.72673882</v>
       </c>
       <c r="K22" s="4" t="n">
@@ -4835,7 +4928,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M22" s="19" t="inlineStr">
+      <c r="M22" s="18" t="inlineStr">
         <is>
           <t>AS-96246</t>
         </is>
@@ -4890,7 +4983,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J23" s="18" t="n">
+      <c r="J23" s="17" t="n">
         <v>0.72673882</v>
       </c>
       <c r="K23" s="4" t="n">
@@ -4901,7 +4994,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M23" s="19" t="inlineStr">
+      <c r="M23" s="18" t="inlineStr">
         <is>
           <t>AS-96512</t>
         </is>
@@ -4956,7 +5049,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J24" s="18" t="n">
+      <c r="J24" s="17" t="n">
         <v>0.72673882</v>
       </c>
       <c r="K24" s="4" t="n">
@@ -4967,7 +5060,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M24" s="19" t="inlineStr">
+      <c r="M24" s="18" t="inlineStr">
         <is>
           <t>AS-96838</t>
         </is>
@@ -5022,7 +5115,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J25" s="18" t="n">
+      <c r="J25" s="17" t="n">
         <v>0.72673882</v>
       </c>
       <c r="K25" s="4" t="n">
@@ -5033,7 +5126,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M25" s="19" t="inlineStr">
+      <c r="M25" s="18" t="inlineStr">
         <is>
           <t>AS-97012</t>
         </is>
@@ -5088,7 +5181,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J26" s="18" t="n">
+      <c r="J26" s="17" t="n">
         <v>0.72673882</v>
       </c>
       <c r="K26" s="4" t="n">
@@ -5099,7 +5192,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M26" s="19" t="inlineStr">
+      <c r="M26" s="18" t="inlineStr">
         <is>
           <t>AS-97038</t>
         </is>
@@ -5154,7 +5247,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J27" s="18" t="n">
+      <c r="J27" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K27" s="4" t="n">
@@ -5165,7 +5258,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M27" s="19" t="inlineStr">
+      <c r="M27" s="18" t="inlineStr">
         <is>
           <t>6032421</t>
         </is>
@@ -5220,7 +5313,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J28" s="18" t="n">
+      <c r="J28" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K28" s="4" t="n">
@@ -5231,7 +5324,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M28" s="19" t="inlineStr">
+      <c r="M28" s="18" t="inlineStr">
         <is>
           <t>6032421</t>
         </is>
@@ -5286,7 +5379,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J29" s="18" t="n">
+      <c r="J29" s="17" t="n">
         <v>0.8662</v>
       </c>
       <c r="K29" s="4" t="n">
@@ -5297,7 +5390,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M29" s="19" t="inlineStr">
+      <c r="M29" s="18" t="inlineStr">
         <is>
           <t>2026-0010</t>
         </is>
@@ -5352,7 +5445,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J30" s="18" t="n">
+      <c r="J30" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K30" s="4" t="n">
@@ -5363,7 +5456,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M30" s="19" t="inlineStr">
+      <c r="M30" s="18" t="inlineStr">
         <is>
           <t>INV-0679_PERIODIFICADA_1_12</t>
         </is>
@@ -5418,7 +5511,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J31" s="18" t="n">
+      <c r="J31" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K31" s="4" t="n">
@@ -5429,7 +5522,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M31" s="19" t="inlineStr">
+      <c r="M31" s="18" t="inlineStr">
         <is>
           <t>INV-0682_PERIODIFICADA_1_12</t>
         </is>
@@ -5484,7 +5577,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J32" s="18" t="n">
+      <c r="J32" s="17" t="n">
         <v>0.74231258</v>
       </c>
       <c r="K32" s="4" t="n">
@@ -5495,7 +5588,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M32" s="19" t="inlineStr">
+      <c r="M32" s="18" t="inlineStr">
         <is>
           <t>AS-97196</t>
         </is>
@@ -5550,7 +5643,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J33" s="18" t="n">
+      <c r="J33" s="17" t="n">
         <v>0.74231258</v>
       </c>
       <c r="K33" s="4" t="n">
@@ -5561,7 +5654,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M33" s="19" t="inlineStr">
+      <c r="M33" s="18" t="inlineStr">
         <is>
           <t>AS-97254</t>
         </is>
@@ -5616,7 +5709,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J34" s="18" t="n">
+      <c r="J34" s="17" t="n">
         <v>0.74231258</v>
       </c>
       <c r="K34" s="4" t="n">
@@ -5627,7 +5720,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M34" s="19" t="inlineStr">
+      <c r="M34" s="18" t="inlineStr">
         <is>
           <t>AS-97464</t>
         </is>
@@ -5682,7 +5775,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J35" s="18" t="n">
+      <c r="J35" s="17" t="n">
         <v>0.74231258</v>
       </c>
       <c r="K35" s="4" t="n">
@@ -5693,7 +5786,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M35" s="19" t="inlineStr">
+      <c r="M35" s="18" t="inlineStr">
         <is>
           <t>AS-97516</t>
         </is>
@@ -5748,7 +5841,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J36" s="18" t="n">
+      <c r="J36" s="17" t="n">
         <v>0.74231258</v>
       </c>
       <c r="K36" s="4" t="n">
@@ -5759,7 +5852,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M36" s="19" t="inlineStr">
+      <c r="M36" s="18" t="inlineStr">
         <is>
           <t>AS-97520</t>
         </is>
@@ -5814,7 +5907,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J37" s="18" t="n">
+      <c r="J37" s="17" t="n">
         <v>0.74231258</v>
       </c>
       <c r="K37" s="4" t="n">
@@ -5825,7 +5918,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M37" s="19" t="inlineStr">
+      <c r="M37" s="18" t="inlineStr">
         <is>
           <t>AS-97602</t>
         </is>
@@ -5880,7 +5973,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J38" s="18" t="n">
+      <c r="J38" s="17" t="n">
         <v>0.74231258</v>
       </c>
       <c r="K38" s="4" t="n">
@@ -5891,7 +5984,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M38" s="19" t="inlineStr">
+      <c r="M38" s="18" t="inlineStr">
         <is>
           <t>AS-98142</t>
         </is>
@@ -5946,7 +6039,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J39" s="18" t="n">
+      <c r="J39" s="17" t="n">
         <v>0.74231258</v>
       </c>
       <c r="K39" s="4" t="n">
@@ -5957,7 +6050,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M39" s="19" t="inlineStr">
+      <c r="M39" s="18" t="inlineStr">
         <is>
           <t>AS-98380</t>
         </is>
@@ -6012,7 +6105,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J40" s="18" t="n">
+      <c r="J40" s="17" t="n">
         <v>0.74231258</v>
       </c>
       <c r="K40" s="4" t="n">
@@ -6023,7 +6116,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M40" s="19" t="inlineStr">
+      <c r="M40" s="18" t="inlineStr">
         <is>
           <t>AS-98382</t>
         </is>
@@ -6078,7 +6171,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J41" s="18" t="n">
+      <c r="J41" s="17" t="n">
         <v>0.74231258</v>
       </c>
       <c r="K41" s="4" t="n">
@@ -6089,7 +6182,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M41" s="19" t="inlineStr">
+      <c r="M41" s="18" t="inlineStr">
         <is>
           <t>AS-98403</t>
         </is>
@@ -6144,7 +6237,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J42" s="18" t="n">
+      <c r="J42" s="17" t="n">
         <v>0.74231258</v>
       </c>
       <c r="K42" s="4" t="n">
@@ -6155,7 +6248,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M42" s="19" t="inlineStr">
+      <c r="M42" s="18" t="inlineStr">
         <is>
           <t>AS-98524</t>
         </is>
@@ -6210,7 +6303,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J43" s="18" t="n">
+      <c r="J43" s="17" t="n">
         <v>0.74231258</v>
       </c>
       <c r="K43" s="4" t="n">
@@ -6221,7 +6314,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M43" s="19" t="inlineStr">
+      <c r="M43" s="18" t="inlineStr">
         <is>
           <t>AS-98544</t>
         </is>
@@ -6276,7 +6369,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J44" s="18" t="n">
+      <c r="J44" s="17" t="n">
         <v>0.74231258</v>
       </c>
       <c r="K44" s="4" t="n">
@@ -6287,7 +6380,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M44" s="19" t="inlineStr">
+      <c r="M44" s="18" t="inlineStr">
         <is>
           <t>AS-98563</t>
         </is>
@@ -6342,7 +6435,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J45" s="18" t="n">
+      <c r="J45" s="17" t="n">
         <v>0.74231258</v>
       </c>
       <c r="K45" s="4" t="n">
@@ -6353,7 +6446,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M45" s="19" t="inlineStr">
+      <c r="M45" s="18" t="inlineStr">
         <is>
           <t>AS-98567</t>
         </is>
@@ -6408,7 +6501,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J46" s="18" t="n">
+      <c r="J46" s="17" t="n">
         <v>0.74231258</v>
       </c>
       <c r="K46" s="4" t="n">
@@ -6419,7 +6512,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M46" s="19" t="inlineStr">
+      <c r="M46" s="18" t="inlineStr">
         <is>
           <t>AS-98978</t>
         </is>
@@ -6474,7 +6567,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J47" s="18" t="n">
+      <c r="J47" s="17" t="n">
         <v>0.74231258</v>
       </c>
       <c r="K47" s="4" t="n">
@@ -6485,7 +6578,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M47" s="19" t="inlineStr">
+      <c r="M47" s="18" t="inlineStr">
         <is>
           <t>AS-99094</t>
         </is>
@@ -6540,7 +6633,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J48" s="18" t="n">
+      <c r="J48" s="17" t="n">
         <v>0.74231258</v>
       </c>
       <c r="K48" s="4" t="n">
@@ -6551,7 +6644,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M48" s="19" t="inlineStr">
+      <c r="M48" s="18" t="inlineStr">
         <is>
           <t>AS-99179</t>
         </is>
@@ -6606,7 +6699,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J49" s="18" t="n">
+      <c r="J49" s="17" t="n">
         <v>0.74231258</v>
       </c>
       <c r="K49" s="4" t="n">
@@ -6617,7 +6710,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M49" s="19" t="inlineStr">
+      <c r="M49" s="18" t="inlineStr">
         <is>
           <t>AS-99349</t>
         </is>
@@ -6672,7 +6765,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J50" s="18" t="n">
+      <c r="J50" s="17" t="n">
         <v>0.74231258</v>
       </c>
       <c r="K50" s="4" t="n">
@@ -6683,7 +6776,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M50" s="19" t="inlineStr">
+      <c r="M50" s="18" t="inlineStr">
         <is>
           <t>AS-99356</t>
         </is>
@@ -6738,7 +6831,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J51" s="18" t="n">
+      <c r="J51" s="17" t="n">
         <v>0.74231258</v>
       </c>
       <c r="K51" s="4" t="n">
@@ -6749,7 +6842,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M51" s="19" t="inlineStr">
+      <c r="M51" s="18" t="inlineStr">
         <is>
           <t>AS-99390</t>
         </is>
@@ -6804,7 +6897,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J52" s="18" t="n">
+      <c r="J52" s="17" t="n">
         <v>0.74231258</v>
       </c>
       <c r="K52" s="4" t="n">
@@ -6815,7 +6908,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M52" s="19" t="inlineStr">
+      <c r="M52" s="18" t="inlineStr">
         <is>
           <t>AS-99509</t>
         </is>
@@ -6870,7 +6963,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J53" s="18" t="n">
+      <c r="J53" s="17" t="n">
         <v>0.74231258</v>
       </c>
       <c r="K53" s="4" t="n">
@@ -6881,7 +6974,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M53" s="19" t="inlineStr">
+      <c r="M53" s="18" t="inlineStr">
         <is>
           <t>AS-99616</t>
         </is>
@@ -6936,7 +7029,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J54" s="18" t="n">
+      <c r="J54" s="17" t="n">
         <v>0.74231258</v>
       </c>
       <c r="K54" s="4" t="n">
@@ -6947,7 +7040,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M54" s="19" t="inlineStr">
+      <c r="M54" s="18" t="inlineStr">
         <is>
           <t>AS-99632</t>
         </is>
@@ -7002,7 +7095,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J55" s="18" t="n">
+      <c r="J55" s="17" t="n">
         <v>0.74231258</v>
       </c>
       <c r="K55" s="4" t="n">
@@ -7013,7 +7106,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M55" s="19" t="inlineStr">
+      <c r="M55" s="18" t="inlineStr">
         <is>
           <t>AS-99779</t>
         </is>
@@ -7068,7 +7161,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J56" s="18" t="n">
+      <c r="J56" s="17" t="n">
         <v>0.74231258</v>
       </c>
       <c r="K56" s="4" t="n">
@@ -7079,7 +7172,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M56" s="19" t="inlineStr">
+      <c r="M56" s="18" t="inlineStr">
         <is>
           <t>AS-99780</t>
         </is>
@@ -7134,7 +7227,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J57" s="18" t="n">
+      <c r="J57" s="17" t="n">
         <v>0.74231258</v>
       </c>
       <c r="K57" s="4" t="n">
@@ -7145,7 +7238,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M57" s="19" t="inlineStr">
+      <c r="M57" s="18" t="inlineStr">
         <is>
           <t>AS-99822</t>
         </is>
@@ -7200,7 +7293,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J58" s="18" t="n">
+      <c r="J58" s="17" t="n">
         <v>0.74231258</v>
       </c>
       <c r="K58" s="4" t="n">
@@ -7211,7 +7304,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M58" s="19" t="inlineStr">
+      <c r="M58" s="18" t="inlineStr">
         <is>
           <t>AS-99880</t>
         </is>
@@ -7266,7 +7359,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J59" s="18" t="n">
+      <c r="J59" s="17" t="n">
         <v>0.74231258</v>
       </c>
       <c r="K59" s="4" t="n">
@@ -7277,7 +7370,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M59" s="19" t="inlineStr">
+      <c r="M59" s="18" t="inlineStr">
         <is>
           <t>AS-99886</t>
         </is>
@@ -7332,7 +7425,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J60" s="18" t="n">
+      <c r="J60" s="17" t="n">
         <v>0.74231258</v>
       </c>
       <c r="K60" s="4" t="n">
@@ -7343,7 +7436,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M60" s="19" t="inlineStr">
+      <c r="M60" s="18" t="inlineStr">
         <is>
           <t>AS-99899</t>
         </is>
@@ -7398,7 +7491,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J61" s="18" t="n">
+      <c r="J61" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K61" s="4" t="n">
@@ -7409,7 +7502,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M61" s="19" t="inlineStr">
+      <c r="M61" s="18" t="inlineStr">
         <is>
           <t>6033326</t>
         </is>
@@ -7464,7 +7557,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J62" s="18" t="n">
+      <c r="J62" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K62" s="4" t="n">
@@ -7475,7 +7568,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M62" s="19" t="inlineStr">
+      <c r="M62" s="18" t="inlineStr">
         <is>
           <t>6033326</t>
         </is>
@@ -7530,7 +7623,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J63" s="18" t="n">
+      <c r="J63" s="17" t="n">
         <v>0.8763</v>
       </c>
       <c r="K63" s="4" t="n">
@@ -7541,7 +7634,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M63" s="19" t="inlineStr">
+      <c r="M63" s="18" t="inlineStr">
         <is>
           <t>2026-0015</t>
         </is>
@@ -7596,7 +7689,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J64" s="18" t="n">
+      <c r="J64" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K64" s="4" t="n">
@@ -7607,7 +7700,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M64" s="19" t="inlineStr">
+      <c r="M64" s="18" t="inlineStr">
         <is>
           <t>INV-0679_PERIODIFICADA_2_12</t>
         </is>
@@ -7662,7 +7755,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J65" s="18" t="n">
+      <c r="J65" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K65" s="4" t="n">
@@ -7673,7 +7766,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M65" s="19" t="inlineStr">
+      <c r="M65" s="18" t="inlineStr">
         <is>
           <t>INV-0681_PERIODIFICADA_1_12</t>
         </is>
@@ -7728,7 +7821,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J66" s="18" t="n">
+      <c r="J66" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K66" s="4" t="n">
@@ -7739,7 +7832,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M66" s="19" t="inlineStr">
+      <c r="M66" s="18" t="inlineStr">
         <is>
           <t>INV-0682_PERIODIFICADA_2_12</t>
         </is>
@@ -7794,7 +7887,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J67" s="18" t="n">
+      <c r="J67" s="17" t="n">
         <v>0.7552009</v>
       </c>
       <c r="K67" s="4" t="n">
@@ -7805,7 +7898,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M67" s="19" t="inlineStr">
+      <c r="M67" s="18" t="inlineStr">
         <is>
           <t>AS-100037</t>
         </is>
@@ -7860,7 +7953,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J68" s="18" t="n">
+      <c r="J68" s="17" t="n">
         <v>0.7552009</v>
       </c>
       <c r="K68" s="4" t="n">
@@ -7871,7 +7964,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M68" s="19" t="inlineStr">
+      <c r="M68" s="18" t="inlineStr">
         <is>
           <t>AS-100054</t>
         </is>
@@ -7926,7 +8019,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J69" s="18" t="n">
+      <c r="J69" s="17" t="n">
         <v>0.7552009</v>
       </c>
       <c r="K69" s="4" t="n">
@@ -7937,7 +8030,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M69" s="19" t="inlineStr">
+      <c r="M69" s="18" t="inlineStr">
         <is>
           <t>AS-100099</t>
         </is>
@@ -7992,7 +8085,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J70" s="18" t="n">
+      <c r="J70" s="17" t="n">
         <v>0.7552009</v>
       </c>
       <c r="K70" s="4" t="n">
@@ -8003,7 +8096,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M70" s="19" t="inlineStr">
+      <c r="M70" s="18" t="inlineStr">
         <is>
           <t>AS-100109</t>
         </is>
@@ -8058,7 +8151,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J71" s="18" t="n">
+      <c r="J71" s="17" t="n">
         <v>0.7552009</v>
       </c>
       <c r="K71" s="4" t="n">
@@ -8069,7 +8162,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M71" s="19" t="inlineStr">
+      <c r="M71" s="18" t="inlineStr">
         <is>
           <t>AS-100157</t>
         </is>
@@ -8124,7 +8217,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J72" s="18" t="n">
+      <c r="J72" s="17" t="n">
         <v>0.7552009</v>
       </c>
       <c r="K72" s="4" t="n">
@@ -8135,7 +8228,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M72" s="19" t="inlineStr">
+      <c r="M72" s="18" t="inlineStr">
         <is>
           <t>AS-100239</t>
         </is>
@@ -8190,7 +8283,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J73" s="18" t="n">
+      <c r="J73" s="17" t="n">
         <v>0.7552009</v>
       </c>
       <c r="K73" s="4" t="n">
@@ -8201,7 +8294,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M73" s="19" t="inlineStr">
+      <c r="M73" s="18" t="inlineStr">
         <is>
           <t>AS-100248</t>
         </is>
@@ -8256,7 +8349,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J74" s="18" t="n">
+      <c r="J74" s="17" t="n">
         <v>0.7552009</v>
       </c>
       <c r="K74" s="4" t="n">
@@ -8267,7 +8360,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M74" s="19" t="inlineStr">
+      <c r="M74" s="18" t="inlineStr">
         <is>
           <t>AS-100286</t>
         </is>
@@ -8322,7 +8415,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J75" s="18" t="n">
+      <c r="J75" s="17" t="n">
         <v>0.7552009</v>
       </c>
       <c r="K75" s="4" t="n">
@@ -8333,7 +8426,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M75" s="19" t="inlineStr">
+      <c r="M75" s="18" t="inlineStr">
         <is>
           <t>AS-100339</t>
         </is>
@@ -8388,7 +8481,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J76" s="18" t="n">
+      <c r="J76" s="17" t="n">
         <v>0.7552009</v>
       </c>
       <c r="K76" s="4" t="n">
@@ -8399,7 +8492,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M76" s="19" t="inlineStr">
+      <c r="M76" s="18" t="inlineStr">
         <is>
           <t>AS-100443</t>
         </is>
@@ -8454,7 +8547,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J77" s="18" t="n">
+      <c r="J77" s="17" t="n">
         <v>0.7552009</v>
       </c>
       <c r="K77" s="4" t="n">
@@ -8465,7 +8558,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M77" s="19" t="inlineStr">
+      <c r="M77" s="18" t="inlineStr">
         <is>
           <t>AS-100562</t>
         </is>
@@ -8520,7 +8613,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J78" s="18" t="n">
+      <c r="J78" s="17" t="n">
         <v>0.7552009</v>
       </c>
       <c r="K78" s="4" t="n">
@@ -8531,7 +8624,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M78" s="19" t="inlineStr">
+      <c r="M78" s="18" t="inlineStr">
         <is>
           <t>AS-100662</t>
         </is>
@@ -8586,7 +8679,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J79" s="18" t="n">
+      <c r="J79" s="17" t="n">
         <v>0.7552009</v>
       </c>
       <c r="K79" s="4" t="n">
@@ -8597,7 +8690,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M79" s="19" t="inlineStr">
+      <c r="M79" s="18" t="inlineStr">
         <is>
           <t>AS-100690</t>
         </is>
@@ -8652,7 +8745,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J80" s="18" t="n">
+      <c r="J80" s="17" t="n">
         <v>0.7552009</v>
       </c>
       <c r="K80" s="4" t="n">
@@ -8663,7 +8756,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M80" s="19" t="inlineStr">
+      <c r="M80" s="18" t="inlineStr">
         <is>
           <t>AS-100702</t>
         </is>
@@ -8718,7 +8811,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J81" s="18" t="n">
+      <c r="J81" s="17" t="n">
         <v>0.7552009</v>
       </c>
       <c r="K81" s="4" t="n">
@@ -8729,7 +8822,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M81" s="19" t="inlineStr">
+      <c r="M81" s="18" t="inlineStr">
         <is>
           <t>AS-100782</t>
         </is>
@@ -8784,7 +8877,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J82" s="18" t="n">
+      <c r="J82" s="17" t="n">
         <v>0.7552009</v>
       </c>
       <c r="K82" s="4" t="n">
@@ -8795,7 +8888,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M82" s="19" t="inlineStr">
+      <c r="M82" s="18" t="inlineStr">
         <is>
           <t>AS-100814</t>
         </is>
@@ -8850,7 +8943,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J83" s="18" t="n">
+      <c r="J83" s="17" t="n">
         <v>0.7552009</v>
       </c>
       <c r="K83" s="4" t="n">
@@ -8861,7 +8954,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M83" s="19" t="inlineStr">
+      <c r="M83" s="18" t="inlineStr">
         <is>
           <t>AS-100856</t>
         </is>
@@ -8916,7 +9009,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J84" s="18" t="n">
+      <c r="J84" s="17" t="n">
         <v>0.7552009</v>
       </c>
       <c r="K84" s="4" t="n">
@@ -8927,7 +9020,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M84" s="19" t="inlineStr">
+      <c r="M84" s="18" t="inlineStr">
         <is>
           <t>AS-100911</t>
         </is>
@@ -8982,7 +9075,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J85" s="18" t="n">
+      <c r="J85" s="17" t="n">
         <v>0.7552009</v>
       </c>
       <c r="K85" s="4" t="n">
@@ -8993,7 +9086,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M85" s="19" t="inlineStr">
+      <c r="M85" s="18" t="inlineStr">
         <is>
           <t>AS-100918</t>
         </is>
@@ -9048,7 +9141,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J86" s="18" t="n">
+      <c r="J86" s="17" t="n">
         <v>0.7552009</v>
       </c>
       <c r="K86" s="4" t="n">
@@ -9059,7 +9152,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M86" s="19" t="inlineStr">
+      <c r="M86" s="18" t="inlineStr">
         <is>
           <t>AS-100977</t>
         </is>
@@ -9114,7 +9207,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J87" s="18" t="n">
+      <c r="J87" s="17" t="n">
         <v>0.7552009</v>
       </c>
       <c r="K87" s="4" t="n">
@@ -9125,7 +9218,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M87" s="19" t="inlineStr">
+      <c r="M87" s="18" t="inlineStr">
         <is>
           <t>AS-101054</t>
         </is>
@@ -9180,7 +9273,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J88" s="18" t="n">
+      <c r="J88" s="17" t="n">
         <v>0.7552009</v>
       </c>
       <c r="K88" s="4" t="n">
@@ -9191,7 +9284,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M88" s="19" t="inlineStr">
+      <c r="M88" s="18" t="inlineStr">
         <is>
           <t>AS-101073</t>
         </is>
@@ -9246,7 +9339,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J89" s="18" t="n">
+      <c r="J89" s="17" t="n">
         <v>0.7552009</v>
       </c>
       <c r="K89" s="4" t="n">
@@ -9257,7 +9350,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M89" s="19" t="inlineStr">
+      <c r="M89" s="18" t="inlineStr">
         <is>
           <t>AS-101183</t>
         </is>
@@ -9312,7 +9405,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J90" s="18" t="n">
+      <c r="J90" s="17" t="n">
         <v>0.7552009</v>
       </c>
       <c r="K90" s="4" t="n">
@@ -9323,7 +9416,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M90" s="19" t="inlineStr">
+      <c r="M90" s="18" t="inlineStr">
         <is>
           <t>AS-101240</t>
         </is>
@@ -9378,7 +9471,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J91" s="18" t="n">
+      <c r="J91" s="17" t="n">
         <v>0.7552009</v>
       </c>
       <c r="K91" s="4" t="n">
@@ -9389,7 +9482,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M91" s="19" t="inlineStr">
+      <c r="M91" s="18" t="inlineStr">
         <is>
           <t>AS-101372</t>
         </is>
@@ -9444,7 +9537,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J92" s="18" t="n">
+      <c r="J92" s="17" t="n">
         <v>0.7552009</v>
       </c>
       <c r="K92" s="4" t="n">
@@ -9455,7 +9548,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M92" s="19" t="inlineStr">
+      <c r="M92" s="18" t="inlineStr">
         <is>
           <t>AS-101435</t>
         </is>
@@ -9510,7 +9603,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J93" s="18" t="n">
+      <c r="J93" s="17" t="n">
         <v>0.7552009</v>
       </c>
       <c r="K93" s="4" t="n">
@@ -9521,7 +9614,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M93" s="19" t="inlineStr">
+      <c r="M93" s="18" t="inlineStr">
         <is>
           <t>AS-101498</t>
         </is>
@@ -9576,7 +9669,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J94" s="18" t="n">
+      <c r="J94" s="17" t="n">
         <v>0.7552009</v>
       </c>
       <c r="K94" s="4" t="n">
@@ -9587,7 +9680,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M94" s="19" t="inlineStr">
+      <c r="M94" s="18" t="inlineStr">
         <is>
           <t>AS-101504</t>
         </is>
@@ -9642,7 +9735,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J95" s="18" t="n">
+      <c r="J95" s="17" t="n">
         <v>0.7552009</v>
       </c>
       <c r="K95" s="4" t="n">
@@ -9653,7 +9746,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M95" s="19" t="inlineStr">
+      <c r="M95" s="18" t="inlineStr">
         <is>
           <t>AS-101728</t>
         </is>
@@ -9708,7 +9801,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J96" s="18" t="n">
+      <c r="J96" s="17" t="n">
         <v>0.7552009</v>
       </c>
       <c r="K96" s="4" t="n">
@@ -9719,7 +9812,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M96" s="19" t="inlineStr">
+      <c r="M96" s="18" t="inlineStr">
         <is>
           <t>AS-101822</t>
         </is>
@@ -9774,7 +9867,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J97" s="18" t="n">
+      <c r="J97" s="17" t="n">
         <v>0.7552009</v>
       </c>
       <c r="K97" s="4" t="n">
@@ -9785,7 +9878,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M97" s="19" t="inlineStr">
+      <c r="M97" s="18" t="inlineStr">
         <is>
           <t>AS-101900</t>
         </is>
@@ -9840,7 +9933,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J98" s="18" t="n">
+      <c r="J98" s="17" t="n">
         <v>0.7552009</v>
       </c>
       <c r="K98" s="4" t="n">
@@ -9851,7 +9944,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M98" s="19" t="inlineStr">
+      <c r="M98" s="18" t="inlineStr">
         <is>
           <t>AS-101969</t>
         </is>
@@ -9906,7 +9999,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J99" s="18" t="n">
+      <c r="J99" s="17" t="n">
         <v>0.7552009</v>
       </c>
       <c r="K99" s="4" t="n">
@@ -9917,7 +10010,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M99" s="19" t="inlineStr">
+      <c r="M99" s="18" t="inlineStr">
         <is>
           <t>AS-102040</t>
         </is>
@@ -9972,7 +10065,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J100" s="18" t="n">
+      <c r="J100" s="17" t="n">
         <v>0.7552009</v>
       </c>
       <c r="K100" s="4" t="n">
@@ -9983,7 +10076,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M100" s="19" t="inlineStr">
+      <c r="M100" s="18" t="inlineStr">
         <is>
           <t>AS-102097</t>
         </is>
@@ -10038,7 +10131,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J101" s="18" t="n">
+      <c r="J101" s="17" t="n">
         <v>0.7552009</v>
       </c>
       <c r="K101" s="4" t="n">
@@ -10049,7 +10142,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M101" s="19" t="inlineStr">
+      <c r="M101" s="18" t="inlineStr">
         <is>
           <t>AS-102102</t>
         </is>
@@ -10104,7 +10197,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J102" s="18" t="n">
+      <c r="J102" s="17" t="n">
         <v>0.7552009</v>
       </c>
       <c r="K102" s="4" t="n">
@@ -10115,7 +10208,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M102" s="19" t="inlineStr">
+      <c r="M102" s="18" t="inlineStr">
         <is>
           <t>AS-102184</t>
         </is>
@@ -10170,7 +10263,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J103" s="18" t="n">
+      <c r="J103" s="17" t="n">
         <v>0.7552009</v>
       </c>
       <c r="K103" s="4" t="n">
@@ -10181,7 +10274,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M103" s="19" t="inlineStr">
+      <c r="M103" s="18" t="inlineStr">
         <is>
           <t>AS-102223</t>
         </is>
@@ -10236,7 +10329,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J104" s="18" t="n">
+      <c r="J104" s="17" t="n">
         <v>0.7552009</v>
       </c>
       <c r="K104" s="4" t="n">
@@ -10247,7 +10340,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M104" s="19" t="inlineStr">
+      <c r="M104" s="18" t="inlineStr">
         <is>
           <t>AS-102380</t>
         </is>
@@ -10302,7 +10395,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J105" s="18" t="n">
+      <c r="J105" s="17" t="n">
         <v>0.7552009</v>
       </c>
       <c r="K105" s="4" t="n">
@@ -10313,7 +10406,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M105" s="19" t="inlineStr">
+      <c r="M105" s="18" t="inlineStr">
         <is>
           <t>AS-102423</t>
         </is>
@@ -10368,7 +10461,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J106" s="18" t="n">
+      <c r="J106" s="17" t="n">
         <v>0.7552009</v>
       </c>
       <c r="K106" s="4" t="n">
@@ -10379,7 +10472,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M106" s="19" t="inlineStr">
+      <c r="M106" s="18" t="inlineStr">
         <is>
           <t>AS-102515</t>
         </is>
@@ -10434,7 +10527,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J107" s="18" t="n">
+      <c r="J107" s="17" t="n">
         <v>0.7552009</v>
       </c>
       <c r="K107" s="4" t="n">
@@ -10445,7 +10538,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M107" s="19" t="inlineStr">
+      <c r="M107" s="18" t="inlineStr">
         <is>
           <t>AS-99937</t>
         </is>
@@ -10500,7 +10593,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J108" s="18" t="n">
+      <c r="J108" s="17" t="n">
         <v>0.7552009</v>
       </c>
       <c r="K108" s="4" t="n">
@@ -10511,7 +10604,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M108" s="19" t="inlineStr">
+      <c r="M108" s="18" t="inlineStr">
         <is>
           <t>AS-99977</t>
         </is>
@@ -10566,7 +10659,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J109" s="18" t="n">
+      <c r="J109" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K109" s="4" t="n">
@@ -10577,7 +10670,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M109" s="19" t="inlineStr">
+      <c r="M109" s="18" t="inlineStr">
         <is>
           <t>PCSI2601529</t>
         </is>
@@ -10632,7 +10725,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J110" s="18" t="n">
+      <c r="J110" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K110" s="4" t="n">
@@ -10643,7 +10736,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M110" s="19" t="inlineStr">
+      <c r="M110" s="18" t="inlineStr">
         <is>
           <t>6033972</t>
         </is>
@@ -10698,7 +10791,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J111" s="18" t="n">
+      <c r="J111" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K111" s="4" t="n">
@@ -10709,7 +10802,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M111" s="19" t="inlineStr">
+      <c r="M111" s="18" t="inlineStr">
         <is>
           <t>6033972</t>
         </is>
@@ -10764,7 +10857,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J112" s="18" t="n">
+      <c r="J112" s="17" t="n">
         <v>0.86833</v>
       </c>
       <c r="K112" s="4" t="n">
@@ -10775,7 +10868,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M112" s="19" t="inlineStr">
+      <c r="M112" s="18" t="inlineStr">
         <is>
           <t>RVR-17773</t>
         </is>
@@ -10830,7 +10923,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J113" s="18" t="n">
+      <c r="J113" s="17" t="n">
         <v>0.86833</v>
       </c>
       <c r="K113" s="4" t="n">
@@ -10841,7 +10934,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M113" s="19" t="inlineStr">
+      <c r="M113" s="18" t="inlineStr">
         <is>
           <t>RVR-18638</t>
         </is>
@@ -10884,7 +10977,7 @@
         </is>
       </c>
       <c r="G114" s="4" t="n">
-        <v>318</v>
+        <v>26.5</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
@@ -10896,25 +10989,25 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J114" s="18" t="n">
+      <c r="J114" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K114" s="4" t="n">
-        <v>318</v>
+        <v>26.5</v>
       </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>documents</t>
         </is>
       </c>
-      <c r="M114" s="19" t="inlineStr">
-        <is>
-          <t>INV-0679</t>
+      <c r="M114" s="18" t="inlineStr">
+        <is>
+          <t>INV-0679_PERIODIFICADA_3_12</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/16A1SDk_rnxsIiyKKtVHTvRr2-aF69zlo/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1SwIai4YdtUV-rQd0AKSUEVkEfdlYRoPA/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -10950,7 +11043,7 @@
         </is>
       </c>
       <c r="G115" s="4" t="n">
-        <v>26.5</v>
+        <v>55</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
@@ -10962,25 +11055,25 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J115" s="18" t="n">
+      <c r="J115" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K115" s="4" t="n">
-        <v>26.5</v>
+        <v>55</v>
       </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>documents</t>
         </is>
       </c>
-      <c r="M115" s="19" t="inlineStr">
-        <is>
-          <t>INV-0679_PERIODIFICADA_3_12</t>
+      <c r="M115" s="18" t="inlineStr">
+        <is>
+          <t>INV-0681_PERIODIFICADA_2_12</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1SwIai4YdtUV-rQd0AKSUEVkEfdlYRoPA/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1CFf2KHZd750hPLNp1Xj5DzzQwrKmlw9L/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -11016,7 +11109,7 @@
         </is>
       </c>
       <c r="G116" s="4" t="n">
-        <v>660</v>
+        <v>103.67</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
@@ -11028,32 +11121,32 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J116" s="18" t="n">
+      <c r="J116" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K116" s="4" t="n">
-        <v>660</v>
+        <v>103.67</v>
       </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>documents</t>
         </is>
       </c>
-      <c r="M116" s="19" t="inlineStr">
-        <is>
-          <t>INV-0681</t>
+      <c r="M116" s="18" t="inlineStr">
+        <is>
+          <t>INV-0682_PERIODIFICADA_3_12</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1g-Prp72FPRTBMj-buYbz9LiYUROZ_W5z/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1LlEUQpBPSqkZ5BKsa4CYacg0DVARYbta/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="117" ht="12" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>202603</t>
+          <t>202604</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -11082,7 +11175,7 @@
         </is>
       </c>
       <c r="G117" s="4" t="n">
-        <v>55</v>
+        <v>26.5</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
@@ -11094,32 +11187,32 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J117" s="18" t="n">
+      <c r="J117" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K117" s="4" t="n">
-        <v>55</v>
+        <v>26.5</v>
       </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>documents</t>
         </is>
       </c>
-      <c r="M117" s="19" t="inlineStr">
-        <is>
-          <t>INV-0681_PERIODIFICADA_2_12</t>
+      <c r="M117" s="18" t="inlineStr">
+        <is>
+          <t>INV-0679_PERIODIFICADA_4_12</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1CFf2KHZd750hPLNp1Xj5DzzQwrKmlw9L/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1gDlq6Zum-eIMUjbaI329tWP9UutsRoFn/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="118" ht="12" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>202603</t>
+          <t>202604</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -11148,7 +11241,7 @@
         </is>
       </c>
       <c r="G118" s="4" t="n">
-        <v>1244.04</v>
+        <v>55</v>
       </c>
       <c r="H118" t="inlineStr">
         <is>
@@ -11160,32 +11253,32 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J118" s="18" t="n">
+      <c r="J118" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K118" s="4" t="n">
-        <v>1244.04</v>
+        <v>55</v>
       </c>
       <c r="L118" t="inlineStr">
         <is>
           <t>documents</t>
         </is>
       </c>
-      <c r="M118" s="19" t="inlineStr">
-        <is>
-          <t>INV-0682</t>
+      <c r="M118" s="18" t="inlineStr">
+        <is>
+          <t>INV-0681_PERIODIFICADA_3_12</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1UOaM_TbloubLFPsLoI7t-sLNfHjmGl_M/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1pNcZKxAtFRGUPPAFVD2p8ORXGSCcvxM8/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="119" ht="12" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>202603</t>
+          <t>202604</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -11226,7 +11319,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J119" s="18" t="n">
+      <c r="J119" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K119" s="4" t="n">
@@ -11237,21 +11330,21 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M119" s="19" t="inlineStr">
-        <is>
-          <t>INV-0682_PERIODIFICADA_3_12</t>
+      <c r="M119" s="18" t="inlineStr">
+        <is>
+          <t>INV-0682_PERIODIFICADA_4_12</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1LlEUQpBPSqkZ5BKsa4CYacg0DVARYbta/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1fWIKp9xwGFVs0EnOaVMSISVNLAoKF55J/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="120" ht="12" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>202604</t>
+          <t>202605</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -11292,7 +11385,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J120" s="18" t="n">
+      <c r="J120" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K120" s="4" t="n">
@@ -11303,21 +11396,21 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M120" s="19" t="inlineStr">
-        <is>
-          <t>INV-0679_PERIODIFICADA_4_12</t>
+      <c r="M120" s="18" t="inlineStr">
+        <is>
+          <t>INV-0679_PERIODIFICADA_5_12</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1gDlq6Zum-eIMUjbaI329tWP9UutsRoFn/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1bP1XnXo2Vs8zIS0sVNRvq52xJQH7BSfD/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="121" ht="12" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>202604</t>
+          <t>202605</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -11358,7 +11451,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J121" s="18" t="n">
+      <c r="J121" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K121" s="4" t="n">
@@ -11369,21 +11462,21 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M121" s="19" t="inlineStr">
-        <is>
-          <t>INV-0681_PERIODIFICADA_3_12</t>
+      <c r="M121" s="18" t="inlineStr">
+        <is>
+          <t>INV-0681_PERIODIFICADA_4_12</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1pNcZKxAtFRGUPPAFVD2p8ORXGSCcvxM8/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1ddnzOxZZgaXtVcRqNHeEt9LTz5s8C26J/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="122" ht="12" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>202604</t>
+          <t>202605</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -11424,7 +11517,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J122" s="18" t="n">
+      <c r="J122" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K122" s="4" t="n">
@@ -11435,21 +11528,21 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M122" s="19" t="inlineStr">
-        <is>
-          <t>INV-0682_PERIODIFICADA_4_12</t>
+      <c r="M122" s="18" t="inlineStr">
+        <is>
+          <t>INV-0682_PERIODIFICADA_5_12</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1fWIKp9xwGFVs0EnOaVMSISVNLAoKF55J/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1Z-NJHduArecH7-687SOBbQfa8Ef1m52p/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="123" ht="12" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>202605</t>
+          <t>202606</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -11490,7 +11583,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J123" s="18" t="n">
+      <c r="J123" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K123" s="4" t="n">
@@ -11501,21 +11594,21 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M123" s="19" t="inlineStr">
-        <is>
-          <t>INV-0679_PERIODIFICADA_5_12</t>
+      <c r="M123" s="18" t="inlineStr">
+        <is>
+          <t>INV-0679_PERIODIFICADA_6_12</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1bP1XnXo2Vs8zIS0sVNRvq52xJQH7BSfD/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1I6H1omawcw5Be01IubiDlz8RDBKB0kcd/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="124" ht="12" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>202605</t>
+          <t>202606</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -11556,7 +11649,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J124" s="18" t="n">
+      <c r="J124" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K124" s="4" t="n">
@@ -11567,21 +11660,21 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M124" s="19" t="inlineStr">
-        <is>
-          <t>INV-0681_PERIODIFICADA_4_12</t>
+      <c r="M124" s="18" t="inlineStr">
+        <is>
+          <t>INV-0681_PERIODIFICADA_5_12</t>
         </is>
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1ddnzOxZZgaXtVcRqNHeEt9LTz5s8C26J/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/14VMCuf4u87NNWjcx9C3H2yysZN1jqyTf/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="125" ht="12" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>202605</t>
+          <t>202606</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -11622,7 +11715,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J125" s="18" t="n">
+      <c r="J125" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K125" s="4" t="n">
@@ -11633,21 +11726,21 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M125" s="19" t="inlineStr">
-        <is>
-          <t>INV-0682_PERIODIFICADA_5_12</t>
+      <c r="M125" s="18" t="inlineStr">
+        <is>
+          <t>INV-0682_PERIODIFICADA_6_12</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1Z-NJHduArecH7-687SOBbQfa8Ef1m52p/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1gmWh5ZgXhifus_kfGZ-bL8_sLe8eUug3/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="126" ht="12" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>202606</t>
+          <t>202607</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11688,7 +11781,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J126" s="18" t="n">
+      <c r="J126" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K126" s="4" t="n">
@@ -11699,21 +11792,21 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M126" s="19" t="inlineStr">
-        <is>
-          <t>INV-0679_PERIODIFICADA_6_12</t>
+      <c r="M126" s="18" t="inlineStr">
+        <is>
+          <t>INV-0679_PERIODIFICADA_7_12</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1I6H1omawcw5Be01IubiDlz8RDBKB0kcd/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/17hLMBW75hT4b6Q8RWmnLCnkK6axE-wzU/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="127" ht="12" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>202606</t>
+          <t>202607</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11754,7 +11847,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J127" s="18" t="n">
+      <c r="J127" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K127" s="4" t="n">
@@ -11765,21 +11858,21 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M127" s="19" t="inlineStr">
-        <is>
-          <t>INV-0681_PERIODIFICADA_5_12</t>
+      <c r="M127" s="18" t="inlineStr">
+        <is>
+          <t>INV-0681_PERIODIFICADA_6_12</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/14VMCuf4u87NNWjcx9C3H2yysZN1jqyTf/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1-4m6d0UYjYO2RBrJjkiKAjW12aRalpOJ/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="128" ht="12" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>202606</t>
+          <t>202607</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11820,7 +11913,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J128" s="18" t="n">
+      <c r="J128" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K128" s="4" t="n">
@@ -11831,21 +11924,21 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M128" s="19" t="inlineStr">
-        <is>
-          <t>INV-0682_PERIODIFICADA_6_12</t>
+      <c r="M128" s="18" t="inlineStr">
+        <is>
+          <t>INV-0682_PERIODIFICADA_7_12</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1gmWh5ZgXhifus_kfGZ-bL8_sLe8eUug3/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1c_luteIVUmgrg6i_GlfSo_qh5drW456A/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="129" ht="12" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>202607</t>
+          <t>202608</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11886,7 +11979,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J129" s="18" t="n">
+      <c r="J129" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K129" s="4" t="n">
@@ -11897,21 +11990,21 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M129" s="19" t="inlineStr">
-        <is>
-          <t>INV-0679_PERIODIFICADA_7_12</t>
+      <c r="M129" s="18" t="inlineStr">
+        <is>
+          <t>INV-0679_PERIODIFICADA_8_12</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/17hLMBW75hT4b6Q8RWmnLCnkK6axE-wzU/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/11RmOMn_ZgHdnziLzDS8hsaK7ZIkvkgTY/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="130" ht="12" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>202607</t>
+          <t>202608</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11952,7 +12045,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J130" s="18" t="n">
+      <c r="J130" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K130" s="4" t="n">
@@ -11963,21 +12056,21 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M130" s="19" t="inlineStr">
-        <is>
-          <t>INV-0681_PERIODIFICADA_6_12</t>
+      <c r="M130" s="18" t="inlineStr">
+        <is>
+          <t>INV-0681_PERIODIFICADA_7_12</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1-4m6d0UYjYO2RBrJjkiKAjW12aRalpOJ/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/11RGpKkEMdK77095ybWBCzfeU7QXtAazR/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="131" ht="12" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>202607</t>
+          <t>202608</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -12018,7 +12111,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J131" s="18" t="n">
+      <c r="J131" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K131" s="4" t="n">
@@ -12029,21 +12122,21 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M131" s="19" t="inlineStr">
-        <is>
-          <t>INV-0682_PERIODIFICADA_7_12</t>
+      <c r="M131" s="18" t="inlineStr">
+        <is>
+          <t>INV-0682_PERIODIFICADA_8_12</t>
         </is>
       </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1c_luteIVUmgrg6i_GlfSo_qh5drW456A/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1YItJo27rxIk2KucnIbPWCgV-kg6_TIFw/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="132" ht="12" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>202608</t>
+          <t>202609</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -12084,7 +12177,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J132" s="18" t="n">
+      <c r="J132" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K132" s="4" t="n">
@@ -12095,21 +12188,21 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M132" s="19" t="inlineStr">
-        <is>
-          <t>INV-0679_PERIODIFICADA_8_12</t>
+      <c r="M132" s="18" t="inlineStr">
+        <is>
+          <t>INV-0679_PERIODIFICADA_9_12</t>
         </is>
       </c>
       <c r="N132" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/11RmOMn_ZgHdnziLzDS8hsaK7ZIkvkgTY/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1TiRvkJ6K7ctWCKH70UZtwyVtiBFJcZS3/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="133" ht="12" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>202608</t>
+          <t>202609</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -12150,7 +12243,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J133" s="18" t="n">
+      <c r="J133" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K133" s="4" t="n">
@@ -12161,21 +12254,21 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M133" s="19" t="inlineStr">
-        <is>
-          <t>INV-0681_PERIODIFICADA_7_12</t>
+      <c r="M133" s="18" t="inlineStr">
+        <is>
+          <t>INV-0681_PERIODIFICADA_8_12</t>
         </is>
       </c>
       <c r="N133" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/11RGpKkEMdK77095ybWBCzfeU7QXtAazR/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1TCM1PAyZN1h600czUy8h9Vl6JYkcuBnA/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="134" ht="12" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>202608</t>
+          <t>202609</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -12216,7 +12309,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J134" s="18" t="n">
+      <c r="J134" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K134" s="4" t="n">
@@ -12227,21 +12320,21 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M134" s="19" t="inlineStr">
-        <is>
-          <t>INV-0682_PERIODIFICADA_8_12</t>
+      <c r="M134" s="18" t="inlineStr">
+        <is>
+          <t>INV-0682_PERIODIFICADA_9_12</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1YItJo27rxIk2KucnIbPWCgV-kg6_TIFw/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1j8eIoueeiDvnTZMGmyiF-LMtx0IPr9pM/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="135" ht="12" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>202609</t>
+          <t>202610</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -12282,7 +12375,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J135" s="18" t="n">
+      <c r="J135" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K135" s="4" t="n">
@@ -12293,21 +12386,21 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M135" s="19" t="inlineStr">
-        <is>
-          <t>INV-0679_PERIODIFICADA_9_12</t>
+      <c r="M135" s="18" t="inlineStr">
+        <is>
+          <t>INV-0679_PERIODIFICADA_10_12</t>
         </is>
       </c>
       <c r="N135" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1TiRvkJ6K7ctWCKH70UZtwyVtiBFJcZS3/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1y9fclbPoT1LX8B-Ccm6UQFRfFv51MzCl/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="136" ht="12" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>202609</t>
+          <t>202610</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -12348,7 +12441,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J136" s="18" t="n">
+      <c r="J136" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K136" s="4" t="n">
@@ -12359,21 +12452,21 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M136" s="19" t="inlineStr">
-        <is>
-          <t>INV-0681_PERIODIFICADA_8_12</t>
+      <c r="M136" s="18" t="inlineStr">
+        <is>
+          <t>INV-0681_PERIODIFICADA_9_12</t>
         </is>
       </c>
       <c r="N136" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1TCM1PAyZN1h600czUy8h9Vl6JYkcuBnA/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1F_ojYavt0rOVF-WoA4DILVHACGqB_Xhn/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="137" ht="12" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>202609</t>
+          <t>202610</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -12414,7 +12507,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J137" s="18" t="n">
+      <c r="J137" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K137" s="4" t="n">
@@ -12425,21 +12518,21 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M137" s="19" t="inlineStr">
-        <is>
-          <t>INV-0682_PERIODIFICADA_9_12</t>
+      <c r="M137" s="18" t="inlineStr">
+        <is>
+          <t>INV-0682_PERIODIFICADA_10_12</t>
         </is>
       </c>
       <c r="N137" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1j8eIoueeiDvnTZMGmyiF-LMtx0IPr9pM/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1AB8Xr6NvMGSBv1SkJcKECSxweSG6nBi-/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="138" ht="12" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>202610</t>
+          <t>202611</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -12480,7 +12573,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J138" s="18" t="n">
+      <c r="J138" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K138" s="4" t="n">
@@ -12491,21 +12584,21 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M138" s="19" t="inlineStr">
-        <is>
-          <t>INV-0679_PERIODIFICADA_10_12</t>
+      <c r="M138" s="18" t="inlineStr">
+        <is>
+          <t>INV-0679_PERIODIFICADA_11_12</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1y9fclbPoT1LX8B-Ccm6UQFRfFv51MzCl/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1L3a_vME8SLzq0VCnSYsQFsMpA3aEhGLE/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="139" ht="12" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>202610</t>
+          <t>202611</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -12546,7 +12639,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J139" s="18" t="n">
+      <c r="J139" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K139" s="4" t="n">
@@ -12557,21 +12650,21 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M139" s="19" t="inlineStr">
-        <is>
-          <t>INV-0681_PERIODIFICADA_9_12</t>
+      <c r="M139" s="18" t="inlineStr">
+        <is>
+          <t>INV-0681_PERIODIFICADA_10_12</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1F_ojYavt0rOVF-WoA4DILVHACGqB_Xhn/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1IG_3iLDTE3hoYuVx4M46MqklrzCKpRhc/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="140" ht="12" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>202610</t>
+          <t>202611</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -12612,7 +12705,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J140" s="18" t="n">
+      <c r="J140" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K140" s="4" t="n">
@@ -12623,21 +12716,21 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M140" s="19" t="inlineStr">
-        <is>
-          <t>INV-0682_PERIODIFICADA_10_12</t>
+      <c r="M140" s="18" t="inlineStr">
+        <is>
+          <t>INV-0682_PERIODIFICADA_11_12</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1AB8Xr6NvMGSBv1SkJcKECSxweSG6nBi-/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/11zNwha_ZMtf4Wq3wVF4QzJj4bweWWdGI/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="141" ht="12" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>202611</t>
+          <t>202612</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -12678,7 +12771,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J141" s="18" t="n">
+      <c r="J141" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K141" s="4" t="n">
@@ -12689,21 +12782,21 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M141" s="19" t="inlineStr">
-        <is>
-          <t>INV-0679_PERIODIFICADA_11_12</t>
+      <c r="M141" s="18" t="inlineStr">
+        <is>
+          <t>INV-0679_PERIODIFICADA_12_12</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1L3a_vME8SLzq0VCnSYsQFsMpA3aEhGLE/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1ynEcwwwFHRw_j4UIzVQllup-ekY2huWO/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="142" ht="12" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>202611</t>
+          <t>202612</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12744,7 +12837,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J142" s="18" t="n">
+      <c r="J142" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K142" s="4" t="n">
@@ -12755,21 +12848,21 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M142" s="19" t="inlineStr">
-        <is>
-          <t>INV-0681_PERIODIFICADA_10_12</t>
+      <c r="M142" s="18" t="inlineStr">
+        <is>
+          <t>INV-0681_PERIODIFICADA_11_12</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1IG_3iLDTE3hoYuVx4M46MqklrzCKpRhc/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1RskEVbYtAKWbS4SEumveN8YHrWbIys-_/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="143" ht="12" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>202611</t>
+          <t>202612</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12810,7 +12903,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J143" s="18" t="n">
+      <c r="J143" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K143" s="4" t="n">
@@ -12821,210 +12914,12 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M143" s="19" t="inlineStr">
-        <is>
-          <t>INV-0682_PERIODIFICADA_11_12</t>
+      <c r="M143" s="18" t="inlineStr">
+        <is>
+          <t>INV-0682_PERIODIFICADA_12_12</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/11zNwha_ZMtf4Wq3wVF4QzJj4bweWWdGI/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="144" ht="12" customHeight="1">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>202612</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>LTD</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>opex</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>administration</t>
-        </is>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>YOURACCOUNTSTAXES</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>invoice</t>
-        </is>
-      </c>
-      <c r="G144" s="4" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>GBP</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t>GBP</t>
-        </is>
-      </c>
-      <c r="J144" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="K144" s="4" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="L144" t="inlineStr">
-        <is>
-          <t>documents</t>
-        </is>
-      </c>
-      <c r="M144" s="19" t="inlineStr">
-        <is>
-          <t>INV-0679_PERIODIFICADA_12_12</t>
-        </is>
-      </c>
-      <c r="N144" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1ynEcwwwFHRw_j4UIzVQllup-ekY2huWO/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="145" ht="12" customHeight="1">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>202612</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>LTD</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>opex</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>administration</t>
-        </is>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>YOURACCOUNTSTAXES</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>invoice</t>
-        </is>
-      </c>
-      <c r="G145" s="4" t="n">
-        <v>55</v>
-      </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>GBP</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr">
-        <is>
-          <t>GBP</t>
-        </is>
-      </c>
-      <c r="J145" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="K145" s="4" t="n">
-        <v>55</v>
-      </c>
-      <c r="L145" t="inlineStr">
-        <is>
-          <t>documents</t>
-        </is>
-      </c>
-      <c r="M145" s="19" t="inlineStr">
-        <is>
-          <t>INV-0681_PERIODIFICADA_11_12</t>
-        </is>
-      </c>
-      <c r="N145" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1RskEVbYtAKWbS4SEumveN8YHrWbIys-_/view?usp=drivesdk</t>
-        </is>
-      </c>
-    </row>
-    <row r="146" ht="12" customHeight="1">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>202612</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>LTD</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>opex</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>administration</t>
-        </is>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>YOURACCOUNTSTAXES</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>invoice</t>
-        </is>
-      </c>
-      <c r="G146" s="4" t="n">
-        <v>103.67</v>
-      </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>GBP</t>
-        </is>
-      </c>
-      <c r="I146" t="inlineStr">
-        <is>
-          <t>GBP</t>
-        </is>
-      </c>
-      <c r="J146" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="K146" s="4" t="n">
-        <v>103.67</v>
-      </c>
-      <c r="L146" t="inlineStr">
-        <is>
-          <t>documents</t>
-        </is>
-      </c>
-      <c r="M146" s="19" t="inlineStr">
-        <is>
-          <t>INV-0682_PERIODIFICADA_12_12</t>
-        </is>
-      </c>
-      <c r="N146" t="inlineStr">
         <is>
           <t>https://drive.google.com/file/d/1vPskc5Qm4-Coe1JxTlzp2VdJWX8WiKRm/view?usp=drivesdk</t>
         </is>
@@ -13174,9 +13069,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M141" r:id="rId139"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M142" r:id="rId140"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M143" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M144" r:id="rId142"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M145" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M146" r:id="rId144"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13203,54 +13095,54 @@
   </cols>
   <sheetData>
     <row r="1" ht="12" customHeight="1">
-      <c r="A1" s="16" t="inlineStr">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>&lt;- Volver a P&amp;G-LTD</t>
         </is>
       </c>
     </row>
     <row r="2" ht="12" customHeight="1">
-      <c r="A2" s="17" t="inlineStr">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>yyyymm</t>
         </is>
       </c>
-      <c r="B2" s="17" t="inlineStr">
+      <c r="B2" s="16" t="inlineStr">
         <is>
           <t>entity</t>
         </is>
       </c>
-      <c r="C2" s="17" t="inlineStr">
+      <c r="C2" s="16" t="inlineStr">
         <is>
           <t>supplier_code</t>
         </is>
       </c>
-      <c r="D2" s="17" t="inlineStr">
+      <c r="D2" s="16" t="inlineStr">
         <is>
           <t>amount_original</t>
         </is>
       </c>
-      <c r="E2" s="17" t="inlineStr">
+      <c r="E2" s="16" t="inlineStr">
         <is>
           <t>currency_original</t>
         </is>
       </c>
-      <c r="F2" s="17" t="inlineStr">
+      <c r="F2" s="16" t="inlineStr">
         <is>
           <t>reporting_currency</t>
         </is>
       </c>
-      <c r="G2" s="17" t="inlineStr">
+      <c r="G2" s="16" t="inlineStr">
         <is>
           <t>fx_rate</t>
         </is>
       </c>
-      <c r="H2" s="17" t="inlineStr">
+      <c r="H2" s="16" t="inlineStr">
         <is>
           <t>amount_reporting</t>
         </is>
       </c>
-      <c r="I2" s="17" t="inlineStr">
+      <c r="I2" s="16" t="inlineStr">
         <is>
           <t>source</t>
         </is>
@@ -13285,7 +13177,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="G3" s="18" t="n">
+      <c r="G3" s="17" t="n">
         <v>1</v>
       </c>
       <c r="H3" s="4" t="n">
@@ -13326,7 +13218,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="G4" s="18" t="n">
+      <c r="G4" s="17" t="n">
         <v>1</v>
       </c>
       <c r="H4" s="4" t="n">
@@ -13367,7 +13259,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="G5" s="18" t="n">
+      <c r="G5" s="17" t="n">
         <v>1</v>
       </c>
       <c r="H5" s="4" t="n">
@@ -13396,7 +13288,7 @@
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>20.55</v>
+        <v>35.85</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -13408,11 +13300,11 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="G6" s="18" t="n">
+      <c r="G6" s="17" t="n">
         <v>1</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>20.55</v>
+        <v>35.85</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -13447,44 +13339,44 @@
   </cols>
   <sheetData>
     <row r="1" ht="12" customHeight="1">
-      <c r="A1" s="16" t="inlineStr">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>&lt;- Volver a P&amp;G-LTD</t>
         </is>
       </c>
     </row>
     <row r="2" ht="12" customHeight="1">
-      <c r="A2" s="17" t="inlineStr">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>yyyymm</t>
         </is>
       </c>
-      <c r="B2" s="17" t="inlineStr">
+      <c r="B2" s="16" t="inlineStr">
         <is>
           <t>rate_date</t>
         </is>
       </c>
-      <c r="C2" s="17" t="inlineStr">
+      <c r="C2" s="16" t="inlineStr">
         <is>
           <t>currency_original</t>
         </is>
       </c>
-      <c r="D2" s="17" t="inlineStr">
+      <c r="D2" s="16" t="inlineStr">
         <is>
           <t>reporting_currency</t>
         </is>
       </c>
-      <c r="E2" s="17" t="inlineStr">
+      <c r="E2" s="16" t="inlineStr">
         <is>
           <t>reference_rate</t>
         </is>
       </c>
-      <c r="F2" s="17" t="inlineStr">
+      <c r="F2" s="16" t="inlineStr">
         <is>
           <t>fx_rate</t>
         </is>
       </c>
-      <c r="G2" s="17" t="inlineStr">
+      <c r="G2" s="16" t="inlineStr">
         <is>
           <t>source</t>
         </is>
@@ -13511,10 +13403,10 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="E3" s="18" t="n">
+      <c r="E3" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="F3" s="18" t="n">
+      <c r="F3" s="17" t="n">
         <v>0.8662</v>
       </c>
       <c r="G3" t="inlineStr">
@@ -13544,10 +13436,10 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="E4" s="18" t="n">
+      <c r="E4" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="F4" s="18" t="n">
+      <c r="F4" s="17" t="n">
         <v>1</v>
       </c>
       <c r="G4" t="inlineStr">
@@ -13577,10 +13469,10 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="E5" s="18" t="n">
+      <c r="E5" s="17" t="n">
         <v>1.1919</v>
       </c>
-      <c r="F5" s="18" t="n">
+      <c r="F5" s="17" t="n">
         <v>0.72673882</v>
       </c>
       <c r="G5" t="inlineStr">
@@ -13610,10 +13502,10 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="E6" s="18" t="n">
+      <c r="E6" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="F6" s="18" t="n">
+      <c r="F6" s="17" t="n">
         <v>0.8763</v>
       </c>
       <c r="G6" t="inlineStr">
@@ -13643,10 +13535,10 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="E7" s="18" t="n">
+      <c r="E7" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="F7" s="18" t="n">
+      <c r="F7" s="17" t="n">
         <v>1</v>
       </c>
       <c r="G7" t="inlineStr">
@@ -13676,10 +13568,10 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="E8" s="18" t="n">
+      <c r="E8" s="17" t="n">
         <v>1.1805</v>
       </c>
-      <c r="F8" s="18" t="n">
+      <c r="F8" s="17" t="n">
         <v>0.74231258</v>
       </c>
       <c r="G8" t="inlineStr">
@@ -13709,10 +13601,10 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="E9" s="18" t="n">
+      <c r="E9" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="F9" s="18" t="n">
+      <c r="F9" s="17" t="n">
         <v>0.86833</v>
       </c>
       <c r="G9" t="inlineStr">
@@ -13742,10 +13634,10 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="E10" s="18" t="n">
+      <c r="E10" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="F10" s="18" t="n">
+      <c r="F10" s="17" t="n">
         <v>1</v>
       </c>
       <c r="G10" t="inlineStr">
@@ -13775,10 +13667,10 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="E11" s="18" t="n">
+      <c r="E11" s="17" t="n">
         <v>1.1498</v>
       </c>
-      <c r="F11" s="18" t="n">
+      <c r="F11" s="17" t="n">
         <v>0.7552009</v>
       </c>
       <c r="G11" t="inlineStr">
@@ -13808,10 +13700,10 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="E12" s="18" t="n">
+      <c r="E12" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="F12" s="18" t="n">
+      <c r="F12" s="17" t="n">
         <v>1</v>
       </c>
       <c r="G12" t="inlineStr">
@@ -13841,10 +13733,10 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="E13" s="18" t="n">
+      <c r="E13" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="F13" s="18" t="n">
+      <c r="F13" s="17" t="n">
         <v>1</v>
       </c>
       <c r="G13" t="inlineStr">
@@ -13874,10 +13766,10 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="E14" s="18" t="n">
+      <c r="E14" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="F14" s="18" t="n">
+      <c r="F14" s="17" t="n">
         <v>1</v>
       </c>
       <c r="G14" t="inlineStr">
@@ -13907,10 +13799,10 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="E15" s="18" t="n">
+      <c r="E15" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="F15" s="18" t="n">
+      <c r="F15" s="17" t="n">
         <v>1</v>
       </c>
       <c r="G15" t="inlineStr">
@@ -13940,10 +13832,10 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="E16" s="18" t="n">
+      <c r="E16" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="F16" s="18" t="n">
+      <c r="F16" s="17" t="n">
         <v>1</v>
       </c>
       <c r="G16" t="inlineStr">
@@ -13973,10 +13865,10 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="E17" s="18" t="n">
+      <c r="E17" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="F17" s="18" t="n">
+      <c r="F17" s="17" t="n">
         <v>1</v>
       </c>
       <c r="G17" t="inlineStr">
@@ -14006,10 +13898,10 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="E18" s="18" t="n">
+      <c r="E18" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="F18" s="18" t="n">
+      <c r="F18" s="17" t="n">
         <v>1</v>
       </c>
       <c r="G18" t="inlineStr">
@@ -14039,10 +13931,10 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="E19" s="18" t="n">
+      <c r="E19" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="F19" s="18" t="n">
+      <c r="F19" s="17" t="n">
         <v>1</v>
       </c>
       <c r="G19" t="inlineStr">
@@ -14072,10 +13964,10 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="E20" s="18" t="n">
+      <c r="E20" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="F20" s="18" t="n">
+      <c r="F20" s="17" t="n">
         <v>1</v>
       </c>
       <c r="G20" t="inlineStr">
@@ -14109,34 +14001,34 @@
   </cols>
   <sheetData>
     <row r="1" ht="12" customHeight="1">
-      <c r="A1" s="16" t="inlineStr">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>&lt;- Volver a P&amp;G-LTD</t>
         </is>
       </c>
     </row>
     <row r="2" ht="12" customHeight="1">
-      <c r="A2" s="17" t="inlineStr">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>supplier_code</t>
         </is>
       </c>
-      <c r="B2" s="17" t="inlineStr">
+      <c r="B2" s="16" t="inlineStr">
         <is>
           <t>supplier_name</t>
         </is>
       </c>
-      <c r="C2" s="17" t="inlineStr">
+      <c r="C2" s="16" t="inlineStr">
         <is>
           <t>current_folder</t>
         </is>
       </c>
-      <c r="D2" s="17" t="inlineStr">
+      <c r="D2" s="16" t="inlineStr">
         <is>
           <t>destination_path</t>
         </is>
       </c>
-      <c r="E2" s="17" t="inlineStr">
+      <c r="E2" s="16" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
@@ -14337,7 +14229,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q30"/>
+  <dimension ref="A1:Q31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -14429,7 +14321,7 @@
       </c>
     </row>
     <row r="2" ht="12" customHeight="1">
-      <c r="A2" s="20" t="inlineStr">
+      <c r="A2" s="19" t="inlineStr">
         <is>
           <t>Nº Facturas LTD 2026</t>
         </is>
@@ -14503,151 +14395,151 @@
       </c>
     </row>
     <row r="4" ht="12" customHeight="1">
-      <c r="A4" s="21" t="inlineStr">
+      <c r="A4" s="20" t="inlineStr">
         <is>
           <t>Turnover</t>
         </is>
       </c>
-      <c r="B4" s="22" t="n"/>
-      <c r="C4" s="22" t="n"/>
-      <c r="D4" s="22" t="n">
+      <c r="B4" s="21" t="n"/>
+      <c r="C4" s="21" t="n"/>
+      <c r="D4" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="E4" s="22" t="n">
+      <c r="E4" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="F4" s="22" t="n">
+      <c r="F4" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="G4" s="22" t="n">
+      <c r="G4" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="H4" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" s="22" t="n">
+      <c r="H4" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="Q4" s="22" t="n"/>
+      <c r="Q4" s="21" t="n"/>
     </row>
     <row r="5" ht="12" customHeight="1">
-      <c r="A5" s="23" t="n"/>
-      <c r="B5" s="24" t="inlineStr">
+      <c r="A5" s="22" t="n"/>
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>Product sales</t>
         </is>
       </c>
-      <c r="C5" s="23" t="n"/>
-      <c r="D5" s="23" t="n">
+      <c r="C5" s="22" t="n"/>
+      <c r="D5" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="E5" s="23" t="n">
+      <c r="E5" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="F5" s="23" t="n">
+      <c r="F5" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="G5" s="23" t="n">
+      <c r="G5" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="H5" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" s="23" t="n">
+      <c r="H5" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" s="22" t="n">
         <v>4</v>
       </c>
-      <c r="Q5" s="23" t="n"/>
+      <c r="Q5" s="22" t="n"/>
     </row>
     <row r="6" ht="12" customHeight="1">
-      <c r="A6" s="25" t="n"/>
-      <c r="B6" s="25" t="n"/>
+      <c r="A6" s="24" t="n"/>
+      <c r="B6" s="24" t="n"/>
       <c r="C6" s="9" t="inlineStr">
         <is>
           <t>Shopify</t>
         </is>
       </c>
-      <c r="D6" s="25" t="n">
+      <c r="D6" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="E6" s="25" t="n">
+      <c r="E6" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="F6" s="25" t="n">
+      <c r="F6" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="G6" s="25" t="n">
+      <c r="G6" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="H6" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" s="25" t="n">
+      <c r="H6" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="Q6" s="25" t="n"/>
+      <c r="Q6" s="24" t="n"/>
     </row>
     <row r="7" ht="12" customHeight="1">
       <c r="C7" t="inlineStr">
@@ -14696,262 +14588,265 @@
       </c>
     </row>
     <row r="8" ht="12" customHeight="1">
-      <c r="A8" s="25" t="n"/>
-      <c r="B8" s="9" t="inlineStr">
-        <is>
-          <t>Otros ingresos</t>
-        </is>
-      </c>
-      <c r="C8" s="25" t="n"/>
-      <c r="D8" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="25" t="n"/>
-    </row>
-    <row r="9" ht="12" customHeight="1"/>
-    <row r="10" ht="12" customHeight="1">
-      <c r="A10" s="21" t="inlineStr">
+      <c r="A8" s="22" t="n"/>
+      <c r="B8" s="23" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="n"/>
+      <c r="D8" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="22" t="n"/>
+    </row>
+    <row r="9" ht="12" customHeight="1">
+      <c r="A9" s="24" t="n"/>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>Uncategorized income</t>
+        </is>
+      </c>
+      <c r="C9" s="24" t="n"/>
+      <c r="D9" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="24" t="n"/>
+    </row>
+    <row r="10" ht="12" customHeight="1"/>
+    <row r="11" ht="12" customHeight="1">
+      <c r="A11" s="20" t="inlineStr">
         <is>
           <t>Expenses</t>
         </is>
       </c>
-      <c r="B10" s="22" t="n"/>
-      <c r="C10" s="22" t="n"/>
-      <c r="D10" s="22" t="n">
+      <c r="B11" s="21" t="n"/>
+      <c r="C11" s="21" t="n"/>
+      <c r="D11" s="21" t="n">
         <v>30</v>
       </c>
-      <c r="E10" s="22" t="n">
+      <c r="E11" s="21" t="n">
         <v>36</v>
       </c>
-      <c r="F10" s="22" t="n">
-        <v>54</v>
-      </c>
-      <c r="G10" s="22" t="n">
+      <c r="F11" s="21" t="n">
+        <v>51</v>
+      </c>
+      <c r="G11" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="H10" s="22" t="n">
+      <c r="H11" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="I10" s="22" t="n">
+      <c r="I11" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="J10" s="22" t="n">
+      <c r="J11" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="K10" s="22" t="n">
+      <c r="K11" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="L10" s="22" t="n">
+      <c r="L11" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="M10" s="22" t="n">
+      <c r="M11" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="N10" s="22" t="n">
+      <c r="N11" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="O10" s="22" t="n">
+      <c r="O11" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="P10" s="22" t="n">
-        <v>148</v>
-      </c>
-      <c r="Q10" s="22" t="n"/>
-    </row>
-    <row r="11" ht="12" customHeight="1">
-      <c r="A11" s="23" t="n"/>
-      <c r="B11" s="24" t="inlineStr">
+      <c r="P11" s="21" t="n">
+        <v>145</v>
+      </c>
+      <c r="Q11" s="21" t="n"/>
+    </row>
+    <row r="12" ht="12" customHeight="1">
+      <c r="A12" s="22" t="n"/>
+      <c r="B12" s="23" t="inlineStr">
         <is>
           <t>COGS</t>
         </is>
       </c>
-      <c r="C11" s="23" t="n"/>
-      <c r="D11" s="23" t="n">
+      <c r="C12" s="22" t="n"/>
+      <c r="D12" s="22" t="n">
         <v>27</v>
       </c>
-      <c r="E11" s="23" t="n">
+      <c r="E12" s="22" t="n">
         <v>32</v>
       </c>
-      <c r="F11" s="23" t="n">
+      <c r="F12" s="22" t="n">
         <v>46</v>
       </c>
-      <c r="G11" s="23" t="n">
+      <c r="G12" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="H11" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" s="23" t="n">
+      <c r="H12" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" s="22" t="n">
         <v>106</v>
       </c>
-      <c r="Q11" s="23" t="n"/>
-    </row>
-    <row r="12" ht="12" customHeight="1">
-      <c r="A12" s="25" t="n"/>
-      <c r="B12" s="25" t="n"/>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="Q12" s="22" t="n"/>
+    </row>
+    <row r="13" ht="12" customHeight="1">
+      <c r="A13" s="24" t="n"/>
+      <c r="B13" s="24" t="n"/>
+      <c r="C13" s="9" t="inlineStr">
         <is>
           <t>Manufacturing</t>
         </is>
       </c>
-      <c r="D12" s="25" t="n">
+      <c r="D13" s="24" t="n">
         <v>25</v>
       </c>
-      <c r="E12" s="25" t="n">
+      <c r="E13" s="24" t="n">
         <v>30</v>
       </c>
-      <c r="F12" s="25" t="n">
+      <c r="F13" s="24" t="n">
         <v>43</v>
       </c>
-      <c r="G12" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" s="25" t="n">
+      <c r="G13" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" s="24" t="n">
         <v>98</v>
       </c>
-      <c r="Q12" s="25" t="n"/>
-    </row>
-    <row r="13" ht="12" customHeight="1">
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>ARTLINK</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q13" s="24" t="n"/>
     </row>
     <row r="14" ht="12" customHeight="1">
       <c r="C14" t="inlineStr">
         <is>
-          <t>JONDO</t>
+          <t>ARTLINK</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -14981,161 +14876,161 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" ht="12" customHeight="1">
       <c r="C15" t="inlineStr">
         <is>
+          <t>JONDO</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>24</v>
+      </c>
+      <c r="E15" t="n">
+        <v>29</v>
+      </c>
+      <c r="F15" t="n">
+        <v>42</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="16" ht="12" customHeight="1">
+      <c r="C16" t="inlineStr">
+        <is>
           <t>PROCO</t>
         </is>
       </c>
-      <c r="D15" t="n">
+      <c r="D16" t="n">
         <v>1</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E16" t="n">
         <v>1</v>
       </c>
-      <c r="F15" t="n">
+      <c r="F16" t="n">
         <v>1</v>
       </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="16" ht="12" customHeight="1">
-      <c r="A16" s="25" t="n"/>
-      <c r="B16" s="25" t="n"/>
-      <c r="C16" s="9" t="inlineStr">
+    <row r="17" ht="12" customHeight="1">
+      <c r="A17" s="24" t="n"/>
+      <c r="B17" s="24" t="n"/>
+      <c r="C17" s="9" t="inlineStr">
         <is>
           <t>Logistics</t>
         </is>
       </c>
-      <c r="D16" s="25" t="n">
+      <c r="D17" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="E16" s="25" t="n">
+      <c r="E17" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="F16" s="25" t="n">
+      <c r="F17" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="G16" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" s="25" t="n">
+      <c r="G17" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="Q16" s="25" t="n"/>
-    </row>
-    <row r="17" ht="12" customHeight="1">
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>PROCO</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E17" t="n">
-        <v>1</v>
-      </c>
-      <c r="F17" t="n">
-        <v>1</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>3</v>
-      </c>
+      <c r="Q17" s="24" t="n"/>
     </row>
     <row r="18" ht="12" customHeight="1">
       <c r="C18" t="inlineStr">
         <is>
-          <t>PORTCLEARANCE</t>
+          <t>PROCO</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F18" t="n">
         <v>1</v>
@@ -15168,536 +15063,582 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" ht="12" customHeight="1">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>PORTCLEARANCE</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="19" ht="12" customHeight="1">
-      <c r="A19" s="25" t="n"/>
-      <c r="B19" s="25" t="n"/>
-      <c r="C19" s="9" t="inlineStr">
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" ht="12" customHeight="1">
+      <c r="A20" s="24" t="n"/>
+      <c r="B20" s="24" t="n"/>
+      <c r="C20" s="9" t="inlineStr">
         <is>
           <t>Payment fees</t>
         </is>
       </c>
-      <c r="D19" s="25" t="n">
+      <c r="D20" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="E19" s="25" t="n">
+      <c r="E20" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="F19" s="25" t="n">
+      <c r="F20" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="G19" s="25" t="n">
+      <c r="G20" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="H19" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" s="25" t="n">
+      <c r="H20" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="Q19" s="25" t="n"/>
-    </row>
-    <row r="20" ht="12" customHeight="1">
-      <c r="C20" t="inlineStr">
+      <c r="Q20" s="24" t="n"/>
+    </row>
+    <row r="21" ht="12" customHeight="1">
+      <c r="C21" t="inlineStr">
         <is>
           <t>SHOPIFY</t>
         </is>
       </c>
-      <c r="D20" t="n">
+      <c r="D21" t="n">
         <v>1</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E21" t="n">
         <v>1</v>
       </c>
-      <c r="F20" t="n">
+      <c r="F21" t="n">
         <v>1</v>
       </c>
-      <c r="G20" t="n">
+      <c r="G21" t="n">
         <v>1</v>
       </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="21" ht="12" customHeight="1"/>
-    <row r="22" ht="12" customHeight="1">
-      <c r="A22" s="23" t="n"/>
-      <c r="B22" s="24" t="inlineStr">
+    <row r="22" ht="12" customHeight="1"/>
+    <row r="23" ht="12" customHeight="1">
+      <c r="A23" s="22" t="n"/>
+      <c r="B23" s="23" t="inlineStr">
         <is>
           <t>Opex</t>
         </is>
       </c>
-      <c r="C22" s="23" t="n"/>
-      <c r="D22" s="23" t="n">
+      <c r="C23" s="22" t="n"/>
+      <c r="D23" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="E22" s="23" t="n">
+      <c r="E23" s="22" t="n">
         <v>4</v>
       </c>
-      <c r="F22" s="23" t="n">
-        <v>8</v>
-      </c>
-      <c r="G22" s="23" t="n">
+      <c r="F23" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="G23" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="H22" s="23" t="n">
+      <c r="H23" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="I22" s="23" t="n">
+      <c r="I23" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="J22" s="23" t="n">
+      <c r="J23" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="K22" s="23" t="n">
+      <c r="K23" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="L22" s="23" t="n">
+      <c r="L23" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="M22" s="23" t="n">
+      <c r="M23" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="N22" s="23" t="n">
+      <c r="N23" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="O22" s="23" t="n">
+      <c r="O23" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="P22" s="23" t="n">
-        <v>42</v>
-      </c>
-      <c r="Q22" s="23" t="n"/>
-    </row>
-    <row r="23" ht="12" customHeight="1">
-      <c r="A23" s="25" t="n"/>
-      <c r="B23" s="25" t="n"/>
-      <c r="C23" s="9" t="inlineStr">
+      <c r="P23" s="22" t="n">
+        <v>39</v>
+      </c>
+      <c r="Q23" s="22" t="n"/>
+    </row>
+    <row r="24" ht="12" customHeight="1">
+      <c r="A24" s="24" t="n"/>
+      <c r="B24" s="24" t="n"/>
+      <c r="C24" s="9" t="inlineStr">
         <is>
           <t>Shared services</t>
         </is>
       </c>
-      <c r="D23" s="25" t="n">
+      <c r="D24" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="E23" s="25" t="n">
+      <c r="E24" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="F23" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" s="25" t="n">
+      <c r="F24" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="Q23" s="25" t="n"/>
-    </row>
-    <row r="24" ht="12" customHeight="1">
-      <c r="C24" t="inlineStr">
+      <c r="Q24" s="24" t="n"/>
+    </row>
+    <row r="25" ht="12" customHeight="1">
+      <c r="C25" t="inlineStr">
         <is>
           <t>SHAREDSERVICESSL</t>
         </is>
       </c>
-      <c r="D24" t="n">
+      <c r="D25" t="n">
         <v>1</v>
       </c>
-      <c r="E24" t="n">
+      <c r="E25" t="n">
         <v>1</v>
       </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="25" ht="12" customHeight="1">
-      <c r="A25" s="25" t="n"/>
-      <c r="B25" s="25" t="n"/>
-      <c r="C25" s="9" t="inlineStr">
+    <row r="26" ht="12" customHeight="1">
+      <c r="A26" s="24" t="n"/>
+      <c r="B26" s="24" t="n"/>
+      <c r="C26" s="9" t="inlineStr">
         <is>
           <t>Administration</t>
         </is>
       </c>
-      <c r="D25" s="25" t="n">
+      <c r="D26" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="E25" s="25" t="n">
+      <c r="E26" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="F25" s="25" t="n">
-        <v>6</v>
-      </c>
-      <c r="G25" s="25" t="n">
+      <c r="F26" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="H25" s="25" t="n">
+      <c r="G26" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="I25" s="25" t="n">
+      <c r="H26" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="J25" s="25" t="n">
+      <c r="I26" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="K25" s="25" t="n">
+      <c r="J26" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="L25" s="25" t="n">
+      <c r="K26" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="M25" s="25" t="n">
+      <c r="L26" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="N25" s="25" t="n">
+      <c r="M26" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="O25" s="25" t="n">
+      <c r="N26" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="P25" s="25" t="n">
-        <v>38</v>
-      </c>
-      <c r="Q25" s="25" t="n"/>
-    </row>
-    <row r="26" ht="12" customHeight="1">
-      <c r="C26" t="inlineStr">
+      <c r="O26" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="P26" s="24" t="n">
+        <v>35</v>
+      </c>
+      <c r="Q26" s="24" t="n"/>
+    </row>
+    <row r="27" ht="12" customHeight="1">
+      <c r="C27" t="inlineStr">
         <is>
           <t>YOURACCOUNTSTAXES</t>
         </is>
       </c>
-      <c r="D26" t="n">
+      <c r="D27" t="n">
         <v>2</v>
       </c>
-      <c r="E26" t="n">
+      <c r="E27" t="n">
         <v>3</v>
       </c>
-      <c r="F26" t="n">
-        <v>6</v>
-      </c>
-      <c r="G26" t="n">
+      <c r="F27" t="n">
         <v>3</v>
       </c>
-      <c r="H26" t="n">
+      <c r="G27" t="n">
         <v>3</v>
       </c>
-      <c r="I26" t="n">
+      <c r="H27" t="n">
         <v>3</v>
       </c>
-      <c r="J26" t="n">
+      <c r="I27" t="n">
         <v>3</v>
       </c>
-      <c r="K26" t="n">
+      <c r="J27" t="n">
         <v>3</v>
       </c>
-      <c r="L26" t="n">
+      <c r="K27" t="n">
         <v>3</v>
       </c>
-      <c r="M26" t="n">
+      <c r="L27" t="n">
         <v>3</v>
       </c>
-      <c r="N26" t="n">
+      <c r="M27" t="n">
         <v>3</v>
       </c>
-      <c r="O26" t="n">
+      <c r="N27" t="n">
         <v>3</v>
       </c>
-      <c r="P26" t="n">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="27" ht="12" customHeight="1">
-      <c r="A27" s="25" t="n"/>
-      <c r="B27" s="25" t="n"/>
-      <c r="C27" s="9" t="inlineStr">
+      <c r="O27" t="n">
+        <v>3</v>
+      </c>
+      <c r="P27" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="28" ht="12" customHeight="1">
+      <c r="A28" s="24" t="n"/>
+      <c r="B28" s="24" t="n"/>
+      <c r="C28" s="9" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
       </c>
-      <c r="D27" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" s="25" t="n">
+      <c r="D28" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="G27" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" s="25" t="n">
+      <c r="G28" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="Q27" s="25" t="n"/>
-    </row>
-    <row r="28" ht="12" customHeight="1">
-      <c r="C28" t="inlineStr">
+      <c r="Q28" s="24" t="n"/>
+    </row>
+    <row r="29" ht="12" customHeight="1">
+      <c r="C29" t="inlineStr">
         <is>
           <t>REVER</t>
         </is>
       </c>
-      <c r="D28" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" t="n">
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
         <v>2</v>
       </c>
-      <c r="G28" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="29" ht="12" customHeight="1">
-      <c r="A29" s="25" t="n"/>
-      <c r="B29" s="25" t="n"/>
-      <c r="C29" s="9" t="inlineStr">
-        <is>
-          <t>Otros gastos</t>
-        </is>
-      </c>
-      <c r="D29" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" s="25" t="n"/>
-    </row>
     <row r="30" ht="12" customHeight="1">
-      <c r="A30" s="25" t="n"/>
-      <c r="B30" s="9" t="inlineStr">
-        <is>
-          <t>Diferencias divisas</t>
-        </is>
-      </c>
-      <c r="C30" s="25" t="n"/>
-      <c r="D30" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" s="25" t="n"/>
+      <c r="A30" s="24" t="n"/>
+      <c r="B30" s="24" t="n"/>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>Uncategorized Expenses</t>
+        </is>
+      </c>
+      <c r="D30" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="24" t="n"/>
+    </row>
+    <row r="31" ht="12" customHeight="1">
+      <c r="A31" s="24" t="n"/>
+      <c r="B31" s="9" t="inlineStr">
+        <is>
+          <t>Currency Adjustment</t>
+        </is>
+      </c>
+      <c r="C31" s="24" t="n"/>
+      <c r="D31" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="24" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/output/spreadsheet/pyg_ltd_2026.xlsx
+++ b/output/spreadsheet/pyg_ltd_2026.xlsx
@@ -28,7 +28,7 @@
     <numFmt numFmtId="165" formatCode="0.00000000"/>
     <numFmt numFmtId="166" formatCode="0.0%;[Red](0.0%);-"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -52,6 +52,9 @@
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <color rgb="00666666"/>
     </font>
     <font>
       <b val="1"/>
@@ -119,9 +122,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -138,15 +141,16 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -521,7 +525,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q47"/>
+  <dimension ref="A1:Q48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -692,7 +696,7 @@
     <row r="3" ht="12" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Actualizado: 04/04/2026 12:00 h</t>
+          <t>Actualizado: 10/04/2026 11:48 h</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -1122,51 +1126,51 @@
       <c r="B11" s="6" t="n"/>
       <c r="C11" s="6" t="n"/>
       <c r="D11" s="6">
-        <f>D12+D33</f>
+        <f>D12+D34</f>
         <v/>
       </c>
       <c r="E11" s="6">
-        <f>E12+E33</f>
+        <f>E12+E34</f>
         <v/>
       </c>
       <c r="F11" s="6">
-        <f>F12+F33</f>
+        <f>F12+F34</f>
         <v/>
       </c>
       <c r="G11" s="6">
-        <f>G12+G33</f>
+        <f>G12+G34</f>
         <v/>
       </c>
       <c r="H11" s="6">
-        <f>H12+H33</f>
+        <f>H12+H34</f>
         <v/>
       </c>
       <c r="I11" s="6">
-        <f>I12+I33</f>
+        <f>I12+I34</f>
         <v/>
       </c>
       <c r="J11" s="6">
-        <f>J12+J33</f>
+        <f>J12+J34</f>
         <v/>
       </c>
       <c r="K11" s="6">
-        <f>K12+K33</f>
+        <f>K12+K34</f>
         <v/>
       </c>
       <c r="L11" s="6">
-        <f>L12+L33</f>
+        <f>L12+L34</f>
         <v/>
       </c>
       <c r="M11" s="6">
-        <f>M12+M33</f>
+        <f>M12+M34</f>
         <v/>
       </c>
       <c r="N11" s="6">
-        <f>N12+N33</f>
+        <f>N12+N34</f>
         <v/>
       </c>
       <c r="O11" s="6">
-        <f>O12+O33</f>
+        <f>O12+O34</f>
         <v/>
       </c>
       <c r="P11" s="6">
@@ -1511,7 +1515,7 @@
         <v>2181.65</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>67.65000000000001</v>
+        <v>284.82</v>
       </c>
       <c r="H17" s="4" t="n"/>
       <c r="I17" s="4" t="n"/>
@@ -1978,11 +1982,22 @@
       </c>
     </row>
     <row r="25" ht="12" customHeight="1">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Royalties</t>
+        </is>
+      </c>
       <c r="B25" s="4" t="n"/>
       <c r="C25" s="4" t="n"/>
-      <c r="D25" s="4" t="n"/>
-      <c r="E25" s="4" t="n"/>
-      <c r="F25" s="4" t="n"/>
+      <c r="D25" s="4" t="n">
+        <v>1101.81</v>
+      </c>
+      <c r="E25" s="4" t="n">
+        <v>1398.57</v>
+      </c>
+      <c r="F25" s="4" t="n">
+        <v>1682.82</v>
+      </c>
       <c r="G25" s="4" t="n"/>
       <c r="H25" s="4" t="n"/>
       <c r="I25" s="4" t="n"/>
@@ -1998,877 +2013,832 @@
       </c>
       <c r="Q25" s="4" t="n"/>
     </row>
-    <row r="26" hidden="1" outlineLevel="2" ht="12" customHeight="1">
-      <c r="A26" s="3" t="inlineStr">
+    <row r="26" ht="12" customHeight="1">
+      <c r="B26" s="4" t="n"/>
+      <c r="C26" s="4" t="n"/>
+      <c r="D26" s="4" t="n"/>
+      <c r="E26" s="4" t="n"/>
+      <c r="F26" s="4" t="n"/>
+      <c r="G26" s="4" t="n"/>
+      <c r="H26" s="4" t="n"/>
+      <c r="I26" s="4" t="n"/>
+      <c r="J26" s="4" t="n"/>
+      <c r="K26" s="4" t="n"/>
+      <c r="L26" s="4" t="n"/>
+      <c r="M26" s="4" t="n"/>
+      <c r="N26" s="4" t="n"/>
+      <c r="O26" s="4" t="n"/>
+      <c r="P26" s="4">
+        <f>SUM(D26:O26)</f>
+        <v/>
+      </c>
+      <c r="Q26" s="4" t="n"/>
+    </row>
+    <row r="27" hidden="1" outlineLevel="2" ht="12" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">    % Payment fees / sales</t>
         </is>
       </c>
-      <c r="B26" s="11" t="n"/>
-      <c r="C26" s="11" t="n"/>
-      <c r="D26" s="11">
+      <c r="B27" s="11" t="n"/>
+      <c r="C27" s="11" t="n"/>
+      <c r="D27" s="11">
         <f>IFERROR(D23/D5,0)</f>
         <v/>
       </c>
-      <c r="E26" s="11">
+      <c r="E27" s="11">
         <f>IFERROR(E23/E5,0)</f>
         <v/>
       </c>
-      <c r="F26" s="11">
+      <c r="F27" s="11">
         <f>IFERROR(F23/F5,0)</f>
         <v/>
       </c>
-      <c r="G26" s="11">
+      <c r="G27" s="11">
         <f>IFERROR(G23/G5,0)</f>
         <v/>
       </c>
-      <c r="H26" s="11">
+      <c r="H27" s="11">
         <f>IFERROR(H23/H5,0)</f>
         <v/>
       </c>
-      <c r="I26" s="11">
+      <c r="I27" s="11">
         <f>IFERROR(I23/I5,0)</f>
         <v/>
       </c>
-      <c r="J26" s="11">
+      <c r="J27" s="11">
         <f>IFERROR(J23/J5,0)</f>
         <v/>
       </c>
-      <c r="K26" s="11">
+      <c r="K27" s="11">
         <f>IFERROR(K23/K5,0)</f>
         <v/>
       </c>
-      <c r="L26" s="11">
+      <c r="L27" s="11">
         <f>IFERROR(L23/L5,0)</f>
         <v/>
       </c>
-      <c r="M26" s="11">
+      <c r="M27" s="11">
         <f>IFERROR(M23/M5,0)</f>
         <v/>
       </c>
-      <c r="N26" s="11">
+      <c r="N27" s="11">
         <f>IFERROR(N23/N5,0)</f>
         <v/>
       </c>
-      <c r="O26" s="11">
+      <c r="O27" s="11">
         <f>IFERROR(O23/O5,0)</f>
         <v/>
       </c>
-      <c r="P26" s="11">
+      <c r="P27" s="11">
         <f>IFERROR(P23/P5,0)</f>
         <v/>
       </c>
-      <c r="Q26" s="11" t="n"/>
-    </row>
-    <row r="27" ht="12" customHeight="1">
-      <c r="B27" s="4" t="n"/>
-      <c r="C27" s="4" t="n"/>
-      <c r="D27" s="4" t="n"/>
-      <c r="E27" s="4" t="n"/>
-      <c r="F27" s="4" t="n"/>
-      <c r="G27" s="4" t="n"/>
-      <c r="H27" s="4" t="n"/>
-      <c r="I27" s="4" t="n"/>
-      <c r="J27" s="4" t="n"/>
-      <c r="K27" s="4" t="n"/>
-      <c r="L27" s="4" t="n"/>
-      <c r="M27" s="4" t="n"/>
-      <c r="N27" s="4" t="n"/>
-      <c r="O27" s="4" t="n"/>
-      <c r="P27" s="4">
-        <f>SUM(D27:O27)</f>
-        <v/>
-      </c>
-      <c r="Q27" s="4" t="n"/>
+      <c r="Q27" s="11" t="n"/>
     </row>
     <row r="28" ht="12" customHeight="1">
-      <c r="A28" s="12" t="inlineStr">
+      <c r="B28" s="4" t="n"/>
+      <c r="C28" s="4" t="n"/>
+      <c r="D28" s="4" t="n"/>
+      <c r="E28" s="4" t="n"/>
+      <c r="F28" s="4" t="n"/>
+      <c r="G28" s="4" t="n"/>
+      <c r="H28" s="4" t="n"/>
+      <c r="I28" s="4" t="n"/>
+      <c r="J28" s="4" t="n"/>
+      <c r="K28" s="4" t="n"/>
+      <c r="L28" s="4" t="n"/>
+      <c r="M28" s="4" t="n"/>
+      <c r="N28" s="4" t="n"/>
+      <c r="O28" s="4" t="n"/>
+      <c r="P28" s="4">
+        <f>SUM(D28:O28)</f>
+        <v/>
+      </c>
+      <c r="Q28" s="4" t="n"/>
+    </row>
+    <row r="29" ht="12" customHeight="1">
+      <c r="A29" s="13" t="inlineStr">
         <is>
           <t>GROSS MARGIN (SALES-MANUFACTURING)</t>
         </is>
       </c>
-      <c r="B28" s="13" t="n"/>
-      <c r="C28" s="13" t="n"/>
-      <c r="D28" s="13">
+      <c r="B29" s="14" t="n"/>
+      <c r="C29" s="14" t="n"/>
+      <c r="D29" s="14">
         <f>D5-D13</f>
         <v/>
       </c>
-      <c r="E28" s="13">
+      <c r="E29" s="14">
         <f>E5-E13</f>
         <v/>
       </c>
-      <c r="F28" s="13">
+      <c r="F29" s="14">
         <f>F5-F13</f>
         <v/>
       </c>
-      <c r="G28" s="13">
+      <c r="G29" s="14">
         <f>G5-G13</f>
         <v/>
       </c>
-      <c r="H28" s="13">
+      <c r="H29" s="14">
         <f>H5-H13</f>
         <v/>
       </c>
-      <c r="I28" s="13">
+      <c r="I29" s="14">
         <f>I5-I13</f>
         <v/>
       </c>
-      <c r="J28" s="13">
+      <c r="J29" s="14">
         <f>J5-J13</f>
         <v/>
       </c>
-      <c r="K28" s="13">
+      <c r="K29" s="14">
         <f>K5-K13</f>
         <v/>
       </c>
-      <c r="L28" s="13">
+      <c r="L29" s="14">
         <f>L5-L13</f>
         <v/>
       </c>
-      <c r="M28" s="13">
+      <c r="M29" s="14">
         <f>M5-M13</f>
         <v/>
       </c>
-      <c r="N28" s="13">
+      <c r="N29" s="14">
         <f>N5-N13</f>
         <v/>
       </c>
-      <c r="O28" s="13">
+      <c r="O29" s="14">
         <f>O5-O13</f>
         <v/>
       </c>
-      <c r="P28" s="13">
-        <f>SUM(D28:O28)</f>
-        <v/>
-      </c>
-      <c r="Q28" s="13" t="n"/>
-    </row>
-    <row r="29" hidden="1" outlineLevel="1" ht="12" customHeight="1">
-      <c r="A29" s="3" t="inlineStr">
+      <c r="P29" s="14">
+        <f>SUM(D29:O29)</f>
+        <v/>
+      </c>
+      <c r="Q29" s="14" t="n"/>
+    </row>
+    <row r="30" hidden="1" outlineLevel="1" ht="12" customHeight="1">
+      <c r="A30" s="3" t="inlineStr">
         <is>
           <t>% gross margin</t>
         </is>
       </c>
-      <c r="B29" s="11" t="n"/>
-      <c r="C29" s="11" t="n"/>
-      <c r="D29" s="11">
-        <f>IFERROR(D28/D5,0)</f>
-        <v/>
-      </c>
-      <c r="E29" s="11">
-        <f>IFERROR(E28/E5,0)</f>
-        <v/>
-      </c>
-      <c r="F29" s="11">
-        <f>IFERROR(F28/F5,0)</f>
-        <v/>
-      </c>
-      <c r="G29" s="11">
-        <f>IFERROR(G28/G5,0)</f>
-        <v/>
-      </c>
-      <c r="H29" s="11">
-        <f>IFERROR(H28/H5,0)</f>
-        <v/>
-      </c>
-      <c r="I29" s="11">
-        <f>IFERROR(I28/I5,0)</f>
-        <v/>
-      </c>
-      <c r="J29" s="11">
-        <f>IFERROR(J28/J5,0)</f>
-        <v/>
-      </c>
-      <c r="K29" s="11">
-        <f>IFERROR(K28/K5,0)</f>
-        <v/>
-      </c>
-      <c r="L29" s="11">
-        <f>IFERROR(L28/L5,0)</f>
-        <v/>
-      </c>
-      <c r="M29" s="11">
-        <f>IFERROR(M28/M5,0)</f>
-        <v/>
-      </c>
-      <c r="N29" s="11">
-        <f>IFERROR(N28/N5,0)</f>
-        <v/>
-      </c>
-      <c r="O29" s="11">
-        <f>IFERROR(O28/O5,0)</f>
-        <v/>
-      </c>
-      <c r="P29" s="11">
-        <f>IFERROR(P28/P5,0)</f>
-        <v/>
-      </c>
-      <c r="Q29" s="11" t="n"/>
-    </row>
-    <row r="30" ht="12" customHeight="1">
-      <c r="A30" s="12" t="inlineStr">
+      <c r="B30" s="11" t="n"/>
+      <c r="C30" s="11" t="n"/>
+      <c r="D30" s="11">
+        <f>IFERROR(D29/D5,0)</f>
+        <v/>
+      </c>
+      <c r="E30" s="11">
+        <f>IFERROR(E29/E5,0)</f>
+        <v/>
+      </c>
+      <c r="F30" s="11">
+        <f>IFERROR(F29/F5,0)</f>
+        <v/>
+      </c>
+      <c r="G30" s="11">
+        <f>IFERROR(G29/G5,0)</f>
+        <v/>
+      </c>
+      <c r="H30" s="11">
+        <f>IFERROR(H29/H5,0)</f>
+        <v/>
+      </c>
+      <c r="I30" s="11">
+        <f>IFERROR(I29/I5,0)</f>
+        <v/>
+      </c>
+      <c r="J30" s="11">
+        <f>IFERROR(J29/J5,0)</f>
+        <v/>
+      </c>
+      <c r="K30" s="11">
+        <f>IFERROR(K29/K5,0)</f>
+        <v/>
+      </c>
+      <c r="L30" s="11">
+        <f>IFERROR(L29/L5,0)</f>
+        <v/>
+      </c>
+      <c r="M30" s="11">
+        <f>IFERROR(M29/M5,0)</f>
+        <v/>
+      </c>
+      <c r="N30" s="11">
+        <f>IFERROR(N29/N5,0)</f>
+        <v/>
+      </c>
+      <c r="O30" s="11">
+        <f>IFERROR(O29/O5,0)</f>
+        <v/>
+      </c>
+      <c r="P30" s="11">
+        <f>IFERROR(P29/P5,0)</f>
+        <v/>
+      </c>
+      <c r="Q30" s="11" t="n"/>
+    </row>
+    <row r="31" ht="12" customHeight="1">
+      <c r="A31" s="13" t="inlineStr">
         <is>
           <t>Contributive margin (product sales-COGS)</t>
         </is>
       </c>
-      <c r="B30" s="13" t="n"/>
-      <c r="C30" s="13" t="n"/>
-      <c r="D30" s="13">
-        <f>D5-D12</f>
-        <v/>
-      </c>
-      <c r="E30" s="13">
-        <f>E5-E12</f>
-        <v/>
-      </c>
-      <c r="F30" s="13">
-        <f>F5-F12</f>
-        <v/>
-      </c>
-      <c r="G30" s="13">
-        <f>G5-G12</f>
-        <v/>
-      </c>
-      <c r="H30" s="13">
-        <f>H5-H12</f>
-        <v/>
-      </c>
-      <c r="I30" s="13">
-        <f>I5-I12</f>
-        <v/>
-      </c>
-      <c r="J30" s="13">
-        <f>J5-J12</f>
-        <v/>
-      </c>
-      <c r="K30" s="13">
-        <f>K5-K12</f>
-        <v/>
-      </c>
-      <c r="L30" s="13">
-        <f>L5-L12</f>
-        <v/>
-      </c>
-      <c r="M30" s="13">
-        <f>M5-M12</f>
-        <v/>
-      </c>
-      <c r="N30" s="13">
-        <f>N5-N12</f>
-        <v/>
-      </c>
-      <c r="O30" s="13">
-        <f>O5-O12</f>
-        <v/>
-      </c>
-      <c r="P30" s="13">
-        <f>SUM(D30:O30)</f>
-        <v/>
-      </c>
-      <c r="Q30" s="13" t="n"/>
-    </row>
-    <row r="31" hidden="1" outlineLevel="1" ht="12" customHeight="1">
-      <c r="A31" s="3" t="inlineStr">
+      <c r="B31" s="14" t="n"/>
+      <c r="C31" s="14" t="n"/>
+      <c r="D31" s="14">
+        <f>D5-D12-D25</f>
+        <v/>
+      </c>
+      <c r="E31" s="14">
+        <f>E5-E12-E25</f>
+        <v/>
+      </c>
+      <c r="F31" s="14">
+        <f>F5-F12-F25</f>
+        <v/>
+      </c>
+      <c r="G31" s="14">
+        <f>G5-G12-G25</f>
+        <v/>
+      </c>
+      <c r="H31" s="14">
+        <f>H5-H12-H25</f>
+        <v/>
+      </c>
+      <c r="I31" s="14">
+        <f>I5-I12-I25</f>
+        <v/>
+      </c>
+      <c r="J31" s="14">
+        <f>J5-J12-J25</f>
+        <v/>
+      </c>
+      <c r="K31" s="14">
+        <f>K5-K12-K25</f>
+        <v/>
+      </c>
+      <c r="L31" s="14">
+        <f>L5-L12-L25</f>
+        <v/>
+      </c>
+      <c r="M31" s="14">
+        <f>M5-M12-M25</f>
+        <v/>
+      </c>
+      <c r="N31" s="14">
+        <f>N5-N12-N25</f>
+        <v/>
+      </c>
+      <c r="O31" s="14">
+        <f>O5-O12-O25</f>
+        <v/>
+      </c>
+      <c r="P31" s="14">
+        <f>SUM(D31:O31)</f>
+        <v/>
+      </c>
+      <c r="Q31" s="14" t="n"/>
+    </row>
+    <row r="32" hidden="1" outlineLevel="1" ht="12" customHeight="1">
+      <c r="A32" s="3" t="inlineStr">
         <is>
           <t>% contributive margin</t>
         </is>
       </c>
-      <c r="B31" s="11" t="n"/>
-      <c r="C31" s="11" t="n"/>
-      <c r="D31" s="11">
-        <f>IFERROR(D30/D5,0)</f>
-        <v/>
-      </c>
-      <c r="E31" s="11">
-        <f>IFERROR(E30/E5,0)</f>
-        <v/>
-      </c>
-      <c r="F31" s="11">
-        <f>IFERROR(F30/F5,0)</f>
-        <v/>
-      </c>
-      <c r="G31" s="11">
-        <f>IFERROR(G30/G5,0)</f>
-        <v/>
-      </c>
-      <c r="H31" s="11">
-        <f>IFERROR(H30/H5,0)</f>
-        <v/>
-      </c>
-      <c r="I31" s="11">
-        <f>IFERROR(I30/I5,0)</f>
-        <v/>
-      </c>
-      <c r="J31" s="11">
-        <f>IFERROR(J30/J5,0)</f>
-        <v/>
-      </c>
-      <c r="K31" s="11">
-        <f>IFERROR(K30/K5,0)</f>
-        <v/>
-      </c>
-      <c r="L31" s="11">
-        <f>IFERROR(L30/L5,0)</f>
-        <v/>
-      </c>
-      <c r="M31" s="11">
-        <f>IFERROR(M30/M5,0)</f>
-        <v/>
-      </c>
-      <c r="N31" s="11">
-        <f>IFERROR(N30/N5,0)</f>
-        <v/>
-      </c>
-      <c r="O31" s="11">
-        <f>IFERROR(O30/O5,0)</f>
-        <v/>
-      </c>
-      <c r="P31" s="11">
-        <f>IFERROR(P30/P5,0)</f>
-        <v/>
-      </c>
-      <c r="Q31" s="11" t="n"/>
-    </row>
-    <row r="32" ht="12" customHeight="1">
-      <c r="B32" s="4" t="n"/>
-      <c r="C32" s="4" t="n"/>
-      <c r="D32" s="4" t="n"/>
-      <c r="E32" s="4" t="n"/>
-      <c r="F32" s="4" t="n"/>
-      <c r="G32" s="4" t="n"/>
-      <c r="H32" s="4" t="n"/>
-      <c r="I32" s="4" t="n"/>
-      <c r="J32" s="4" t="n"/>
-      <c r="K32" s="4" t="n"/>
-      <c r="L32" s="4" t="n"/>
-      <c r="M32" s="4" t="n"/>
-      <c r="N32" s="4" t="n"/>
-      <c r="O32" s="4" t="n"/>
-      <c r="P32" s="4">
-        <f>SUM(D32:O32)</f>
-        <v/>
-      </c>
-      <c r="Q32" s="4" t="n"/>
-    </row>
-    <row r="33" outlineLevel="1" ht="12" customHeight="1">
-      <c r="A33" s="7" t="inlineStr">
+      <c r="B32" s="11" t="n"/>
+      <c r="C32" s="11" t="n"/>
+      <c r="D32" s="11">
+        <f>IFERROR(D31/D5,0)</f>
+        <v/>
+      </c>
+      <c r="E32" s="11">
+        <f>IFERROR(E31/E5,0)</f>
+        <v/>
+      </c>
+      <c r="F32" s="11">
+        <f>IFERROR(F31/F5,0)</f>
+        <v/>
+      </c>
+      <c r="G32" s="11">
+        <f>IFERROR(G31/G5,0)</f>
+        <v/>
+      </c>
+      <c r="H32" s="11">
+        <f>IFERROR(H31/H5,0)</f>
+        <v/>
+      </c>
+      <c r="I32" s="11">
+        <f>IFERROR(I31/I5,0)</f>
+        <v/>
+      </c>
+      <c r="J32" s="11">
+        <f>IFERROR(J31/J5,0)</f>
+        <v/>
+      </c>
+      <c r="K32" s="11">
+        <f>IFERROR(K31/K5,0)</f>
+        <v/>
+      </c>
+      <c r="L32" s="11">
+        <f>IFERROR(L31/L5,0)</f>
+        <v/>
+      </c>
+      <c r="M32" s="11">
+        <f>IFERROR(M31/M5,0)</f>
+        <v/>
+      </c>
+      <c r="N32" s="11">
+        <f>IFERROR(N31/N5,0)</f>
+        <v/>
+      </c>
+      <c r="O32" s="11">
+        <f>IFERROR(O31/O5,0)</f>
+        <v/>
+      </c>
+      <c r="P32" s="11">
+        <f>IFERROR(P31/P5,0)</f>
+        <v/>
+      </c>
+      <c r="Q32" s="11" t="n"/>
+    </row>
+    <row r="33" ht="12" customHeight="1">
+      <c r="B33" s="4" t="n"/>
+      <c r="C33" s="4" t="n"/>
+      <c r="D33" s="4" t="n"/>
+      <c r="E33" s="4" t="n"/>
+      <c r="F33" s="4" t="n"/>
+      <c r="G33" s="4" t="n"/>
+      <c r="H33" s="4" t="n"/>
+      <c r="I33" s="4" t="n"/>
+      <c r="J33" s="4" t="n"/>
+      <c r="K33" s="4" t="n"/>
+      <c r="L33" s="4" t="n"/>
+      <c r="M33" s="4" t="n"/>
+      <c r="N33" s="4" t="n"/>
+      <c r="O33" s="4" t="n"/>
+      <c r="P33" s="4">
+        <f>SUM(D33:O33)</f>
+        <v/>
+      </c>
+      <c r="Q33" s="4" t="n"/>
+    </row>
+    <row r="34" outlineLevel="1" ht="12" customHeight="1">
+      <c r="A34" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Opex</t>
         </is>
       </c>
-      <c r="B33" s="8" t="n"/>
-      <c r="C33" s="8" t="n"/>
-      <c r="D33" s="8">
-        <f>D34+D36+D38+D40</f>
-        <v/>
-      </c>
-      <c r="E33" s="8">
-        <f>E34+E36+E38+E40</f>
-        <v/>
-      </c>
-      <c r="F33" s="8">
-        <f>F34+F36+F38+F40</f>
-        <v/>
-      </c>
-      <c r="G33" s="8">
-        <f>G34+G36+G38+G40</f>
-        <v/>
-      </c>
-      <c r="H33" s="8">
-        <f>H34+H36+H38+H40</f>
-        <v/>
-      </c>
-      <c r="I33" s="8">
-        <f>I34+I36+I38+I40</f>
-        <v/>
-      </c>
-      <c r="J33" s="8">
-        <f>J34+J36+J38+J40</f>
-        <v/>
-      </c>
-      <c r="K33" s="8">
-        <f>K34+K36+K38+K40</f>
-        <v/>
-      </c>
-      <c r="L33" s="8">
-        <f>L34+L36+L38+L40</f>
-        <v/>
-      </c>
-      <c r="M33" s="8">
-        <f>M34+M36+M38+M40</f>
-        <v/>
-      </c>
-      <c r="N33" s="8">
-        <f>N34+N36+N38+N40</f>
-        <v/>
-      </c>
-      <c r="O33" s="8">
-        <f>O34+O36+O38+O40</f>
-        <v/>
-      </c>
-      <c r="P33" s="8">
-        <f>SUM(D33:O33)</f>
-        <v/>
-      </c>
-      <c r="Q33" s="8" t="n"/>
-    </row>
-    <row r="34" hidden="1" outlineLevel="2" ht="12" customHeight="1">
-      <c r="A34" s="9" t="inlineStr">
+      <c r="B34" s="8" t="n"/>
+      <c r="C34" s="8" t="n"/>
+      <c r="D34" s="8">
+        <f>D35+D37+D39+D41</f>
+        <v/>
+      </c>
+      <c r="E34" s="8">
+        <f>E35+E37+E39+E41</f>
+        <v/>
+      </c>
+      <c r="F34" s="8">
+        <f>F35+F37+F39+F41</f>
+        <v/>
+      </c>
+      <c r="G34" s="8">
+        <f>G35+G37+G39+G41</f>
+        <v/>
+      </c>
+      <c r="H34" s="8">
+        <f>H35+H37+H39+H41</f>
+        <v/>
+      </c>
+      <c r="I34" s="8">
+        <f>I35+I37+I39+I41</f>
+        <v/>
+      </c>
+      <c r="J34" s="8">
+        <f>J35+J37+J39+J41</f>
+        <v/>
+      </c>
+      <c r="K34" s="8">
+        <f>K35+K37+K39+K41</f>
+        <v/>
+      </c>
+      <c r="L34" s="8">
+        <f>L35+L37+L39+L41</f>
+        <v/>
+      </c>
+      <c r="M34" s="8">
+        <f>M35+M37+M39+M41</f>
+        <v/>
+      </c>
+      <c r="N34" s="8">
+        <f>N35+N37+N39+N41</f>
+        <v/>
+      </c>
+      <c r="O34" s="8">
+        <f>O35+O37+O39+O41</f>
+        <v/>
+      </c>
+      <c r="P34" s="8">
+        <f>SUM(D34:O34)</f>
+        <v/>
+      </c>
+      <c r="Q34" s="8" t="n"/>
+    </row>
+    <row r="35" hidden="1" outlineLevel="2" ht="12" customHeight="1">
+      <c r="A35" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">    Shared services</t>
         </is>
       </c>
-      <c r="B34" s="10" t="n"/>
-      <c r="C34" s="10" t="n"/>
-      <c r="D34" s="10">
-        <f>SUM(D35:D35)</f>
-        <v/>
-      </c>
-      <c r="E34" s="10">
-        <f>SUM(E35:E35)</f>
-        <v/>
-      </c>
-      <c r="F34" s="10">
-        <f>SUM(F35:F35)</f>
-        <v/>
-      </c>
-      <c r="G34" s="10">
-        <f>SUM(G35:G35)</f>
-        <v/>
-      </c>
-      <c r="H34" s="10">
-        <f>SUM(H35:H35)</f>
-        <v/>
-      </c>
-      <c r="I34" s="10">
-        <f>SUM(I35:I35)</f>
-        <v/>
-      </c>
-      <c r="J34" s="10">
-        <f>SUM(J35:J35)</f>
-        <v/>
-      </c>
-      <c r="K34" s="10">
-        <f>SUM(K35:K35)</f>
-        <v/>
-      </c>
-      <c r="L34" s="10">
-        <f>SUM(L35:L35)</f>
-        <v/>
-      </c>
-      <c r="M34" s="10">
-        <f>SUM(M35:M35)</f>
-        <v/>
-      </c>
-      <c r="N34" s="10">
-        <f>SUM(N35:N35)</f>
-        <v/>
-      </c>
-      <c r="O34" s="10">
-        <f>SUM(O35:O35)</f>
-        <v/>
-      </c>
-      <c r="P34" s="10">
-        <f>SUM(D34:O34)</f>
-        <v/>
-      </c>
-      <c r="Q34" s="10" t="inlineStr">
+      <c r="B35" s="10" t="n"/>
+      <c r="C35" s="10" t="n"/>
+      <c r="D35" s="10">
+        <f>SUM(D36:D36)</f>
+        <v/>
+      </c>
+      <c r="E35" s="10">
+        <f>SUM(E36:E36)</f>
+        <v/>
+      </c>
+      <c r="F35" s="10">
+        <f>SUM(F36:F36)</f>
+        <v/>
+      </c>
+      <c r="G35" s="10">
+        <f>SUM(G36:G36)</f>
+        <v/>
+      </c>
+      <c r="H35" s="10">
+        <f>SUM(H36:H36)</f>
+        <v/>
+      </c>
+      <c r="I35" s="10">
+        <f>SUM(I36:I36)</f>
+        <v/>
+      </c>
+      <c r="J35" s="10">
+        <f>SUM(J36:J36)</f>
+        <v/>
+      </c>
+      <c r="K35" s="10">
+        <f>SUM(K36:K36)</f>
+        <v/>
+      </c>
+      <c r="L35" s="10">
+        <f>SUM(L36:L36)</f>
+        <v/>
+      </c>
+      <c r="M35" s="10">
+        <f>SUM(M36:M36)</f>
+        <v/>
+      </c>
+      <c r="N35" s="10">
+        <f>SUM(N36:N36)</f>
+        <v/>
+      </c>
+      <c r="O35" s="10">
+        <f>SUM(O36:O36)</f>
+        <v/>
+      </c>
+      <c r="P35" s="10">
+        <f>SUM(D35:O35)</f>
+        <v/>
+      </c>
+      <c r="Q35" s="10" t="inlineStr">
         <is>
           <t>-&gt;</t>
         </is>
       </c>
     </row>
-    <row r="35" hidden="1" outlineLevel="3" ht="12" customHeight="1">
-      <c r="A35" t="inlineStr">
+    <row r="36" hidden="1" outlineLevel="3" ht="12" customHeight="1">
+      <c r="A36" t="inlineStr">
         <is>
           <t xml:space="preserve">      SHAREDSERVICESSL</t>
         </is>
       </c>
-      <c r="B35" s="4" t="n"/>
-      <c r="C35" s="4" t="n"/>
-      <c r="D35" s="4">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,D$1,'g-expenses-ltd'!$D:$D,"shared_services",'g-expenses-ltd'!$E:$E,TRIM($A35))</f>
-        <v/>
-      </c>
-      <c r="E35" s="4">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,E$1,'g-expenses-ltd'!$D:$D,"shared_services",'g-expenses-ltd'!$E:$E,TRIM($A35))</f>
-        <v/>
-      </c>
-      <c r="F35" s="4">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,F$1,'g-expenses-ltd'!$D:$D,"shared_services",'g-expenses-ltd'!$E:$E,TRIM($A35))</f>
-        <v/>
-      </c>
-      <c r="G35" s="4">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,G$1,'g-expenses-ltd'!$D:$D,"shared_services",'g-expenses-ltd'!$E:$E,TRIM($A35))</f>
-        <v/>
-      </c>
-      <c r="H35" s="4">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,H$1,'g-expenses-ltd'!$D:$D,"shared_services",'g-expenses-ltd'!$E:$E,TRIM($A35))</f>
-        <v/>
-      </c>
-      <c r="I35" s="4">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,I$1,'g-expenses-ltd'!$D:$D,"shared_services",'g-expenses-ltd'!$E:$E,TRIM($A35))</f>
-        <v/>
-      </c>
-      <c r="J35" s="4">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,J$1,'g-expenses-ltd'!$D:$D,"shared_services",'g-expenses-ltd'!$E:$E,TRIM($A35))</f>
-        <v/>
-      </c>
-      <c r="K35" s="4">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,K$1,'g-expenses-ltd'!$D:$D,"shared_services",'g-expenses-ltd'!$E:$E,TRIM($A35))</f>
-        <v/>
-      </c>
-      <c r="L35" s="4">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,L$1,'g-expenses-ltd'!$D:$D,"shared_services",'g-expenses-ltd'!$E:$E,TRIM($A35))</f>
-        <v/>
-      </c>
-      <c r="M35" s="4">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,M$1,'g-expenses-ltd'!$D:$D,"shared_services",'g-expenses-ltd'!$E:$E,TRIM($A35))</f>
-        <v/>
-      </c>
-      <c r="N35" s="4">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,N$1,'g-expenses-ltd'!$D:$D,"shared_services",'g-expenses-ltd'!$E:$E,TRIM($A35))</f>
-        <v/>
-      </c>
-      <c r="O35" s="4">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,O$1,'g-expenses-ltd'!$D:$D,"shared_services",'g-expenses-ltd'!$E:$E,TRIM($A35))</f>
-        <v/>
-      </c>
-      <c r="P35" s="4">
-        <f>SUM(D35:O35)</f>
-        <v/>
-      </c>
-      <c r="Q35" s="4" t="inlineStr">
+      <c r="B36" s="4" t="n"/>
+      <c r="C36" s="4" t="n"/>
+      <c r="D36" s="4">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,D$1,'g-expenses-ltd'!$D:$D,"shared_services",'g-expenses-ltd'!$E:$E,TRIM($A36))</f>
+        <v/>
+      </c>
+      <c r="E36" s="4">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,E$1,'g-expenses-ltd'!$D:$D,"shared_services",'g-expenses-ltd'!$E:$E,TRIM($A36))</f>
+        <v/>
+      </c>
+      <c r="F36" s="4">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,F$1,'g-expenses-ltd'!$D:$D,"shared_services",'g-expenses-ltd'!$E:$E,TRIM($A36))</f>
+        <v/>
+      </c>
+      <c r="G36" s="4">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,G$1,'g-expenses-ltd'!$D:$D,"shared_services",'g-expenses-ltd'!$E:$E,TRIM($A36))</f>
+        <v/>
+      </c>
+      <c r="H36" s="4">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,H$1,'g-expenses-ltd'!$D:$D,"shared_services",'g-expenses-ltd'!$E:$E,TRIM($A36))</f>
+        <v/>
+      </c>
+      <c r="I36" s="4">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,I$1,'g-expenses-ltd'!$D:$D,"shared_services",'g-expenses-ltd'!$E:$E,TRIM($A36))</f>
+        <v/>
+      </c>
+      <c r="J36" s="4">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,J$1,'g-expenses-ltd'!$D:$D,"shared_services",'g-expenses-ltd'!$E:$E,TRIM($A36))</f>
+        <v/>
+      </c>
+      <c r="K36" s="4">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,K$1,'g-expenses-ltd'!$D:$D,"shared_services",'g-expenses-ltd'!$E:$E,TRIM($A36))</f>
+        <v/>
+      </c>
+      <c r="L36" s="4">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,L$1,'g-expenses-ltd'!$D:$D,"shared_services",'g-expenses-ltd'!$E:$E,TRIM($A36))</f>
+        <v/>
+      </c>
+      <c r="M36" s="4">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,M$1,'g-expenses-ltd'!$D:$D,"shared_services",'g-expenses-ltd'!$E:$E,TRIM($A36))</f>
+        <v/>
+      </c>
+      <c r="N36" s="4">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,N$1,'g-expenses-ltd'!$D:$D,"shared_services",'g-expenses-ltd'!$E:$E,TRIM($A36))</f>
+        <v/>
+      </c>
+      <c r="O36" s="4">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,O$1,'g-expenses-ltd'!$D:$D,"shared_services",'g-expenses-ltd'!$E:$E,TRIM($A36))</f>
+        <v/>
+      </c>
+      <c r="P36" s="4">
+        <f>SUM(D36:O36)</f>
+        <v/>
+      </c>
+      <c r="Q36" s="4" t="inlineStr">
         <is>
           <t>-&gt;</t>
         </is>
       </c>
     </row>
-    <row r="36" hidden="1" outlineLevel="2" ht="12" customHeight="1">
-      <c r="A36" s="9" t="inlineStr">
+    <row r="37" hidden="1" outlineLevel="2" ht="12" customHeight="1">
+      <c r="A37" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">    Administration</t>
         </is>
       </c>
-      <c r="B36" s="10" t="n"/>
-      <c r="C36" s="10" t="n"/>
-      <c r="D36" s="10">
-        <f>SUM(D37:D37)</f>
-        <v/>
-      </c>
-      <c r="E36" s="10">
-        <f>SUM(E37:E37)</f>
-        <v/>
-      </c>
-      <c r="F36" s="10">
-        <f>SUM(F37:F37)</f>
-        <v/>
-      </c>
-      <c r="G36" s="10">
-        <f>SUM(G37:G37)</f>
-        <v/>
-      </c>
-      <c r="H36" s="10">
-        <f>SUM(H37:H37)</f>
-        <v/>
-      </c>
-      <c r="I36" s="10">
-        <f>SUM(I37:I37)</f>
-        <v/>
-      </c>
-      <c r="J36" s="10">
-        <f>SUM(J37:J37)</f>
-        <v/>
-      </c>
-      <c r="K36" s="10">
-        <f>SUM(K37:K37)</f>
-        <v/>
-      </c>
-      <c r="L36" s="10">
-        <f>SUM(L37:L37)</f>
-        <v/>
-      </c>
-      <c r="M36" s="10">
-        <f>SUM(M37:M37)</f>
-        <v/>
-      </c>
-      <c r="N36" s="10">
-        <f>SUM(N37:N37)</f>
-        <v/>
-      </c>
-      <c r="O36" s="10">
-        <f>SUM(O37:O37)</f>
-        <v/>
-      </c>
-      <c r="P36" s="10">
-        <f>SUM(D36:O36)</f>
-        <v/>
-      </c>
-      <c r="Q36" s="10" t="inlineStr">
+      <c r="B37" s="10" t="n"/>
+      <c r="C37" s="10" t="n"/>
+      <c r="D37" s="10">
+        <f>SUM(D38:D38)</f>
+        <v/>
+      </c>
+      <c r="E37" s="10">
+        <f>SUM(E38:E38)</f>
+        <v/>
+      </c>
+      <c r="F37" s="10">
+        <f>SUM(F38:F38)</f>
+        <v/>
+      </c>
+      <c r="G37" s="10">
+        <f>SUM(G38:G38)</f>
+        <v/>
+      </c>
+      <c r="H37" s="10">
+        <f>SUM(H38:H38)</f>
+        <v/>
+      </c>
+      <c r="I37" s="10">
+        <f>SUM(I38:I38)</f>
+        <v/>
+      </c>
+      <c r="J37" s="10">
+        <f>SUM(J38:J38)</f>
+        <v/>
+      </c>
+      <c r="K37" s="10">
+        <f>SUM(K38:K38)</f>
+        <v/>
+      </c>
+      <c r="L37" s="10">
+        <f>SUM(L38:L38)</f>
+        <v/>
+      </c>
+      <c r="M37" s="10">
+        <f>SUM(M38:M38)</f>
+        <v/>
+      </c>
+      <c r="N37" s="10">
+        <f>SUM(N38:N38)</f>
+        <v/>
+      </c>
+      <c r="O37" s="10">
+        <f>SUM(O38:O38)</f>
+        <v/>
+      </c>
+      <c r="P37" s="10">
+        <f>SUM(D37:O37)</f>
+        <v/>
+      </c>
+      <c r="Q37" s="10" t="inlineStr">
         <is>
           <t>-&gt;</t>
         </is>
       </c>
     </row>
-    <row r="37" hidden="1" outlineLevel="3" ht="12" customHeight="1">
-      <c r="A37" t="inlineStr">
+    <row r="38" hidden="1" outlineLevel="3" ht="12" customHeight="1">
+      <c r="A38" t="inlineStr">
         <is>
           <t xml:space="preserve">      YOURACCOUNTSTAXES</t>
         </is>
       </c>
-      <c r="B37" s="4" t="n"/>
-      <c r="C37" s="4" t="n"/>
-      <c r="D37" s="4">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,D$1,'g-expenses-ltd'!$D:$D,"administration",'g-expenses-ltd'!$E:$E,TRIM($A37))</f>
-        <v/>
-      </c>
-      <c r="E37" s="4">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,E$1,'g-expenses-ltd'!$D:$D,"administration",'g-expenses-ltd'!$E:$E,TRIM($A37))</f>
-        <v/>
-      </c>
-      <c r="F37" s="4">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,F$1,'g-expenses-ltd'!$D:$D,"administration",'g-expenses-ltd'!$E:$E,TRIM($A37))</f>
-        <v/>
-      </c>
-      <c r="G37" s="4">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,G$1,'g-expenses-ltd'!$D:$D,"administration",'g-expenses-ltd'!$E:$E,TRIM($A37))</f>
-        <v/>
-      </c>
-      <c r="H37" s="4">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,H$1,'g-expenses-ltd'!$D:$D,"administration",'g-expenses-ltd'!$E:$E,TRIM($A37))</f>
-        <v/>
-      </c>
-      <c r="I37" s="4">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,I$1,'g-expenses-ltd'!$D:$D,"administration",'g-expenses-ltd'!$E:$E,TRIM($A37))</f>
-        <v/>
-      </c>
-      <c r="J37" s="4">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,J$1,'g-expenses-ltd'!$D:$D,"administration",'g-expenses-ltd'!$E:$E,TRIM($A37))</f>
-        <v/>
-      </c>
-      <c r="K37" s="4">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,K$1,'g-expenses-ltd'!$D:$D,"administration",'g-expenses-ltd'!$E:$E,TRIM($A37))</f>
-        <v/>
-      </c>
-      <c r="L37" s="4">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,L$1,'g-expenses-ltd'!$D:$D,"administration",'g-expenses-ltd'!$E:$E,TRIM($A37))</f>
-        <v/>
-      </c>
-      <c r="M37" s="4">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,M$1,'g-expenses-ltd'!$D:$D,"administration",'g-expenses-ltd'!$E:$E,TRIM($A37))</f>
-        <v/>
-      </c>
-      <c r="N37" s="4">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,N$1,'g-expenses-ltd'!$D:$D,"administration",'g-expenses-ltd'!$E:$E,TRIM($A37))</f>
-        <v/>
-      </c>
-      <c r="O37" s="4">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,O$1,'g-expenses-ltd'!$D:$D,"administration",'g-expenses-ltd'!$E:$E,TRIM($A37))</f>
-        <v/>
-      </c>
-      <c r="P37" s="4">
-        <f>SUM(D37:O37)</f>
-        <v/>
-      </c>
-      <c r="Q37" s="4" t="inlineStr">
+      <c r="B38" s="4" t="n"/>
+      <c r="C38" s="4" t="n"/>
+      <c r="D38" s="4">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,D$1,'g-expenses-ltd'!$D:$D,"administration",'g-expenses-ltd'!$E:$E,TRIM($A38))</f>
+        <v/>
+      </c>
+      <c r="E38" s="4">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,E$1,'g-expenses-ltd'!$D:$D,"administration",'g-expenses-ltd'!$E:$E,TRIM($A38))</f>
+        <v/>
+      </c>
+      <c r="F38" s="4">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,F$1,'g-expenses-ltd'!$D:$D,"administration",'g-expenses-ltd'!$E:$E,TRIM($A38))</f>
+        <v/>
+      </c>
+      <c r="G38" s="4">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,G$1,'g-expenses-ltd'!$D:$D,"administration",'g-expenses-ltd'!$E:$E,TRIM($A38))</f>
+        <v/>
+      </c>
+      <c r="H38" s="4">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,H$1,'g-expenses-ltd'!$D:$D,"administration",'g-expenses-ltd'!$E:$E,TRIM($A38))</f>
+        <v/>
+      </c>
+      <c r="I38" s="4">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,I$1,'g-expenses-ltd'!$D:$D,"administration",'g-expenses-ltd'!$E:$E,TRIM($A38))</f>
+        <v/>
+      </c>
+      <c r="J38" s="4">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,J$1,'g-expenses-ltd'!$D:$D,"administration",'g-expenses-ltd'!$E:$E,TRIM($A38))</f>
+        <v/>
+      </c>
+      <c r="K38" s="4">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,K$1,'g-expenses-ltd'!$D:$D,"administration",'g-expenses-ltd'!$E:$E,TRIM($A38))</f>
+        <v/>
+      </c>
+      <c r="L38" s="4">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,L$1,'g-expenses-ltd'!$D:$D,"administration",'g-expenses-ltd'!$E:$E,TRIM($A38))</f>
+        <v/>
+      </c>
+      <c r="M38" s="4">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,M$1,'g-expenses-ltd'!$D:$D,"administration",'g-expenses-ltd'!$E:$E,TRIM($A38))</f>
+        <v/>
+      </c>
+      <c r="N38" s="4">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,N$1,'g-expenses-ltd'!$D:$D,"administration",'g-expenses-ltd'!$E:$E,TRIM($A38))</f>
+        <v/>
+      </c>
+      <c r="O38" s="4">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,O$1,'g-expenses-ltd'!$D:$D,"administration",'g-expenses-ltd'!$E:$E,TRIM($A38))</f>
+        <v/>
+      </c>
+      <c r="P38" s="4">
+        <f>SUM(D38:O38)</f>
+        <v/>
+      </c>
+      <c r="Q38" s="4" t="inlineStr">
         <is>
           <t>-&gt;</t>
         </is>
       </c>
     </row>
-    <row r="38" hidden="1" outlineLevel="2" ht="12" customHeight="1">
-      <c r="A38" s="9" t="inlineStr">
+    <row r="39" hidden="1" outlineLevel="2" ht="12" customHeight="1">
+      <c r="A39" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">    Technology</t>
         </is>
       </c>
-      <c r="B38" s="10" t="n"/>
-      <c r="C38" s="10" t="n"/>
-      <c r="D38" s="10">
-        <f>SUM(D39:D39)</f>
-        <v/>
-      </c>
-      <c r="E38" s="10">
-        <f>SUM(E39:E39)</f>
-        <v/>
-      </c>
-      <c r="F38" s="10">
-        <f>SUM(F39:F39)</f>
-        <v/>
-      </c>
-      <c r="G38" s="10">
-        <f>SUM(G39:G39)</f>
-        <v/>
-      </c>
-      <c r="H38" s="10">
-        <f>SUM(H39:H39)</f>
-        <v/>
-      </c>
-      <c r="I38" s="10">
-        <f>SUM(I39:I39)</f>
-        <v/>
-      </c>
-      <c r="J38" s="10">
-        <f>SUM(J39:J39)</f>
-        <v/>
-      </c>
-      <c r="K38" s="10">
-        <f>SUM(K39:K39)</f>
-        <v/>
-      </c>
-      <c r="L38" s="10">
-        <f>SUM(L39:L39)</f>
-        <v/>
-      </c>
-      <c r="M38" s="10">
-        <f>SUM(M39:M39)</f>
-        <v/>
-      </c>
-      <c r="N38" s="10">
-        <f>SUM(N39:N39)</f>
-        <v/>
-      </c>
-      <c r="O38" s="10">
-        <f>SUM(O39:O39)</f>
-        <v/>
-      </c>
-      <c r="P38" s="10">
-        <f>SUM(D38:O38)</f>
-        <v/>
-      </c>
-      <c r="Q38" s="10" t="inlineStr">
+      <c r="B39" s="10" t="n"/>
+      <c r="C39" s="10" t="n"/>
+      <c r="D39" s="10">
+        <f>SUM(D40:D40)</f>
+        <v/>
+      </c>
+      <c r="E39" s="10">
+        <f>SUM(E40:E40)</f>
+        <v/>
+      </c>
+      <c r="F39" s="10">
+        <f>SUM(F40:F40)</f>
+        <v/>
+      </c>
+      <c r="G39" s="10">
+        <f>SUM(G40:G40)</f>
+        <v/>
+      </c>
+      <c r="H39" s="10">
+        <f>SUM(H40:H40)</f>
+        <v/>
+      </c>
+      <c r="I39" s="10">
+        <f>SUM(I40:I40)</f>
+        <v/>
+      </c>
+      <c r="J39" s="10">
+        <f>SUM(J40:J40)</f>
+        <v/>
+      </c>
+      <c r="K39" s="10">
+        <f>SUM(K40:K40)</f>
+        <v/>
+      </c>
+      <c r="L39" s="10">
+        <f>SUM(L40:L40)</f>
+        <v/>
+      </c>
+      <c r="M39" s="10">
+        <f>SUM(M40:M40)</f>
+        <v/>
+      </c>
+      <c r="N39" s="10">
+        <f>SUM(N40:N40)</f>
+        <v/>
+      </c>
+      <c r="O39" s="10">
+        <f>SUM(O40:O40)</f>
+        <v/>
+      </c>
+      <c r="P39" s="10">
+        <f>SUM(D39:O39)</f>
+        <v/>
+      </c>
+      <c r="Q39" s="10" t="inlineStr">
         <is>
           <t>-&gt;</t>
         </is>
       </c>
     </row>
-    <row r="39" hidden="1" outlineLevel="3" ht="12" customHeight="1">
-      <c r="A39" t="inlineStr">
+    <row r="40" hidden="1" outlineLevel="3" ht="12" customHeight="1">
+      <c r="A40" t="inlineStr">
         <is>
           <t xml:space="preserve">      REVER</t>
         </is>
       </c>
-      <c r="B39" s="4" t="n"/>
-      <c r="C39" s="4" t="n"/>
-      <c r="D39" s="4">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,D$1,'g-expenses-ltd'!$D:$D,"technology",'g-expenses-ltd'!$E:$E,TRIM($A39))</f>
-        <v/>
-      </c>
-      <c r="E39" s="4">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,E$1,'g-expenses-ltd'!$D:$D,"technology",'g-expenses-ltd'!$E:$E,TRIM($A39))</f>
-        <v/>
-      </c>
-      <c r="F39" s="4">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,F$1,'g-expenses-ltd'!$D:$D,"technology",'g-expenses-ltd'!$E:$E,TRIM($A39))</f>
-        <v/>
-      </c>
-      <c r="G39" s="4">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,G$1,'g-expenses-ltd'!$D:$D,"technology",'g-expenses-ltd'!$E:$E,TRIM($A39))</f>
-        <v/>
-      </c>
-      <c r="H39" s="4">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,H$1,'g-expenses-ltd'!$D:$D,"technology",'g-expenses-ltd'!$E:$E,TRIM($A39))</f>
-        <v/>
-      </c>
-      <c r="I39" s="4">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,I$1,'g-expenses-ltd'!$D:$D,"technology",'g-expenses-ltd'!$E:$E,TRIM($A39))</f>
-        <v/>
-      </c>
-      <c r="J39" s="4">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,J$1,'g-expenses-ltd'!$D:$D,"technology",'g-expenses-ltd'!$E:$E,TRIM($A39))</f>
-        <v/>
-      </c>
-      <c r="K39" s="4">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,K$1,'g-expenses-ltd'!$D:$D,"technology",'g-expenses-ltd'!$E:$E,TRIM($A39))</f>
-        <v/>
-      </c>
-      <c r="L39" s="4">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,L$1,'g-expenses-ltd'!$D:$D,"technology",'g-expenses-ltd'!$E:$E,TRIM($A39))</f>
-        <v/>
-      </c>
-      <c r="M39" s="4">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,M$1,'g-expenses-ltd'!$D:$D,"technology",'g-expenses-ltd'!$E:$E,TRIM($A39))</f>
-        <v/>
-      </c>
-      <c r="N39" s="4">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,N$1,'g-expenses-ltd'!$D:$D,"technology",'g-expenses-ltd'!$E:$E,TRIM($A39))</f>
-        <v/>
-      </c>
-      <c r="O39" s="4">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,O$1,'g-expenses-ltd'!$D:$D,"technology",'g-expenses-ltd'!$E:$E,TRIM($A39))</f>
-        <v/>
-      </c>
-      <c r="P39" s="4">
-        <f>SUM(D39:O39)</f>
-        <v/>
-      </c>
-      <c r="Q39" s="4" t="inlineStr">
-        <is>
-          <t>-&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" hidden="1" outlineLevel="2" ht="12" customHeight="1">
-      <c r="A40" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Uncategorized Expenses</t>
-        </is>
-      </c>
-      <c r="B40" s="10" t="n"/>
-      <c r="C40" s="10" t="n"/>
-      <c r="D40" s="10">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,D$1,'g-expenses-ltd'!$D:$D,"otros_gastos")</f>
-        <v/>
-      </c>
-      <c r="E40" s="10">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,E$1,'g-expenses-ltd'!$D:$D,"otros_gastos")</f>
-        <v/>
-      </c>
-      <c r="F40" s="10">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,F$1,'g-expenses-ltd'!$D:$D,"otros_gastos")</f>
-        <v/>
-      </c>
-      <c r="G40" s="10">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,G$1,'g-expenses-ltd'!$D:$D,"otros_gastos")</f>
-        <v/>
-      </c>
-      <c r="H40" s="10">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,H$1,'g-expenses-ltd'!$D:$D,"otros_gastos")</f>
-        <v/>
-      </c>
-      <c r="I40" s="10">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,I$1,'g-expenses-ltd'!$D:$D,"otros_gastos")</f>
-        <v/>
-      </c>
-      <c r="J40" s="10">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,J$1,'g-expenses-ltd'!$D:$D,"otros_gastos")</f>
-        <v/>
-      </c>
-      <c r="K40" s="10">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,K$1,'g-expenses-ltd'!$D:$D,"otros_gastos")</f>
-        <v/>
-      </c>
-      <c r="L40" s="10">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,L$1,'g-expenses-ltd'!$D:$D,"otros_gastos")</f>
-        <v/>
-      </c>
-      <c r="M40" s="10">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,M$1,'g-expenses-ltd'!$D:$D,"otros_gastos")</f>
-        <v/>
-      </c>
-      <c r="N40" s="10">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,N$1,'g-expenses-ltd'!$D:$D,"otros_gastos")</f>
-        <v/>
-      </c>
-      <c r="O40" s="10">
-        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,O$1,'g-expenses-ltd'!$D:$D,"otros_gastos")</f>
-        <v/>
-      </c>
-      <c r="P40" s="10">
+      <c r="B40" s="4" t="n"/>
+      <c r="C40" s="4" t="n"/>
+      <c r="D40" s="4">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,D$1,'g-expenses-ltd'!$D:$D,"technology",'g-expenses-ltd'!$E:$E,TRIM($A40))</f>
+        <v/>
+      </c>
+      <c r="E40" s="4">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,E$1,'g-expenses-ltd'!$D:$D,"technology",'g-expenses-ltd'!$E:$E,TRIM($A40))</f>
+        <v/>
+      </c>
+      <c r="F40" s="4">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,F$1,'g-expenses-ltd'!$D:$D,"technology",'g-expenses-ltd'!$E:$E,TRIM($A40))</f>
+        <v/>
+      </c>
+      <c r="G40" s="4">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,G$1,'g-expenses-ltd'!$D:$D,"technology",'g-expenses-ltd'!$E:$E,TRIM($A40))</f>
+        <v/>
+      </c>
+      <c r="H40" s="4">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,H$1,'g-expenses-ltd'!$D:$D,"technology",'g-expenses-ltd'!$E:$E,TRIM($A40))</f>
+        <v/>
+      </c>
+      <c r="I40" s="4">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,I$1,'g-expenses-ltd'!$D:$D,"technology",'g-expenses-ltd'!$E:$E,TRIM($A40))</f>
+        <v/>
+      </c>
+      <c r="J40" s="4">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,J$1,'g-expenses-ltd'!$D:$D,"technology",'g-expenses-ltd'!$E:$E,TRIM($A40))</f>
+        <v/>
+      </c>
+      <c r="K40" s="4">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,K$1,'g-expenses-ltd'!$D:$D,"technology",'g-expenses-ltd'!$E:$E,TRIM($A40))</f>
+        <v/>
+      </c>
+      <c r="L40" s="4">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,L$1,'g-expenses-ltd'!$D:$D,"technology",'g-expenses-ltd'!$E:$E,TRIM($A40))</f>
+        <v/>
+      </c>
+      <c r="M40" s="4">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,M$1,'g-expenses-ltd'!$D:$D,"technology",'g-expenses-ltd'!$E:$E,TRIM($A40))</f>
+        <v/>
+      </c>
+      <c r="N40" s="4">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,N$1,'g-expenses-ltd'!$D:$D,"technology",'g-expenses-ltd'!$E:$E,TRIM($A40))</f>
+        <v/>
+      </c>
+      <c r="O40" s="4">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,O$1,'g-expenses-ltd'!$D:$D,"technology",'g-expenses-ltd'!$E:$E,TRIM($A40))</f>
+        <v/>
+      </c>
+      <c r="P40" s="4">
         <f>SUM(D40:O40)</f>
         <v/>
       </c>
-      <c r="Q40" s="10" t="inlineStr">
+      <c r="Q40" s="4" t="inlineStr">
         <is>
           <t>-&gt;</t>
         </is>
@@ -2877,212 +2847,247 @@
     <row r="41" hidden="1" outlineLevel="2" ht="12" customHeight="1">
       <c r="A41" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Currency Adjustment</t>
+          <t xml:space="preserve">    Uncategorized Expenses</t>
         </is>
       </c>
       <c r="B41" s="10" t="n"/>
       <c r="C41" s="10" t="n"/>
-      <c r="D41" s="10" t="n"/>
-      <c r="E41" s="10" t="n"/>
-      <c r="F41" s="10" t="n"/>
-      <c r="G41" s="10" t="n"/>
-      <c r="H41" s="10" t="n"/>
-      <c r="I41" s="10" t="n"/>
-      <c r="J41" s="10" t="n"/>
-      <c r="K41" s="10" t="n"/>
-      <c r="L41" s="10" t="n"/>
-      <c r="M41" s="10" t="n"/>
-      <c r="N41" s="10" t="n"/>
-      <c r="O41" s="10" t="n"/>
+      <c r="D41" s="10">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,D$1,'g-expenses-ltd'!$D:$D,"otros_gastos")</f>
+        <v/>
+      </c>
+      <c r="E41" s="10">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,E$1,'g-expenses-ltd'!$D:$D,"otros_gastos")</f>
+        <v/>
+      </c>
+      <c r="F41" s="10">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,F$1,'g-expenses-ltd'!$D:$D,"otros_gastos")</f>
+        <v/>
+      </c>
+      <c r="G41" s="10">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,G$1,'g-expenses-ltd'!$D:$D,"otros_gastos")</f>
+        <v/>
+      </c>
+      <c r="H41" s="10">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,H$1,'g-expenses-ltd'!$D:$D,"otros_gastos")</f>
+        <v/>
+      </c>
+      <c r="I41" s="10">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,I$1,'g-expenses-ltd'!$D:$D,"otros_gastos")</f>
+        <v/>
+      </c>
+      <c r="J41" s="10">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,J$1,'g-expenses-ltd'!$D:$D,"otros_gastos")</f>
+        <v/>
+      </c>
+      <c r="K41" s="10">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,K$1,'g-expenses-ltd'!$D:$D,"otros_gastos")</f>
+        <v/>
+      </c>
+      <c r="L41" s="10">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,L$1,'g-expenses-ltd'!$D:$D,"otros_gastos")</f>
+        <v/>
+      </c>
+      <c r="M41" s="10">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,M$1,'g-expenses-ltd'!$D:$D,"otros_gastos")</f>
+        <v/>
+      </c>
+      <c r="N41" s="10">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,N$1,'g-expenses-ltd'!$D:$D,"otros_gastos")</f>
+        <v/>
+      </c>
+      <c r="O41" s="10">
+        <f>SUMIFS('g-expenses-ltd'!$K:$K,'g-expenses-ltd'!$A:$A,O$1,'g-expenses-ltd'!$D:$D,"otros_gastos")</f>
+        <v/>
+      </c>
       <c r="P41" s="10">
         <f>SUM(D41:O41)</f>
         <v/>
       </c>
-      <c r="Q41" s="10" t="n"/>
-    </row>
-    <row r="42" ht="12" customHeight="1">
-      <c r="B42" s="4" t="n"/>
-      <c r="C42" s="4" t="n"/>
-      <c r="D42" s="4" t="n"/>
-      <c r="E42" s="4" t="n"/>
-      <c r="F42" s="4" t="n"/>
-      <c r="G42" s="4" t="n"/>
-      <c r="H42" s="4" t="n"/>
-      <c r="I42" s="4" t="n"/>
-      <c r="J42" s="4" t="n"/>
-      <c r="K42" s="4" t="n"/>
-      <c r="L42" s="4" t="n"/>
-      <c r="M42" s="4" t="n"/>
-      <c r="N42" s="4" t="n"/>
-      <c r="O42" s="4" t="n"/>
-      <c r="P42" s="4">
+      <c r="Q41" s="10" t="inlineStr">
+        <is>
+          <t>-&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" hidden="1" outlineLevel="2" ht="12" customHeight="1">
+      <c r="A42" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Currency Adjustment</t>
+        </is>
+      </c>
+      <c r="B42" s="10" t="n"/>
+      <c r="C42" s="10" t="n"/>
+      <c r="D42" s="10" t="n"/>
+      <c r="E42" s="10" t="n"/>
+      <c r="F42" s="10" t="n"/>
+      <c r="G42" s="10" t="n"/>
+      <c r="H42" s="10" t="n"/>
+      <c r="I42" s="10" t="n"/>
+      <c r="J42" s="10" t="n"/>
+      <c r="K42" s="10" t="n"/>
+      <c r="L42" s="10" t="n"/>
+      <c r="M42" s="10" t="n"/>
+      <c r="N42" s="10" t="n"/>
+      <c r="O42" s="10" t="n"/>
+      <c r="P42" s="10">
         <f>SUM(D42:O42)</f>
         <v/>
       </c>
-      <c r="Q42" s="4" t="n"/>
+      <c r="Q42" s="10" t="n"/>
     </row>
     <row r="43" ht="12" customHeight="1">
-      <c r="A43" s="12" t="inlineStr">
+      <c r="B43" s="4" t="n"/>
+      <c r="C43" s="4" t="n"/>
+      <c r="D43" s="4" t="n"/>
+      <c r="E43" s="4" t="n"/>
+      <c r="F43" s="4" t="n"/>
+      <c r="G43" s="4" t="n"/>
+      <c r="H43" s="4" t="n"/>
+      <c r="I43" s="4" t="n"/>
+      <c r="J43" s="4" t="n"/>
+      <c r="K43" s="4" t="n"/>
+      <c r="L43" s="4" t="n"/>
+      <c r="M43" s="4" t="n"/>
+      <c r="N43" s="4" t="n"/>
+      <c r="O43" s="4" t="n"/>
+      <c r="P43" s="4">
+        <f>SUM(D43:O43)</f>
+        <v/>
+      </c>
+      <c r="Q43" s="4" t="n"/>
+    </row>
+    <row r="44" ht="12" customHeight="1">
+      <c r="A44" s="13" t="inlineStr">
         <is>
           <t>PROFIT</t>
         </is>
       </c>
-      <c r="B43" s="13" t="n"/>
-      <c r="C43" s="13" t="n"/>
-      <c r="D43" s="13">
-        <f>D4-D12-D33-D41</f>
-        <v/>
-      </c>
-      <c r="E43" s="13">
-        <f>E4-E12-E33-E41</f>
-        <v/>
-      </c>
-      <c r="F43" s="13">
-        <f>F4-F12-F33-F41</f>
-        <v/>
-      </c>
-      <c r="G43" s="13">
-        <f>G4-G12-G33-G41</f>
-        <v/>
-      </c>
-      <c r="H43" s="13">
-        <f>H4-H12-H33-H41</f>
-        <v/>
-      </c>
-      <c r="I43" s="13">
-        <f>I4-I12-I33-I41</f>
-        <v/>
-      </c>
-      <c r="J43" s="13">
-        <f>J4-J12-J33-J41</f>
-        <v/>
-      </c>
-      <c r="K43" s="13">
-        <f>K4-K12-K33-K41</f>
-        <v/>
-      </c>
-      <c r="L43" s="13">
-        <f>L4-L12-L33-L41</f>
-        <v/>
-      </c>
-      <c r="M43" s="13">
-        <f>M4-M12-M33-M41</f>
-        <v/>
-      </c>
-      <c r="N43" s="13">
-        <f>N4-N12-N33-N41</f>
-        <v/>
-      </c>
-      <c r="O43" s="13">
-        <f>O4-O12-O33-O41</f>
-        <v/>
-      </c>
-      <c r="P43" s="13">
-        <f>SUM(D43:O43)</f>
-        <v/>
-      </c>
-      <c r="Q43" s="13" t="n"/>
-    </row>
-    <row r="44" hidden="1" outlineLevel="1" ht="12" customHeight="1">
-      <c r="A44" s="3" t="inlineStr">
+      <c r="B44" s="14" t="n"/>
+      <c r="C44" s="14" t="n"/>
+      <c r="D44" s="14">
+        <f>D4-D12-D34-D42</f>
+        <v/>
+      </c>
+      <c r="E44" s="14">
+        <f>E4-E12-E34-E42</f>
+        <v/>
+      </c>
+      <c r="F44" s="14">
+        <f>F4-F12-F34-F42</f>
+        <v/>
+      </c>
+      <c r="G44" s="14">
+        <f>G4-G12-G34-G42</f>
+        <v/>
+      </c>
+      <c r="H44" s="14">
+        <f>H4-H12-H34-H42</f>
+        <v/>
+      </c>
+      <c r="I44" s="14">
+        <f>I4-I12-I34-I42</f>
+        <v/>
+      </c>
+      <c r="J44" s="14">
+        <f>J4-J12-J34-J42</f>
+        <v/>
+      </c>
+      <c r="K44" s="14">
+        <f>K4-K12-K34-K42</f>
+        <v/>
+      </c>
+      <c r="L44" s="14">
+        <f>L4-L12-L34-L42</f>
+        <v/>
+      </c>
+      <c r="M44" s="14">
+        <f>M4-M12-M34-M42</f>
+        <v/>
+      </c>
+      <c r="N44" s="14">
+        <f>N4-N12-N34-N42</f>
+        <v/>
+      </c>
+      <c r="O44" s="14">
+        <f>O4-O12-O34-O42</f>
+        <v/>
+      </c>
+      <c r="P44" s="14">
+        <f>SUM(D44:O44)</f>
+        <v/>
+      </c>
+      <c r="Q44" s="14" t="n"/>
+    </row>
+    <row r="45" hidden="1" outlineLevel="1" ht="12" customHeight="1">
+      <c r="A45" s="3" t="inlineStr">
         <is>
           <t>% profit / product sales</t>
         </is>
       </c>
-      <c r="B44" s="11" t="n"/>
-      <c r="C44" s="11" t="n"/>
-      <c r="D44" s="11">
-        <f>IFERROR(D43/D5,0)</f>
-        <v/>
-      </c>
-      <c r="E44" s="11">
-        <f>IFERROR(E43/E5,0)</f>
-        <v/>
-      </c>
-      <c r="F44" s="11">
-        <f>IFERROR(F43/F5,0)</f>
-        <v/>
-      </c>
-      <c r="G44" s="11">
-        <f>IFERROR(G43/G5,0)</f>
-        <v/>
-      </c>
-      <c r="H44" s="11">
-        <f>IFERROR(H43/H5,0)</f>
-        <v/>
-      </c>
-      <c r="I44" s="11">
-        <f>IFERROR(I43/I5,0)</f>
-        <v/>
-      </c>
-      <c r="J44" s="11">
-        <f>IFERROR(J43/J5,0)</f>
-        <v/>
-      </c>
-      <c r="K44" s="11">
-        <f>IFERROR(K43/K5,0)</f>
-        <v/>
-      </c>
-      <c r="L44" s="11">
-        <f>IFERROR(L43/L5,0)</f>
-        <v/>
-      </c>
-      <c r="M44" s="11">
-        <f>IFERROR(M43/M5,0)</f>
-        <v/>
-      </c>
-      <c r="N44" s="11">
-        <f>IFERROR(N43/N5,0)</f>
-        <v/>
-      </c>
-      <c r="O44" s="11">
-        <f>IFERROR(O43/O5,0)</f>
-        <v/>
-      </c>
-      <c r="P44" s="11">
-        <f>IFERROR(P43/P5,0)</f>
-        <v/>
-      </c>
-      <c r="Q44" s="11" t="n"/>
-    </row>
-    <row r="45">
-      <c r="B45" s="4" t="n"/>
-      <c r="C45" s="4" t="n"/>
-      <c r="D45" s="4" t="n"/>
-      <c r="E45" s="4" t="n"/>
-      <c r="F45" s="4" t="n"/>
-      <c r="G45" s="4" t="n"/>
-      <c r="H45" s="4" t="n"/>
-      <c r="I45" s="4" t="n"/>
-      <c r="J45" s="4" t="n"/>
-      <c r="K45" s="4" t="n"/>
-      <c r="L45" s="4" t="n"/>
-      <c r="M45" s="4" t="n"/>
-      <c r="N45" s="4" t="n"/>
-      <c r="O45" s="4" t="n"/>
-      <c r="P45" s="4" t="n"/>
-      <c r="Q45" s="4" t="n"/>
+      <c r="B45" s="11" t="n"/>
+      <c r="C45" s="11" t="n"/>
+      <c r="D45" s="11">
+        <f>IFERROR(D44/D5,0)</f>
+        <v/>
+      </c>
+      <c r="E45" s="11">
+        <f>IFERROR(E44/E5,0)</f>
+        <v/>
+      </c>
+      <c r="F45" s="11">
+        <f>IFERROR(F44/F5,0)</f>
+        <v/>
+      </c>
+      <c r="G45" s="11">
+        <f>IFERROR(G44/G5,0)</f>
+        <v/>
+      </c>
+      <c r="H45" s="11">
+        <f>IFERROR(H44/H5,0)</f>
+        <v/>
+      </c>
+      <c r="I45" s="11">
+        <f>IFERROR(I44/I5,0)</f>
+        <v/>
+      </c>
+      <c r="J45" s="11">
+        <f>IFERROR(J44/J5,0)</f>
+        <v/>
+      </c>
+      <c r="K45" s="11">
+        <f>IFERROR(K44/K5,0)</f>
+        <v/>
+      </c>
+      <c r="L45" s="11">
+        <f>IFERROR(L44/L5,0)</f>
+        <v/>
+      </c>
+      <c r="M45" s="11">
+        <f>IFERROR(M44/M5,0)</f>
+        <v/>
+      </c>
+      <c r="N45" s="11">
+        <f>IFERROR(N44/N5,0)</f>
+        <v/>
+      </c>
+      <c r="O45" s="11">
+        <f>IFERROR(O44/O5,0)</f>
+        <v/>
+      </c>
+      <c r="P45" s="11">
+        <f>IFERROR(P44/P5,0)</f>
+        <v/>
+      </c>
+      <c r="Q45" s="11" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="14" t="inlineStr">
-        <is>
-          <t>Stock inicial marcos</t>
-        </is>
-      </c>
       <c r="B46" s="4" t="n"/>
       <c r="C46" s="4" t="n"/>
-      <c r="D46" s="4" t="n">
-        <v>7471.59</v>
-      </c>
-      <c r="E46" s="4" t="n">
-        <v>13032.64</v>
-      </c>
-      <c r="F46" s="4" t="n">
-        <v>10643.86</v>
-      </c>
-      <c r="G46" s="4" t="n">
-        <v>19745.79</v>
-      </c>
+      <c r="D46" s="4" t="n"/>
+      <c r="E46" s="4" t="n"/>
+      <c r="F46" s="4" t="n"/>
+      <c r="G46" s="4" t="n"/>
       <c r="H46" s="4" t="n"/>
       <c r="I46" s="4" t="n"/>
       <c r="J46" s="4" t="n"/>
@@ -3091,31 +3096,28 @@
       <c r="M46" s="4" t="n"/>
       <c r="N46" s="4" t="n"/>
       <c r="O46" s="4" t="n"/>
-      <c r="P46" s="4">
-        <f>SUM(D46:O46)</f>
-        <v/>
-      </c>
+      <c r="P46" s="4" t="n"/>
       <c r="Q46" s="4" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="14" t="inlineStr">
-        <is>
-          <t>Stock final marcos</t>
+      <c r="A47" s="15" t="inlineStr">
+        <is>
+          <t>Stock inicial marcos</t>
         </is>
       </c>
       <c r="B47" s="4" t="n"/>
       <c r="C47" s="4" t="n"/>
       <c r="D47" s="4" t="n">
+        <v>7471.59</v>
+      </c>
+      <c r="E47" s="4" t="n">
         <v>13032.64</v>
       </c>
-      <c r="E47" s="4" t="n">
+      <c r="F47" s="4" t="n">
         <v>10643.86</v>
       </c>
-      <c r="F47" s="4" t="n">
+      <c r="G47" s="4" t="n">
         <v>19745.79</v>
-      </c>
-      <c r="G47" s="4" t="n">
-        <v>19678.14</v>
       </c>
       <c r="H47" s="4" t="n"/>
       <c r="I47" s="4" t="n"/>
@@ -3130,6 +3132,40 @@
         <v/>
       </c>
       <c r="Q47" s="4" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="15" t="inlineStr">
+        <is>
+          <t>Stock final marcos</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="n"/>
+      <c r="C48" s="4" t="n"/>
+      <c r="D48" s="4" t="n">
+        <v>13032.64</v>
+      </c>
+      <c r="E48" s="4" t="n">
+        <v>10643.86</v>
+      </c>
+      <c r="F48" s="4" t="n">
+        <v>19745.79</v>
+      </c>
+      <c r="G48" s="4" t="n">
+        <v>19460.97</v>
+      </c>
+      <c r="H48" s="4" t="n"/>
+      <c r="I48" s="4" t="n"/>
+      <c r="J48" s="4" t="n"/>
+      <c r="K48" s="4" t="n"/>
+      <c r="L48" s="4" t="n"/>
+      <c r="M48" s="4" t="n"/>
+      <c r="N48" s="4" t="n"/>
+      <c r="O48" s="4" t="n"/>
+      <c r="P48" s="4">
+        <f>SUM(D48:O48)</f>
+        <v/>
+      </c>
+      <c r="Q48" s="4" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3145,13 +3181,13 @@
     <hyperlink ref="Q20" location="'g-expenses-ltd'!A1" display="-&gt;"/>
     <hyperlink ref="Q23" location="'g-payment-fees-ltd'!A1" display="-&gt;"/>
     <hyperlink ref="Q24" location="'g-payment-fees-ltd'!A1" display="-&gt;"/>
-    <hyperlink ref="Q34" location="'g-expenses-ltd'!A1" display="-&gt;"/>
     <hyperlink ref="Q35" location="'g-expenses-ltd'!A1" display="-&gt;"/>
     <hyperlink ref="Q36" location="'g-expenses-ltd'!A1" display="-&gt;"/>
     <hyperlink ref="Q37" location="'g-expenses-ltd'!A1" display="-&gt;"/>
     <hyperlink ref="Q38" location="'g-expenses-ltd'!A1" display="-&gt;"/>
     <hyperlink ref="Q39" location="'g-expenses-ltd'!A1" display="-&gt;"/>
     <hyperlink ref="Q40" location="'g-expenses-ltd'!A1" display="-&gt;"/>
+    <hyperlink ref="Q41" location="'g-expenses-ltd'!A1" display="-&gt;"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3171,19 +3207,19 @@
   </cols>
   <sheetData>
     <row r="1" ht="12" customHeight="1">
-      <c r="A1" s="15" t="inlineStr">
+      <c r="A1" s="16" t="inlineStr">
         <is>
           <t>&lt;- Volver a P&amp;G-LTD</t>
         </is>
       </c>
     </row>
     <row r="2" ht="12" customHeight="1">
-      <c r="A2" s="16" t="inlineStr">
+      <c r="A2" s="17" t="inlineStr">
         <is>
           <t>key</t>
         </is>
       </c>
-      <c r="B2" s="16" t="inlineStr">
+      <c r="B2" s="17" t="inlineStr">
         <is>
           <t>value</t>
         </is>
@@ -3231,7 +3267,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-04-04T10:00:15Z</t>
+          <t>2026-04-10T09:48:00Z</t>
         </is>
       </c>
     </row>
@@ -3265,59 +3301,59 @@
   </cols>
   <sheetData>
     <row r="1" ht="12" customHeight="1">
-      <c r="A1" s="15" t="inlineStr">
+      <c r="A1" s="16" t="inlineStr">
         <is>
           <t>&lt;- Volver a P&amp;G-LTD</t>
         </is>
       </c>
     </row>
     <row r="2" ht="12" customHeight="1">
-      <c r="A2" s="16" t="inlineStr">
+      <c r="A2" s="17" t="inlineStr">
         <is>
           <t>yyyymm</t>
         </is>
       </c>
-      <c r="B2" s="16" t="inlineStr">
+      <c r="B2" s="17" t="inlineStr">
         <is>
           <t>entity</t>
         </is>
       </c>
-      <c r="C2" s="16" t="inlineStr">
+      <c r="C2" s="17" t="inlineStr">
         <is>
           <t>line_item</t>
         </is>
       </c>
-      <c r="D2" s="16" t="inlineStr">
+      <c r="D2" s="17" t="inlineStr">
         <is>
           <t>detail</t>
         </is>
       </c>
-      <c r="E2" s="16" t="inlineStr">
+      <c r="E2" s="17" t="inlineStr">
         <is>
           <t>amount_original</t>
         </is>
       </c>
-      <c r="F2" s="16" t="inlineStr">
+      <c r="F2" s="17" t="inlineStr">
         <is>
           <t>currency_original</t>
         </is>
       </c>
-      <c r="G2" s="16" t="inlineStr">
+      <c r="G2" s="17" t="inlineStr">
         <is>
           <t>reporting_currency</t>
         </is>
       </c>
-      <c r="H2" s="16" t="inlineStr">
+      <c r="H2" s="17" t="inlineStr">
         <is>
           <t>fx_rate</t>
         </is>
       </c>
-      <c r="I2" s="16" t="inlineStr">
+      <c r="I2" s="17" t="inlineStr">
         <is>
           <t>amount_reporting</t>
         </is>
       </c>
-      <c r="J2" s="16" t="inlineStr">
+      <c r="J2" s="17" t="inlineStr">
         <is>
           <t>source</t>
         </is>
@@ -3357,7 +3393,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="H3" s="17" t="n">
+      <c r="H3" s="18" t="n">
         <v>1</v>
       </c>
       <c r="I3" s="4" t="n">
@@ -3403,7 +3439,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="H4" s="17" t="n">
+      <c r="H4" s="18" t="n">
         <v>1</v>
       </c>
       <c r="I4" s="4" t="n">
@@ -3449,7 +3485,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="H5" s="17" t="n">
+      <c r="H5" s="18" t="n">
         <v>1</v>
       </c>
       <c r="I5" s="4" t="n">
@@ -3483,7 +3519,7 @@
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>1333.46</v>
+        <v>5572.05</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -3495,11 +3531,11 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="H6" s="17" t="n">
+      <c r="H6" s="18" t="n">
         <v>1</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>1333.46</v>
+        <v>5572.05</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -3521,7 +3557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N143"/>
+  <dimension ref="A1:N146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3541,79 +3577,79 @@
   </cols>
   <sheetData>
     <row r="1" ht="12" customHeight="1">
-      <c r="A1" s="15" t="inlineStr">
+      <c r="A1" s="16" t="inlineStr">
         <is>
           <t>&lt;- Volver a P&amp;G-LTD</t>
         </is>
       </c>
     </row>
     <row r="2" ht="12" customHeight="1">
-      <c r="A2" s="16" t="inlineStr">
+      <c r="A2" s="17" t="inlineStr">
         <is>
           <t>yyyymm</t>
         </is>
       </c>
-      <c r="B2" s="16" t="inlineStr">
+      <c r="B2" s="17" t="inlineStr">
         <is>
           <t>entity</t>
         </is>
       </c>
-      <c r="C2" s="16" t="inlineStr">
+      <c r="C2" s="17" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="D2" s="16" t="inlineStr">
+      <c r="D2" s="17" t="inlineStr">
         <is>
           <t>subcategory</t>
         </is>
       </c>
-      <c r="E2" s="16" t="inlineStr">
+      <c r="E2" s="17" t="inlineStr">
         <is>
           <t>supplier_code</t>
         </is>
       </c>
-      <c r="F2" s="16" t="inlineStr">
+      <c r="F2" s="17" t="inlineStr">
         <is>
           <t>detail</t>
         </is>
       </c>
-      <c r="G2" s="16" t="inlineStr">
+      <c r="G2" s="17" t="inlineStr">
         <is>
           <t>amount_original</t>
         </is>
       </c>
-      <c r="H2" s="16" t="inlineStr">
+      <c r="H2" s="17" t="inlineStr">
         <is>
           <t>currency_original</t>
         </is>
       </c>
-      <c r="I2" s="16" t="inlineStr">
+      <c r="I2" s="17" t="inlineStr">
         <is>
           <t>reporting_currency</t>
         </is>
       </c>
-      <c r="J2" s="16" t="inlineStr">
+      <c r="J2" s="17" t="inlineStr">
         <is>
           <t>fx_rate</t>
         </is>
       </c>
-      <c r="K2" s="16" t="inlineStr">
+      <c r="K2" s="17" t="inlineStr">
         <is>
           <t>amount_reporting</t>
         </is>
       </c>
-      <c r="L2" s="16" t="inlineStr">
+      <c r="L2" s="17" t="inlineStr">
         <is>
           <t>source</t>
         </is>
       </c>
-      <c r="M2" s="16" t="inlineStr">
+      <c r="M2" s="17" t="inlineStr">
         <is>
           <t>invoice_number</t>
         </is>
       </c>
-      <c r="N2" s="16" t="inlineStr">
+      <c r="N2" s="17" t="inlineStr">
         <is>
           <t>drive_url</t>
         </is>
@@ -3663,7 +3699,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J3" s="17" t="n">
+      <c r="J3" s="18" t="n">
         <v>0.72673882</v>
       </c>
       <c r="K3" s="4" t="n">
@@ -3674,7 +3710,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M3" s="18" t="inlineStr">
+      <c r="M3" s="19" t="inlineStr">
         <is>
           <t>AS-94763</t>
         </is>
@@ -3729,7 +3765,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J4" s="17" t="n">
+      <c r="J4" s="18" t="n">
         <v>0.72673882</v>
       </c>
       <c r="K4" s="4" t="n">
@@ -3740,7 +3776,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M4" s="18" t="inlineStr">
+      <c r="M4" s="19" t="inlineStr">
         <is>
           <t>AS-94832</t>
         </is>
@@ -3795,7 +3831,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J5" s="17" t="n">
+      <c r="J5" s="18" t="n">
         <v>0.72673882</v>
       </c>
       <c r="K5" s="4" t="n">
@@ -3806,7 +3842,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M5" s="18" t="inlineStr">
+      <c r="M5" s="19" t="inlineStr">
         <is>
           <t>AS-95021</t>
         </is>
@@ -3861,7 +3897,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J6" s="17" t="n">
+      <c r="J6" s="18" t="n">
         <v>0.72673882</v>
       </c>
       <c r="K6" s="4" t="n">
@@ -3872,7 +3908,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M6" s="18" t="inlineStr">
+      <c r="M6" s="19" t="inlineStr">
         <is>
           <t>AS-95024</t>
         </is>
@@ -3927,7 +3963,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J7" s="17" t="n">
+      <c r="J7" s="18" t="n">
         <v>0.72673882</v>
       </c>
       <c r="K7" s="4" t="n">
@@ -3938,7 +3974,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M7" s="18" t="inlineStr">
+      <c r="M7" s="19" t="inlineStr">
         <is>
           <t>AS-95158</t>
         </is>
@@ -3993,7 +4029,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J8" s="17" t="n">
+      <c r="J8" s="18" t="n">
         <v>0.72673882</v>
       </c>
       <c r="K8" s="4" t="n">
@@ -4004,7 +4040,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M8" s="18" t="inlineStr">
+      <c r="M8" s="19" t="inlineStr">
         <is>
           <t>AS-95275</t>
         </is>
@@ -4059,7 +4095,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J9" s="17" t="n">
+      <c r="J9" s="18" t="n">
         <v>0.72673882</v>
       </c>
       <c r="K9" s="4" t="n">
@@ -4070,7 +4106,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M9" s="18" t="inlineStr">
+      <c r="M9" s="19" t="inlineStr">
         <is>
           <t>AS-95319</t>
         </is>
@@ -4125,7 +4161,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J10" s="17" t="n">
+      <c r="J10" s="18" t="n">
         <v>0.72673882</v>
       </c>
       <c r="K10" s="4" t="n">
@@ -4136,7 +4172,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M10" s="18" t="inlineStr">
+      <c r="M10" s="19" t="inlineStr">
         <is>
           <t>AS-95383</t>
         </is>
@@ -4191,7 +4227,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J11" s="17" t="n">
+      <c r="J11" s="18" t="n">
         <v>0.72673882</v>
       </c>
       <c r="K11" s="4" t="n">
@@ -4202,7 +4238,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M11" s="18" t="inlineStr">
+      <c r="M11" s="19" t="inlineStr">
         <is>
           <t>AS-95462</t>
         </is>
@@ -4257,7 +4293,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J12" s="17" t="n">
+      <c r="J12" s="18" t="n">
         <v>0.72673882</v>
       </c>
       <c r="K12" s="4" t="n">
@@ -4268,7 +4304,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M12" s="18" t="inlineStr">
+      <c r="M12" s="19" t="inlineStr">
         <is>
           <t>AS-95630</t>
         </is>
@@ -4323,7 +4359,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J13" s="17" t="n">
+      <c r="J13" s="18" t="n">
         <v>0.72673882</v>
       </c>
       <c r="K13" s="4" t="n">
@@ -4334,7 +4370,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M13" s="18" t="inlineStr">
+      <c r="M13" s="19" t="inlineStr">
         <is>
           <t>AS-95636</t>
         </is>
@@ -4389,7 +4425,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J14" s="17" t="n">
+      <c r="J14" s="18" t="n">
         <v>0.72673882</v>
       </c>
       <c r="K14" s="4" t="n">
@@ -4400,7 +4436,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M14" s="18" t="inlineStr">
+      <c r="M14" s="19" t="inlineStr">
         <is>
           <t>AS-95652</t>
         </is>
@@ -4455,7 +4491,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J15" s="17" t="n">
+      <c r="J15" s="18" t="n">
         <v>0.72673882</v>
       </c>
       <c r="K15" s="4" t="n">
@@ -4466,7 +4502,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M15" s="18" t="inlineStr">
+      <c r="M15" s="19" t="inlineStr">
         <is>
           <t>AS-95716</t>
         </is>
@@ -4521,7 +4557,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J16" s="17" t="n">
+      <c r="J16" s="18" t="n">
         <v>0.72673882</v>
       </c>
       <c r="K16" s="4" t="n">
@@ -4532,7 +4568,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M16" s="18" t="inlineStr">
+      <c r="M16" s="19" t="inlineStr">
         <is>
           <t>AS-95748</t>
         </is>
@@ -4587,7 +4623,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J17" s="17" t="n">
+      <c r="J17" s="18" t="n">
         <v>0.72673882</v>
       </c>
       <c r="K17" s="4" t="n">
@@ -4598,7 +4634,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M17" s="18" t="inlineStr">
+      <c r="M17" s="19" t="inlineStr">
         <is>
           <t>AS-95763</t>
         </is>
@@ -4653,7 +4689,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J18" s="17" t="n">
+      <c r="J18" s="18" t="n">
         <v>0.72673882</v>
       </c>
       <c r="K18" s="4" t="n">
@@ -4664,7 +4700,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M18" s="18" t="inlineStr">
+      <c r="M18" s="19" t="inlineStr">
         <is>
           <t>AS-95778</t>
         </is>
@@ -4719,7 +4755,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J19" s="17" t="n">
+      <c r="J19" s="18" t="n">
         <v>0.72673882</v>
       </c>
       <c r="K19" s="4" t="n">
@@ -4730,7 +4766,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M19" s="18" t="inlineStr">
+      <c r="M19" s="19" t="inlineStr">
         <is>
           <t>AS-96078</t>
         </is>
@@ -4785,7 +4821,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J20" s="17" t="n">
+      <c r="J20" s="18" t="n">
         <v>0.72673882</v>
       </c>
       <c r="K20" s="4" t="n">
@@ -4796,7 +4832,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M20" s="18" t="inlineStr">
+      <c r="M20" s="19" t="inlineStr">
         <is>
           <t>AS-96170</t>
         </is>
@@ -4851,7 +4887,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J21" s="17" t="n">
+      <c r="J21" s="18" t="n">
         <v>0.72673882</v>
       </c>
       <c r="K21" s="4" t="n">
@@ -4862,7 +4898,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M21" s="18" t="inlineStr">
+      <c r="M21" s="19" t="inlineStr">
         <is>
           <t>AS-96234</t>
         </is>
@@ -4917,7 +4953,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J22" s="17" t="n">
+      <c r="J22" s="18" t="n">
         <v>0.72673882</v>
       </c>
       <c r="K22" s="4" t="n">
@@ -4928,7 +4964,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M22" s="18" t="inlineStr">
+      <c r="M22" s="19" t="inlineStr">
         <is>
           <t>AS-96246</t>
         </is>
@@ -4983,7 +5019,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J23" s="17" t="n">
+      <c r="J23" s="18" t="n">
         <v>0.72673882</v>
       </c>
       <c r="K23" s="4" t="n">
@@ -4994,7 +5030,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M23" s="18" t="inlineStr">
+      <c r="M23" s="19" t="inlineStr">
         <is>
           <t>AS-96512</t>
         </is>
@@ -5049,7 +5085,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J24" s="17" t="n">
+      <c r="J24" s="18" t="n">
         <v>0.72673882</v>
       </c>
       <c r="K24" s="4" t="n">
@@ -5060,7 +5096,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M24" s="18" t="inlineStr">
+      <c r="M24" s="19" t="inlineStr">
         <is>
           <t>AS-96838</t>
         </is>
@@ -5115,7 +5151,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J25" s="17" t="n">
+      <c r="J25" s="18" t="n">
         <v>0.72673882</v>
       </c>
       <c r="K25" s="4" t="n">
@@ -5126,7 +5162,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M25" s="18" t="inlineStr">
+      <c r="M25" s="19" t="inlineStr">
         <is>
           <t>AS-97012</t>
         </is>
@@ -5181,7 +5217,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J26" s="17" t="n">
+      <c r="J26" s="18" t="n">
         <v>0.72673882</v>
       </c>
       <c r="K26" s="4" t="n">
@@ -5192,7 +5228,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M26" s="18" t="inlineStr">
+      <c r="M26" s="19" t="inlineStr">
         <is>
           <t>AS-97038</t>
         </is>
@@ -5247,7 +5283,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J27" s="17" t="n">
+      <c r="J27" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K27" s="4" t="n">
@@ -5258,7 +5294,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M27" s="18" t="inlineStr">
+      <c r="M27" s="19" t="inlineStr">
         <is>
           <t>6032421</t>
         </is>
@@ -5313,7 +5349,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J28" s="17" t="n">
+      <c r="J28" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K28" s="4" t="n">
@@ -5324,7 +5360,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M28" s="18" t="inlineStr">
+      <c r="M28" s="19" t="inlineStr">
         <is>
           <t>6032421</t>
         </is>
@@ -5379,7 +5415,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J29" s="17" t="n">
+      <c r="J29" s="18" t="n">
         <v>0.8662</v>
       </c>
       <c r="K29" s="4" t="n">
@@ -5390,7 +5426,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M29" s="18" t="inlineStr">
+      <c r="M29" s="19" t="inlineStr">
         <is>
           <t>2026-0010</t>
         </is>
@@ -5445,7 +5481,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J30" s="17" t="n">
+      <c r="J30" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K30" s="4" t="n">
@@ -5456,7 +5492,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M30" s="18" t="inlineStr">
+      <c r="M30" s="19" t="inlineStr">
         <is>
           <t>INV-0679_PERIODIFICADA_1_12</t>
         </is>
@@ -5511,7 +5547,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J31" s="17" t="n">
+      <c r="J31" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K31" s="4" t="n">
@@ -5522,7 +5558,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M31" s="18" t="inlineStr">
+      <c r="M31" s="19" t="inlineStr">
         <is>
           <t>INV-0682_PERIODIFICADA_1_12</t>
         </is>
@@ -5577,7 +5613,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J32" s="17" t="n">
+      <c r="J32" s="18" t="n">
         <v>0.74231258</v>
       </c>
       <c r="K32" s="4" t="n">
@@ -5588,7 +5624,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M32" s="18" t="inlineStr">
+      <c r="M32" s="19" t="inlineStr">
         <is>
           <t>AS-97196</t>
         </is>
@@ -5643,7 +5679,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J33" s="17" t="n">
+      <c r="J33" s="18" t="n">
         <v>0.74231258</v>
       </c>
       <c r="K33" s="4" t="n">
@@ -5654,7 +5690,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M33" s="18" t="inlineStr">
+      <c r="M33" s="19" t="inlineStr">
         <is>
           <t>AS-97254</t>
         </is>
@@ -5709,7 +5745,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J34" s="17" t="n">
+      <c r="J34" s="18" t="n">
         <v>0.74231258</v>
       </c>
       <c r="K34" s="4" t="n">
@@ -5720,7 +5756,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M34" s="18" t="inlineStr">
+      <c r="M34" s="19" t="inlineStr">
         <is>
           <t>AS-97464</t>
         </is>
@@ -5775,7 +5811,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J35" s="17" t="n">
+      <c r="J35" s="18" t="n">
         <v>0.74231258</v>
       </c>
       <c r="K35" s="4" t="n">
@@ -5786,7 +5822,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M35" s="18" t="inlineStr">
+      <c r="M35" s="19" t="inlineStr">
         <is>
           <t>AS-97516</t>
         </is>
@@ -5841,7 +5877,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J36" s="17" t="n">
+      <c r="J36" s="18" t="n">
         <v>0.74231258</v>
       </c>
       <c r="K36" s="4" t="n">
@@ -5852,7 +5888,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M36" s="18" t="inlineStr">
+      <c r="M36" s="19" t="inlineStr">
         <is>
           <t>AS-97520</t>
         </is>
@@ -5907,7 +5943,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J37" s="17" t="n">
+      <c r="J37" s="18" t="n">
         <v>0.74231258</v>
       </c>
       <c r="K37" s="4" t="n">
@@ -5918,7 +5954,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M37" s="18" t="inlineStr">
+      <c r="M37" s="19" t="inlineStr">
         <is>
           <t>AS-97602</t>
         </is>
@@ -5973,7 +6009,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J38" s="17" t="n">
+      <c r="J38" s="18" t="n">
         <v>0.74231258</v>
       </c>
       <c r="K38" s="4" t="n">
@@ -5984,7 +6020,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M38" s="18" t="inlineStr">
+      <c r="M38" s="19" t="inlineStr">
         <is>
           <t>AS-98142</t>
         </is>
@@ -6039,7 +6075,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J39" s="17" t="n">
+      <c r="J39" s="18" t="n">
         <v>0.74231258</v>
       </c>
       <c r="K39" s="4" t="n">
@@ -6050,7 +6086,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M39" s="18" t="inlineStr">
+      <c r="M39" s="19" t="inlineStr">
         <is>
           <t>AS-98380</t>
         </is>
@@ -6105,7 +6141,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J40" s="17" t="n">
+      <c r="J40" s="18" t="n">
         <v>0.74231258</v>
       </c>
       <c r="K40" s="4" t="n">
@@ -6116,7 +6152,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M40" s="18" t="inlineStr">
+      <c r="M40" s="19" t="inlineStr">
         <is>
           <t>AS-98382</t>
         </is>
@@ -6171,7 +6207,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J41" s="17" t="n">
+      <c r="J41" s="18" t="n">
         <v>0.74231258</v>
       </c>
       <c r="K41" s="4" t="n">
@@ -6182,7 +6218,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M41" s="18" t="inlineStr">
+      <c r="M41" s="19" t="inlineStr">
         <is>
           <t>AS-98403</t>
         </is>
@@ -6237,7 +6273,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J42" s="17" t="n">
+      <c r="J42" s="18" t="n">
         <v>0.74231258</v>
       </c>
       <c r="K42" s="4" t="n">
@@ -6248,7 +6284,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M42" s="18" t="inlineStr">
+      <c r="M42" s="19" t="inlineStr">
         <is>
           <t>AS-98524</t>
         </is>
@@ -6303,7 +6339,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J43" s="17" t="n">
+      <c r="J43" s="18" t="n">
         <v>0.74231258</v>
       </c>
       <c r="K43" s="4" t="n">
@@ -6314,7 +6350,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M43" s="18" t="inlineStr">
+      <c r="M43" s="19" t="inlineStr">
         <is>
           <t>AS-98544</t>
         </is>
@@ -6369,7 +6405,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J44" s="17" t="n">
+      <c r="J44" s="18" t="n">
         <v>0.74231258</v>
       </c>
       <c r="K44" s="4" t="n">
@@ -6380,7 +6416,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M44" s="18" t="inlineStr">
+      <c r="M44" s="19" t="inlineStr">
         <is>
           <t>AS-98563</t>
         </is>
@@ -6435,7 +6471,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J45" s="17" t="n">
+      <c r="J45" s="18" t="n">
         <v>0.74231258</v>
       </c>
       <c r="K45" s="4" t="n">
@@ -6446,7 +6482,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M45" s="18" t="inlineStr">
+      <c r="M45" s="19" t="inlineStr">
         <is>
           <t>AS-98567</t>
         </is>
@@ -6501,7 +6537,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J46" s="17" t="n">
+      <c r="J46" s="18" t="n">
         <v>0.74231258</v>
       </c>
       <c r="K46" s="4" t="n">
@@ -6512,7 +6548,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M46" s="18" t="inlineStr">
+      <c r="M46" s="19" t="inlineStr">
         <is>
           <t>AS-98978</t>
         </is>
@@ -6567,7 +6603,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J47" s="17" t="n">
+      <c r="J47" s="18" t="n">
         <v>0.74231258</v>
       </c>
       <c r="K47" s="4" t="n">
@@ -6578,7 +6614,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M47" s="18" t="inlineStr">
+      <c r="M47" s="19" t="inlineStr">
         <is>
           <t>AS-99094</t>
         </is>
@@ -6633,7 +6669,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J48" s="17" t="n">
+      <c r="J48" s="18" t="n">
         <v>0.74231258</v>
       </c>
       <c r="K48" s="4" t="n">
@@ -6644,7 +6680,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M48" s="18" t="inlineStr">
+      <c r="M48" s="19" t="inlineStr">
         <is>
           <t>AS-99179</t>
         </is>
@@ -6699,7 +6735,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J49" s="17" t="n">
+      <c r="J49" s="18" t="n">
         <v>0.74231258</v>
       </c>
       <c r="K49" s="4" t="n">
@@ -6710,7 +6746,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M49" s="18" t="inlineStr">
+      <c r="M49" s="19" t="inlineStr">
         <is>
           <t>AS-99349</t>
         </is>
@@ -6765,7 +6801,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J50" s="17" t="n">
+      <c r="J50" s="18" t="n">
         <v>0.74231258</v>
       </c>
       <c r="K50" s="4" t="n">
@@ -6776,7 +6812,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M50" s="18" t="inlineStr">
+      <c r="M50" s="19" t="inlineStr">
         <is>
           <t>AS-99356</t>
         </is>
@@ -6831,7 +6867,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J51" s="17" t="n">
+      <c r="J51" s="18" t="n">
         <v>0.74231258</v>
       </c>
       <c r="K51" s="4" t="n">
@@ -6842,7 +6878,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M51" s="18" t="inlineStr">
+      <c r="M51" s="19" t="inlineStr">
         <is>
           <t>AS-99390</t>
         </is>
@@ -6897,7 +6933,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J52" s="17" t="n">
+      <c r="J52" s="18" t="n">
         <v>0.74231258</v>
       </c>
       <c r="K52" s="4" t="n">
@@ -6908,7 +6944,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M52" s="18" t="inlineStr">
+      <c r="M52" s="19" t="inlineStr">
         <is>
           <t>AS-99509</t>
         </is>
@@ -6963,7 +6999,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J53" s="17" t="n">
+      <c r="J53" s="18" t="n">
         <v>0.74231258</v>
       </c>
       <c r="K53" s="4" t="n">
@@ -6974,7 +7010,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M53" s="18" t="inlineStr">
+      <c r="M53" s="19" t="inlineStr">
         <is>
           <t>AS-99616</t>
         </is>
@@ -7029,7 +7065,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J54" s="17" t="n">
+      <c r="J54" s="18" t="n">
         <v>0.74231258</v>
       </c>
       <c r="K54" s="4" t="n">
@@ -7040,7 +7076,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M54" s="18" t="inlineStr">
+      <c r="M54" s="19" t="inlineStr">
         <is>
           <t>AS-99632</t>
         </is>
@@ -7095,7 +7131,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J55" s="17" t="n">
+      <c r="J55" s="18" t="n">
         <v>0.74231258</v>
       </c>
       <c r="K55" s="4" t="n">
@@ -7106,7 +7142,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M55" s="18" t="inlineStr">
+      <c r="M55" s="19" t="inlineStr">
         <is>
           <t>AS-99779</t>
         </is>
@@ -7161,7 +7197,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J56" s="17" t="n">
+      <c r="J56" s="18" t="n">
         <v>0.74231258</v>
       </c>
       <c r="K56" s="4" t="n">
@@ -7172,7 +7208,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M56" s="18" t="inlineStr">
+      <c r="M56" s="19" t="inlineStr">
         <is>
           <t>AS-99780</t>
         </is>
@@ -7227,7 +7263,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J57" s="17" t="n">
+      <c r="J57" s="18" t="n">
         <v>0.74231258</v>
       </c>
       <c r="K57" s="4" t="n">
@@ -7238,7 +7274,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M57" s="18" t="inlineStr">
+      <c r="M57" s="19" t="inlineStr">
         <is>
           <t>AS-99822</t>
         </is>
@@ -7293,7 +7329,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J58" s="17" t="n">
+      <c r="J58" s="18" t="n">
         <v>0.74231258</v>
       </c>
       <c r="K58" s="4" t="n">
@@ -7304,7 +7340,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M58" s="18" t="inlineStr">
+      <c r="M58" s="19" t="inlineStr">
         <is>
           <t>AS-99880</t>
         </is>
@@ -7359,7 +7395,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J59" s="17" t="n">
+      <c r="J59" s="18" t="n">
         <v>0.74231258</v>
       </c>
       <c r="K59" s="4" t="n">
@@ -7370,7 +7406,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M59" s="18" t="inlineStr">
+      <c r="M59" s="19" t="inlineStr">
         <is>
           <t>AS-99886</t>
         </is>
@@ -7425,7 +7461,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J60" s="17" t="n">
+      <c r="J60" s="18" t="n">
         <v>0.74231258</v>
       </c>
       <c r="K60" s="4" t="n">
@@ -7436,7 +7472,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M60" s="18" t="inlineStr">
+      <c r="M60" s="19" t="inlineStr">
         <is>
           <t>AS-99899</t>
         </is>
@@ -7465,7 +7501,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>logistics</t>
+          <t>manufacturing</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -7475,11 +7511,11 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>logistics</t>
+          <t>manufacturing</t>
         </is>
       </c>
       <c r="G61" s="4" t="n">
-        <v>1670.3</v>
+        <v>4593.8</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
@@ -7491,18 +7527,18 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J61" s="17" t="n">
+      <c r="J61" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>1670.3</v>
+        <v>4593.8</v>
       </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>documents</t>
         </is>
       </c>
-      <c r="M61" s="18" t="inlineStr">
+      <c r="M61" s="19" t="inlineStr">
         <is>
           <t>6033326</t>
         </is>
@@ -7531,7 +7567,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>manufacturing</t>
+          <t>logistics</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -7541,11 +7577,11 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>manufacturing</t>
+          <t>logistics</t>
         </is>
       </c>
       <c r="G62" s="4" t="n">
-        <v>4593.8</v>
+        <v>1670.3</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -7557,18 +7593,18 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J62" s="17" t="n">
+      <c r="J62" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>4593.8</v>
+        <v>1670.3</v>
       </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>documents</t>
         </is>
       </c>
-      <c r="M62" s="18" t="inlineStr">
+      <c r="M62" s="19" t="inlineStr">
         <is>
           <t>6033326</t>
         </is>
@@ -7623,7 +7659,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J63" s="17" t="n">
+      <c r="J63" s="18" t="n">
         <v>0.8763</v>
       </c>
       <c r="K63" s="4" t="n">
@@ -7634,7 +7670,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M63" s="18" t="inlineStr">
+      <c r="M63" s="19" t="inlineStr">
         <is>
           <t>2026-0015</t>
         </is>
@@ -7689,7 +7725,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J64" s="17" t="n">
+      <c r="J64" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K64" s="4" t="n">
@@ -7700,7 +7736,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M64" s="18" t="inlineStr">
+      <c r="M64" s="19" t="inlineStr">
         <is>
           <t>INV-0679_PERIODIFICADA_2_12</t>
         </is>
@@ -7755,7 +7791,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J65" s="17" t="n">
+      <c r="J65" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K65" s="4" t="n">
@@ -7766,7 +7802,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M65" s="18" t="inlineStr">
+      <c r="M65" s="19" t="inlineStr">
         <is>
           <t>INV-0681_PERIODIFICADA_1_12</t>
         </is>
@@ -7821,7 +7857,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J66" s="17" t="n">
+      <c r="J66" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K66" s="4" t="n">
@@ -7832,7 +7868,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M66" s="18" t="inlineStr">
+      <c r="M66" s="19" t="inlineStr">
         <is>
           <t>INV-0682_PERIODIFICADA_2_12</t>
         </is>
@@ -7887,7 +7923,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J67" s="17" t="n">
+      <c r="J67" s="18" t="n">
         <v>0.7552009</v>
       </c>
       <c r="K67" s="4" t="n">
@@ -7898,7 +7934,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M67" s="18" t="inlineStr">
+      <c r="M67" s="19" t="inlineStr">
         <is>
           <t>AS-100037</t>
         </is>
@@ -7953,7 +7989,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J68" s="17" t="n">
+      <c r="J68" s="18" t="n">
         <v>0.7552009</v>
       </c>
       <c r="K68" s="4" t="n">
@@ -7964,7 +8000,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M68" s="18" t="inlineStr">
+      <c r="M68" s="19" t="inlineStr">
         <is>
           <t>AS-100054</t>
         </is>
@@ -8019,7 +8055,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J69" s="17" t="n">
+      <c r="J69" s="18" t="n">
         <v>0.7552009</v>
       </c>
       <c r="K69" s="4" t="n">
@@ -8030,7 +8066,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M69" s="18" t="inlineStr">
+      <c r="M69" s="19" t="inlineStr">
         <is>
           <t>AS-100099</t>
         </is>
@@ -8085,7 +8121,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J70" s="17" t="n">
+      <c r="J70" s="18" t="n">
         <v>0.7552009</v>
       </c>
       <c r="K70" s="4" t="n">
@@ -8096,7 +8132,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M70" s="18" t="inlineStr">
+      <c r="M70" s="19" t="inlineStr">
         <is>
           <t>AS-100109</t>
         </is>
@@ -8151,7 +8187,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J71" s="17" t="n">
+      <c r="J71" s="18" t="n">
         <v>0.7552009</v>
       </c>
       <c r="K71" s="4" t="n">
@@ -8162,7 +8198,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M71" s="18" t="inlineStr">
+      <c r="M71" s="19" t="inlineStr">
         <is>
           <t>AS-100157</t>
         </is>
@@ -8217,7 +8253,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J72" s="17" t="n">
+      <c r="J72" s="18" t="n">
         <v>0.7552009</v>
       </c>
       <c r="K72" s="4" t="n">
@@ -8228,7 +8264,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M72" s="18" t="inlineStr">
+      <c r="M72" s="19" t="inlineStr">
         <is>
           <t>AS-100239</t>
         </is>
@@ -8283,7 +8319,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J73" s="17" t="n">
+      <c r="J73" s="18" t="n">
         <v>0.7552009</v>
       </c>
       <c r="K73" s="4" t="n">
@@ -8294,7 +8330,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M73" s="18" t="inlineStr">
+      <c r="M73" s="19" t="inlineStr">
         <is>
           <t>AS-100248</t>
         </is>
@@ -8349,7 +8385,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J74" s="17" t="n">
+      <c r="J74" s="18" t="n">
         <v>0.7552009</v>
       </c>
       <c r="K74" s="4" t="n">
@@ -8360,7 +8396,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M74" s="18" t="inlineStr">
+      <c r="M74" s="19" t="inlineStr">
         <is>
           <t>AS-100286</t>
         </is>
@@ -8415,7 +8451,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J75" s="17" t="n">
+      <c r="J75" s="18" t="n">
         <v>0.7552009</v>
       </c>
       <c r="K75" s="4" t="n">
@@ -8426,7 +8462,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M75" s="18" t="inlineStr">
+      <c r="M75" s="19" t="inlineStr">
         <is>
           <t>AS-100339</t>
         </is>
@@ -8481,7 +8517,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J76" s="17" t="n">
+      <c r="J76" s="18" t="n">
         <v>0.7552009</v>
       </c>
       <c r="K76" s="4" t="n">
@@ -8492,7 +8528,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M76" s="18" t="inlineStr">
+      <c r="M76" s="19" t="inlineStr">
         <is>
           <t>AS-100443</t>
         </is>
@@ -8547,7 +8583,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J77" s="17" t="n">
+      <c r="J77" s="18" t="n">
         <v>0.7552009</v>
       </c>
       <c r="K77" s="4" t="n">
@@ -8558,7 +8594,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M77" s="18" t="inlineStr">
+      <c r="M77" s="19" t="inlineStr">
         <is>
           <t>AS-100562</t>
         </is>
@@ -8613,7 +8649,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J78" s="17" t="n">
+      <c r="J78" s="18" t="n">
         <v>0.7552009</v>
       </c>
       <c r="K78" s="4" t="n">
@@ -8624,7 +8660,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M78" s="18" t="inlineStr">
+      <c r="M78" s="19" t="inlineStr">
         <is>
           <t>AS-100662</t>
         </is>
@@ -8679,7 +8715,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J79" s="17" t="n">
+      <c r="J79" s="18" t="n">
         <v>0.7552009</v>
       </c>
       <c r="K79" s="4" t="n">
@@ -8690,7 +8726,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M79" s="18" t="inlineStr">
+      <c r="M79" s="19" t="inlineStr">
         <is>
           <t>AS-100690</t>
         </is>
@@ -8745,7 +8781,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J80" s="17" t="n">
+      <c r="J80" s="18" t="n">
         <v>0.7552009</v>
       </c>
       <c r="K80" s="4" t="n">
@@ -8756,7 +8792,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M80" s="18" t="inlineStr">
+      <c r="M80" s="19" t="inlineStr">
         <is>
           <t>AS-100702</t>
         </is>
@@ -8811,7 +8847,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J81" s="17" t="n">
+      <c r="J81" s="18" t="n">
         <v>0.7552009</v>
       </c>
       <c r="K81" s="4" t="n">
@@ -8822,7 +8858,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M81" s="18" t="inlineStr">
+      <c r="M81" s="19" t="inlineStr">
         <is>
           <t>AS-100782</t>
         </is>
@@ -8877,7 +8913,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J82" s="17" t="n">
+      <c r="J82" s="18" t="n">
         <v>0.7552009</v>
       </c>
       <c r="K82" s="4" t="n">
@@ -8888,7 +8924,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M82" s="18" t="inlineStr">
+      <c r="M82" s="19" t="inlineStr">
         <is>
           <t>AS-100814</t>
         </is>
@@ -8943,7 +8979,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J83" s="17" t="n">
+      <c r="J83" s="18" t="n">
         <v>0.7552009</v>
       </c>
       <c r="K83" s="4" t="n">
@@ -8954,7 +8990,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M83" s="18" t="inlineStr">
+      <c r="M83" s="19" t="inlineStr">
         <is>
           <t>AS-100856</t>
         </is>
@@ -9009,7 +9045,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J84" s="17" t="n">
+      <c r="J84" s="18" t="n">
         <v>0.7552009</v>
       </c>
       <c r="K84" s="4" t="n">
@@ -9020,7 +9056,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M84" s="18" t="inlineStr">
+      <c r="M84" s="19" t="inlineStr">
         <is>
           <t>AS-100911</t>
         </is>
@@ -9075,7 +9111,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J85" s="17" t="n">
+      <c r="J85" s="18" t="n">
         <v>0.7552009</v>
       </c>
       <c r="K85" s="4" t="n">
@@ -9086,7 +9122,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M85" s="18" t="inlineStr">
+      <c r="M85" s="19" t="inlineStr">
         <is>
           <t>AS-100918</t>
         </is>
@@ -9141,7 +9177,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J86" s="17" t="n">
+      <c r="J86" s="18" t="n">
         <v>0.7552009</v>
       </c>
       <c r="K86" s="4" t="n">
@@ -9152,7 +9188,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M86" s="18" t="inlineStr">
+      <c r="M86" s="19" t="inlineStr">
         <is>
           <t>AS-100977</t>
         </is>
@@ -9207,7 +9243,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J87" s="17" t="n">
+      <c r="J87" s="18" t="n">
         <v>0.7552009</v>
       </c>
       <c r="K87" s="4" t="n">
@@ -9218,7 +9254,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M87" s="18" t="inlineStr">
+      <c r="M87" s="19" t="inlineStr">
         <is>
           <t>AS-101054</t>
         </is>
@@ -9273,7 +9309,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J88" s="17" t="n">
+      <c r="J88" s="18" t="n">
         <v>0.7552009</v>
       </c>
       <c r="K88" s="4" t="n">
@@ -9284,7 +9320,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M88" s="18" t="inlineStr">
+      <c r="M88" s="19" t="inlineStr">
         <is>
           <t>AS-101073</t>
         </is>
@@ -9339,7 +9375,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J89" s="17" t="n">
+      <c r="J89" s="18" t="n">
         <v>0.7552009</v>
       </c>
       <c r="K89" s="4" t="n">
@@ -9350,7 +9386,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M89" s="18" t="inlineStr">
+      <c r="M89" s="19" t="inlineStr">
         <is>
           <t>AS-101183</t>
         </is>
@@ -9405,7 +9441,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J90" s="17" t="n">
+      <c r="J90" s="18" t="n">
         <v>0.7552009</v>
       </c>
       <c r="K90" s="4" t="n">
@@ -9416,7 +9452,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M90" s="18" t="inlineStr">
+      <c r="M90" s="19" t="inlineStr">
         <is>
           <t>AS-101240</t>
         </is>
@@ -9471,7 +9507,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J91" s="17" t="n">
+      <c r="J91" s="18" t="n">
         <v>0.7552009</v>
       </c>
       <c r="K91" s="4" t="n">
@@ -9482,7 +9518,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M91" s="18" t="inlineStr">
+      <c r="M91" s="19" t="inlineStr">
         <is>
           <t>AS-101372</t>
         </is>
@@ -9537,7 +9573,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J92" s="17" t="n">
+      <c r="J92" s="18" t="n">
         <v>0.7552009</v>
       </c>
       <c r="K92" s="4" t="n">
@@ -9548,7 +9584,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M92" s="18" t="inlineStr">
+      <c r="M92" s="19" t="inlineStr">
         <is>
           <t>AS-101435</t>
         </is>
@@ -9603,7 +9639,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J93" s="17" t="n">
+      <c r="J93" s="18" t="n">
         <v>0.7552009</v>
       </c>
       <c r="K93" s="4" t="n">
@@ -9614,7 +9650,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M93" s="18" t="inlineStr">
+      <c r="M93" s="19" t="inlineStr">
         <is>
           <t>AS-101498</t>
         </is>
@@ -9669,7 +9705,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J94" s="17" t="n">
+      <c r="J94" s="18" t="n">
         <v>0.7552009</v>
       </c>
       <c r="K94" s="4" t="n">
@@ -9680,7 +9716,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M94" s="18" t="inlineStr">
+      <c r="M94" s="19" t="inlineStr">
         <is>
           <t>AS-101504</t>
         </is>
@@ -9735,7 +9771,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J95" s="17" t="n">
+      <c r="J95" s="18" t="n">
         <v>0.7552009</v>
       </c>
       <c r="K95" s="4" t="n">
@@ -9746,7 +9782,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M95" s="18" t="inlineStr">
+      <c r="M95" s="19" t="inlineStr">
         <is>
           <t>AS-101728</t>
         </is>
@@ -9801,7 +9837,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J96" s="17" t="n">
+      <c r="J96" s="18" t="n">
         <v>0.7552009</v>
       </c>
       <c r="K96" s="4" t="n">
@@ -9812,7 +9848,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M96" s="18" t="inlineStr">
+      <c r="M96" s="19" t="inlineStr">
         <is>
           <t>AS-101822</t>
         </is>
@@ -9867,7 +9903,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J97" s="17" t="n">
+      <c r="J97" s="18" t="n">
         <v>0.7552009</v>
       </c>
       <c r="K97" s="4" t="n">
@@ -9878,7 +9914,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M97" s="18" t="inlineStr">
+      <c r="M97" s="19" t="inlineStr">
         <is>
           <t>AS-101900</t>
         </is>
@@ -9933,7 +9969,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J98" s="17" t="n">
+      <c r="J98" s="18" t="n">
         <v>0.7552009</v>
       </c>
       <c r="K98" s="4" t="n">
@@ -9944,7 +9980,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M98" s="18" t="inlineStr">
+      <c r="M98" s="19" t="inlineStr">
         <is>
           <t>AS-101969</t>
         </is>
@@ -9999,7 +10035,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J99" s="17" t="n">
+      <c r="J99" s="18" t="n">
         <v>0.7552009</v>
       </c>
       <c r="K99" s="4" t="n">
@@ -10010,7 +10046,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M99" s="18" t="inlineStr">
+      <c r="M99" s="19" t="inlineStr">
         <is>
           <t>AS-102040</t>
         </is>
@@ -10065,7 +10101,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J100" s="17" t="n">
+      <c r="J100" s="18" t="n">
         <v>0.7552009</v>
       </c>
       <c r="K100" s="4" t="n">
@@ -10076,7 +10112,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M100" s="18" t="inlineStr">
+      <c r="M100" s="19" t="inlineStr">
         <is>
           <t>AS-102097</t>
         </is>
@@ -10131,7 +10167,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J101" s="17" t="n">
+      <c r="J101" s="18" t="n">
         <v>0.7552009</v>
       </c>
       <c r="K101" s="4" t="n">
@@ -10142,7 +10178,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M101" s="18" t="inlineStr">
+      <c r="M101" s="19" t="inlineStr">
         <is>
           <t>AS-102102</t>
         </is>
@@ -10197,7 +10233,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J102" s="17" t="n">
+      <c r="J102" s="18" t="n">
         <v>0.7552009</v>
       </c>
       <c r="K102" s="4" t="n">
@@ -10208,7 +10244,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M102" s="18" t="inlineStr">
+      <c r="M102" s="19" t="inlineStr">
         <is>
           <t>AS-102184</t>
         </is>
@@ -10263,7 +10299,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J103" s="17" t="n">
+      <c r="J103" s="18" t="n">
         <v>0.7552009</v>
       </c>
       <c r="K103" s="4" t="n">
@@ -10274,7 +10310,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M103" s="18" t="inlineStr">
+      <c r="M103" s="19" t="inlineStr">
         <is>
           <t>AS-102223</t>
         </is>
@@ -10329,7 +10365,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J104" s="17" t="n">
+      <c r="J104" s="18" t="n">
         <v>0.7552009</v>
       </c>
       <c r="K104" s="4" t="n">
@@ -10340,7 +10376,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M104" s="18" t="inlineStr">
+      <c r="M104" s="19" t="inlineStr">
         <is>
           <t>AS-102380</t>
         </is>
@@ -10395,7 +10431,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J105" s="17" t="n">
+      <c r="J105" s="18" t="n">
         <v>0.7552009</v>
       </c>
       <c r="K105" s="4" t="n">
@@ -10406,7 +10442,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M105" s="18" t="inlineStr">
+      <c r="M105" s="19" t="inlineStr">
         <is>
           <t>AS-102423</t>
         </is>
@@ -10461,7 +10497,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J106" s="17" t="n">
+      <c r="J106" s="18" t="n">
         <v>0.7552009</v>
       </c>
       <c r="K106" s="4" t="n">
@@ -10472,7 +10508,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M106" s="18" t="inlineStr">
+      <c r="M106" s="19" t="inlineStr">
         <is>
           <t>AS-102515</t>
         </is>
@@ -10527,7 +10563,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J107" s="17" t="n">
+      <c r="J107" s="18" t="n">
         <v>0.7552009</v>
       </c>
       <c r="K107" s="4" t="n">
@@ -10538,7 +10574,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M107" s="18" t="inlineStr">
+      <c r="M107" s="19" t="inlineStr">
         <is>
           <t>AS-99937</t>
         </is>
@@ -10593,7 +10629,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J108" s="17" t="n">
+      <c r="J108" s="18" t="n">
         <v>0.7552009</v>
       </c>
       <c r="K108" s="4" t="n">
@@ -10604,7 +10640,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M108" s="18" t="inlineStr">
+      <c r="M108" s="19" t="inlineStr">
         <is>
           <t>AS-99977</t>
         </is>
@@ -10659,7 +10695,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J109" s="17" t="n">
+      <c r="J109" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K109" s="4" t="n">
@@ -10670,7 +10706,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M109" s="18" t="inlineStr">
+      <c r="M109" s="19" t="inlineStr">
         <is>
           <t>PCSI2601529</t>
         </is>
@@ -10725,7 +10761,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J110" s="17" t="n">
+      <c r="J110" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K110" s="4" t="n">
@@ -10736,7 +10772,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M110" s="18" t="inlineStr">
+      <c r="M110" s="19" t="inlineStr">
         <is>
           <t>6033972</t>
         </is>
@@ -10791,7 +10827,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J111" s="17" t="n">
+      <c r="J111" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K111" s="4" t="n">
@@ -10802,7 +10838,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M111" s="18" t="inlineStr">
+      <c r="M111" s="19" t="inlineStr">
         <is>
           <t>6033972</t>
         </is>
@@ -10857,7 +10893,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J112" s="17" t="n">
+      <c r="J112" s="18" t="n">
         <v>0.86833</v>
       </c>
       <c r="K112" s="4" t="n">
@@ -10868,7 +10904,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M112" s="18" t="inlineStr">
+      <c r="M112" s="19" t="inlineStr">
         <is>
           <t>RVR-17773</t>
         </is>
@@ -10923,7 +10959,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J113" s="17" t="n">
+      <c r="J113" s="18" t="n">
         <v>0.86833</v>
       </c>
       <c r="K113" s="4" t="n">
@@ -10934,7 +10970,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M113" s="18" t="inlineStr">
+      <c r="M113" s="19" t="inlineStr">
         <is>
           <t>RVR-18638</t>
         </is>
@@ -10963,12 +10999,12 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>administration</t>
+          <t>shared_services</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>YOURACCOUNTSTAXES</t>
+          <t>SHAREDSERVICESSL</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -10977,11 +11013,11 @@
         </is>
       </c>
       <c r="G114" s="4" t="n">
-        <v>26.5</v>
+        <v>14144.1</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -10989,25 +11025,25 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J114" s="17" t="n">
-        <v>1</v>
+      <c r="J114" s="18" t="n">
+        <v>0.86833</v>
       </c>
       <c r="K114" s="4" t="n">
-        <v>26.5</v>
+        <v>12281.75</v>
       </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>documents</t>
         </is>
       </c>
-      <c r="M114" s="18" t="inlineStr">
-        <is>
-          <t>INV-0679_PERIODIFICADA_3_12</t>
+      <c r="M114" s="19" t="inlineStr">
+        <is>
+          <t>2026-0016</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1SwIai4YdtUV-rQd0AKSUEVkEfdlYRoPA/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1KdK-Ik0l5-TAvrDmyV47ighudMtGRrKE/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -11043,7 +11079,7 @@
         </is>
       </c>
       <c r="G115" s="4" t="n">
-        <v>55</v>
+        <v>26.5</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
@@ -11055,25 +11091,25 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J115" s="17" t="n">
+      <c r="J115" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K115" s="4" t="n">
-        <v>55</v>
+        <v>26.5</v>
       </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>documents</t>
         </is>
       </c>
-      <c r="M115" s="18" t="inlineStr">
-        <is>
-          <t>INV-0681_PERIODIFICADA_2_12</t>
+      <c r="M115" s="19" t="inlineStr">
+        <is>
+          <t>INV-0679_PERIODIFICADA_3_12</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1CFf2KHZd750hPLNp1Xj5DzzQwrKmlw9L/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1SwIai4YdtUV-rQd0AKSUEVkEfdlYRoPA/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -11109,7 +11145,7 @@
         </is>
       </c>
       <c r="G116" s="4" t="n">
-        <v>103.67</v>
+        <v>55</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
@@ -11121,32 +11157,32 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J116" s="17" t="n">
+      <c r="J116" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K116" s="4" t="n">
-        <v>103.67</v>
+        <v>55</v>
       </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>documents</t>
         </is>
       </c>
-      <c r="M116" s="18" t="inlineStr">
-        <is>
-          <t>INV-0682_PERIODIFICADA_3_12</t>
+      <c r="M116" s="19" t="inlineStr">
+        <is>
+          <t>INV-0681_PERIODIFICADA_2_12</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1LlEUQpBPSqkZ5BKsa4CYacg0DVARYbta/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1CFf2KHZd750hPLNp1Xj5DzzQwrKmlw9L/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="117" ht="12" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>202604</t>
+          <t>202603</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -11175,7 +11211,7 @@
         </is>
       </c>
       <c r="G117" s="4" t="n">
-        <v>26.5</v>
+        <v>103.67</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
@@ -11187,32 +11223,32 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J117" s="17" t="n">
+      <c r="J117" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K117" s="4" t="n">
-        <v>26.5</v>
+        <v>103.67</v>
       </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>documents</t>
         </is>
       </c>
-      <c r="M117" s="18" t="inlineStr">
-        <is>
-          <t>INV-0679_PERIODIFICADA_4_12</t>
+      <c r="M117" s="19" t="inlineStr">
+        <is>
+          <t>INV-0682_PERIODIFICADA_3_12</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1gDlq6Zum-eIMUjbaI329tWP9UutsRoFn/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1LlEUQpBPSqkZ5BKsa4CYacg0DVARYbta/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="118" ht="12" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>202604</t>
+          <t>202603</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -11241,7 +11277,7 @@
         </is>
       </c>
       <c r="G118" s="4" t="n">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="H118" t="inlineStr">
         <is>
@@ -11253,25 +11289,25 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J118" s="17" t="n">
+      <c r="J118" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K118" s="4" t="n">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="L118" t="inlineStr">
         <is>
           <t>documents</t>
         </is>
       </c>
-      <c r="M118" s="18" t="inlineStr">
-        <is>
-          <t>INV-0681_PERIODIFICADA_3_12</t>
+      <c r="M118" s="19" t="inlineStr">
+        <is>
+          <t>INV-0683</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1pNcZKxAtFRGUPPAFVD2p8ORXGSCcvxM8/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1uULQPI6E_iQgTyBEkDnDPTe-Xg6fqGiO/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -11307,7 +11343,7 @@
         </is>
       </c>
       <c r="G119" s="4" t="n">
-        <v>103.67</v>
+        <v>26.5</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
@@ -11319,32 +11355,32 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J119" s="17" t="n">
+      <c r="J119" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K119" s="4" t="n">
-        <v>103.67</v>
+        <v>26.5</v>
       </c>
       <c r="L119" t="inlineStr">
         <is>
           <t>documents</t>
         </is>
       </c>
-      <c r="M119" s="18" t="inlineStr">
-        <is>
-          <t>INV-0682_PERIODIFICADA_4_12</t>
+      <c r="M119" s="19" t="inlineStr">
+        <is>
+          <t>INV-0679_PERIODIFICADA_4_12</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1fWIKp9xwGFVs0EnOaVMSISVNLAoKF55J/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1gDlq6Zum-eIMUjbaI329tWP9UutsRoFn/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="120" ht="12" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>202605</t>
+          <t>202604</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -11373,7 +11409,7 @@
         </is>
       </c>
       <c r="G120" s="4" t="n">
-        <v>26.5</v>
+        <v>55</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
@@ -11385,32 +11421,32 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J120" s="17" t="n">
+      <c r="J120" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K120" s="4" t="n">
-        <v>26.5</v>
+        <v>55</v>
       </c>
       <c r="L120" t="inlineStr">
         <is>
           <t>documents</t>
         </is>
       </c>
-      <c r="M120" s="18" t="inlineStr">
-        <is>
-          <t>INV-0679_PERIODIFICADA_5_12</t>
+      <c r="M120" s="19" t="inlineStr">
+        <is>
+          <t>INV-0681_PERIODIFICADA_3_12</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1bP1XnXo2Vs8zIS0sVNRvq52xJQH7BSfD/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1pNcZKxAtFRGUPPAFVD2p8ORXGSCcvxM8/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="121" ht="12" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>202605</t>
+          <t>202604</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -11439,7 +11475,7 @@
         </is>
       </c>
       <c r="G121" s="4" t="n">
-        <v>55</v>
+        <v>103.67</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
@@ -11451,32 +11487,32 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J121" s="17" t="n">
+      <c r="J121" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K121" s="4" t="n">
-        <v>55</v>
+        <v>103.67</v>
       </c>
       <c r="L121" t="inlineStr">
         <is>
           <t>documents</t>
         </is>
       </c>
-      <c r="M121" s="18" t="inlineStr">
-        <is>
-          <t>INV-0681_PERIODIFICADA_4_12</t>
+      <c r="M121" s="19" t="inlineStr">
+        <is>
+          <t>INV-0682_PERIODIFICADA_4_12</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1ddnzOxZZgaXtVcRqNHeEt9LTz5s8C26J/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1fWIKp9xwGFVs0EnOaVMSISVNLAoKF55J/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="122" ht="12" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>202605</t>
+          <t>202604</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -11505,7 +11541,7 @@
         </is>
       </c>
       <c r="G122" s="4" t="n">
-        <v>103.67</v>
+        <v>850</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
@@ -11517,32 +11553,32 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J122" s="17" t="n">
+      <c r="J122" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K122" s="4" t="n">
-        <v>103.67</v>
+        <v>850</v>
       </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>documents</t>
         </is>
       </c>
-      <c r="M122" s="18" t="inlineStr">
-        <is>
-          <t>INV-0682_PERIODIFICADA_5_12</t>
+      <c r="M122" s="19" t="inlineStr">
+        <is>
+          <t>INV-0684</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1Z-NJHduArecH7-687SOBbQfa8Ef1m52p/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/14aG7eyxDXqZhJN0vFlOv-hyu-GR-ZjH-/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="123" ht="12" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>202606</t>
+          <t>202605</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -11583,7 +11619,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J123" s="17" t="n">
+      <c r="J123" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K123" s="4" t="n">
@@ -11594,21 +11630,21 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M123" s="18" t="inlineStr">
-        <is>
-          <t>INV-0679_PERIODIFICADA_6_12</t>
+      <c r="M123" s="19" t="inlineStr">
+        <is>
+          <t>INV-0679_PERIODIFICADA_5_12</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1I6H1omawcw5Be01IubiDlz8RDBKB0kcd/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1bP1XnXo2Vs8zIS0sVNRvq52xJQH7BSfD/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="124" ht="12" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>202606</t>
+          <t>202605</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -11649,7 +11685,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J124" s="17" t="n">
+      <c r="J124" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K124" s="4" t="n">
@@ -11660,21 +11696,21 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M124" s="18" t="inlineStr">
-        <is>
-          <t>INV-0681_PERIODIFICADA_5_12</t>
+      <c r="M124" s="19" t="inlineStr">
+        <is>
+          <t>INV-0681_PERIODIFICADA_4_12</t>
         </is>
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/14VMCuf4u87NNWjcx9C3H2yysZN1jqyTf/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1ddnzOxZZgaXtVcRqNHeEt9LTz5s8C26J/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="125" ht="12" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>202606</t>
+          <t>202605</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -11715,7 +11751,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J125" s="17" t="n">
+      <c r="J125" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K125" s="4" t="n">
@@ -11726,21 +11762,21 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M125" s="18" t="inlineStr">
-        <is>
-          <t>INV-0682_PERIODIFICADA_6_12</t>
+      <c r="M125" s="19" t="inlineStr">
+        <is>
+          <t>INV-0682_PERIODIFICADA_5_12</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1gmWh5ZgXhifus_kfGZ-bL8_sLe8eUug3/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1Z-NJHduArecH7-687SOBbQfa8Ef1m52p/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="126" ht="12" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>202607</t>
+          <t>202606</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11781,7 +11817,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J126" s="17" t="n">
+      <c r="J126" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K126" s="4" t="n">
@@ -11792,21 +11828,21 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M126" s="18" t="inlineStr">
-        <is>
-          <t>INV-0679_PERIODIFICADA_7_12</t>
+      <c r="M126" s="19" t="inlineStr">
+        <is>
+          <t>INV-0679_PERIODIFICADA_6_12</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/17hLMBW75hT4b6Q8RWmnLCnkK6axE-wzU/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1I6H1omawcw5Be01IubiDlz8RDBKB0kcd/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="127" ht="12" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>202607</t>
+          <t>202606</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11847,7 +11883,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J127" s="17" t="n">
+      <c r="J127" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K127" s="4" t="n">
@@ -11858,21 +11894,21 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M127" s="18" t="inlineStr">
-        <is>
-          <t>INV-0681_PERIODIFICADA_6_12</t>
+      <c r="M127" s="19" t="inlineStr">
+        <is>
+          <t>INV-0681_PERIODIFICADA_5_12</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1-4m6d0UYjYO2RBrJjkiKAjW12aRalpOJ/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/14VMCuf4u87NNWjcx9C3H2yysZN1jqyTf/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="128" ht="12" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>202607</t>
+          <t>202606</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11913,7 +11949,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J128" s="17" t="n">
+      <c r="J128" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K128" s="4" t="n">
@@ -11924,21 +11960,21 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M128" s="18" t="inlineStr">
-        <is>
-          <t>INV-0682_PERIODIFICADA_7_12</t>
+      <c r="M128" s="19" t="inlineStr">
+        <is>
+          <t>INV-0682_PERIODIFICADA_6_12</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1c_luteIVUmgrg6i_GlfSo_qh5drW456A/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1gmWh5ZgXhifus_kfGZ-bL8_sLe8eUug3/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="129" ht="12" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>202608</t>
+          <t>202607</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11979,7 +12015,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J129" s="17" t="n">
+      <c r="J129" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K129" s="4" t="n">
@@ -11990,21 +12026,21 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M129" s="18" t="inlineStr">
-        <is>
-          <t>INV-0679_PERIODIFICADA_8_12</t>
+      <c r="M129" s="19" t="inlineStr">
+        <is>
+          <t>INV-0679_PERIODIFICADA_7_12</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/11RmOMn_ZgHdnziLzDS8hsaK7ZIkvkgTY/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/17hLMBW75hT4b6Q8RWmnLCnkK6axE-wzU/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="130" ht="12" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>202608</t>
+          <t>202607</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -12045,7 +12081,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J130" s="17" t="n">
+      <c r="J130" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K130" s="4" t="n">
@@ -12056,21 +12092,21 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M130" s="18" t="inlineStr">
-        <is>
-          <t>INV-0681_PERIODIFICADA_7_12</t>
+      <c r="M130" s="19" t="inlineStr">
+        <is>
+          <t>INV-0681_PERIODIFICADA_6_12</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/11RGpKkEMdK77095ybWBCzfeU7QXtAazR/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1-4m6d0UYjYO2RBrJjkiKAjW12aRalpOJ/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="131" ht="12" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>202608</t>
+          <t>202607</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -12111,7 +12147,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J131" s="17" t="n">
+      <c r="J131" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K131" s="4" t="n">
@@ -12122,21 +12158,21 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M131" s="18" t="inlineStr">
-        <is>
-          <t>INV-0682_PERIODIFICADA_8_12</t>
+      <c r="M131" s="19" t="inlineStr">
+        <is>
+          <t>INV-0682_PERIODIFICADA_7_12</t>
         </is>
       </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1YItJo27rxIk2KucnIbPWCgV-kg6_TIFw/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1c_luteIVUmgrg6i_GlfSo_qh5drW456A/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="132" ht="12" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>202609</t>
+          <t>202608</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -12177,7 +12213,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J132" s="17" t="n">
+      <c r="J132" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K132" s="4" t="n">
@@ -12188,21 +12224,21 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M132" s="18" t="inlineStr">
-        <is>
-          <t>INV-0679_PERIODIFICADA_9_12</t>
+      <c r="M132" s="19" t="inlineStr">
+        <is>
+          <t>INV-0679_PERIODIFICADA_8_12</t>
         </is>
       </c>
       <c r="N132" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1TiRvkJ6K7ctWCKH70UZtwyVtiBFJcZS3/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/11RmOMn_ZgHdnziLzDS8hsaK7ZIkvkgTY/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="133" ht="12" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>202609</t>
+          <t>202608</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -12243,7 +12279,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J133" s="17" t="n">
+      <c r="J133" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K133" s="4" t="n">
@@ -12254,21 +12290,21 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M133" s="18" t="inlineStr">
-        <is>
-          <t>INV-0681_PERIODIFICADA_8_12</t>
+      <c r="M133" s="19" t="inlineStr">
+        <is>
+          <t>INV-0681_PERIODIFICADA_7_12</t>
         </is>
       </c>
       <c r="N133" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1TCM1PAyZN1h600czUy8h9Vl6JYkcuBnA/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/11RGpKkEMdK77095ybWBCzfeU7QXtAazR/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="134" ht="12" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>202609</t>
+          <t>202608</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -12309,7 +12345,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J134" s="17" t="n">
+      <c r="J134" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K134" s="4" t="n">
@@ -12320,21 +12356,21 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M134" s="18" t="inlineStr">
-        <is>
-          <t>INV-0682_PERIODIFICADA_9_12</t>
+      <c r="M134" s="19" t="inlineStr">
+        <is>
+          <t>INV-0682_PERIODIFICADA_8_12</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1j8eIoueeiDvnTZMGmyiF-LMtx0IPr9pM/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1YItJo27rxIk2KucnIbPWCgV-kg6_TIFw/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="135" ht="12" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>202610</t>
+          <t>202609</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -12375,7 +12411,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J135" s="17" t="n">
+      <c r="J135" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K135" s="4" t="n">
@@ -12386,21 +12422,21 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M135" s="18" t="inlineStr">
-        <is>
-          <t>INV-0679_PERIODIFICADA_10_12</t>
+      <c r="M135" s="19" t="inlineStr">
+        <is>
+          <t>INV-0679_PERIODIFICADA_9_12</t>
         </is>
       </c>
       <c r="N135" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1y9fclbPoT1LX8B-Ccm6UQFRfFv51MzCl/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1TiRvkJ6K7ctWCKH70UZtwyVtiBFJcZS3/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="136" ht="12" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>202610</t>
+          <t>202609</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -12441,7 +12477,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J136" s="17" t="n">
+      <c r="J136" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K136" s="4" t="n">
@@ -12452,21 +12488,21 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M136" s="18" t="inlineStr">
-        <is>
-          <t>INV-0681_PERIODIFICADA_9_12</t>
+      <c r="M136" s="19" t="inlineStr">
+        <is>
+          <t>INV-0681_PERIODIFICADA_8_12</t>
         </is>
       </c>
       <c r="N136" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1F_ojYavt0rOVF-WoA4DILVHACGqB_Xhn/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1TCM1PAyZN1h600czUy8h9Vl6JYkcuBnA/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="137" ht="12" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>202610</t>
+          <t>202609</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -12507,7 +12543,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J137" s="17" t="n">
+      <c r="J137" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K137" s="4" t="n">
@@ -12518,21 +12554,21 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M137" s="18" t="inlineStr">
-        <is>
-          <t>INV-0682_PERIODIFICADA_10_12</t>
+      <c r="M137" s="19" t="inlineStr">
+        <is>
+          <t>INV-0682_PERIODIFICADA_9_12</t>
         </is>
       </c>
       <c r="N137" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1AB8Xr6NvMGSBv1SkJcKECSxweSG6nBi-/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1j8eIoueeiDvnTZMGmyiF-LMtx0IPr9pM/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="138" ht="12" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>202611</t>
+          <t>202610</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -12573,7 +12609,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J138" s="17" t="n">
+      <c r="J138" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K138" s="4" t="n">
@@ -12584,21 +12620,21 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M138" s="18" t="inlineStr">
-        <is>
-          <t>INV-0679_PERIODIFICADA_11_12</t>
+      <c r="M138" s="19" t="inlineStr">
+        <is>
+          <t>INV-0679_PERIODIFICADA_10_12</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1L3a_vME8SLzq0VCnSYsQFsMpA3aEhGLE/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1y9fclbPoT1LX8B-Ccm6UQFRfFv51MzCl/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="139" ht="12" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>202611</t>
+          <t>202610</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -12639,7 +12675,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J139" s="17" t="n">
+      <c r="J139" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K139" s="4" t="n">
@@ -12650,21 +12686,21 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M139" s="18" t="inlineStr">
-        <is>
-          <t>INV-0681_PERIODIFICADA_10_12</t>
+      <c r="M139" s="19" t="inlineStr">
+        <is>
+          <t>INV-0681_PERIODIFICADA_9_12</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1IG_3iLDTE3hoYuVx4M46MqklrzCKpRhc/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1F_ojYavt0rOVF-WoA4DILVHACGqB_Xhn/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="140" ht="12" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>202611</t>
+          <t>202610</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -12705,7 +12741,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J140" s="17" t="n">
+      <c r="J140" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K140" s="4" t="n">
@@ -12716,21 +12752,21 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M140" s="18" t="inlineStr">
-        <is>
-          <t>INV-0682_PERIODIFICADA_11_12</t>
+      <c r="M140" s="19" t="inlineStr">
+        <is>
+          <t>INV-0682_PERIODIFICADA_10_12</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/11zNwha_ZMtf4Wq3wVF4QzJj4bweWWdGI/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1AB8Xr6NvMGSBv1SkJcKECSxweSG6nBi-/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="141" ht="12" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>202612</t>
+          <t>202611</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -12771,7 +12807,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J141" s="17" t="n">
+      <c r="J141" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K141" s="4" t="n">
@@ -12782,21 +12818,21 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M141" s="18" t="inlineStr">
-        <is>
-          <t>INV-0679_PERIODIFICADA_12_12</t>
+      <c r="M141" s="19" t="inlineStr">
+        <is>
+          <t>INV-0679_PERIODIFICADA_11_12</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1ynEcwwwFHRw_j4UIzVQllup-ekY2huWO/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1L3a_vME8SLzq0VCnSYsQFsMpA3aEhGLE/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="142" ht="12" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>202612</t>
+          <t>202611</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12837,7 +12873,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J142" s="17" t="n">
+      <c r="J142" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K142" s="4" t="n">
@@ -12848,21 +12884,21 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M142" s="18" t="inlineStr">
-        <is>
-          <t>INV-0681_PERIODIFICADA_11_12</t>
+      <c r="M142" s="19" t="inlineStr">
+        <is>
+          <t>INV-0681_PERIODIFICADA_10_12</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1RskEVbYtAKWbS4SEumveN8YHrWbIys-_/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1IG_3iLDTE3hoYuVx4M46MqklrzCKpRhc/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="143" ht="12" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>202612</t>
+          <t>202611</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12903,7 +12939,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="J143" s="17" t="n">
+      <c r="J143" s="18" t="n">
         <v>1</v>
       </c>
       <c r="K143" s="4" t="n">
@@ -12914,12 +12950,210 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M143" s="18" t="inlineStr">
+      <c r="M143" s="19" t="inlineStr">
+        <is>
+          <t>INV-0682_PERIODIFICADA_11_12</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/11zNwha_ZMtf4Wq3wVF4QzJj4bweWWdGI/view?usp=drivesdk</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="12" customHeight="1">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>202612</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>LTD</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>opex</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>administration</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>YOURACCOUNTSTAXES</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>invoice</t>
+        </is>
+      </c>
+      <c r="G144" s="4" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="J144" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K144" s="4" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>documents</t>
+        </is>
+      </c>
+      <c r="M144" s="19" t="inlineStr">
+        <is>
+          <t>INV-0679_PERIODIFICADA_12_12</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1ynEcwwwFHRw_j4UIzVQllup-ekY2huWO/view?usp=drivesdk</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="12" customHeight="1">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>202612</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>LTD</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>opex</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>administration</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>YOURACCOUNTSTAXES</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>invoice</t>
+        </is>
+      </c>
+      <c r="G145" s="4" t="n">
+        <v>55</v>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="J145" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K145" s="4" t="n">
+        <v>55</v>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>documents</t>
+        </is>
+      </c>
+      <c r="M145" s="19" t="inlineStr">
+        <is>
+          <t>INV-0681_PERIODIFICADA_11_12</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1RskEVbYtAKWbS4SEumveN8YHrWbIys-_/view?usp=drivesdk</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="12" customHeight="1">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>202612</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>LTD</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>opex</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>administration</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>YOURACCOUNTSTAXES</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>invoice</t>
+        </is>
+      </c>
+      <c r="G146" s="4" t="n">
+        <v>103.67</v>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="J146" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K146" s="4" t="n">
+        <v>103.67</v>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>documents</t>
+        </is>
+      </c>
+      <c r="M146" s="19" t="inlineStr">
         <is>
           <t>INV-0682_PERIODIFICADA_12_12</t>
         </is>
       </c>
-      <c r="N143" t="inlineStr">
+      <c r="N146" t="inlineStr">
         <is>
           <t>https://drive.google.com/file/d/1vPskc5Qm4-Coe1JxTlzp2VdJWX8WiKRm/view?usp=drivesdk</t>
         </is>
@@ -13069,6 +13303,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M141" r:id="rId139"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M142" r:id="rId140"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M143" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M144" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M145" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M146" r:id="rId144"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13095,54 +13332,54 @@
   </cols>
   <sheetData>
     <row r="1" ht="12" customHeight="1">
-      <c r="A1" s="15" t="inlineStr">
+      <c r="A1" s="16" t="inlineStr">
         <is>
           <t>&lt;- Volver a P&amp;G-LTD</t>
         </is>
       </c>
     </row>
     <row r="2" ht="12" customHeight="1">
-      <c r="A2" s="16" t="inlineStr">
+      <c r="A2" s="17" t="inlineStr">
         <is>
           <t>yyyymm</t>
         </is>
       </c>
-      <c r="B2" s="16" t="inlineStr">
+      <c r="B2" s="17" t="inlineStr">
         <is>
           <t>entity</t>
         </is>
       </c>
-      <c r="C2" s="16" t="inlineStr">
+      <c r="C2" s="17" t="inlineStr">
         <is>
           <t>supplier_code</t>
         </is>
       </c>
-      <c r="D2" s="16" t="inlineStr">
+      <c r="D2" s="17" t="inlineStr">
         <is>
           <t>amount_original</t>
         </is>
       </c>
-      <c r="E2" s="16" t="inlineStr">
+      <c r="E2" s="17" t="inlineStr">
         <is>
           <t>currency_original</t>
         </is>
       </c>
-      <c r="F2" s="16" t="inlineStr">
+      <c r="F2" s="17" t="inlineStr">
         <is>
           <t>reporting_currency</t>
         </is>
       </c>
-      <c r="G2" s="16" t="inlineStr">
+      <c r="G2" s="17" t="inlineStr">
         <is>
           <t>fx_rate</t>
         </is>
       </c>
-      <c r="H2" s="16" t="inlineStr">
+      <c r="H2" s="17" t="inlineStr">
         <is>
           <t>amount_reporting</t>
         </is>
       </c>
-      <c r="I2" s="16" t="inlineStr">
+      <c r="I2" s="17" t="inlineStr">
         <is>
           <t>source</t>
         </is>
@@ -13177,7 +13414,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="G3" s="17" t="n">
+      <c r="G3" s="18" t="n">
         <v>1</v>
       </c>
       <c r="H3" s="4" t="n">
@@ -13218,7 +13455,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="G4" s="17" t="n">
+      <c r="G4" s="18" t="n">
         <v>1</v>
       </c>
       <c r="H4" s="4" t="n">
@@ -13259,7 +13496,7 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="G5" s="17" t="n">
+      <c r="G5" s="18" t="n">
         <v>1</v>
       </c>
       <c r="H5" s="4" t="n">
@@ -13288,7 +13525,7 @@
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>35.85</v>
+        <v>117.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -13300,11 +13537,11 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="G6" s="17" t="n">
+      <c r="G6" s="18" t="n">
         <v>1</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>35.85</v>
+        <v>117.4</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -13339,44 +13576,44 @@
   </cols>
   <sheetData>
     <row r="1" ht="12" customHeight="1">
-      <c r="A1" s="15" t="inlineStr">
+      <c r="A1" s="16" t="inlineStr">
         <is>
           <t>&lt;- Volver a P&amp;G-LTD</t>
         </is>
       </c>
     </row>
     <row r="2" ht="12" customHeight="1">
-      <c r="A2" s="16" t="inlineStr">
+      <c r="A2" s="17" t="inlineStr">
         <is>
           <t>yyyymm</t>
         </is>
       </c>
-      <c r="B2" s="16" t="inlineStr">
+      <c r="B2" s="17" t="inlineStr">
         <is>
           <t>rate_date</t>
         </is>
       </c>
-      <c r="C2" s="16" t="inlineStr">
+      <c r="C2" s="17" t="inlineStr">
         <is>
           <t>currency_original</t>
         </is>
       </c>
-      <c r="D2" s="16" t="inlineStr">
+      <c r="D2" s="17" t="inlineStr">
         <is>
           <t>reporting_currency</t>
         </is>
       </c>
-      <c r="E2" s="16" t="inlineStr">
+      <c r="E2" s="17" t="inlineStr">
         <is>
           <t>reference_rate</t>
         </is>
       </c>
-      <c r="F2" s="16" t="inlineStr">
+      <c r="F2" s="17" t="inlineStr">
         <is>
           <t>fx_rate</t>
         </is>
       </c>
-      <c r="G2" s="16" t="inlineStr">
+      <c r="G2" s="17" t="inlineStr">
         <is>
           <t>source</t>
         </is>
@@ -13403,10 +13640,10 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="E3" s="17" t="n">
+      <c r="E3" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="F3" s="17" t="n">
+      <c r="F3" s="18" t="n">
         <v>0.8662</v>
       </c>
       <c r="G3" t="inlineStr">
@@ -13436,10 +13673,10 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="E4" s="17" t="n">
+      <c r="E4" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="F4" s="17" t="n">
+      <c r="F4" s="18" t="n">
         <v>1</v>
       </c>
       <c r="G4" t="inlineStr">
@@ -13469,10 +13706,10 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="E5" s="17" t="n">
+      <c r="E5" s="18" t="n">
         <v>1.1919</v>
       </c>
-      <c r="F5" s="17" t="n">
+      <c r="F5" s="18" t="n">
         <v>0.72673882</v>
       </c>
       <c r="G5" t="inlineStr">
@@ -13502,10 +13739,10 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="E6" s="17" t="n">
+      <c r="E6" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="F6" s="17" t="n">
+      <c r="F6" s="18" t="n">
         <v>0.8763</v>
       </c>
       <c r="G6" t="inlineStr">
@@ -13535,10 +13772,10 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="E7" s="17" t="n">
+      <c r="E7" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="F7" s="17" t="n">
+      <c r="F7" s="18" t="n">
         <v>1</v>
       </c>
       <c r="G7" t="inlineStr">
@@ -13568,10 +13805,10 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="E8" s="17" t="n">
+      <c r="E8" s="18" t="n">
         <v>1.1805</v>
       </c>
-      <c r="F8" s="17" t="n">
+      <c r="F8" s="18" t="n">
         <v>0.74231258</v>
       </c>
       <c r="G8" t="inlineStr">
@@ -13601,10 +13838,10 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="E9" s="17" t="n">
+      <c r="E9" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="F9" s="17" t="n">
+      <c r="F9" s="18" t="n">
         <v>0.86833</v>
       </c>
       <c r="G9" t="inlineStr">
@@ -13634,10 +13871,10 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="E10" s="17" t="n">
+      <c r="E10" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="F10" s="17" t="n">
+      <c r="F10" s="18" t="n">
         <v>1</v>
       </c>
       <c r="G10" t="inlineStr">
@@ -13667,10 +13904,10 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="E11" s="17" t="n">
+      <c r="E11" s="18" t="n">
         <v>1.1498</v>
       </c>
-      <c r="F11" s="17" t="n">
+      <c r="F11" s="18" t="n">
         <v>0.7552009</v>
       </c>
       <c r="G11" t="inlineStr">
@@ -13700,10 +13937,10 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="E12" s="17" t="n">
+      <c r="E12" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="F12" s="17" t="n">
+      <c r="F12" s="18" t="n">
         <v>1</v>
       </c>
       <c r="G12" t="inlineStr">
@@ -13733,10 +13970,10 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="E13" s="17" t="n">
+      <c r="E13" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="F13" s="17" t="n">
+      <c r="F13" s="18" t="n">
         <v>1</v>
       </c>
       <c r="G13" t="inlineStr">
@@ -13766,10 +14003,10 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="E14" s="17" t="n">
+      <c r="E14" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="F14" s="17" t="n">
+      <c r="F14" s="18" t="n">
         <v>1</v>
       </c>
       <c r="G14" t="inlineStr">
@@ -13799,10 +14036,10 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="E15" s="17" t="n">
+      <c r="E15" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="F15" s="17" t="n">
+      <c r="F15" s="18" t="n">
         <v>1</v>
       </c>
       <c r="G15" t="inlineStr">
@@ -13832,10 +14069,10 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="E16" s="17" t="n">
+      <c r="E16" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="F16" s="17" t="n">
+      <c r="F16" s="18" t="n">
         <v>1</v>
       </c>
       <c r="G16" t="inlineStr">
@@ -13865,10 +14102,10 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="E17" s="17" t="n">
+      <c r="E17" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="F17" s="17" t="n">
+      <c r="F17" s="18" t="n">
         <v>1</v>
       </c>
       <c r="G17" t="inlineStr">
@@ -13898,10 +14135,10 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="E18" s="17" t="n">
+      <c r="E18" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="F18" s="17" t="n">
+      <c r="F18" s="18" t="n">
         <v>1</v>
       </c>
       <c r="G18" t="inlineStr">
@@ -13931,10 +14168,10 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="E19" s="17" t="n">
+      <c r="E19" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="F19" s="17" t="n">
+      <c r="F19" s="18" t="n">
         <v>1</v>
       </c>
       <c r="G19" t="inlineStr">
@@ -13964,10 +14201,10 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="E20" s="17" t="n">
+      <c r="E20" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="F20" s="17" t="n">
+      <c r="F20" s="18" t="n">
         <v>1</v>
       </c>
       <c r="G20" t="inlineStr">
@@ -14001,34 +14238,34 @@
   </cols>
   <sheetData>
     <row r="1" ht="12" customHeight="1">
-      <c r="A1" s="15" t="inlineStr">
+      <c r="A1" s="16" t="inlineStr">
         <is>
           <t>&lt;- Volver a P&amp;G-LTD</t>
         </is>
       </c>
     </row>
     <row r="2" ht="12" customHeight="1">
-      <c r="A2" s="16" t="inlineStr">
+      <c r="A2" s="17" t="inlineStr">
         <is>
           <t>supplier_code</t>
         </is>
       </c>
-      <c r="B2" s="16" t="inlineStr">
+      <c r="B2" s="17" t="inlineStr">
         <is>
           <t>supplier_name</t>
         </is>
       </c>
-      <c r="C2" s="16" t="inlineStr">
+      <c r="C2" s="17" t="inlineStr">
         <is>
           <t>current_folder</t>
         </is>
       </c>
-      <c r="D2" s="16" t="inlineStr">
+      <c r="D2" s="17" t="inlineStr">
         <is>
           <t>destination_path</t>
         </is>
       </c>
-      <c r="E2" s="16" t="inlineStr">
+      <c r="E2" s="17" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
@@ -14321,7 +14558,7 @@
       </c>
     </row>
     <row r="2" ht="12" customHeight="1">
-      <c r="A2" s="19" t="inlineStr">
+      <c r="A2" s="20" t="inlineStr">
         <is>
           <t>Nº Facturas LTD 2026</t>
         </is>
@@ -14395,151 +14632,151 @@
       </c>
     </row>
     <row r="4" ht="12" customHeight="1">
-      <c r="A4" s="20" t="inlineStr">
+      <c r="A4" s="21" t="inlineStr">
         <is>
           <t>Turnover</t>
         </is>
       </c>
-      <c r="B4" s="21" t="n"/>
-      <c r="C4" s="21" t="n"/>
-      <c r="D4" s="21" t="n">
+      <c r="B4" s="22" t="n"/>
+      <c r="C4" s="22" t="n"/>
+      <c r="D4" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="E4" s="21" t="n">
+      <c r="E4" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="F4" s="21" t="n">
+      <c r="F4" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="G4" s="21" t="n">
+      <c r="G4" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="H4" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" s="21" t="n">
+      <c r="H4" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" s="22" t="n">
         <v>4</v>
       </c>
-      <c r="Q4" s="21" t="n"/>
+      <c r="Q4" s="22" t="n"/>
     </row>
     <row r="5" ht="12" customHeight="1">
-      <c r="A5" s="22" t="n"/>
-      <c r="B5" s="23" t="inlineStr">
+      <c r="A5" s="23" t="n"/>
+      <c r="B5" s="24" t="inlineStr">
         <is>
           <t>Product sales</t>
         </is>
       </c>
-      <c r="C5" s="22" t="n"/>
-      <c r="D5" s="22" t="n">
+      <c r="C5" s="23" t="n"/>
+      <c r="D5" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E5" s="22" t="n">
+      <c r="E5" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="F5" s="22" t="n">
+      <c r="F5" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="G5" s="22" t="n">
+      <c r="G5" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="H5" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" s="22" t="n">
+      <c r="H5" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="Q5" s="22" t="n"/>
+      <c r="Q5" s="23" t="n"/>
     </row>
     <row r="6" ht="12" customHeight="1">
-      <c r="A6" s="24" t="n"/>
-      <c r="B6" s="24" t="n"/>
+      <c r="A6" s="25" t="n"/>
+      <c r="B6" s="25" t="n"/>
       <c r="C6" s="9" t="inlineStr">
         <is>
           <t>Shopify</t>
         </is>
       </c>
-      <c r="D6" s="24" t="n">
+      <c r="D6" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="E6" s="24" t="n">
+      <c r="E6" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="F6" s="24" t="n">
+      <c r="F6" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="G6" s="24" t="n">
+      <c r="G6" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="H6" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" s="24" t="n">
+      <c r="H6" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="Q6" s="24" t="n"/>
+      <c r="Q6" s="25" t="n"/>
     </row>
     <row r="7" ht="12" customHeight="1">
       <c r="C7" t="inlineStr">
@@ -14588,250 +14825,250 @@
       </c>
     </row>
     <row r="8" ht="12" customHeight="1">
-      <c r="A8" s="22" t="n"/>
-      <c r="B8" s="23" t="inlineStr">
+      <c r="A8" s="23" t="n"/>
+      <c r="B8" s="24" t="inlineStr">
         <is>
           <t>Services</t>
         </is>
       </c>
-      <c r="C8" s="22" t="n"/>
-      <c r="D8" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="22" t="n"/>
+      <c r="C8" s="23" t="n"/>
+      <c r="D8" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="23" t="n"/>
     </row>
     <row r="9" ht="12" customHeight="1">
-      <c r="A9" s="24" t="n"/>
+      <c r="A9" s="25" t="n"/>
       <c r="B9" s="9" t="inlineStr">
         <is>
           <t>Uncategorized income</t>
         </is>
       </c>
-      <c r="C9" s="24" t="n"/>
-      <c r="D9" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="24" t="n"/>
+      <c r="C9" s="25" t="n"/>
+      <c r="D9" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="25" t="n"/>
     </row>
     <row r="10" ht="12" customHeight="1"/>
     <row r="11" ht="12" customHeight="1">
-      <c r="A11" s="20" t="inlineStr">
+      <c r="A11" s="21" t="inlineStr">
         <is>
           <t>Expenses</t>
         </is>
       </c>
-      <c r="B11" s="21" t="n"/>
-      <c r="C11" s="21" t="n"/>
-      <c r="D11" s="21" t="n">
+      <c r="B11" s="22" t="n"/>
+      <c r="C11" s="22" t="n"/>
+      <c r="D11" s="22" t="n">
         <v>30</v>
       </c>
-      <c r="E11" s="21" t="n">
+      <c r="E11" s="22" t="n">
         <v>36</v>
       </c>
-      <c r="F11" s="21" t="n">
-        <v>51</v>
-      </c>
-      <c r="G11" s="21" t="n">
-        <v>4</v>
-      </c>
-      <c r="H11" s="21" t="n">
+      <c r="F11" s="22" t="n">
+        <v>53</v>
+      </c>
+      <c r="G11" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="H11" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="I11" s="21" t="n">
+      <c r="I11" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="J11" s="21" t="n">
+      <c r="J11" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="K11" s="21" t="n">
+      <c r="K11" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="L11" s="21" t="n">
+      <c r="L11" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="M11" s="21" t="n">
+      <c r="M11" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="N11" s="21" t="n">
+      <c r="N11" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="O11" s="21" t="n">
+      <c r="O11" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="P11" s="21" t="n">
-        <v>145</v>
-      </c>
-      <c r="Q11" s="21" t="n"/>
+      <c r="P11" s="22" t="n">
+        <v>148</v>
+      </c>
+      <c r="Q11" s="22" t="n"/>
     </row>
     <row r="12" ht="12" customHeight="1">
-      <c r="A12" s="22" t="n"/>
-      <c r="B12" s="23" t="inlineStr">
+      <c r="A12" s="23" t="n"/>
+      <c r="B12" s="24" t="inlineStr">
         <is>
           <t>COGS</t>
         </is>
       </c>
-      <c r="C12" s="22" t="n"/>
-      <c r="D12" s="22" t="n">
+      <c r="C12" s="23" t="n"/>
+      <c r="D12" s="23" t="n">
         <v>27</v>
       </c>
-      <c r="E12" s="22" t="n">
+      <c r="E12" s="23" t="n">
         <v>32</v>
       </c>
-      <c r="F12" s="22" t="n">
+      <c r="F12" s="23" t="n">
         <v>46</v>
       </c>
-      <c r="G12" s="22" t="n">
+      <c r="G12" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="H12" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" s="22" t="n">
+      <c r="H12" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" s="23" t="n">
         <v>106</v>
       </c>
-      <c r="Q12" s="22" t="n"/>
+      <c r="Q12" s="23" t="n"/>
     </row>
     <row r="13" ht="12" customHeight="1">
-      <c r="A13" s="24" t="n"/>
-      <c r="B13" s="24" t="n"/>
+      <c r="A13" s="25" t="n"/>
+      <c r="B13" s="25" t="n"/>
       <c r="C13" s="9" t="inlineStr">
         <is>
           <t>Manufacturing</t>
         </is>
       </c>
-      <c r="D13" s="24" t="n">
+      <c r="D13" s="25" t="n">
         <v>25</v>
       </c>
-      <c r="E13" s="24" t="n">
+      <c r="E13" s="25" t="n">
         <v>30</v>
       </c>
-      <c r="F13" s="24" t="n">
+      <c r="F13" s="25" t="n">
         <v>43</v>
       </c>
-      <c r="G13" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" s="24" t="n">
+      <c r="G13" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" s="25" t="n">
         <v>98</v>
       </c>
-      <c r="Q13" s="24" t="n"/>
+      <c r="Q13" s="25" t="n"/>
     </row>
     <row r="14" ht="12" customHeight="1">
       <c r="C14" t="inlineStr">
@@ -14972,53 +15209,53 @@
       </c>
     </row>
     <row r="17" ht="12" customHeight="1">
-      <c r="A17" s="24" t="n"/>
-      <c r="B17" s="24" t="n"/>
+      <c r="A17" s="25" t="n"/>
+      <c r="B17" s="25" t="n"/>
       <c r="C17" s="9" t="inlineStr">
         <is>
           <t>Logistics</t>
         </is>
       </c>
-      <c r="D17" s="24" t="n">
+      <c r="D17" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="E17" s="24" t="n">
+      <c r="E17" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="F17" s="24" t="n">
+      <c r="F17" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="G17" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" s="24" t="n">
+      <c r="G17" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="Q17" s="24" t="n"/>
+      <c r="Q17" s="25" t="n"/>
     </row>
     <row r="18" ht="12" customHeight="1">
       <c r="C18" t="inlineStr">
@@ -15113,53 +15350,53 @@
       </c>
     </row>
     <row r="20" ht="12" customHeight="1">
-      <c r="A20" s="24" t="n"/>
-      <c r="B20" s="24" t="n"/>
+      <c r="A20" s="25" t="n"/>
+      <c r="B20" s="25" t="n"/>
       <c r="C20" s="9" t="inlineStr">
         <is>
           <t>Payment fees</t>
         </is>
       </c>
-      <c r="D20" s="24" t="n">
+      <c r="D20" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="E20" s="24" t="n">
+      <c r="E20" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="F20" s="24" t="n">
+      <c r="F20" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="G20" s="24" t="n">
+      <c r="G20" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="H20" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" s="24" t="n">
+      <c r="H20" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="Q20" s="24" t="n"/>
+      <c r="Q20" s="25" t="n"/>
     </row>
     <row r="21" ht="12" customHeight="1">
       <c r="C21" t="inlineStr">
@@ -15209,102 +15446,102 @@
     </row>
     <row r="22" ht="12" customHeight="1"/>
     <row r="23" ht="12" customHeight="1">
-      <c r="A23" s="22" t="n"/>
-      <c r="B23" s="23" t="inlineStr">
+      <c r="A23" s="23" t="n"/>
+      <c r="B23" s="24" t="inlineStr">
         <is>
           <t>Opex</t>
         </is>
       </c>
-      <c r="C23" s="22" t="n"/>
-      <c r="D23" s="22" t="n">
+      <c r="C23" s="23" t="n"/>
+      <c r="D23" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="E23" s="22" t="n">
+      <c r="E23" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="F23" s="22" t="n">
-        <v>5</v>
-      </c>
-      <c r="G23" s="22" t="n">
+      <c r="F23" s="23" t="n">
+        <v>7</v>
+      </c>
+      <c r="G23" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="H23" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="H23" s="22" t="n">
+      <c r="I23" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="I23" s="22" t="n">
+      <c r="J23" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="J23" s="22" t="n">
+      <c r="K23" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="K23" s="22" t="n">
+      <c r="L23" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="L23" s="22" t="n">
+      <c r="M23" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="M23" s="22" t="n">
+      <c r="N23" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="N23" s="22" t="n">
+      <c r="O23" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="O23" s="22" t="n">
+      <c r="P23" s="23" t="n">
+        <v>42</v>
+      </c>
+      <c r="Q23" s="23" t="n"/>
+    </row>
+    <row r="24" ht="12" customHeight="1">
+      <c r="A24" s="25" t="n"/>
+      <c r="B24" s="25" t="n"/>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>Shared services</t>
+        </is>
+      </c>
+      <c r="D24" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="P23" s="22" t="n">
-        <v>39</v>
-      </c>
-      <c r="Q23" s="22" t="n"/>
-    </row>
-    <row r="24" ht="12" customHeight="1">
-      <c r="A24" s="24" t="n"/>
-      <c r="B24" s="24" t="n"/>
-      <c r="C24" s="9" t="inlineStr">
-        <is>
-          <t>Shared services</t>
-        </is>
-      </c>
-      <c r="D24" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="E24" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="F24" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" s="24" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q24" s="24" t="n"/>
+      <c r="Q24" s="25" t="n"/>
     </row>
     <row r="25" ht="12" customHeight="1">
       <c r="C25" t="inlineStr">
@@ -15319,7 +15556,7 @@
         <v>1</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -15349,57 +15586,57 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" ht="12" customHeight="1">
+      <c r="A26" s="25" t="n"/>
+      <c r="B26" s="25" t="n"/>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>Administration</t>
+        </is>
+      </c>
+      <c r="D26" s="25" t="n">
         <v>2</v>
       </c>
-    </row>
-    <row r="26" ht="12" customHeight="1">
-      <c r="A26" s="24" t="n"/>
-      <c r="B26" s="24" t="n"/>
-      <c r="C26" s="9" t="inlineStr">
-        <is>
-          <t>Administration</t>
-        </is>
-      </c>
-      <c r="D26" s="24" t="n">
-        <v>2</v>
-      </c>
-      <c r="E26" s="24" t="n">
+      <c r="E26" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="F26" s="24" t="n">
+      <c r="F26" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="G26" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="H26" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="G26" s="24" t="n">
+      <c r="I26" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="H26" s="24" t="n">
+      <c r="J26" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="I26" s="24" t="n">
+      <c r="K26" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="J26" s="24" t="n">
+      <c r="L26" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="K26" s="24" t="n">
+      <c r="M26" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="L26" s="24" t="n">
+      <c r="N26" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="M26" s="24" t="n">
+      <c r="O26" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="N26" s="24" t="n">
-        <v>3</v>
-      </c>
-      <c r="O26" s="24" t="n">
-        <v>3</v>
-      </c>
-      <c r="P26" s="24" t="n">
-        <v>35</v>
-      </c>
-      <c r="Q26" s="24" t="n"/>
+      <c r="P26" s="25" t="n">
+        <v>37</v>
+      </c>
+      <c r="Q26" s="25" t="n"/>
     </row>
     <row r="27" ht="12" customHeight="1">
       <c r="C27" t="inlineStr">
@@ -15414,10 +15651,10 @@
         <v>3</v>
       </c>
       <c r="F27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H27" t="n">
         <v>3</v>
@@ -15444,57 +15681,57 @@
         <v>3</v>
       </c>
       <c r="P27" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="28" ht="12" customHeight="1">
-      <c r="A28" s="24" t="n"/>
-      <c r="B28" s="24" t="n"/>
+      <c r="A28" s="25" t="n"/>
+      <c r="B28" s="25" t="n"/>
       <c r="C28" s="9" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
       </c>
-      <c r="D28" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" s="24" t="n">
+      <c r="D28" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="G28" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" s="24" t="n">
+      <c r="G28" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="Q28" s="24" t="n"/>
+      <c r="Q28" s="25" t="n"/>
     </row>
     <row r="29" ht="12" customHeight="1">
       <c r="C29" t="inlineStr">
@@ -15543,102 +15780,102 @@
       </c>
     </row>
     <row r="30" ht="12" customHeight="1">
-      <c r="A30" s="24" t="n"/>
-      <c r="B30" s="24" t="n"/>
+      <c r="A30" s="25" t="n"/>
+      <c r="B30" s="25" t="n"/>
       <c r="C30" s="9" t="inlineStr">
         <is>
           <t>Uncategorized Expenses</t>
         </is>
       </c>
-      <c r="D30" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" s="24" t="n"/>
+      <c r="D30" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="25" t="n"/>
     </row>
     <row r="31" ht="12" customHeight="1">
-      <c r="A31" s="24" t="n"/>
+      <c r="A31" s="25" t="n"/>
       <c r="B31" s="9" t="inlineStr">
         <is>
           <t>Currency Adjustment</t>
         </is>
       </c>
-      <c r="C31" s="24" t="n"/>
-      <c r="D31" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" s="24" t="n"/>
+      <c r="C31" s="25" t="n"/>
+      <c r="D31" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="25" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/output/spreadsheet/pyg_ltd_2026.xlsx
+++ b/output/spreadsheet/pyg_ltd_2026.xlsx
@@ -696,7 +696,7 @@
     <row r="3" ht="12" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Actualizado: 10/04/2026 11:48 h</t>
+          <t>Actualizado: 10/04/2026 12:53 h</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -3267,7 +3267,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-04-10T09:48:00Z</t>
+          <t>2026-04-10T10:53:47Z</t>
         </is>
       </c>
     </row>
